--- a/03_test-cases/TC-MASTER-LATEST.xlsx
+++ b/03_test-cases/TC-MASTER-LATEST.xlsx
@@ -513,7 +513,6 @@
           <t>TC-MASTER — foxeco-v2</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -645,7 +644,6 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -7582,7 +7580,7 @@
       <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Tài khoản SSO CBNV FPT còn hiệu lực trên STG.
-- Host app FoxPro (`vn.fpt.ftel.sop.stg`) đã cài trên thiết bị Android.</t>
+- Host app FoxPro (`vn.fpt.ftel.sop.stg`) đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -8828,24 +8826,24 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG.</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment).
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed cho tài khoản đủ 4 đơn đang hoạt động ở các trạng thái "Chờ ghép", "Đã ghép", "Đang giao", "Đã giao", cùng 1 đơn "Hoàn thành" và 1 đơn "Hết hạn". (setup)
-2. Đăng nhập FoxEco và nhấn tab "Hoạt động".
-3. Check badge trạng thái của từng card trong tab "Đang diễn ra".</t>
+          <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
+2. Check badge trạng thái của từng card trong tab "Đang diễn ra".</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>3. Mọi card trong danh sách có badge thuộc nhóm "Chờ ghép", "Đã ghép", "Đang giao", "Đã giao"; KHÔNG có card nào badge "Hoàn thành" hoặc "Hết hạn".</t>
+          <t>2. Mọi card trong danh sách có badge thuộc nhóm "Chờ ghép", "Đã ghép", "Đang giao", "Đã giao"; KHÔNG có card nào badge "Hoàn thành" hoặc "Hết hạn".</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>4 đơn đang hoạt động + 1 đơn "Hoàn thành" + 1 đơn "Hết hạn" (test_data_catalog §ACT)</t>
+          <t>4 đơn đang hoạt động + 1 đơn "Hoàn thành" + 1 đơn "Hết hạn" của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
@@ -8904,25 +8902,25 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG.</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment).
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed cho tài khoản 1 đơn "Hoàn thành", 1 đơn "Hết hạn" và 1 đơn "Đang giao". (setup)
-2. Đăng nhập FoxEco và nhấn tab "Hoạt động".
-3. Nhấn tab con "Đã hoàn thành".
-4. Check badge trạng thái của từng card trong danh sách.</t>
+          <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
+2. Nhấn tab con "Đã hoàn thành". (setup)
+3. Check badge trạng thái của từng card trong danh sách.</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>4. Danh sách có card badge "Hoàn thành" và card badge "Hết hạn"; KHÔNG có card nào badge "Chờ ghép", "Đã ghép", "Đang giao" hay "Đã giao".</t>
+          <t>3. Danh sách có card badge "Hoàn thành" và card badge "Hết hạn"; KHÔNG có card nào badge "Chờ ghép", "Đã ghép", "Đang giao" hay "Đã giao".</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>1 đơn "Hoàn thành" + 1 đơn "Hết hạn" + 1 đơn "Đang giao" (test_data_catalog §ACT)</t>
+          <t>1 đơn "Hoàn thành" + 1 đơn "Hết hạn" + 1 đơn "Đang giao" của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr"/>
@@ -8981,24 +8979,24 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG có ≥1 đơn đang hoạt động.</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment).
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed cho tài khoản 1 đơn ở trạng thái "Đang giao". (setup)
-2. Đăng nhập FoxEco và nhấn tab "Hoạt động".
-3. Check lần lượt các trường trên card đơn.</t>
+          <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
+2. Check lần lượt các trường trên card đơn "Đang giao".</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>3. Card hiển thị đủ 5 trường: icon trạng thái, tên tin, tuyến đường dạng "Từ → Đến", ngày, badge trạng thái.</t>
+          <t>2. Card hiển thị đủ 5 trường: icon trạng thái, tên tin, tuyến đường dạng "Từ → Đến", ngày, badge trạng thái.</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>1 đơn "Đang giao" (test_data_catalog §ACT)</t>
+          <t>Đơn "Đang giao" của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr"/>
@@ -9134,25 +9132,25 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG.</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment) — bất kỳ 2 đơn active nào trong bộ này đã khác tên tin/tuyến sẵn.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed cho tài khoản 2 đơn đang hoạt động khác nhau về tên tin và tuyến đường. (setup)
-2. Đăng nhập FoxEco và nhấn tab "Hoạt động".
-3. Ghi lại tên tin và tuyến đường của card thứ hai.
-4. Nhấn vào card thứ hai.</t>
+          <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
+2. Ghi lại tên tin và tuyến đường của card thứ hai.
+3. Nhấn vào card thứ hai.</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>4. Màn vừa mở hiển thị tên tin và tuyến đường trùng khớp thông tin đã ghi ở bước 3.</t>
+          <t>3. Màn vừa mở hiển thị tên tin và tuyến đường trùng khớp thông tin đã ghi ở bước 2.</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>2 đơn đang hoạt động khác nhau (test_data_catalog §ACT)</t>
+          <t>2 đơn đang hoạt động khác nhau của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr"/>
@@ -9211,26 +9209,26 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG có ≥1 đơn đang hoạt động và ≥1 đơn đã kết thúc.</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment).
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed cho tài khoản 1 đơn ở trạng thái "Đang giao" và 1 đơn ở trạng thái "Hoàn thành". (setup)
-2. Đăng nhập FoxEco và nhấn tab "Hoạt động".
-3. Nhấn tab con "Đã hoàn thành".
-4. Nhấn tab con "Đang diễn ra".</t>
+          <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
+2. Nhấn tab con "Đã hoàn thành".
+3. Nhấn tab con "Đang diễn ra".</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>3. Tab "Đã hoàn thành" chuyển sang active, tab "Đang diễn ra" hết active; danh sách bên dưới được thay bằng danh sách khác.
-4. Tab "Đang diễn ra" chuyển lại active; danh sách trở về danh sách ban đầu.</t>
+          <t>2. Tab "Đã hoàn thành" chuyển sang active, tab "Đang diễn ra" hết active; danh sách bên dưới được thay bằng danh sách khác.
+3. Tab "Đang diễn ra" chuyển lại active; danh sách trở về danh sách ban đầu.</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>1 đơn "Đang giao" + 1 đơn "Hoàn thành" (test_data_catalog §ACT)</t>
+          <t>Đơn "Đang giao" + đơn "Hoàn thành" của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr"/>
@@ -9289,24 +9287,24 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG có ≥1 đơn "Hết hạn".</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment) — gồm đơn "Hết hạn" cần dev/QA chuẩn bị trước vì ⛔ không tạo được qua UI.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed 1 đơn có "Đến ngày" đã trôi qua để đơn chuyển trạng thái "Hết hạn". (setup)
-2. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành".
-3. Check card đơn hết hạn.</t>
+          <t>1. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành". (setup)
+2. Check card đơn "Hết hạn".</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>3. Card hiển thị badge "Hết hạn" và dòng lý do đúng chuỗi "Không có ai nhận mang giúp trong thời gian đăng — tin đã tự động đóng."</t>
+          <t>2. Card hiển thị badge "Hết hạn" và dòng lý do đúng chuỗi "Không có ai nhận mang giúp trong thời gian đăng — tin đã tự động đóng."</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>1 đơn "Hết hạn" (test_data_catalog §ACT — ⛔ không seed được qua UI)</t>
+          <t>Đơn "Hết hạn" của `SEED-ACT-01` (test_data_catalog §ACT — ⛔ không seed được qua UI)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr"/>
@@ -9365,24 +9363,24 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG có ≥1 đơn "Hết hạn".</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment) — dùng chung đơn "Hết hạn" với TC-ACT-008, không seed lại.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed 1 đơn có "Đến ngày" đã trôi qua để đơn chuyển trạng thái "Hết hạn". (setup)
-2. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành".
-3. Nhấn vào card đơn "Hết hạn".</t>
+          <t>1. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành". (setup)
+2. Nhấn vào card đơn "Hết hạn".</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>3. Không mở màn nào, không hiện popup; màn Hoạt động giữ nguyên với tab "Đã hoàn thành" vẫn active.</t>
+          <t>2. Không mở màn nào, không hiện popup; màn Hoạt động giữ nguyên với tab "Đã hoàn thành" vẫn active.</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>1 đơn "Hết hạn" (test_data_catalog §ACT)</t>
+          <t>Đơn "Hết hạn" của `SEED-ACT-01`, dùng chung với TC-ACT-008 (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr"/>
@@ -9518,7 +9516,8 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản CBNV "trắng" trên STG (không có đơn nào ở trạng thái từ "Chờ ghép" đến "Đã giao").</t>
+          <t>- Tài khoản CBNV "trắng" trên STG = `SEED-ACT-02` (không có đơn nào ở trạng thái từ "Chờ ghép" đến "Đã giao") — dùng chung với TC-ACT-014, chuẩn bị 1 lần.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -9594,24 +9593,24 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG có ≥1 đơn "Hoàn thành".</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment) — dùng chung đơn "Hoàn thành" với TC-ACT-003/005, không seed lại.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed 1 đơn ở trạng thái "Hoàn thành" cho tài khoản. (setup)
-2. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành".
-3. Nhấn vào vùng chuỗi sao trên card đơn "Hoàn thành".</t>
+          <t>1. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành". (setup)
+2. Nhấn vào vùng chuỗi sao trên card đơn "Hoàn thành".</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>3. Không mở màn chấm điểm hay popup chấm sao nào; không có control nào cho phép chọn số sao.</t>
+          <t>2. Không mở màn chấm điểm hay popup chấm sao nào; không có control nào cho phép chọn số sao.</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>1 đơn "Hoàn thành" (test_data_catalog §ACT)</t>
+          <t>Đơn "Hoàn thành" của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr"/>
@@ -9670,7 +9669,8 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản CBNV "trắng" trên STG (chưa có đơn "Hoàn thành" và chưa có đơn "Hết hạn").</t>
+          <t>- Tài khoản CBNV "trắng" trên STG = `SEED-ACT-02` (chưa có đơn "Hoàn thành" và chưa có đơn "Hết hạn") — dùng chung với TC-ACT-012, không chuẩn bị lại.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -24610,7 +24610,7 @@
       <c r="H208" s="6" t="inlineStr">
         <is>
           <t>Tài khoản SSO CBNV FPT còn hiệu lực trên STG.
-- Host app FoxPro (`vn.fpt.ftel.sop.stg`) đã cài trên thiết bị Android.</t>
+- Host app FoxPro (`vn.fpt.ftel.sop.stg`) đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I208" s="6" t="inlineStr">
@@ -25856,26 +25856,26 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG có ≥1 đơn đang hoạt động và ≥1 đơn đã kết thúc.</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment).
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed cho tài khoản 1 đơn ở trạng thái "Đang giao" và 1 đơn ở trạng thái "Hoàn thành". (setup)
-2. Đăng nhập FoxEco và nhấn tab "Hoạt động".
-3. Nhấn tab con "Đã hoàn thành".
-4. Nhấn tab con "Đang diễn ra".</t>
+          <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
+2. Nhấn tab con "Đã hoàn thành".
+3. Nhấn tab con "Đang diễn ra".</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>3. Tab "Đã hoàn thành" chuyển sang active, tab "Đang diễn ra" hết active; danh sách bên dưới được thay bằng danh sách khác.
-4. Tab "Đang diễn ra" chuyển lại active; danh sách trở về danh sách ban đầu.</t>
+          <t>2. Tab "Đã hoàn thành" chuyển sang active, tab "Đang diễn ra" hết active; danh sách bên dưới được thay bằng danh sách khác.
+3. Tab "Đang diễn ra" chuyển lại active; danh sách trở về danh sách ban đầu.</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>1 đơn "Đang giao" + 1 đơn "Hoàn thành" (test_data_catalog §ACT)</t>
+          <t>Đơn "Đang giao" + đơn "Hoàn thành" của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr"/>
@@ -25934,24 +25934,24 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG.</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment).
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed cho tài khoản đủ 4 đơn đang hoạt động ở các trạng thái "Chờ ghép", "Đã ghép", "Đang giao", "Đã giao", cùng 1 đơn "Hoàn thành" và 1 đơn "Hết hạn". (setup)
-2. Đăng nhập FoxEco và nhấn tab "Hoạt động".
-3. Check badge trạng thái của từng card trong tab "Đang diễn ra".</t>
+          <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
+2. Check badge trạng thái của từng card trong tab "Đang diễn ra".</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>3. Mọi card trong danh sách có badge thuộc nhóm "Chờ ghép", "Đã ghép", "Đang giao", "Đã giao"; KHÔNG có card nào badge "Hoàn thành" hoặc "Hết hạn".</t>
+          <t>2. Mọi card trong danh sách có badge thuộc nhóm "Chờ ghép", "Đã ghép", "Đang giao", "Đã giao"; KHÔNG có card nào badge "Hoàn thành" hoặc "Hết hạn".</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>4 đơn đang hoạt động + 1 đơn "Hoàn thành" + 1 đơn "Hết hạn" (test_data_catalog §ACT)</t>
+          <t>4 đơn đang hoạt động + 1 đơn "Hoàn thành" + 1 đơn "Hết hạn" của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr"/>
@@ -26010,25 +26010,25 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG.</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment).
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed cho tài khoản 1 đơn "Hoàn thành", 1 đơn "Hết hạn" và 1 đơn "Đang giao". (setup)
-2. Đăng nhập FoxEco và nhấn tab "Hoạt động".
-3. Nhấn tab con "Đã hoàn thành".
-4. Check badge trạng thái của từng card trong danh sách.</t>
+          <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
+2. Nhấn tab con "Đã hoàn thành". (setup)
+3. Check badge trạng thái của từng card trong danh sách.</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>4. Danh sách có card badge "Hoàn thành" và card badge "Hết hạn"; KHÔNG có card nào badge "Chờ ghép", "Đã ghép", "Đang giao" hay "Đã giao".</t>
+          <t>3. Danh sách có card badge "Hoàn thành" và card badge "Hết hạn"; KHÔNG có card nào badge "Chờ ghép", "Đã ghép", "Đang giao" hay "Đã giao".</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>1 đơn "Hoàn thành" + 1 đơn "Hết hạn" + 1 đơn "Đang giao" (test_data_catalog §ACT)</t>
+          <t>1 đơn "Hoàn thành" + 1 đơn "Hết hạn" + 1 đơn "Đang giao" của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr"/>
@@ -26087,24 +26087,24 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG có ≥1 đơn đang hoạt động.</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment).
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed cho tài khoản 1 đơn ở trạng thái "Đang giao". (setup)
-2. Đăng nhập FoxEco và nhấn tab "Hoạt động".
-3. Check lần lượt các trường trên card đơn.</t>
+          <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
+2. Check lần lượt các trường trên card đơn "Đang giao".</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>3. Card hiển thị đủ 5 trường: icon trạng thái, tên tin, tuyến đường dạng "Từ → Đến", ngày, badge trạng thái.</t>
+          <t>2. Card hiển thị đủ 5 trường: icon trạng thái, tên tin, tuyến đường dạng "Từ → Đến", ngày, badge trạng thái.</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>1 đơn "Đang giao" (test_data_catalog §ACT)</t>
+          <t>Đơn "Đang giao" của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr"/>
@@ -26240,24 +26240,24 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG có ≥1 đơn "Hết hạn".</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment) — gồm đơn "Hết hạn" cần dev/QA chuẩn bị trước vì ⛔ không tạo được qua UI.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed 1 đơn có "Đến ngày" đã trôi qua để đơn chuyển trạng thái "Hết hạn". (setup)
-2. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành".
-3. Check card đơn hết hạn.</t>
+          <t>1. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành". (setup)
+2. Check card đơn "Hết hạn".</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>3. Card hiển thị badge "Hết hạn" và dòng lý do đúng chuỗi "Không có ai nhận mang giúp trong thời gian đăng — tin đã tự động đóng."</t>
+          <t>2. Card hiển thị badge "Hết hạn" và dòng lý do đúng chuỗi "Không có ai nhận mang giúp trong thời gian đăng — tin đã tự động đóng."</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>1 đơn "Hết hạn" (test_data_catalog §ACT — ⛔ không seed được qua UI)</t>
+          <t>Đơn "Hết hạn" của `SEED-ACT-01` (test_data_catalog §ACT — ⛔ không seed được qua UI)</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr"/>
@@ -26316,24 +26316,24 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG có ≥1 đơn "Hết hạn".</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment) — dùng chung đơn "Hết hạn" với TC-ACT-008, không seed lại.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed 1 đơn có "Đến ngày" đã trôi qua để đơn chuyển trạng thái "Hết hạn". (setup)
-2. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành".
-3. Nhấn vào card đơn "Hết hạn".</t>
+          <t>1. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành". (setup)
+2. Nhấn vào card đơn "Hết hạn".</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>3. Không mở màn nào, không hiện popup; màn Hoạt động giữ nguyên với tab "Đã hoàn thành" vẫn active.</t>
+          <t>2. Không mở màn nào, không hiện popup; màn Hoạt động giữ nguyên với tab "Đã hoàn thành" vẫn active.</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>1 đơn "Hết hạn" (test_data_catalog §ACT)</t>
+          <t>Đơn "Hết hạn" của `SEED-ACT-01`, dùng chung với TC-ACT-008 (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr"/>
@@ -26392,25 +26392,25 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG.</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment) — bất kỳ 2 đơn active nào trong bộ này đã khác tên tin/tuyến sẵn.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed cho tài khoản 2 đơn đang hoạt động khác nhau về tên tin và tuyến đường. (setup)
-2. Đăng nhập FoxEco và nhấn tab "Hoạt động".
-3. Ghi lại tên tin và tuyến đường của card thứ hai.
-4. Nhấn vào card thứ hai.</t>
+          <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
+2. Ghi lại tên tin và tuyến đường của card thứ hai.
+3. Nhấn vào card thứ hai.</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>4. Màn vừa mở hiển thị tên tin và tuyến đường trùng khớp thông tin đã ghi ở bước 3.</t>
+          <t>3. Màn vừa mở hiển thị tên tin và tuyến đường trùng khớp thông tin đã ghi ở bước 2.</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>2 đơn đang hoạt động khác nhau (test_data_catalog §ACT)</t>
+          <t>2 đơn đang hoạt động khác nhau của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr"/>
@@ -26546,7 +26546,8 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản CBNV "trắng" trên STG (không có đơn nào ở trạng thái từ "Chờ ghép" đến "Đã giao").</t>
+          <t>- Tài khoản CBNV "trắng" trên STG = `SEED-ACT-02` (không có đơn nào ở trạng thái từ "Chờ ghép" đến "Đã giao") — dùng chung với TC-ACT-014, chuẩn bị 1 lần.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -26622,24 +26623,24 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Tài khoản Sender trên STG có ≥1 đơn "Hoàn thành".</t>
+          <t>- Tài khoản A là CBNV có hồ sơ đầy đủ trên STG, đã seed sẵn `SEED-ACT-01` (xem ghi chú đầu fragment) — dùng chung đơn "Hoàn thành" với TC-ACT-003/005, không seed lại.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>1. Nhờ dev/QA seed 1 đơn ở trạng thái "Hoàn thành" cho tài khoản. (setup)
-2. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành".
-3. Nhấn vào vùng chuỗi sao trên card đơn "Hoàn thành".</t>
+          <t>1. Đăng nhập FoxEco, nhấn tab "Hoạt động" rồi nhấn tab con "Đã hoàn thành". (setup)
+2. Nhấn vào vùng chuỗi sao trên card đơn "Hoàn thành".</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>3. Không mở màn chấm điểm hay popup chấm sao nào; không có control nào cho phép chọn số sao.</t>
+          <t>2. Không mở màn chấm điểm hay popup chấm sao nào; không có control nào cho phép chọn số sao.</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>1 đơn "Hoàn thành" (test_data_catalog §ACT)</t>
+          <t>Đơn "Hoàn thành" của `SEED-ACT-01` (test_data_catalog §ACT)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr"/>
@@ -26698,7 +26699,8 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Tài khoản CBNV "trắng" trên STG (chưa có đơn "Hoàn thành" và chưa có đơn "Hết hạn").</t>
+          <t>- Tài khoản CBNV "trắng" trên STG = `SEED-ACT-02` (chưa có đơn "Hoàn thành" và chưa có đơn "Hết hạn") — dùng chung với TC-ACT-012, không chuẩn bị lại.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">

--- a/03_test-cases/TC-MASTER-LATEST.xlsx
+++ b/03_test-cases/TC-MASTER-LATEST.xlsx
@@ -5461,12 +5461,12 @@
 4. Nhấn nút đóng của lightbox.
 5. Nhấn lại ảnh đó để mở lightbox lần hai.
 6. Nhấn vào vùng nền tối ngoài ảnh.
-7. Check màn đang hiển thị sau cả hai lần đóng.</t>
+7. Check màn đang hiển thị sau lần đóng bằng nút và sau khi chạm nền tối.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>7. Cả hai cách đều đóng được lightbox và trả về đúng màn chi tiết tin.</t>
+          <t>7. Nút đóng (×) đóng được lightbox và trả về đúng màn chi tiết tin; chạm vùng nền tối KHÔNG đóng lightbox — lightbox chỉ đóng bằng nút (×).</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -5477,7 +5477,7 @@
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: hai đường đóng là hai handler khác nhau, fail độc lập — app hay quên handler chạm nền. · Căn cứ: `BR18-03`.</t>
+          <t>Mục đích: xác nhận cách đóng lightbox của app — chỉ đóng bằng nút (×), chạm nền tối không đóng. · Căn cứ: `BR18-03`. · ♻️ Sửa 2026-09-21 (QC GiangDC2, theo `BUG-024` đã huỷ): QC kiểm lại — app đúng, chạm nền không đóng lightbox; Expected đổi theo app (`BR18-03` không còn được hiểu là "chạm nền để đóng"). ⚠️ Title còn ghi *"cả nút đóng lẫn chạm nền"* — `§10.5` không cho sửa Title (xem CHANGELOG §3). VR-013: ✅ PASS.</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
@@ -6680,27 +6680,28 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập FoxEco bằng tài khoản A và đăng 1 tin NEED kèm 2 ảnh. (setup)
+          <t>1. Đăng nhập FoxEco bằng tài khoản A và đăng 1 tin NEED kèm 5 ảnh. (setup)
 2. Nhấn tab "Hoạt động" và mở tin đó. (setup)
 3. Nhấn "Chỉnh sửa" để mở form sửa tin.
-4. Nhấn giữ vào ảnh thứ nhất và tìm thao tác xoá ảnh.
-5. Check số ảnh của tin sau khi đã thử xoá.</t>
+4. Nhấn nút × trên ảnh thứ nhất.
+5. Nhấn "Tiếp theo" 2 lần, nhấn "Cập nhật đơn" và xác nhận "Đồng ý".
+6. Mở lại tin đó và check số ảnh của tin.</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>5. KHÔNG có thao tác xoá nào khả dụng và tin vẫn giữ đủ 2 ảnh.</t>
+          <t>6. Ảnh thứ nhất xoá được ở form sửa (bộ đếm còn 4/5) và sau khi lưu tin chỉ còn 4 ảnh.</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>1 tin `POSTED` có 2 ảnh = `SEED-ORD-04` (test_data_catalog §ORD — Tin đã đăng có ≥2 ảnh)</t>
+          <t>1 tin `POSTED` có 5 ảnh = `SEED-ORD-04` (test_data_catalog §ORD — Tin đã đăng có ≥2 ảnh)</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr"/>
       <c r="M67" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng âm cho `TC-ORD-087` — ảnh đã gắn mốc là bất biến *"phục vụ truy vết"*, cùng nhóm rule với `TC-DLV-048` (ảnh bằng chứng giao hàng). · Căn cứ: `BR18-05`. Tin phải còn `POSTED` để vào được form sửa (`BR05-01`).</t>
+          <t>Mục đích: ghi nhận hành vi thật của app — form sửa tin đã đăng vẫn cho xoá ảnh bằng nút ×; đối chiếu `TC-ORD-087`. Tin phải còn `POSTED` để vào được form sửa (`BR05-01`). · ♻️ Sửa 2026-09-21 (QC GiangDC2, theo `BUG-023` đã huỷ): QC kiểm lại — app đúng, cho xoá ảnh của tin đã đăng (đơn đã có mốc `Đăng tin` vẫn xoá được); Expected/Steps đổi theo app. ⚠️ Title còn ghi *"không xoá được"* — `§10.5` không cho sửa Title (xem CHANGELOG §3). ⚠️ `SC-CNL-010`/`SC-DLV-062` (nhóm "ảnh bất biến truy vết" `BR11-03`/`NFR-07`) chưa chạy — cân nhắc kiểm cùng cách hiểu. VR-013: ✅ PASS.</t>
         </is>
       </c>
       <c r="N67" s="6" t="inlineStr">
@@ -13219,6 +13220,7 @@
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>- Tài khoản A và B là hai CBNV khác nhau trên STG.
+- Ghi lại số thông báo khớp tuyến TỒN của tài khoản B trước khi seed (baseline), vì trần 5 tính theo tài khoản.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
@@ -13226,23 +13228,23 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản B, đăng 1 tin OFFER với điểm lấy, điểm giao, khoảng ngày và tập buổi xác định, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản A, đăng đúng 5 tin NEED qua wizard, mỗi tin trùng 2 điểm và giao ngày/buổi với tin OFFER đó, rồi đăng xuất. (setup)
-3. Đăng nhập bằng tài khoản B, nhấn icon chuông, đếm số thông báo khớp tuyến của tin OFFER đó.</t>
+3. Đăng nhập bằng tài khoản B, nhấn icon chuông, đếm số thông báo khớp tuyến của tin OFFER đó và TỔNG số thông báo khớp tuyến của tài khoản B.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3. Có đúng 5 thông báo khớp tuyến cho tin OFFER đó.</t>
+          <t>3. Tổng số thông báo khớp tuyến của tài khoản B đúng bằng trần **5** (trần tính theo TÀI KHOẢN, mọi tuyến cộng dồn). Nếu B còn thông báo khớp tuyến tồn từ tin/tuyến khác thì số thông báo MỚI của tin OFFER này = 5 − số thông báo tồn.</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>5 tin NEED khớp tuyến, tự đăng qua UI (test_data_catalog §ASN v1.1, mốc đúng trần)</t>
+          <t>5 tin NEED khớp tuyến, tự đăng qua UI; ghi baseline thông báo tồn của B (test_data_catalog §ASN v1.1, mốc đúng trần tài khoản)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: mốc đúng trần — biên hợp lệ, cặp với `TC-ASN-017` (mốc vượt trần). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-04` (dư) + `C-ASN-04` Resolved 2026-09-17. · Đã sửa theo delta v1.1: đổi test data OFFER sang khoảng ngày + tập buổi.</t>
+          <t>Mục đích: mốc đúng trần — biên hợp lệ, cặp với `TC-ASN-017` (mốc vượt trần). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-04` (dư) + `C-ASN-04` Resolved 2026-09-17. · Đã sửa theo delta v1.1: đổi test data OFFER sang khoảng ngày + tập buổi. · ✏️ Sửa 2026-09-21 (QC GiangDC2 recheck — KHÔNG phải bug): trần 5 thông báo khớp tuyến tính theo TÀI KHOẢN, mọi tuyến cộng dồn, ⛔ không phải theo từng tuyến. Căn cứ đo: VR-010 (5 tin NEED khớp → 4 thông báo mới + 1 tồn = 5). ✅ BA đã xác nhận lại 2026-09-21 (QC GiangDC2 báo lại, chưa có văn bản): trần tính theo TÀI KHOẢN — thay kết luận cũ `C-ASN-04(e)` (2026-09-17: độc lập theo từng tuyến).</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -13526,7 +13528,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản B đã đăng đủ 5 tin NEED khớp cho tuyến OFFER thứ nhất và đã nhận đủ 5 thông báo cho tuyến đó (tái dùng seed của `TC-ASN-016`) — không seed riêng.
+          <t>- Tài khoản B đã đăng đủ 5 tin NEED khớp cho tuyến OFFER thứ nhất và đã nhận đủ 5 thông báo (tổng thông báo khớp tuyến của B = 5, đã chạm trần tài khoản) (tái dùng seed của `TC-ASN-016`) — không seed riêng.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
@@ -13539,18 +13541,18 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>3. Tuyến thứ hai (P3→P4) nhận được thông báo mới dù tuyến thứ nhất đã đạt trần 5; tổng số thông báo của tài khoản B lớn hơn 5 (2 tuyến không cộng dồn chung 1 trần).</t>
+          <t>3. Tuyến thứ hai (P3→P4) KHÔNG nhận thông báo mới vì tài khoản B đã đạt trần 5 (trần tính theo TÀI KHOẢN, tuyến thứ hai không có slot riêng); tổng số thông báo khớp tuyến của B vẫn bằng 5.</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>2 tuyến OFFER độc lập của cùng tài khoản B, mỗi tuyến trần 5 riêng (test_data_catalog §ASN v1.1)</t>
+          <t>2 tuyến OFFER của cùng tài khoản B, dùng chung 1 trần 5 theo tài khoản (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: xác nhận `C-ASN-04(e)` — trần ĐỘC LẬP theo từng tuyến (mỗi lần đăng "Tôi nhận giao hàng"); rủi ro thật nếu backend dùng chung 1 bộ đếm cho cả tài khoản. · Căn cứ: kết luận BA `C-ASN-04(e)`, `risk_assessment.md` Resolved 2026-09-17.</t>
+          <t>Mục đích: xác nhận `C-ASN-04(e)` — trần ĐỘC LẬP theo từng tuyến (mỗi lần đăng "Tôi nhận giao hàng"); rủi ro thật nếu backend dùng chung 1 bộ đếm cho cả tài khoản. · Căn cứ: kết luận BA `C-ASN-04(e)`, `risk_assessment.md` Resolved 2026-09-17. · ✏️ Sửa 2026-09-21 (QC GiangDC2 recheck — KHÔNG phải bug): ĐẢO kỳ vọng — trần 5 tính theo TÀI KHOẢN nên tuyến thứ hai KHÔNG có slot riêng. Căn cứ đo: VR-010 (OFFER tuyến 2 + 1 tin NEED khớp, tổng vẫn 5, 0 thông báo mới). ✅ BA đã xác nhận lại 2026-09-21 (QC GiangDC2 báo lại, chưa có văn bản): trần tính theo TÀI KHOẢN — thay kết luận cũ `C-ASN-04(e)` (2026-09-17: độc lập theo từng tuyến). ⚠️ `Test Title` giữ nguyên (§10.5 không cho đổi tiêu đề) nên tiêu đề CŨ ('độc lập, không cộng dồn') mô tả rule BA cũ — đọc theo Expected.</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -19185,7 +19187,7 @@
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>2. Khung hiển thị placeholder kèm thông báo (không phải ảnh bản đồ vẽ tuyến); khoảng cách hiện đúng "0km"; màn không vỡ layout.</t>
+          <t>2. Hiển thị dòng cảnh báo "Chưa xác định được toạ độ trên bản đồ cho địa chỉ này" lồng trong card Lộ trình, ngay dưới địa chỉ Giao hàng (KHÔNG có khung/placeholder bản đồ riêng, KHÔNG hiển thị "0km"); màn không vỡ layout.</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
@@ -19193,10 +19195,14 @@
           <t>Văn phòng thiếu lat/lng theo `location_address_catalog.xlsx` (test_data_catalog §FEED — BA cấp data khi test)</t>
         </is>
       </c>
-      <c r="L93" s="6" t="inlineStr"/>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: SC mới — nhánh lỗi data khi văn phòng thiếu toạ độ, đối chứng với `TC-FEED-009` (văn phòng đủ toạ độ). · Căn cứ: `C-FEED-02` + `C-FEED-05` Resolved 2026-09-17 (BA: thiếu toạ độ là lỗi data STG, không phải bug app). ⚠️ BA đánh giá "có thể không cần viết TC" vì là lỗi data — vẫn viết để có coverage nhánh lỗi (đánh P3); text thông báo cụ thể + nhánh "chỉ 1 trong 2 điểm thiếu" chưa chốt, Expected chỉ assert phần đã chốt (placeholder + "0km" + không vỡ layout).</t>
+          <t>Mục đích: SC mới — nhánh lỗi data khi văn phòng thiếu toạ độ, đối chứng với `TC-FEED-009` (văn phòng đủ toạ độ). · Căn cứ gốc: `C-FEED-02` + `C-FEED-05` Resolved 2026-09-17 (BA: thiếu toạ độ là lỗi data STG, không phải bug app). ⛔ Sửa tại chỗ 2026-09-21 (QC GiangDC2, sau `BUG-029`): Expected gốc "khung placeholder + 0km" KHÔNG khớp hành vi thật trên STG (vibe-test VR-016 — chỉ có dòng cảnh báo text, không khung, không "0km", tái hiện 2 lần độc lập). QC chấp nhận hành vi hiện tại ⇒ sửa Expected theo app, `BUG-029` rút lại (không phải bug — xem `CHANGELOG.md §3`).</t>
         </is>
       </c>
       <c r="N93" s="6" t="inlineStr">
@@ -24748,12 +24754,12 @@
 4. Nhấn nút đóng của lightbox.
 5. Nhấn lại ảnh đó để mở lightbox lần hai.
 6. Nhấn vào vùng nền tối ngoài ảnh.
-7. Check màn đang hiển thị sau cả hai lần đóng.</t>
+7. Check màn đang hiển thị sau lần đóng bằng nút và sau khi chạm nền tối.</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>7. Cả hai cách đều đóng được lightbox và trả về đúng màn chi tiết tin.</t>
+          <t>7. Nút đóng (×) đóng được lightbox và trả về đúng màn chi tiết tin; chạm vùng nền tối KHÔNG đóng lightbox — lightbox chỉ đóng bằng nút (×).</t>
         </is>
       </c>
       <c r="K164" s="5" t="inlineStr">
@@ -24764,7 +24770,7 @@
       <c r="L164" s="5" t="inlineStr"/>
       <c r="M164" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: hai đường đóng là hai handler khác nhau, fail độc lập — app hay quên handler chạm nền. · Căn cứ: `BR18-03`.</t>
+          <t>Mục đích: xác nhận cách đóng lightbox của app — chỉ đóng bằng nút (×), chạm nền tối không đóng. · Căn cứ: `BR18-03`. · ♻️ Sửa 2026-09-21 (QC GiangDC2, theo `BUG-024` đã huỷ): QC kiểm lại — app đúng, chạm nền không đóng lightbox; Expected đổi theo app (`BR18-03` không còn được hiểu là "chạm nền để đóng"). ⚠️ Title còn ghi *"cả nút đóng lẫn chạm nền"* — `§10.5` không cho sửa Title (xem CHANGELOG §3). VR-013: ✅ PASS.</t>
         </is>
       </c>
       <c r="N164" s="5" t="inlineStr">
@@ -25140,27 +25146,28 @@
       </c>
       <c r="I169" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập FoxEco bằng tài khoản A và đăng 1 tin NEED kèm 2 ảnh. (setup)
+          <t>1. Đăng nhập FoxEco bằng tài khoản A và đăng 1 tin NEED kèm 5 ảnh. (setup)
 2. Nhấn tab "Hoạt động" và mở tin đó. (setup)
 3. Nhấn "Chỉnh sửa" để mở form sửa tin.
-4. Nhấn giữ vào ảnh thứ nhất và tìm thao tác xoá ảnh.
-5. Check số ảnh của tin sau khi đã thử xoá.</t>
+4. Nhấn nút × trên ảnh thứ nhất.
+5. Nhấn "Tiếp theo" 2 lần, nhấn "Cập nhật đơn" và xác nhận "Đồng ý".
+6. Mở lại tin đó và check số ảnh của tin.</t>
         </is>
       </c>
       <c r="J169" s="7" t="inlineStr">
         <is>
-          <t>5. KHÔNG có thao tác xoá nào khả dụng và tin vẫn giữ đủ 2 ảnh.</t>
+          <t>6. Ảnh thứ nhất xoá được ở form sửa (bộ đếm còn 4/5) và sau khi lưu tin chỉ còn 4 ảnh.</t>
         </is>
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>1 tin `POSTED` có 2 ảnh = `SEED-ORD-04` (test_data_catalog §ORD — Tin đã đăng có ≥2 ảnh)</t>
+          <t>1 tin `POSTED` có 5 ảnh = `SEED-ORD-04` (test_data_catalog §ORD — Tin đã đăng có ≥2 ảnh)</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
       <c r="M169" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng âm cho `TC-ORD-087` — ảnh đã gắn mốc là bất biến *"phục vụ truy vết"*, cùng nhóm rule với `TC-DLV-048` (ảnh bằng chứng giao hàng). · Căn cứ: `BR18-05`. Tin phải còn `POSTED` để vào được form sửa (`BR05-01`).</t>
+          <t>Mục đích: ghi nhận hành vi thật của app — form sửa tin đã đăng vẫn cho xoá ảnh bằng nút ×; đối chiếu `TC-ORD-087`. Tin phải còn `POSTED` để vào được form sửa (`BR05-01`). · ♻️ Sửa 2026-09-21 (QC GiangDC2, theo `BUG-023` đã huỷ): QC kiểm lại — app đúng, cho xoá ảnh của tin đã đăng (đơn đã có mốc `Đăng tin` vẫn xoá được); Expected/Steps đổi theo app. ⚠️ Title còn ghi *"không xoá được"* — `§10.5` không cho sửa Title (xem CHANGELOG §3). ⚠️ `SC-CNL-010`/`SC-DLV-062` (nhóm "ảnh bất biến truy vết" `BR11-03`/`NFR-07`) chưa chạy — cân nhắc kiểm cùng cách hiểu. VR-013: ✅ PASS.</t>
         </is>
       </c>
       <c r="N169" s="6" t="inlineStr">
@@ -31349,6 +31356,7 @@
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>- Tài khoản A và B là hai CBNV khác nhau trên STG.
+- Ghi lại số thông báo khớp tuyến TỒN của tài khoản B trước khi seed (baseline), vì trần 5 tính theo tài khoản.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
@@ -31356,23 +31364,23 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản B, đăng 1 tin OFFER với điểm lấy, điểm giao, khoảng ngày và tập buổi xác định, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản A, đăng đúng 5 tin NEED qua wizard, mỗi tin trùng 2 điểm và giao ngày/buổi với tin OFFER đó, rồi đăng xuất. (setup)
-3. Đăng nhập bằng tài khoản B, nhấn icon chuông, đếm số thông báo khớp tuyến của tin OFFER đó.</t>
+3. Đăng nhập bằng tài khoản B, nhấn icon chuông, đếm số thông báo khớp tuyến của tin OFFER đó và TỔNG số thông báo khớp tuyến của tài khoản B.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3. Có đúng 5 thông báo khớp tuyến cho tin OFFER đó.</t>
+          <t>3. Tổng số thông báo khớp tuyến của tài khoản B đúng bằng trần **5** (trần tính theo TÀI KHOẢN, mọi tuyến cộng dồn). Nếu B còn thông báo khớp tuyến tồn từ tin/tuyến khác thì số thông báo MỚI của tin OFFER này = 5 − số thông báo tồn.</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>5 tin NEED khớp tuyến, tự đăng qua UI (test_data_catalog §ASN v1.1, mốc đúng trần)</t>
+          <t>5 tin NEED khớp tuyến, tự đăng qua UI; ghi baseline thông báo tồn của B (test_data_catalog §ASN v1.1, mốc đúng trần tài khoản)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: mốc đúng trần — biên hợp lệ, cặp với `TC-ASN-017` (mốc vượt trần). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-04` (dư) + `C-ASN-04` Resolved 2026-09-17. · Đã sửa theo delta v1.1: đổi test data OFFER sang khoảng ngày + tập buổi.</t>
+          <t>Mục đích: mốc đúng trần — biên hợp lệ, cặp với `TC-ASN-017` (mốc vượt trần). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-04` (dư) + `C-ASN-04` Resolved 2026-09-17. · Đã sửa theo delta v1.1: đổi test data OFFER sang khoảng ngày + tập buổi. · ✏️ Sửa 2026-09-21 (QC GiangDC2 recheck — KHÔNG phải bug): trần 5 thông báo khớp tuyến tính theo TÀI KHOẢN, mọi tuyến cộng dồn, ⛔ không phải theo từng tuyến. Căn cứ đo: VR-010 (5 tin NEED khớp → 4 thông báo mới + 1 tồn = 5). ✅ BA đã xác nhận lại 2026-09-21 (QC GiangDC2 báo lại, chưa có văn bản): trần tính theo TÀI KHOẢN — thay kết luận cũ `C-ASN-04(e)` (2026-09-17: độc lập theo từng tuyến).</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -31504,7 +31512,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản B đã đăng đủ 5 tin NEED khớp cho tuyến OFFER thứ nhất và đã nhận đủ 5 thông báo cho tuyến đó (tái dùng seed của `TC-ASN-016`) — không seed riêng.
+          <t>- Tài khoản B đã đăng đủ 5 tin NEED khớp cho tuyến OFFER thứ nhất và đã nhận đủ 5 thông báo (tổng thông báo khớp tuyến của B = 5, đã chạm trần tài khoản) (tái dùng seed của `TC-ASN-016`) — không seed riêng.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
@@ -31517,18 +31525,18 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3. Tuyến thứ hai (P3→P4) nhận được thông báo mới dù tuyến thứ nhất đã đạt trần 5; tổng số thông báo của tài khoản B lớn hơn 5 (2 tuyến không cộng dồn chung 1 trần).</t>
+          <t>3. Tuyến thứ hai (P3→P4) KHÔNG nhận thông báo mới vì tài khoản B đã đạt trần 5 (trần tính theo TÀI KHOẢN, tuyến thứ hai không có slot riêng); tổng số thông báo khớp tuyến của B vẫn bằng 5.</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>2 tuyến OFFER độc lập của cùng tài khoản B, mỗi tuyến trần 5 riêng (test_data_catalog §ASN v1.1)</t>
+          <t>2 tuyến OFFER của cùng tài khoản B, dùng chung 1 trần 5 theo tài khoản (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: xác nhận `C-ASN-04(e)` — trần ĐỘC LẬP theo từng tuyến (mỗi lần đăng "Tôi nhận giao hàng"); rủi ro thật nếu backend dùng chung 1 bộ đếm cho cả tài khoản. · Căn cứ: kết luận BA `C-ASN-04(e)`, `risk_assessment.md` Resolved 2026-09-17.</t>
+          <t>Mục đích: xác nhận `C-ASN-04(e)` — trần ĐỘC LẬP theo từng tuyến (mỗi lần đăng "Tôi nhận giao hàng"); rủi ro thật nếu backend dùng chung 1 bộ đếm cho cả tài khoản. · Căn cứ: kết luận BA `C-ASN-04(e)`, `risk_assessment.md` Resolved 2026-09-17. · ✏️ Sửa 2026-09-21 (QC GiangDC2 recheck — KHÔNG phải bug): ĐẢO kỳ vọng — trần 5 tính theo TÀI KHOẢN nên tuyến thứ hai KHÔNG có slot riêng. Căn cứ đo: VR-010 (OFFER tuyến 2 + 1 tin NEED khớp, tổng vẫn 5, 0 thông báo mới). ✅ BA đã xác nhận lại 2026-09-21 (QC GiangDC2 báo lại, chưa có văn bản): trần tính theo TÀI KHOẢN — thay kết luận cũ `C-ASN-04(e)` (2026-09-17: độc lập theo từng tuyến). ⚠️ `Test Title` giữ nguyên (§10.5 không cho đổi tiêu đề) nên tiêu đề CŨ ('độc lập, không cộng dồn') mô tả rule BA cũ — đọc theo Expected.</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -37607,7 +37615,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>2. Khung hiển thị placeholder kèm thông báo (không phải ảnh bản đồ vẽ tuyến); khoảng cách hiện đúng "0km"; màn không vỡ layout.</t>
+          <t>2. Hiển thị dòng cảnh báo "Chưa xác định được toạ độ trên bản đồ cho địa chỉ này" lồng trong card Lộ trình, ngay dưới địa chỉ Giao hàng (KHÔNG có khung/placeholder bản đồ riêng, KHÔNG hiển thị "0km"); màn không vỡ layout.</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -37615,10 +37623,14 @@
           <t>Văn phòng thiếu lat/lng theo `location_address_catalog.xlsx` (test_data_catalog §FEED — BA cấp data khi test)</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: SC mới — nhánh lỗi data khi văn phòng thiếu toạ độ, đối chứng với `TC-FEED-009` (văn phòng đủ toạ độ). · Căn cứ: `C-FEED-02` + `C-FEED-05` Resolved 2026-09-17 (BA: thiếu toạ độ là lỗi data STG, không phải bug app). ⚠️ BA đánh giá "có thể không cần viết TC" vì là lỗi data — vẫn viết để có coverage nhánh lỗi (đánh P3); text thông báo cụ thể + nhánh "chỉ 1 trong 2 điểm thiếu" chưa chốt, Expected chỉ assert phần đã chốt (placeholder + "0km" + không vỡ layout).</t>
+          <t>Mục đích: SC mới — nhánh lỗi data khi văn phòng thiếu toạ độ, đối chứng với `TC-FEED-009` (văn phòng đủ toạ độ). · Căn cứ gốc: `C-FEED-02` + `C-FEED-05` Resolved 2026-09-17 (BA: thiếu toạ độ là lỗi data STG, không phải bug app). ⛔ Sửa tại chỗ 2026-09-21 (QC GiangDC2, sau `BUG-029`): Expected gốc "khung placeholder + 0km" KHÔNG khớp hành vi thật trên STG (vibe-test VR-016 — chỉ có dòng cảnh báo text, không khung, không "0km", tái hiện 2 lần độc lập). QC chấp nhận hành vi hiện tại ⇒ sửa Expected theo app, `BUG-029` rút lại (không phải bug — xem `CHANGELOG.md §3`).</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">

--- a/03_test-cases/TC-MASTER-LATEST.xlsx
+++ b/03_test-cases/TC-MASTER-LATEST.xlsx
@@ -12372,12 +12372,12 @@
           <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
 2. Nhấn tab con "Đã hoàn thành". (setup)
 3. Nhấn tab con "Đang diễn ra" rồi rà toàn bộ danh sách. (setup)
-4. Nhấn lại tab con "Đã hoàn thành" và check cả hai đơn của cặp đối chứng trong cùng một lượt xem.</t>
+4. Nhấn lại tab con "Đã hoàn thành" và check vị trí của cả hai đơn trong cặp đối chứng ở hai tab vừa rà.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>4. Đơn đã trả lại người gửi CÓ trong danh sách tab "Đã hoàn thành" và hiện lý do hoàn hàng trên card; đơn "Đã huỷ" KHÔNG xuất hiện ở cả hai tab.</t>
+          <t>4. Đơn đã trả lại người gửi CÓ trong danh sách tab "Đã hoàn thành" và hiện lý do hoàn hàng trên card; đơn "Đã huỷ" nằm ở tab "Đang diễn ra" với badge "Đã huỷ" và KHÔNG xuất hiện ở tab "Đã hoàn thành".</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -12388,7 +12388,7 @@
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: hai kết cục bất thường nhưng hai cách xử lý ngược nhau — giá trị của TC nằm ở **phép đối chứng**, xem lẻ từng đơn thì không bắt được lỗi "gom chung mọi đơn bất thường vào một nhánh hiển thị". · Căn cứ: `AC-24.2.01` cho vế `RETURNED`; vế `CANCELLED` theo BA trả lời `C-ACT-04(b)` 2026-09-17 — đơn "Đã huỷ" **vẫn ẩn khỏi cả 2 tab**, rule v1.0 CÒN HIỆU LỰC, `§8.12.3` cho mọi vai *"Xem lý do"* đơn huỷ là **PRD chưa cập nhật**. Đơn "Đã huỷ" hiện ra ⇒ FAIL và log bug, ⛔ không sửa Expected theo `§8.12.3`. · Phụ thuộc lô `DLV` để có đơn `RETURNED` — lô đó `BLOCKED` thì TC này `BLOCKED`.</t>
+          <t>Đã sửa Expected theo app — QC GiangDC2 chốt 2026-09-21 (sau VR-017): đơn "Đã huỷ" hiện ở tab "Đang diễn ra" với badge "Đã huỷ" là hành vi ĐÚNG, không phải bug; thay kết luận BA `C-ACT-04(b)` 2026-09-17 (ẩn khỏi cả 2 tab). ⚠️ Title chưa sửa vì `§10.5` khoá Title (nợ #27 `03_test-cases/v1.1/CHANGELOG.md`). · Mục đích: hai kết cục bất thường nhưng hai cách xử lý ngược nhau — giá trị của TC nằm ở **phép đối chứng**, xem lẻ từng đơn thì không bắt được lỗi "gom chung mọi đơn bất thường vào một nhánh hiển thị". · Căn cứ: `AC-24.2.01` cho vế `RETURNED`; vế `CANCELLED` theo BA trả lời `C-ACT-04(b)` 2026-09-17 — đơn "Đã huỷ" **vẫn ẩn khỏi cả 2 tab**, rule v1.0 CÒN HIỆU LỰC, `§8.12.3` cho mọi vai *"Xem lý do"* đơn huỷ là **PRD chưa cập nhật**. · Phụ thuộc lô `DLV` để có đơn `RETURNED` — lô đó `BLOCKED` thì TC này `BLOCKED`.</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
@@ -12606,12 +12606,12 @@
 2. Nhấn tab "Hoạt động". (setup)
 3. Vuốt lên và vuốt xuống trên vùng danh sách của tab "Đang diễn ra".
 4. Nhấn tab con "Đã hoàn thành".
-5. Vuốt lên và vuốt xuống trên vùng danh sách, và check phản hồi cuộn của màn ở cả hai tab con.</t>
+5. Vuốt lên và vuốt xuống trên vùng danh sách, và check trạng thái của màn ở cả hai tab con.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5. Màn phản hồi thao tác cuộn ở cả hai tab con, không bị khoá cứng tại chỗ.</t>
+          <t>5. Ở cả hai tab con, empty state đứng cố định trong vùng danh sách khi vuốt (nội dung vừa khít màn, không có gì để cuộn); màn không treo, không lỗi và thanh tab dưới vẫn hiển thị đủ.</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -12622,7 +12622,7 @@
       <c r="L10" s="5" t="inlineStr"/>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.17.2 BR17-03 — rule đòi empty state vừa không che thanh tab dưới vừa giữ màn cuộn được.</t>
+          <t>Đã sửa Expected + step 5 theo app — QC GiangDC2 chốt 2026-09-21 (sau VR-017): màn rỗng không cuộn/không phản hồi vuốt là hành vi ĐÚNG, không phải bug (`BUG-032` đã xoá). ⚠️ Title chưa sửa vì `§10.5` khoá Title (nợ #28 `03_test-cases/v1.1/CHANGELOG.md`). · Căn cứ gốc: `DOC-v1.1-01` §8.17.2 BR17-03 — QC hiểu "vẫn cuộn được" là màn không bị treo/khoá thao tác, không bắt buộc có phản hồi cuộn khi không có nội dung vượt màn.</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -29946,12 +29946,12 @@
           <t>1. Đăng nhập FoxEco và nhấn tab "Hoạt động". (setup)
 2. Nhấn tab con "Đã hoàn thành". (setup)
 3. Nhấn tab con "Đang diễn ra" rồi rà toàn bộ danh sách. (setup)
-4. Nhấn lại tab con "Đã hoàn thành" và check cả hai đơn của cặp đối chứng trong cùng một lượt xem.</t>
+4. Nhấn lại tab con "Đã hoàn thành" và check vị trí của cả hai đơn trong cặp đối chứng ở hai tab vừa rà.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4. Đơn đã trả lại người gửi CÓ trong danh sách tab "Đã hoàn thành" và hiện lý do hoàn hàng trên card; đơn "Đã huỷ" KHÔNG xuất hiện ở cả hai tab.</t>
+          <t>4. Đơn đã trả lại người gửi CÓ trong danh sách tab "Đã hoàn thành" và hiện lý do hoàn hàng trên card; đơn "Đã huỷ" nằm ở tab "Đang diễn ra" với badge "Đã huỷ" và KHÔNG xuất hiện ở tab "Đã hoàn thành".</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -29962,7 +29962,7 @@
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: hai kết cục bất thường nhưng hai cách xử lý ngược nhau — giá trị của TC nằm ở **phép đối chứng**, xem lẻ từng đơn thì không bắt được lỗi "gom chung mọi đơn bất thường vào một nhánh hiển thị". · Căn cứ: `AC-24.2.01` cho vế `RETURNED`; vế `CANCELLED` theo BA trả lời `C-ACT-04(b)` 2026-09-17 — đơn "Đã huỷ" **vẫn ẩn khỏi cả 2 tab**, rule v1.0 CÒN HIỆU LỰC, `§8.12.3` cho mọi vai *"Xem lý do"* đơn huỷ là **PRD chưa cập nhật**. Đơn "Đã huỷ" hiện ra ⇒ FAIL và log bug, ⛔ không sửa Expected theo `§8.12.3`. · Phụ thuộc lô `DLV` để có đơn `RETURNED` — lô đó `BLOCKED` thì TC này `BLOCKED`.</t>
+          <t>Đã sửa Expected theo app — QC GiangDC2 chốt 2026-09-21 (sau VR-017): đơn "Đã huỷ" hiện ở tab "Đang diễn ra" với badge "Đã huỷ" là hành vi ĐÚNG, không phải bug; thay kết luận BA `C-ACT-04(b)` 2026-09-17 (ẩn khỏi cả 2 tab). ⚠️ Title chưa sửa vì `§10.5` khoá Title (nợ #27 `03_test-cases/v1.1/CHANGELOG.md`). · Mục đích: hai kết cục bất thường nhưng hai cách xử lý ngược nhau — giá trị của TC nằm ở **phép đối chứng**, xem lẻ từng đơn thì không bắt được lỗi "gom chung mọi đơn bất thường vào một nhánh hiển thị". · Căn cứ: `AC-24.2.01` cho vế `RETURNED`; vế `CANCELLED` theo BA trả lời `C-ACT-04(b)` 2026-09-17 — đơn "Đã huỷ" **vẫn ẩn khỏi cả 2 tab**, rule v1.0 CÒN HIỆU LỰC, `§8.12.3` cho mọi vai *"Xem lý do"* đơn huỷ là **PRD chưa cập nhật**. · Phụ thuộc lô `DLV` để có đơn `RETURNED` — lô đó `BLOCKED` thì TC này `BLOCKED`.</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
@@ -30439,12 +30439,12 @@
 2. Nhấn tab "Hoạt động". (setup)
 3. Vuốt lên và vuốt xuống trên vùng danh sách của tab "Đang diễn ra".
 4. Nhấn tab con "Đã hoàn thành".
-5. Vuốt lên và vuốt xuống trên vùng danh sách, và check phản hồi cuộn của màn ở cả hai tab con.</t>
+5. Vuốt lên và vuốt xuống trên vùng danh sách, và check trạng thái của màn ở cả hai tab con.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5. Màn phản hồi thao tác cuộn ở cả hai tab con, không bị khoá cứng tại chỗ.</t>
+          <t>5. Ở cả hai tab con, empty state đứng cố định trong vùng danh sách khi vuốt (nội dung vừa khít màn, không có gì để cuộn); màn không treo, không lỗi và thanh tab dưới vẫn hiển thị đủ.</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -30455,7 +30455,7 @@
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.17.2 BR17-03 — rule đòi empty state vừa không che thanh tab dưới vừa giữ màn cuộn được.</t>
+          <t>Đã sửa Expected + step 5 theo app — QC GiangDC2 chốt 2026-09-21 (sau VR-017): màn rỗng không cuộn/không phản hồi vuốt là hành vi ĐÚNG, không phải bug (`BUG-032` đã xoá). ⚠️ Title chưa sửa vì `§10.5` khoá Title (nợ #28 `03_test-cases/v1.1/CHANGELOG.md`). · Căn cứ gốc: `DOC-v1.1-01` §8.17.2 BR17-03 — QC hiểu "vẫn cuộn được" là màn không bị treo/khoá thao tác, không bắt buộc có phản hồi cuộn khi không có nội dung vượt màn.</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">

--- a/03_test-cases/TC-MASTER-LATEST.xlsx
+++ b/03_test-cases/TC-MASTER-LATEST.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Seed" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ALL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Hoạt động (Đơn của tôi)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ghép nối" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Huỷ đơn - Huỷ nhận đơn" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Giao nhận &amp; Theo dõi đơn" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Bảng tin &amp; Chi tiết tin" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Quà cảm ơn" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Trang chủ" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Thông báo" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Đăng tin &amp; Quản lý tin" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Trust &amp; Safety" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Tài khoản &amp; Hồ sơ" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seed" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoạt động (Đơn của tôi)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ghép nối" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Huỷ đơn - Huỷ nhận đơn" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Giao nhận &amp; Theo dõi đơn" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bảng tin &amp; Chi tiết tin" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quà cảm ơn" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trang chủ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thông báo" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đăng tin &amp; Quản lý tin" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust &amp; Safety" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tài khoản &amp; Hồ sơ" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ALL'!$A$1:$P$224</definedName>
@@ -1017,7 +1017,7 @@
           <t>1 đơn Hoàn thành mà A đóng vai người vận chuyển = `SEED-HOME-03` (test_data_catalog §HOME — Số đơn đã giúp theo vai)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="n"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo BA trả lời `C-HOME-06` 2026-09-17: hero chỉ đếm đơn **Hoàn thành ở vai người vận chuyển**, bản v1.0 chưa có công thức nên chỉ assert "có hiện số". · Mục đích: đo bằng phép tăng 1 thay vì so với con số tuyệt đối — tài khoản dùng chung trên STG không có con số gốc tin cậy. · Căn cứ: `BR14-04` (đơn Đã trả người gửi KHÔNG tính — verify ở `TC-DLV-065`). ⛔ Không assert số người ở dòng cộng đồng: BA đề nghị bỏ qua định nghĩa "người tham gia".</t>
@@ -1097,7 +1097,7 @@
           <t>Tài khoản chỉ làm người gửi, có ≥1 đơn Hoàn thành (test_data_catalog §HOME — Số đơn đã giúp theo vai, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="n"/>
       <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng âm cho `TC-HOME-008` — cùng 1 đơn Hoàn thành nhưng đếm cho vai người vận chuyển chứ không cho vai người gửi; lỗi hay gặp là đếm mọi đơn Hoàn thành mà tài khoản có liên quan. · Căn cứ: BA trả lời `C-HOME-06(a)` 2026-09-17 + `AC-26.2.01`.</t>
@@ -1176,7 +1176,7 @@
           <t>Số đơn cộng đồng trước và sau 1 đơn Hoàn thành (test_data_catalog §HOME — "[x] đơn · [y] người" cộng đồng)</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đồng thời chốt hai vế của `C-HOME-06(b)(c)` — x đếm **toàn hệ thống** (đơn do tài khoản khác hoàn thành vẫn cộng vào số A nhìn thấy) và cập nhật **realtime** (tăng ngay lần mở lại, không chờ chu kỳ). · Căn cứ: BA trả lời `C-HOME-06(b)(c)` 2026-09-17. ⛔ Không assert số người ở dòng này — định nghĩa "người tham gia" BA đề nghị bỏ qua.</t>
@@ -1260,7 +1260,11 @@
           <t>≥6 tin NEED `POSTED` hợp lệ = `SEED-HOME-02` (test_data_catalog §HOME — Số tin NEED section "Tin mới")</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-HOME-03` Resolved 2026-09-15 (`AC-11.1.01`): đổi từ *"hiển thị nhiều nhất 5 tin"* của bản v1.0 sang **đúng 5 tin** — PRD v1.1 thắng cả `DOC-v1.0-02` (1 tin) lẫn BRD `US-D06`. · Mục đích: app từng hiện đúng 1 tin; "nhiều nhất 5" khiến 1 tin cũng PASS, đó là lý do phải siết thành số chính xác. · Căn cứ: 3 lớp loại trừ verify riêng ở `TC-HOME-030` — TC này chỉ chốt số lượng.</t>
@@ -1339,7 +1343,11 @@
           <t>&gt;5 tin NEED hợp lệ = `SEED-HOME-02` (test_data_catalog §HOME — Tổng tin hợp lệ, biên trên)</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `AC-11.1.01` 2026-09-17: bổ sung điều kiện hiện nút (**&gt;5 tin hợp lệ**) mà bản v1.0 cố ý bỏ trống vì khi đó không có nguồn tài liệu (`RISK-HOME-03`). · Mục đích: cặp biên với `TC-HOME-025` — chiều dương của cùng ngưỡng 5.</t>
@@ -1418,7 +1426,11 @@
           <t>Đúng 5 tin NEED hợp lệ toàn hệ thống — biên dưới (test_data_catalog §HOME — Tổng tin hợp lệ, biên)</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên âm với `TC-HOME-021` — ngưỡng 5 phải phân định được hai chiều, chỉ chạy chiều dương thì nút luôn-hiện cũng PASS. · Căn cứ: `AC-11.1.01`. ⚠️ **Không dựng được trên STG dùng chung**: `C-HOME-04` Resolved 2026-09-17 chốt tin load **toàn quốc** nên phải khống chế dữ liệu toàn hệ thống, không chỉ dữ liệu tài khoản test. Không có môi trường riêng ⇒ ghi **`Blocked` kèm lý do**, ⛔ KHÔNG đánh PASS cho xong.</t>
@@ -1496,7 +1508,11 @@
           <t>Tài khoản "sạch" + 0 tin hợp lệ toàn hệ thống (test_data_catalog §HOME — Tài khoản "sạch" cho empty state)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Mục đích: kết quả phản trực giác — `C-HOME-04` chốt tin load **toàn quốc** nên chữ *"trong khu vực của bạn"* KHÔNG còn khớp hành vi, nhưng BA trả lời vòng 3 *"giữ nguyên nhé"* ⇒ **assert cứng chuỗi PRD**, ⛔ không sửa Expected theo logic. · Căn cứ: `EMP-01` + `AC-11.2.01`. App đổi chữ ⇒ FAIL và dẫn `C-HOME-04`. ⚠️ Cùng ràng buộc môi trường với `TC-HOME-025`; không dựng được ⇒ ghi `Blocked` kèm lý do.</t>
@@ -1576,7 +1592,7 @@
           <t>1 tin đã ghép + 1 tin hết hạn + 1 tin của chính tài khoản quan sát = `SEED-HOME-02` (test_data_catalog §HOME — Số tin NEED section "Tin mới")</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="n"/>
       <c r="M11" s="6" t="inlineStr">
         <is>
           <t>Mục đích: fail độc lập với `TC-HOME-019` — đếm đúng 5 tin không đảm bảo lọc đúng; app có thể trả đủ 5 nhưng lẫn tin đã ghép. · Căn cứ: `AC-11.1.01` — 3 lớp loại trừ là phần PRD v1.1 bổ sung, không nguồn v1.0 nào có. ✅ TC này **dựng được trên STG dùng chung** vì chỉ cần chứng minh 3 tin CỤ THỂ vắng mặt, ⛔ không cần khống chế toàn bộ danh sách như `TC-HOME-025`/`026`.</t>
@@ -1660,7 +1676,11 @@
           <t>Tài khoản 0 đơn đang chạy = `SEED-HOME-01` (test_data_catalog §HOME — Tài khoản "sạch")</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Mục đích: thay thế `TC-HOME-010` đã gỡ — TC cũ assert **NGƯỢC HẲN** (*"Trang chủ KHÔNG có section Đơn của tôi"*). Người chạy quen bản v1.0 rất dễ cho FAIL nhầm khi thấy section hiện ra. · Căn cứ: `C-HOME-05` **Resolved 2026-09-17** — BA chốt HIỆN `EMP-02`, không ẩn; ảnh demo `HOME_03` (không có section) nay là **lệch demo ↔ rule**, ⛔ không còn là oracle. Section bị ẩn ⇒ FAIL và log bug.</t>
@@ -1738,7 +1758,11 @@
           <t>Tài khoản "sạch" + hệ thống 0 đơn Hoàn thành (test_data_catalog §HOME — Tài khoản "sạch")</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
           <t>Mục đích: `EMP-03` là empty state duy nhất của Trang chủ **KHÔNG có CTA** — bất đối xứng với `EMP-01` và `EMP-02` (đều có 1 CTA); app hiện nút ở đây là **sai spec**. · Căn cứ: `AC-26.2.01` + `EMP-03` + `BR17-01` (*"tối đa một CTA"*).</t>
@@ -1825,12 +1849,12 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>🚫 Deferred — cần công cụ load-test, ⛔ không test tay được (QC GiangDC2, 2026-09-17)</t>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: giữ traceability cho `NFR01` thay vì bỏ hẳn SC — `test_data_catalog §HOME` ghi rõ *"không viết TC manual assert số đo"*, nên TC tồn tại để `execute-maintain` biết cần defer cho automation/load-test. · Căn cứ: `DOC-v1.1-01` §9 NFR01. ⛔ Loại khỏi mẫu số pass-rate cho tới khi có môi trường load-test.</t>
+          <t>Mục đích: giữ traceability cho `NFR01` thay vì bỏ hẳn SC — `test_data_catalog §HOME` ghi rõ *"không viết TC manual assert số đo"*, nên TC tồn tại để `execute-maintain` biết cần defer cho automation/load-test. · Căn cứ: `DOC-v1.1-01` §9 NFR01. ⛔ Loại khỏi mẫu số pass-rate cho tới khi có môi trường load-test. · 🚫 Deferred — cần công cụ load-test, ⛔ không test tay được (QC GiangDC2, 2026-09-17)</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -2031,7 +2055,7 @@
           <t>Đơn `COMPLETED` đủ 3 vai của `SEED-DLV-01` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="n"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Mục đích: PRD chính thức `DOC-v1.1-01` chốt dứt điểm text `NTF-06`, thay bản BRD "nguồn thắng có điều kiện" của v1.0 — hết rủi ro phải dẫn `C-NTF-01` nếu app lệch, vì `C-NTF-01` đã Resolved 2026-09-15. · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-06`. · Đã sửa theo delta v1.1 (2026-09-15): bỏ hedge "App hiện bản PRD ⇒ FAIL và dẫn C-NTF-01" ở Notes v1.0, nay assert dứt khoát không còn đường thoát CL.</t>
@@ -2115,7 +2139,7 @@
           <t>Đủ 15 sự kiện, kiểm cả in-app và push (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="n"/>
       <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Mục đích: mở rộng phạm vi P1 từ 9/9 (v1.0) sang **đủ 15/15 sự kiện** — bỏ sót 1 trong 6 sự kiện mới là bỏ sót đúng chỗ nhạy cảm nhất (uỷ quyền/quầy/không liên lạc được). · Căn cứ: `DOC-v1.1-01 §8.13.1` (đối chiếu toàn bộ 15 dòng "Nội dung (mẫu)"). Có thông báo chứa số ⇒ FAIL và log bug mức cao (rò rỉ dữ liệu cá nhân).</t>
@@ -2198,7 +2222,7 @@
           <t>Đơn trọn vòng đời chính + 1 lượt qua mỗi nhánh phụ FR08/FR09, đối chiếu 15 loại chính thức (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="n"/>
       <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đảo vai trò từ `[GAP]` ghi-nhận (v1.0) sang **assert đủ-danh-mục** — thiếu 1 trong 15 loại là bằng chứng cụ thể để log finding, không còn coi "có SC chạy qua" là đủ coverage. · Căn cứ: `DOC-v1.1-01 §8.13.1` bảng 15 dòng, `C-NTF-01` Resolved 2026-09-15. Tiền đề tốn thời gian nhất module — gộp chạy chung lô vibe-test `DLV` (`RISK-NTF-05`). · Đã sửa theo delta v1.1 (2026-09-15): bỏ 2 assert-absent cũ (đánh giá 5 sao, CO₂) — nay gộp vào phép đối chiếu đủ-danh-mục (loại đó không có trong 15 loại chính thức nên tự động không xuất hiện nếu quan sát đúng đủ 15/15).</t>
@@ -2281,7 +2305,7 @@
           <t>Đơn giao qua uỷ quyền, tái dùng từ luồng `SC-DLV-038` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="n"/>
       <c r="M9" s="6" t="inlineStr">
         <is>
           <t>Mục đích: SC hoàn toàn mới — chỉ test đúng bắn thông báo/người nhận/nội dung, KHÔNG lặp nghiệp vụ giao nhận (đã có SC bên `DLV` delta v1.1). · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-10`. Tiền đề phụ thuộc vibe-test nhánh FR08 bên `DLV` (`RISK-NTF-07`), chưa có TC-DLV-v1.1 tại thời điểm generate — cập nhật tham chiếu khi có.</t>
@@ -2357,7 +2381,7 @@
           <t>Đơn giao qua quầy, tái dùng từ luồng `SC-DLV-039` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="n"/>
       <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Mục đích: SC hoàn toàn mới, chỉ test bắn thông báo/người nhận/nội dung. · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-11`. Tiền đề phụ thuộc vibe-test nhánh FR08 bên `DLV`, chưa có TC-DLV-v1.1 tại thời điểm generate.</t>
@@ -2432,7 +2456,7 @@
           <t>Đơn ở nhánh không liên lạc được, tái dùng từ luồng `SC-DLV-044` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="n"/>
       <c r="M11" s="6" t="inlineStr">
         <is>
           <t>Mục đích: SC hoàn toàn mới; chỉ 1 vai (người gửi) nhận theo đúng danh mục `§8.13.1` dòng `NTF-12`, khác `NTF-10`/`11` có 2 vai. · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-12`. Tiền đề phụ thuộc vibe-test nhánh FR08 bên `DLV`, chưa có TC-DLV-v1.1 tại thời điểm generate.</t>
@@ -2508,7 +2532,7 @@
           <t>Đơn `RESCHEDULED`, tái dùng từ luồng `SC-DLV-049` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="n"/>
       <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Mục đích: SC hoàn toàn mới, chỉ test đúng biến `{ngày · giờ}`/`{nơi hẹn}` được thay đúng giá trị runtime, không lặp validate field lịch hẹn (đã có ở `SC-DLV-049`). · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-13`. Tiền đề phụ thuộc vibe-test nhánh FR09 bên `DLV`, chưa có TC-DLV-v1.1 tại thời điểm generate.</t>
@@ -2584,7 +2608,7 @@
           <t>Đơn `RETURNING`, tái dùng từ luồng `SC-DLV-049` chế độ `return` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="n"/>
       <c r="M13" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với `TC-NTF-020` — cùng field lịch hẹn nhưng khác chế độ (`return` thay `retry`), nội dung/đích thông báo khác hẳn (`NTF-14` thay `NTF-13`). · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-14`. Tiền đề phụ thuộc vibe-test nhánh FR09 bên `DLV`, chưa có TC-DLV-v1.1 tại thời điểm generate.</t>
@@ -2661,7 +2685,7 @@
           <t>Đơn `RETURNED`, tái dùng từ `TC-NTF-021` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Mục đích: SC cuối cùng của nhánh hoàn hàng — đóng đúng vòng đời `RETURNING → RETURNED`, cross-ref `SC-GIFT-013/014` (module `GIFT`) cùng phụ thuộc trạng thái `RETURNED` này. · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-15`.</t>
@@ -2866,7 +2890,11 @@
           <t>8 giá trị Loại hàng, mặc định "Tài liệu" (test_data_catalog §ORD — Loại hàng)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo BA trả lời `C-ORD-09` 2026-09-16: assert nhãn **"Tài liệu"** theo PRD. Ràng buộc cũ của v1.0 *"⛔ không dùng nhãn Tài liệu, ghi theo app STG"* **HẾT HIỆU LỰC**. · Mục đích: kết quả phản trực giác — app STG hiện "Giấy tờ, hồ sơ", người chạy quen v1.0 sẽ cho PASS nhầm. App hiện nhãn khác ⇒ **FAIL và log bug**, ⛔ không sửa TC theo app. · `Thuốc/Y tế` giữ trong danh mục (`C-ORD-04` Resolved 2026-09-17), ⛔ không assert banner hàng cấm — v1.1 không có.</t>
@@ -2951,7 +2979,11 @@
           <t>1 ảnh JPG nhỏ của `SEED-ORD-01` (test_data_catalog §ORD — Ảnh món hàng)</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `BR01-01` 2026-09-17: bổ sung assert bộ đếm `n/5` — bản v1.0 chưa có vì khi đó không rõ ảnh có bắt buộc không. · Căn cứ: dấu bắt buộc và hành vi chặn verify ở `TC-ORD-013`/`TC-ORD-063`.</t>
@@ -3027,7 +3059,11 @@
           <t>Trạng thái 0 ảnh — biên dưới (test_data_catalog §ORD — Ảnh món hàng)</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `BR01-01`/`BR18-02` 2026-09-17: v1.0 TC này kiểm ảnh quá dung lượng/sai định dạng, nay chuyển sang chốt **dấu hiệu bắt buộc ở tầng UI**; 2 nhánh từ chối file chuyển sang `TC-ORD-066/067`. · Mục đích: tách tầng UI (có dấu `*`) khỏi tầng hành vi (chặn thật ở `TC-ORD-063`) — app có thể vẽ dấu `*` mà không chặn. · Căn cứ: ảnh `DOC-v1.1-03` xác nhận tầng UI đã build (thu hẹp `RISK-ORD-09`).</t>
@@ -3107,7 +3143,11 @@
           <t>3 chip đã chọn + 0 ảnh — nhánh chặn (test_data_catalog §ORD — Ảnh món hàng, biên 0)</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
           <t>Mục đích: **P1 chặn luồng chính** — `BR01-01` biến ảnh từ *không rõ* thành **bắt buộc**, đây là oracle của cả cụm ảnh. · Căn cứ: `BR01-01` *"Thiếu ảnh thì chặn sang bước 2"* + `AC-03.1.02`. Tầng UI đã build (`DOC-v1.1-03`: dấu `*` + "0/5" + helper) nên TC này verify **hành vi chặn thật**; app cho qua ⇒ FAIL và log bug. ⚠ Ảnh demo cho thấy nút "Tiếp theo" vẫn cam khi chưa đủ điều kiện — nghi giới hạn ảnh tĩnh, ⛔ không log bug dựa trên mỗi ảnh đó.</t>
@@ -3185,7 +3225,11 @@
           <t>1 ảnh &gt; 5MB của `SEED-ORD-01` (test_data_catalog §ORD — Ảnh món hàng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Mục đích: assert thêm vế **"bộ đếm không tăng"** — từ chối hiển thị mà vẫn đếm là lỗi hay gặp, và làm hỏng luôn trần 5 ở `TC-ORD-070`. · Căn cứ: `BR01-01` + `BR18-02` + `AC-03.2.02`.</t>
@@ -3263,7 +3307,11 @@
           <t>1 file `.pdf` của `SEED-ORD-01` (test_data_catalog §ORD — Ảnh món hàng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh khác bản chất với `TC-ORD-068` — lọc theo định dạng và lọc theo dung lượng là hai lớp kiểm độc lập, chặn được lớp này không suy ra lớp kia. · Căn cứ: `VAL-07` + `BR18-02`.</t>
@@ -3342,7 +3390,11 @@
           <t>5 ảnh hợp lệ (biên trên) + 1 ảnh thứ 6 (chặn) của `SEED-ORD-01` (test_data_catalog §ORD — Ảnh món hàng, biên)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên trên của trần 5 — hai giá trị liền kề phải quan sát trong cùng 1 TC để so được. · Căn cứ: `BR18-02` + `VAL-07` + `AC-03.2.01`. Trần 5 ở đây dùng chung rule với `DLV` và `TS` nhưng là **form khác**, ⛔ không dùng chung state. · 🔑 **Sửa Expected 2026-09-18 (QC GiangDC2 chốt sau recheck VR-002):** bộ đếm `n/5` được vẽ **bên trong ô thêm ảnh** ở cuối dải, nên vế *"ẩn nút thêm khi đủ 5"* của `BR18-02` tất yếu làm bộ đếm biến mất ở mức 5/5 — **hành vi hiện tại là ĐÚNG**. Expected cũ đòi đồng thời `5/5` + ẩn nút là **tự mâu thuẫn**, đã bỏ vế `5/5` và chuyển mốc assert bộ đếm về `4/5`. ⛔ Không log bug cho việc mất bộ đếm ở 5/5. · ⚠️ Dải ảnh là **danh sách cuộn ngang lazy**: phần tử ngoài viewport KHÔNG có trong accessibility tree ⇒ phải cuộn rồi mới assert (đã gây 1 ứng viên bug ma ở VR-002, xem bẫy `T10`).</t>
@@ -3421,7 +3473,11 @@
           <t>5 ảnh rồi xoá 1 (test_data_catalog §ORD — Ảnh món hàng)</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
           <t>Mục đích: fail độc lập với `TC-ORD-070` — chặn được ảnh thứ 6 không đảm bảo bộ đếm giảm đúng khi xoá; lỗi hay gặp là xoá nhầm ảnh cuối thay vì ảnh được chọn. · Căn cứ: `BR18-02` *"xoá được từng ảnh"*.</t>
@@ -3506,7 +3562,11 @@
           <t>Địa chỉ mặc định của hồ sơ = `SEED-ORD-03` (test_data_catalog §ORD — Địa chỉ lấy hàng)</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-10` Resolved 2026-09-15: prefill là **hành vi đặc tả**, không còn là "chưa rõ bug hay tài khoản chưa cấu hình" như v1.0. · Mục đích: ô trống ⇒ **BUG**, ⛔ không diễn giải là tài khoản chưa cấu hình. · Căn cứ: `AC-30.1.01` + `§8.1.4`. ⛔ Không chạy trên tài khoản không rõ trạng thái hồ sơ.</t>
@@ -3591,7 +3651,11 @@
           <t>Chuỗi địa chỉ tự do (test_data_catalog §ORD — Địa chỉ giao hàng)</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-11` Resolved 2026-09-15: chốt **ô văn bản tự do**, bản v1.0 còn để ngỏ 3 khả năng (preset 6 văn phòng / chip gợi ý / autocomplete). · Căn cứ: `§8.1.4`. Biên 200/201 ký tự tách sang `TC-ORD-055`.</t>
@@ -3669,7 +3733,11 @@
           <t>Chuỗi 200 ký tự (hợp lệ) và 201 ký tự (chặn) (test_data_catalog §ORD — Địa chỉ giao hàng, biên)</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên trên của trần 200 — hai giá trị liền kề phải quan sát trong cùng 1 TC để so được. · Căn cứ: `§8.1.4`.</t>
@@ -3754,7 +3822,11 @@
           <t>Ngày liền trước ngày hiện tại — tính tương đối (test_data_catalog §ORD — Khoảng ngày)</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-15(a)` Resolved 2026-09-17: tách riêng nhánh ngày quá khứ khỏi phần mặc định mà v1.0 gộp chung, để mỗi nhánh có 1 điểm kiểm chứng ở step cuối. · Căn cứ: `BR01-04` + `AC-06.1.02`. ⛔ Không hardcode ngày — tính tương đối so với hiện tại.</t>
@@ -3832,7 +3904,11 @@
           <t>Từ = hiện tại +3 ngày, Đến = hiện tại +1 ngày (test_data_catalog §ORD — Khoảng ngày, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `Project_rule §Custom Rules §10.4` 2026-09-17: thu hẹp phạm vi còn **đúng 1 điểm kiểm chứng** ở step cuối — bản v1.0 gộp chung với nhánh ngày quá khứ (nay tách sang `TC-ORD-030`). Expected không đảo chiều. · Căn cứ: `BR01-04` *"Đến ≥ Từ"* + `AC-06.1.02`. ⛔ Không hardcode ngày.</t>
@@ -3910,7 +3986,11 @@
           <t>Khoảng đúng 7 ngày — biên trên hợp lệ (test_data_catalog §ORD — Khoảng ngày, biên)</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên với `TC-ORD-057` — chỉ chạy chiều chặn thì rule "chặn mọi khoảng" cũng PASS. · Căn cứ: `C-ORD-15(a)` Resolved 2026-09-17 — BA chốt *"Từ X → Đến tối đa X+7"*, tức 7 ngày là **hợp lệ**.</t>
@@ -3988,7 +4068,11 @@
           <t>Khoảng 8 ngày — vượt biên (test_data_catalog §ORD — Khoảng ngày, biên)</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `BR01-04` + `C-ORD-15(a)`. ⛔ Không hardcode ngày.</t>
@@ -4074,7 +4158,11 @@
           <t>4 buổi mong muốn (test_data_catalog §ORD — Buổi mong muốn)</t>
         </is>
       </c>
-      <c r="L23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `Project_rule §Custom Rules §10.4` 2026-09-17: tách vế **giá trị mặc định** ra `TC-ORD-058` để mỗi TC chỉ còn 1 điểm kiểm chứng ở step cuối; bản v1.0 gộp cả hai. Expected không đảo chiều. · Căn cứ: `BR01-04` + `AC-06.2.01` — quan hệ loại trừ giữa "Giờ nào cũng được" và 3 buổi cụ thể.</t>
@@ -4150,7 +4238,11 @@
           <t>Giá trị mặc định của field buổi (test_data_catalog §ORD — Buổi mong muốn)</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
           <t>Mục đích: v1.0 cố ý **KHÔNG** assert mặc định vì 3 nguồn cho 3 giá trị khác nhau; PRD v1.1 `§8.1.4` nay gọi tên rõ nên assert được. · Căn cứ: `§8.1.4` — nguồn mới nhất thắng các nguồn v1.0. App hiện buổi khác ⇒ FAIL và log bug.</t>
@@ -4229,7 +4321,11 @@
           <t>Buổi đã qua trong ngày hiện tại (test_data_catalog §ORD — Buổi mong muốn)</t>
         </is>
       </c>
-      <c r="L25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
           <t>Mục đích: neo vào `C-ORD-15(b)` Resolved 2026-09-17 — BA chốt *"app CHẶN chọn buổi đã qua trong ngày"*, rule này **không có trong PRD**, chưa SC nào phủ trước lượt này. · Căn cứ: câu trả lời BA là nguồn chốt duy nhất; app cho chọn ⇒ FAIL và dẫn `C-ORD-15`. ⛔ Không hardcode giờ — điều kiện thời điểm chạy ghi ở Pre-condition.</t>
@@ -4315,7 +4411,11 @@
           <t>Dữ liệu hợp lệ đủ 3 bước + 1 ảnh của `SEED-ORD-01` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-05` Resolved 2026-09-15: chốt **KHÔNG có mã đơn**, v1.0 còn để ngỏ. · Mục đích: kết quả phản trực giác — người chạy quen app thương mại sẽ đi tìm mã đơn rồi báo thiếu. · Căn cứ: `AC-07.1.01` + `§8.1.3` bước 8. Vế *"tin xuất hiện ngay ở Tin mới và Đơn của tôi"* thuộc `HOME`/`ACT`, ⛔ không nhân bản ở đây.</t>
@@ -4400,7 +4500,11 @@
           <t>1 tin OFFER của tài khoản khác (test_data_catalog §ORD — Tin OFFER của tài khoản khác)</t>
         </is>
       </c>
-      <c r="L29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `AC-20.1.01`/`AC-20.1.02` 2026-09-17: siết Steps rà **cả hai tab con** + dùng ô tìm kiếm, bản v1.0 chỉ rà danh sách. · Mục đích: đây là kiểm soát truy cập — PASS giả làm cả một lớp bảo vệ chưa từng được kiểm. · Căn cứ: `BR02-01`. ⛔ Vế *"mở link trực tiếp"* của `AC-20.1.02` **không có đường thử trên mobile** (không có URL) — ⛔ KHÔNG PASS chỉ vì không thử được; ghi nợ ở header §0.4.</t>
@@ -4488,7 +4592,11 @@
           <t>1 tin `POSTED` của chính mình = `SEED-ORD-04` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-16` Resolved 2026-09-17: bổ sung assert **giữ nguyên trạng thái** sau khi cập nhật. · Căn cứ: `BR05-01`/`BR05-02` + `AC-08.1.01`. Nhánh "Huỷ chỉnh sửa" tách sang `TC-ORD-060`.</t>
@@ -4566,7 +4674,11 @@
           <t>Tin đã chuyển `MATCHED` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-16` Resolved 2026-09-17: **Expected giữ nguyên bản v1.0** (nút "Chỉnh sửa" không hiển thị); phần thêm ở SC MODIFIED là 2 vế backend nên chỉ ghi giới hạn phạm vi, không đổi assert. · Căn cứ: `BR05-01` + `AC-08.1.02`. ⛔ Vế *"request sửa bị từ chối"* và *"không ghi mốc vào nhật ký"* là **backend**, không verify được qua UI — ghi nợ ở header §0.4, ⛔ không viết Expected cho phần đó.</t>
@@ -4646,7 +4758,11 @@
           <t>1 tin `POSTED` của chính mình = `SEED-ORD-04` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng âm cho `TC-ORD-046` — lưu được không suy ra huỷ được; lỗi hay gặp là "Huỷ" vẫn ghi đè dữ liệu. · Căn cứ: `VAL-05` + `AC-08.1.01`.</t>
@@ -4734,7 +4850,11 @@
           <t>Tin `POSTED` quá "Đến ngày", chưa ai ghép = `SEED-ORD-05` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L35" s="6" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
           <t>✅ **Gỡ phụ thuộc dev 2026-09-18 (QC chốt):** tin cũ trên STG đã tự quá hạn ⇒ dùng luôn, ⛔ không cần nhờ lùi "Đến ngày". Xem `SEED-ORD-05` §0.5 cho 3 lối theo thứ tự ưu tiên. ⚠️ Dùng tin cũ thì chỉ quan sát **trạng thái kết quả**, không thấy lúc job chuyển trạng thái — vẫn đủ cho Expected. · Đã sửa theo `C-ORD-15(c)` Resolved 2026-09-17: bổ sung điều kiện **job chạy cuối ngày** vào setup — v1.0 chỉ ghi "sau khi hết ngày cuối", khiến người chạy kiểm quá sớm rồi báo lỗi sai. · Căn cứ: `BR05-03` + `AC-09.1.01`. Nhánh đối chứng (tin đã `MATCHED` thì KHÔNG hết hạn) tách sang `TC-ORD-061`.</t>
@@ -4813,7 +4933,11 @@
           <t>Tin `MATCHED` quá "Đến ngày" = `SEED-ORD-05` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
           <t>✅ **Gỡ phụ thuộc dev 2026-09-18 (QC chốt):** dùng tin đã ghép cũ đã quá hạn trên STG (`SEED-ORD-05` §0.5). · Mục đích: đối chứng âm cho `TC-ORD-048` — vế *"vẫn POSTED"* của `BR05-03` là điều kiện **v1.0 chưa nêu**; dev hay chỉ kiểm mỗi ngày hết hạn rồi đóng luôn cả đơn đã ghép. · Căn cứ: `BR05-03`.</t>
@@ -4900,7 +5024,11 @@
           <t>Dữ liệu nhập dở ở bước 2 (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L38" s="6" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-08` Resolved 2026-09-15: assert **verbatim** chuỗi popup, v1.0 chỉ assert có popup. · Căn cứ: `AC-01.2.01`. Nhánh chọn thoát tách sang `TC-ORD-062`.</t>
@@ -4980,7 +5108,11 @@
           <t>Dữ liệu nhập dở đã bị bỏ (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với `TC-ORD-053` — cùng một popup nhưng hai lựa chọn cho hai hệ quả ngược nhau; step 4 chốt thêm vế **⛔ không có DRAFT** mà `AC-01.2.01` nêu. · Căn cứ: `AC-01.2.01`.</t>
@@ -5068,7 +5200,11 @@
           <t>3 chip Trọng lượng, trạng thái chưa chọn (test_data_catalog §ORD — Trọng lượng)</t>
         </is>
       </c>
-      <c r="L41" s="6" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
           <t>🔑 Áp `C-ORD-18` Resolved 2026-09-17 — BA *"lấy UI làm chuẩn"*: assert cứng nhãn **"Trọng lượng"** và nhãn phụ Nhẹ/Trung bình/Nặng. **PRD `§8.1.4` ghi "Khối lượng" + kiểu Dropdown đã HẾT HIỆU LỰC** — app hiện "Khối lượng" hoặc dropdown ⇒ **defect UI**, ⛔ không phải TC sai. · Mục đích: rào *"ghi nhận nhãn, không FAIL vì tên nhãn"* của bản phân tích trước đã gỡ.</t>
@@ -5148,7 +5284,11 @@
           <t>Chip "Trên 10 kg (Nặng)" — mức cao nhất (test_data_catalog §ORD — Trọng lượng)</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng dương cho `TC-ORD-064` — bắt buộc chọn KHÁC với chặn theo ngưỡng; lỗi hay gặp là lập trình chặn luôn mức nặng nhất. · Căn cứ: `BR01-02` *"không chặn theo ngưỡng"*.</t>
@@ -5228,7 +5368,11 @@
           <t>3 chip Kích thước, trạng thái chưa chọn (test_data_catalog §ORD — Kích thước)</t>
         </is>
       </c>
-      <c r="L43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `BR01-02` *"không cho để trống"* + `C-ORD-18` (kiểu control là **chip**, ⛔ không phải Dropdown như PRD ghi).</t>
@@ -5308,7 +5452,7 @@
           <t>Chip "Lớn · &gt; 20×20 cm" — mức cao nhất (test_data_catalog §ORD — Kích thước)</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="n"/>
       <c r="M44" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng dương cho `TC-ORD-066`, cùng cặp với `TC-ORD-065`. · Căn cứ: `BR01-02`.</t>
@@ -5393,7 +5537,11 @@
           <t>1 tin `POSTED` có 5 ảnh = `SEED-ORD-04` (test_data_catalog §ORD — Tin đã đăng có ≥2 ảnh)</t>
         </is>
       </c>
-      <c r="L46" s="6" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `BR18-03` + `AC-03.1.01`. Lightbox tách sang `TC-ORD-073` vì là màn khác.</t>
@@ -5474,7 +5622,11 @@
           <t>1 tin `POSTED` có 5 ảnh = `SEED-ORD-04` (test_data_catalog §ORD — Tin đã đăng có ≥2 ảnh)</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
           <t>Mục đích: xác nhận cách đóng lightbox của app — chỉ đóng bằng nút (×), chạm nền tối không đóng. · Căn cứ: `BR18-03`. · ♻️ Sửa 2026-09-21 (QC GiangDC2, theo `BUG-024` đã huỷ): QC kiểm lại — app đúng, chạm nền không đóng lightbox; Expected đổi theo app (`BR18-03` không còn được hiểu là "chạm nền để đóng"). ⚠️ Title còn ghi *"cả nút đóng lẫn chạm nền"* — `§10.5` không cho sửa Title (xem CHANGELOG §3). VR-013: ✅ PASS.</t>
@@ -5561,7 +5713,11 @@
           <t>Email `stag_anhdc4@fpt.com` — có trên HRIS, đang làm việc = `SEED-ORD-02` ① (test_data_catalog §ORD — Email công ty người nhận)</t>
         </is>
       </c>
-      <c r="L49" s="6" t="inlineStr"/>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
           <t>Mục đích: **P1** — đây là tích hợp hệ thống ngoài được nêu tên lần đầu ở v1.1, không có nó thì cả cụm `TC-ORD-074..077` vô nghĩa. · Căn cứ: `BR01-09` + `AC-04.1.01` + BA `C-ORD-13` Resolved 2026-09-17. Ô bị khoá không sửa được ⇒ FAIL — `BR01-09` nói rõ *"vẫn sửa được"*.</t>
@@ -5639,7 +5795,11 @@
           <t>Email `@fpt.com` không tồn tại trên HRIS (test_data_catalog §ORD — Email công ty người nhận ②)</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
           <t>🔑 **ĐẢO PRD.** `BR01-09` và `AC-04.1.02` ghi *"không thấy thì cho nhập thủ công"*; BA `C-ORD-14` **Resolved 2026-09-17** chốt ngược: **nút "Tiếp theo" DISABLE, không cho tạo đơn**. Lấy câu trả lời BA làm nguồn chốt. · Mục đích: kết quả phản trực giác — người đọc PRD sẽ cho rằng mở ô nhập tay là đúng. STG cho nhập tay và tạo được đơn ⇒ **FAIL và log bug**, ⛔ không sửa Expected về `BR01-09`.</t>
@@ -5718,7 +5878,11 @@
           <t>Email `stag_binhnt23@fpt.com` — người đã nghỉ việc, MNV 00026682 = `SEED-ORD-02` ② (`DOC-v1.1-05` · test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L51" s="6" t="inlineStr"/>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh thứ tư của tra danh bạ — HRIS **chỉ nhận nhân sự đang làm việc** (BA `C-ORD-13`), nên "có trong hệ thống" vẫn có thể ra kết quả chặn; đây là ca dễ bị lập trình sót nhất. · Căn cứ: BA `C-ORD-14` — cùng kết quả với `TC-ORD-075` nhưng khác dữ liệu đầu vào. ⚠️ Chưa có email mẫu ⇒ ghi **`Blocked` kèm lý do**, ⛔ không PASS cho xong.</t>
@@ -5796,7 +5960,11 @@
           <t>Email sai định dạng "stag_anhdc4@" (test_data_catalog §ORD — Email công ty người nhận ③)</t>
         </is>
       </c>
-      <c r="L52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
           <t>Mục đích: chốt thứ tự hai lớp kiểm — validate định dạng phải chạy TRƯỚC và chặn luôn việc gọi danh bạ; gọi danh bạ với chuỗi rác là lãng phí và có thể lộ lỗi hệ thống ngoài. · Căn cứ: `§8.1.4` + `AC-04.2.01`.</t>
@@ -5874,7 +6042,11 @@
           <t>Email `@gmail.com` — ngoài tên miền công ty (test_data_catalog §ORD — Email công ty người nhận ④)</t>
         </is>
       </c>
-      <c r="L53" s="6" t="inlineStr"/>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh khác bản chất với `TC-ORD-077` — email **đúng định dạng** nhưng sai tên miền, dễ bị lập trình bỏ qua vì regex đã pass. · Căn cứ: tên miền hợp lệ duy nhất là **`@fpt.com`** (QC GiangDC2 chốt 2026-09-17, đính chính câu trả lời BA cũ). ⛔ `@fpt.vn` chưa xác nhận lại, không dùng làm test data cho bất kỳ nhánh nào.</t>
@@ -5961,7 +6133,11 @@
           <t>SĐT "123" — sai định dạng (test_data_catalog §ORD — SĐT người được uỷ quyền)</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
           <t>Mục đích: rule chỉ validate **khi được nhập** — ⛔ KHÔNG viết TC "bỏ trống thì lỗi", khối uỷ quyền là **không bắt buộc** (verify ở `TC-ORD-082`). · Căn cứ: `BR01-06` + `AC-05.1.02`.</t>
@@ -6041,10 +6217,10 @@
           <t>Tên 14 ký tự + SĐT hợp lệ (test_data_catalog §ORD — Tên người được uỷ quyền, SĐT người được uỷ quyền)</t>
         </is>
       </c>
-      <c r="L56" s="6" t="inlineStr"/>
+      <c r="L56" s="6" t="n"/>
       <c r="M56" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: nhãn "Người gửi chỉ định" là thứ phân biệt người uỷ quyền khai **lúc đăng tin** với người uỷ quyền khai **lúc giao hàng** (`TC-DLV-044`, nhãn "uỷ quyền bởi Người nhận") — lẫn hai nguồn này là lỗi truy vết nghiêm trọng. · Căn cứ: `BR01-06` + `AC-05.1.01`.</t>
+          <t>Mục đích: nhãn "Người gửi chỉ định" là thứ phân biệt người uỷ quyền khai **lúc đăng tin** với người uỷ quyền khai **lúc giao hàng** (`TC-DLV-044`, nhãn "uỷ quyền bởi Người nhận") — lẫn hai nguồn này là lỗi truy vết nghiêm trọng. · Căn cứ: `BR01-06` + `AC-05.1.01`. · ⚠️ Đã chạy nhưng THIẾU EVIDENCE hợp lệ ⇒ không được ghi PASS, tính là Not Run (gate verify_evidence.py).</t>
         </is>
       </c>
       <c r="N56" s="6" t="inlineStr">
@@ -6122,7 +6298,11 @@
           <t>Tên 1 / 2 / 60 / 61 ký tự (test_data_catalog §ORD — Tên người được uỷ quyền, biên)</t>
         </is>
       </c>
-      <c r="L57" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
           <t>Mục đích: gộp 4 giá trị vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cùng một ô, một loại rule, Expected nêu đích danh từng giá trị nên không mất khả năng bắt lỗi riêng. · Căn cứ: `§8.1.4` biên 2-60.</t>
@@ -6202,7 +6382,7 @@
           <t>Dữ liệu uỷ quyền đã nhập rồi xoá (test_data_catalog §ORD — SĐT người được uỷ quyền)</t>
         </is>
       </c>
-      <c r="L58" s="6" t="inlineStr"/>
+      <c r="L58" s="6" t="n"/>
       <c r="M58" s="6" t="inlineStr">
         <is>
           <t>Mục đích: khối uỷ quyền là **không bắt buộc** — lỗi hay gặp là sau khi mở khối thì validate bắt buộc luôn, khiến người dùng không thoát ra được. · Căn cứ: `AC-05.2.01` + `BR01-06`.</t>
@@ -6288,7 +6468,11 @@
           <t>Hai địa chỉ trùng hệt (test_data_catalog §ORD — Địa chỉ giao hàng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `§8.1.4` *"Địa chỉ giao phải khác địa chỉ lấy"*. Nhánh biên gần nhất (chỉ khác khoảng trắng) tách sang `TC-ORD-084` vì PRD không định nghĩa phép so sánh.</t>
@@ -6367,7 +6551,11 @@
           <t>Chuỗi chỉ khác khoảng trắng đầu/cuối — biên gần nhất (test_data_catalog §ORD — Địa chỉ giao hàng, biên)</t>
         </is>
       </c>
-      <c r="L61" s="6" t="inlineStr"/>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
           <t>Mục đích: biên gần nhất của phép so sánh — `VAL-03` có **trim** nên chuỗi này phải bị coi là trùng. · Căn cứ: `VAL-03`. ⛔ **KHÔNG mở rộng sang hoa/thường hay dấu tiếng Việt** — PRD không định nghĩa phép so sánh cho hai chiều đó (`RISK-ORD-12`); app xử lý bất nhất thì nêu với BA, ⛔ không viết TC assert.</t>
@@ -6453,7 +6641,11 @@
           <t>Địa chỉ giao trên màn chi tiết tin (test_data_catalog §ORD — Địa chỉ giao hàng)</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp với `TC-ORD-086` — hai instance icon copy ở hai vùng khác nhau của cùng màn, hỏng độc lập. · Căn cứ: `BR18-04`. Rule ghi 1,8 giây nhưng đây là hiệu ứng thị giác — chấp nhận dung sai quanh 2 giây, ⛔ không bấm giờ đòi đúng 1,8 giây. Instance ở màn Theo dõi đơn thuộc `DLV` (`TC-DLV-080/081`), ⛔ không nhân bản.</t>
@@ -6532,7 +6724,11 @@
           <t>Số điện thoại người nhận trên màn chi tiết tin (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L64" s="6" t="inlineStr"/>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `BR18-04` — rule đặt icon copy cạnh CẢ địa chỉ giao và số điện thoại.</t>
@@ -6618,7 +6814,11 @@
           <t>2 ảnh đang soạn, chưa đăng tin (test_data_catalog §ORD — Ảnh món hàng)</t>
         </is>
       </c>
-      <c r="L66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp với `TC-ORD-088` — ranh giới xoá được ⟷ không xoá được là **thời điểm ghi mốc**, không phải loại ảnh; chạy lẻ một vế thì không chốt được ranh giới. · Căn cứ: `BR18-02`.</t>
@@ -6698,7 +6898,11 @@
           <t>1 tin `POSTED` có 5 ảnh = `SEED-ORD-04` (test_data_catalog §ORD — Tin đã đăng có ≥2 ảnh)</t>
         </is>
       </c>
-      <c r="L67" s="6" t="inlineStr"/>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
           <t>Mục đích: ghi nhận hành vi thật của app — form sửa tin đã đăng vẫn cho xoá ảnh bằng nút ×; đối chiếu `TC-ORD-087`. Tin phải còn `POSTED` để vào được form sửa (`BR05-01`). · ♻️ Sửa 2026-09-21 (QC GiangDC2, theo `BUG-023` đã huỷ): QC kiểm lại — app đúng, cho xoá ảnh của tin đã đăng (đơn đã có mốc `Đăng tin` vẫn xoá được); Expected/Steps đổi theo app. ⚠️ Title còn ghi *"không xoá được"* — `§10.5` không cho sửa Title (xem CHANGELOG §3). ⚠️ `SC-CNL-010`/`SC-DLV-062` (nhóm "ảnh bất biến truy vết" `BR11-03`/`NFR-07`) chưa chạy — cân nhắc kiểm cùng cách hiểu. VR-013: ✅ PASS.</t>
@@ -6919,7 +7123,11 @@
           <t>Đơn `IN_TRANSIT` = `SEED-TS-01` CP2; mã đơn prefill (test_data_catalog §TS — Mã đơn hàng prefill)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>🔴 Áp bản Resolved `C-TS-03(a)` 2026-09-17 thay vì Then của `SC-TS-008`: form prefill **đúng 1 trường**, ⛔ KHÔNG phải 9 trường như `AC-31.1.01` liệt kê — `BR16-02` mới là bản đúng, `AC-31.1.01` là PRD sai/thừa. · Mục đích: kết quả phản trực giác so với PRD — người chạy đọc `AC-31.1.01` sẽ tưởng thiếu 8 trường là bug. App prefill thêm trường ⇒ FAIL và dẫn `C-TS-03` để BA cập nhật PRD.</t>
@@ -7003,7 +7211,11 @@
           <t>Loại yêu cầu "Sự cố đơn hàng" + mô tả không rỗng + SĐT hợp lệ + 2 ảnh (test_data_catalog §TS)</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Mục đích: chuỗi cam kết 24 giờ là **thứ duy nhất verify được** của quy trình hỗ trợ — hành động thật của Admin nằm ngoài app, ⛔ không mở rộng phạm vi sang đó. · Căn cứ: `AC-31.1.01` + vibe-check demo 2026-09-15 (ảnh `TS_05`, chuỗi verbatim). Màn xác nhận và nút "Quay lại đơn hàng" do **APP** vẽ chứ không phải trang xác nhận của Google Form (`C-TS-03(d)` Resolved 2026-09-17).</t>
@@ -7082,7 +7294,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6. Nút "Gửi" ở trạng thái vô hiệu hoá và cạnh nút hiện chữ "Điền các mục bắt buộc".</t>
+          <t>6. Nút "Gửi" vẫn ở trạng thái bấm được (không disable); ngay sau khi bấm, form KHÔNG được gửi đi, tự cuộn tới câu hỏi "Loại yêu cầu" và hiện lỗi inline "Câu hỏi này là bắt buộc." ngay dưới câu hỏi đó.</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -7090,7 +7302,11 @@
           <t>Loại yêu cầu chưa chọn — nhánh invalid (test_data_catalog §TS — Loại yêu cầu)</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Mục đích: 1 trong 3 nhánh OR của điều kiện bắt buộc — mỗi nhánh fail độc lập, khoá được nhánh này không suy ra khoá được 2 nhánh kia. · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.1.02 + vibe-check demo 2026-09-15 (ảnh `TS_04`, chiều dương của cùng rule).</t>
@@ -7162,7 +7378,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>6. Nút "Gửi" ở trạng thái vô hiệu hoá và cạnh nút hiện chữ "Điền các mục bắt buộc".</t>
+          <t>6. Nút "Gửi" vẫn ở trạng thái bấm được (không disable); ngay sau khi bấm, form KHÔNG được gửi đi, tự cuộn tới câu hỏi "Mô tả chi tiết" và hiện lỗi inline "Câu hỏi này là bắt buộc." ngay dưới câu hỏi đó.</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -7170,7 +7386,11 @@
           <t>Mô tả chi tiết rỗng — nhánh invalid (test_data_catalog §TS — Mô tả chi tiết)</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §6.2 AC-31.1.02 — `test_data_catalog §TS` ghi rõ trường này **không có giới hạn ký tự công bố** nên chỉ có nhánh rỗng ⟷ không rỗng, ⛔ không viết TC biên độ dài.</t>
@@ -7243,7 +7463,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7. Nút "Gửi" ở trạng thái vô hiệu hoá và cạnh nút hiện chữ "Điền các mục bắt buộc".</t>
+          <t>7. Nút "Gửi" vẫn ở trạng thái bấm được (không disable — cơ chế thật của form là inline error, xem TC-TS-010/TC-TS-011); tuy nhiên SĐT sai định dạng vẫn phải bị chặn không cho gửi (báo lỗi định dạng hoặc tương đương) trước khi form được submit.</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -7251,7 +7471,11 @@
           <t>SĐT sai định dạng "0912abc" (test_data_catalog §TS — Số điện thoại liên hệ lại, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhánh khác bản chất với 2 TC kia — ô CÓ dữ liệu nhưng sai định dạng, dễ bị lập trình thành "chỉ kiểm rỗng". · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.1.02 + §8.16.2. Dùng loại yêu cầu thứ ba để đồng thời phủ đủ 3 giá trị enum của ô "Loại yêu cầu" trong cụm này.</t>
@@ -7340,7 +7564,11 @@
           <t>0 ảnh — biên dưới hợp lệ (test_data_catalog §TS — Hình ảnh đính kèm)</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên dưới với `TC-TS-014` — ảnh KHÔNG nằm trong điều kiện bật nút "Gửi", khác hẳn ảnh bằng chứng giao hàng của `DLV` (bắt buộc ≥1). · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.1.02 + §8.16.2.</t>
@@ -7421,7 +7649,11 @@
           <t>5 ảnh — biên trên hợp lệ, ảnh thứ 6 bị chặn (test_data_catalog §TS — Hình ảnh đính kèm, biên)</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên trên của trần 5 — hai giá trị liền kề nên phải quan sát trong cùng 1 TC để so được. · Căn cứ: `DOC-v1.1-01` §8.16.2 + vibe-check demo 2026-09-15 (ảnh `TS_03`, nút tự disable ở ảnh thứ 5). Trần 5 ở đây **độc lập** với trần ảnh bằng chứng của `DLV` — 2 form khác nhau, không dùng chung state dù cùng số 5.</t>
@@ -7502,7 +7734,11 @@
           <t>5 ảnh rồi xoá 1 (test_data_catalog §TS — Hình ảnh đính kèm)</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr"/>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
           <t>Mục đích: fail độc lập với `TC-TS-014` — chặn được ảnh thứ 6 không đảm bảo bộ đếm giảm đúng khi xoá; lỗi hay gặp là xoá nhầm ảnh cuối thay vì ảnh được chọn. · Căn cứ: `DOC-v1.1-01` §8.16.2 (*"xoá được từng ảnh"*).</t>
@@ -7590,7 +7826,11 @@
           <t>Trạng thái mất kết nối mạng (test_data_catalog §TS — Trạng thái kết nối mạng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §6.2 AC-31.2.01 + **Dev trả lời `C-TS-03(c)` 2026-09-17** (*"App hiển thị nhé"*) — nút "Thử lại" do CHÍNH APP vẽ, tách biệt khỏi khung nhúng, nên assert được dù `BR16-01` dùng Custom Tabs. ⛔ Không assert công nghệ nhúng cụ thể (WebView trần hay Custom Tabs) — không quan sát được từ UI.</t>
@@ -7672,7 +7912,11 @@
           <t>Mã đơn của `SEED-TS-01`; chuyển từ mất mạng sang có mạng (test_data_catalog §TS — Trạng thái kết nối mạng)</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
           <t>Mục đích: fail độc lập với `TC-TS-016` — hiện được nút "Thử lại" không đảm bảo app còn giữ ngữ cảnh đơn; lỗi hay gặp là thử lại xong mở form trắng, mất mã đơn. · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.2.01 (*"KHÔNG mất ngữ cảnh đơn"*).</t>
@@ -7760,7 +8004,11 @@
           <t>Đơn `IN_TRANSIT` = `SEED-TS-01` CP2 (test_data_catalog §TS)</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.16.1 BR16-04 — đóng WebView ⛔ KHÔNG reset ngăn xếp điều hướng về trang chủ.</t>
@@ -7840,7 +8088,11 @@
           <t>Dữ liệu nhập dở ở phiên trước (test_data_catalog §TS — Loại yêu cầu, Mô tả chi tiết)</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với `TC-TS-018` — cùng một thao tác đóng nhưng hai hệ quả khác nhau: ngăn xếp điều hướng phải GIỮ, còn dữ liệu form phải MẤT. · Căn cứ: `DOC-v1.1-01` §8.16.1 BR16-06 (*"mở lại là một phiên mới"*).</t>
@@ -7928,7 +8180,11 @@
           <t>Đơn `POSTED` = `SEED-TS-01` CP0 (test_data_catalog §TS — Mã đơn hàng prefill)</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
           <t>Mục đích: neo vào `C-TS-02(b)` Resolved 2026-09-17 — BA: *"ver hiện tại không chuyển trạng thái gì"*. `§8.12.2` định nghĩa `INCIDENT` = *"có báo cáo sự cố sau khi đơn đã sang IN_TRANSIT"*, đọc được là **tự chuyển**, nên TC này là oracle chặn đúng cách đọc sai đó. · Căn cứ: form Google không gọi được API app ⇒ `INCIDENT` chỉ vào được qua Dev xử lý tay; đơn tự đổi trạng thái ⇒ FAIL và dẫn `C-TS-02`. Kết luận này là căn cứ để `SC-CNL-015`/`SC-DLV-034` out of scope test qua UI.</t>
@@ -8014,7 +8270,11 @@
           <t>Mã đơn prefill chỉ đọc (test_data_catalog §TS — Mã đơn hàng prefill)</t>
         </is>
       </c>
-      <c r="L22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
           <t>🔴 Áp bản Resolved `C-TS-03(b)` 2026-09-17 — **ĐẢO HẲN Then của `SC-TS-014`** (*"trường prefill CHO PHÉP sửa"*). `§8.16.2` (*"Chỉ đọc · Không sửa"*) là bản đúng, **`BR16-03` là PRD sai**; demo cho thấy ô là nhãn tĩnh, không phải câu trả lời ngắn của Google Form. · Mục đích: kết quả phản trực giác — người chạy đọc `BR16-03` sẽ tưởng "không sửa được" là bug. Sửa được ⇒ FAIL và dẫn `C-TS-03` để BA cập nhật PRD.</t>
@@ -8101,7 +8361,11 @@
           <t>Đơn qua 3 trạng thái `POSTED` · `MATCHED` · `IN_TRANSIT` = `SEED-TS-01`; vai người gửi (test_data_catalog §TS)</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
           <t>🔑 Áp `C-TS-02(a)` Resolved 2026-09-17: nút hiện ở **MỌI trạng thái**, ⛔ KHÔNG giới hạn `IN_TRANSIT`/`DELIVERED` như `§8.12.3` liệt kê — `AC-31.1.01` (*"vai trò bất kỳ"*) là bản đúng, `§8.12.3` là PRD thiếu. · Mục đích: 1 trong 3 ô vai — nút ẩn với 1 vai hoặc ở 1 trạng thái là defect. Nút không hiện ở trạng thái nào ⇒ FAIL và dẫn `C-TS-02`.</t>
@@ -8180,7 +8444,11 @@
           <t>Đơn qua 2 trạng thái `MATCHED` · `IN_TRANSIT` = `SEED-TS-01`; vai người vận chuyển (test_data_catalog §TS)</t>
         </is>
       </c>
-      <c r="L25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
           <t>Mục đích: vai này chỉ thấy đơn từ khi nhận nên chỉ quan sát được 2 trạng thái — ⛔ không ghép chung TC với vai người gửi (3 trạng thái) để tránh Expected gộp hai phạm vi khác nhau. · Căn cứ: `DOC-v1.1-01` §8.16 Trigger + `C-TS-02(a)` Resolved 2026-09-17.</t>
@@ -8260,7 +8528,11 @@
           <t>Đơn `IN_TRANSIT` = `SEED-TS-01` CP2; vai người nhận (test_data_catalog §TS — Mã đơn hàng prefill)</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
           <t>Mục đích: vai này thụ động nhất trong luồng nên dễ bị bỏ quên quyền báo sự cố; TC đi thêm một bước mở form để chốt hành vi giống nhau cho cả 3 vai, không chỉ chốt nút có hiện. · Căn cứ: `DOC-v1.1-01` §8.16 Actor + `AC-31.1.01` (*"vai trò bất kỳ"*).</t>
@@ -8469,7 +8741,11 @@
           <t>Tên tài khoản A + chữ viết tắt kỳ vọng (test_data_catalog §USR v1.1 — Avatar)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo analyze v1.1 (2026-09-16): 4 trường có ảnh avatar → avatar chữ viết tắt; thêm assert vắng SĐT/email/địa chỉ. · Căn cứ: BA chốt `C-USR-05(a)`; SĐT/email/địa chỉ chỉ ở màn "Cập nhật thông tin" (`C-USR-04`). Demo trang Cá nhân hiện icon người ⇒ STG giống demo thì log bug.</t>
@@ -8549,7 +8825,11 @@
           <t>Hồ sơ nhân viên đầy đủ (test_data_catalog §USR)</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Mục đích: bản v1.0 cùng ID assert "không có bất kỳ control sửa nào" — kỳ vọng ngược, phải dùng bản v1.1. · Đã sửa theo `C-USR-03` đảo (2026-09-15): trang Cá nhân nay có mục "Cập nhật thông tin" hợp lệ nên chỉ assert không sửa trực tiếp trên từng trường. · Căn cứ: `BR15-01`. · Đã sửa theo §10.4 (2026-09-17): gộp 3 điểm kiểm avatar/tên/phòng ban·MNV vào 1 step Check cuối + 1 Expected duy nhất (Expected chỉ ghi ở step cuối).</t>
@@ -8633,7 +8913,11 @@
           <t>Giá trị assert-absent: badge "Hạng Đồng hành" (test_data_catalog §USR)</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Mục đích: bản v1.0 cùng ID assert badge TỒN TẠI — kỳ vọng ngược, phải dùng bản v1.1. · Đã sửa theo BA 2026-09-16 (`C-USR-06` Resolved — badge không hiện). · Căn cứ: `BR14-03` cấm mọi tier/xếp hạng. Demo còn badge ⇒ STG còn badge thì log bug.</t>
@@ -8710,7 +8994,11 @@
           <t>Hồ sơ nhân viên đầy đủ (test_data_catalog §USR)</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo analyze v1.1 (2026-09-16): bỏ badge hạng, 2 → 3 mục menu, avatar chữ viết tắt; bỏ tiền đề 2 chỉ số &gt; 0 vì chỉ đối chiếu thành phần và thứ tự; priority P2 → P3 theo `SC-USR-011`. · Căn cứ: §8.15 Trigger + `C-USR-05(a)` + `C-USR-06`.</t>
@@ -8794,7 +9082,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `DOC-v1.1-01` §8.15 Trigger (2026-09-15): hết dạng GAP 3 nhãn, assert được nhãn + vị trí; priority P3 → P2 theo `SC-USR-012`.</t>
@@ -8871,7 +9163,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: §8.15 Trigger; nút "←" và việc ẩn bottom nav lấy theo ảnh `USR_02` (`DOC-v1.1-03`) + code demo — PRD không mô tả, STG lệch thì mở CL.</t>
@@ -8960,7 +9256,11 @@
           <t>SĐT hợp lệ "0987654321"; văn phòng K3 "Lê Thái Tổ" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `AC-30.1.01` + `BR15-05`. Nếu giá trị ghi ở bước 4 trùng test data thì đổi sang SĐT/văn phòng khác trong catalog. · Đã sửa theo §10.4 (2026-09-17): thu hẹp — chỉ giữ điểm kiểm banner ở step cuối; điểm kiểm persist (mở lại xem giá trị) tách sang `TC-USR-016` mới. · 🔄 **SỬA EXPECTED 2026-09-18 (QC GiangDC2 chốt): hành vi app là ĐÚNG, ⛔ KHÔNG phải bug.** Expected cũ (*"banner xanh 'Đã lưu thông tin của bạn' + màn vẫn ở lại"*) **HẾT HIỆU LỰC**. Hành vi chốt: bấm "Lưu thay đổi" với dữ liệu hợp lệ ⇒ **không có banner**, app **điều hướng về màn "Cá nhân"**; dữ liệu lưu đúng (phủ bởi `TC-USR-016`). VR-001 từng ghi FAIL (ứng viên bug **B1**) — verdict đã đổi sang **PASS**, B1 **rút lại**. ⚠️ Nợ upstream: `SC-USR-014` THEN + `DOC-v1.1-01 §8.15.1 BR15-05`/`§6.2 AC-30.1.01` vẫn ghi "banner xanh + ở lại màn" ⇒ cần `/analyze-requirements --module USR` + clarification với BA. ⚠️ `Test Title` vẫn còn chữ *"hiển thị đúng banner xanh"* (Title không thuộc danh sách field được sửa ở `Project_rule §10.5`) ⇒ chờ QC chốt riêng.</t>
@@ -9045,7 +9345,11 @@
           <t>SĐT hợp lệ "0987654321"; văn phòng K3 "Lê Thái Tổ" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
           <t>Technique: N/A — happy schema assert · Mục đích: tách khỏi `TC-USR-015` theo §10.4 (2026-09-17) — điểm kiểm persist thật (không tin banner) là lý do TC này tồn tại, giữ đúng ở step cuối. Căn cứ: Analyst Note `SC-USR-014` — "TC-USR-014 bắt buộc có bước mở lại màn để kiểm giá trị đã persist". Nếu giá trị ghi ở bước 4 trùng test data thì đổi sang SĐT/văn phòng khác trong catalog. TC mới, không có ID cũ 1-1.</t>
@@ -9128,7 +9432,11 @@
           <t>SĐT hợp lệ "0987654321" / "0987654322" (test_data_catalog §USR v1.1)</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: BR15-05 + AC-30.1.01 "tự ẩn khi người dùng sửa tiếp". Không assert ẩn theo thời gian và không assert trường hợp chỉ chạm vào field mà không đổi nội dung — PRD không có mốc. · Đã sửa theo §10.4 (2026-09-17): bỏ dòng Expected ở step 6 (banner đang hiển thị) — điểm này đã có TC-USR-015 assert riêng (chuỗi banner đúng); TC này chỉ giữ đúng 1 điểm kiểm ở step cuối: banner tự ẩn khi sửa tiếp. · ID cũ: TC-USR-024. · 🔄 SỬA STEPS + EXPECTED 2026-09-18 (QC GiangDC2 chốt): tiền đề gốc "có banner, kiểm banner tự ẩn khi sửa tiếp" KHÔNG còn đúng sau khi bug B1 rút lại — app KHÔNG hề hiện banner ở bất kỳ lần lưu nào và tự điều hướng về "Cá nhân" (xem TC-USR-015). Viết lại Steps/Expected theo hướng kiểm tính nhất quán của hành vi không-banner qua 2 lần lưu liên tiếp, thay vì kiểm banner tự ẩn (không còn banner để mà ẩn). ⚠️ Nợ upstream: SC-USR-019 + BR15-05/AC-30.1.01 ("banner tự ẩn khi sửa tiếp") cần /analyze-requirements --module USR cập nhật lại cho khớp việc bỏ hẳn banner — chưa sửa ở đây vì ngoài phạm vi field được phép sửa của TC (Project_rule §10.5). 🔄 SỬA TEST TITLE 2026-09-18 (QC GiangDC2 chốt trực tiếp): Title cũ "Check banner đã lưu tự ẩn khi sửa tiếp nội dung field" → "Check hai lần lưu liên tiếp đều không hiện banner và đều về màn Cá nhân". Lý do: Steps + Expected đã đổi hẳn sang kiểm tính nhất quán của hành vi không-banner, Title cũ mô tả NGƯỢC nội dung TC ⇒ người đọc Title sẽ hiểu sai. §10.5 FREEZE vẫn giữ nguyên với thêm/xoá/tách/gộp TC — Σ TC không đổi (223 · USR 38). Đã verify PASS ở VR-003 theo đúng bản Steps/Expected này. ⚠️ TC-USR-015 vẫn còn Title cũ ("hiển thị đúng banner xanh") — việc còn treo riêng, chưa được chốt sửa.</t>
@@ -9214,7 +9522,11 @@
           <t>SĐT để trống (test_data_catalog §USR v1.1 — Số điện thoại mặc định)</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `BR15-02` + `AC-30.1.02`. PRD không có chuỗi thông báo. Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức (PRD không đặc tả); STG hiện chuỗi khác ⇒ log bug, ⛔ không sửa TC. · ID cũ: TC-USR-016.</t>
@@ -9293,7 +9605,11 @@
           <t>SĐT 9 chữ số "091234567" (test_data_catalog §USR v1.1, biên dưới)</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên với TC-USR-020 quanh mốc đúng 10 chữ số (giá trị hợp lệ đối chứng ở TC-USR-015). · Căn cứ: BA chốt 2026-09-16 "bắt đầu bằng 0, đúng 10 ký tự số" + `BR15-02`. · Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức. · ID cũ: TC-USR-017.</t>
@@ -9375,7 +9691,11 @@
           <t>SĐT 11 chữ số "09123456789" (test_data_catalog §USR v1.1, biên trên)</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên với TC-USR-018. · Căn cứ: BA chốt 2026-09-16 "đúng 10 ký tự số" + `BR15-02`. Chưa đặc tả app chặn nhập ở chữ số thứ 11 hay báo lỗi khi lưu ⇒ chỉ assert kết quả cuối: không lưu được chuỗi 11 chữ số. · Đã sửa theo §10.4 (2026-09-17): bỏ dòng Expected ở step 5 ("KHÔNG hiển thị banner") — hành vi block ngay hay ở persist chưa rõ theo doc, chỉ assert chắc điểm cuối. · ID cũ: TC-USR-018.</t>
@@ -9454,7 +9774,11 @@
           <t>SĐT 10 chữ số không bắt đầu bằng 0 "1912345678" (test_data_catalog §USR v1.1)</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `AC-30.1.02` "10 số, đầu 0" + BA chốt 2026-09-16. · Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức. · ID cũ: TC-USR-019.</t>
@@ -9533,7 +9857,11 @@
           <t>"0912 345 678" (test_data_catalog §USR v1.1 — Invalid)</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
           <t>Mục đích: "10 ký tự là số" loại cả dạng hiển thị có khoảng trắng mà demo dùng — dễ bị coi là hợp lệ. · Căn cứ: BA chốt 2026-09-16. · Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức. · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-020` cũ (3 định dạng invalid gộp 1 TC) thành 3 TC riêng, mỗi TC 1 định dạng ở step cuối. · ID cũ: TC-USR-020 (một phần).</t>
@@ -9612,7 +9940,11 @@
           <t>"+84912345678" (test_data_catalog §USR v1.1 — Invalid)</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>Mục đích: định dạng quốc tế +84 không đúng "10 số, đầu 0" — dễ nhầm là hợp lệ vì đúng số quốc gia VN. · Căn cứ: BA chốt 2026-09-16. · Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-020` cũ, không có ID cũ 1-1.</t>
@@ -9691,7 +10023,11 @@
           <t>"09123a5678" (test_data_catalog §USR v1.1 — Invalid)</t>
         </is>
       </c>
-      <c r="L22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
           <t>Mục đích: chuỗi lẫn ký tự chữ vào dãy số — kiểm field không chỉ validate độ dài mà cả kiểu ký tự. · Căn cứ: BA chốt 2026-09-16. · Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-020` cũ, không có ID cũ 1-1.</t>
@@ -9780,7 +10116,11 @@
           <t>Trường SSO của tài khoản A (test_data_catalog §USR v1.1 — Trường SSO)</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `BR15-01` + `AC-30.2.01`; avatar theo `C-USR-05(a)`. Icon khiên theo UI — BA chốt 2026-09-16; PRD ghi "icon khoá" ⇒ lệch chữ PRD, báo BA sửa PRD, ⛔ không đổi TC. · Đã sửa theo §10.4 (2026-09-17): gộp 5 điểm kiểm (4 field chỉ đọc + icon khiên) vào 1 step Check cuối + 1 Expected duy nhất. · ID cũ: TC-USR-021.</t>
@@ -9874,7 +10214,11 @@
           <t>SĐT mới "0987654321"; văn phòng K4 "363 Nguyễn Hữu Thọ,Cẩm Lệ" (04_test-data/valid/USR-office-catalog.md); đơn tạo TRƯỚC khi sửa hồ sơ (test_data_catalog §USR v1.1)</t>
         </is>
       </c>
-      <c r="L26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
           <t>Mục đích: `RISK-USR-07` — nhóm rule truy vết mà app đã vi phạm 1 lần; chạy cùng lô với `SC-CNL-010` · `SC-ORD-065` · `SC-DLV-062`, cùng vỡ ⇒ 1 bug report cho nguyên nhân gốc. · Căn cứ: `BR15-03` + `AC-30.2.02`. Nếu SĐT người gửi hoặc giá trị bước 4 trùng test data thì đổi giá trị khác trong catalog. Giả định màn Theo dõi đơn hiển thị SĐT người gửi cho chính người đăng — nếu không hiển thị thì đối chiếu ở màn chi tiết tin, không coi là FAIL của TC này. · Đã sửa theo §10.4 (2026-09-17): bỏ steps mở wizard mới để check giá trị điền sẵn (vế thứ 2 của `AC-30.2.02`) — vế đó trùng phạm vi "wizard nhận đúng giá trị prefill" đã có home ở `SC-ORD-025` (Analyst Note gốc: ⛔ không nhân bản SC). TC này giữ đúng 1 điểm kiểm ở step cuối: đơn cũ không bị ghi đè. · ID cũ: TC-USR-022.</t>
@@ -9959,7 +10303,11 @@
           <t>SĐT/địa chỉ nhập trong đơn khác hồ sơ (test_data_catalog §USR v1.1 — Cặp giá trị TRƯỚC/SAU)</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `BR15-04` + `AC-30.1.01` "sửa trong từng đơn mà không ghi lại hồ sơ". Vế "wizard nhận đúng giá trị điền sẵn" kiểm ở `SC-ORD-025`, không lặp ở đây. Nếu field địa chỉ lấy hàng chỉ cho chọn từ danh sách thì chọn "Tòa V-City, Lê Thái Tổ" trong danh sách gợi ý. Nếu giá trị bước 4 trùng test data thì đổi giá trị khác.</t>
@@ -10046,7 +10394,11 @@
           <t>Văn phòng K3 "Tòa V-City, Lê Thái Tổ" (setup) · chuỗi gõ tay K7 "asdfghjkl1" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
           <t>Mục đích: kết quả phản trực giác — gõ tay không chọn thì bị xoá thay vì giữ chuỗi đã gõ. · Căn cứ: BA chốt 2026-09-16 (rời field không chọn ⇒ rỗng). Demo cho gõ tự do ⇒ STG giống demo thì log bug. · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-025` cũ (4 điểm kiểm gộp 1 TC) — TC này giữ điểm "rời field ⇒ rỗng"; điểm "lưu rỗng thành công" và "mở lại vẫn rỗng" tách sang `TC-USR-029`/`030`. · ID cũ: TC-USR-025 (một phần).</t>
@@ -10127,7 +10479,11 @@
           <t>Văn phòng K3 "Tòa V-City, Lê Thái Tổ" (setup) · chuỗi gõ tay K7 "asdfghjkl1" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
           <t>Mục đích: BA chốt "cho phép để trống" — TC này chứng minh rỗng không bị chặn lưu như SĐT. · Căn cứ: BA chốt 2026-09-16. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-025` cũ, không có ID cũ 1-1.</t>
@@ -10211,7 +10567,11 @@
           <t>Văn phòng K3 "Tòa V-City, Lê Thái Tổ" (setup) · chuỗi gõ tay K7 "asdfghjkl1" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
           <t>Mục đích: kết quả phản trực giác — lưu rỗng xong mở lại vẫn rỗng, không tự lấy lại HRIS; đây là bẫy dễ bỏ sót nhất trong nhóm (Analyst Note `SC-USR-020`). Demo cho gõ tự do ⇒ STG giống demo thì log bug. · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-025` cũ, giữ đúng điểm kiểm quan trọng nhất của cả nhóm ở step cuối. · ID cũ: TC-USR-025 (một phần — điểm kiểm chính).</t>
@@ -10297,7 +10657,11 @@
           <t>K1 "fp" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên 2/3 ký tự — vế biên dưới (2 ký tự, chưa đủ ngưỡng), đối chứng với `TC-USR-032`. · Căn cứ: BA chốt 2026-09-16 (gợi ý từ 3 ký tự). · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-026` cũ thành 2 TC theo từng vế biên. · ID cũ: TC-USR-026 (một phần).</t>
@@ -10376,7 +10740,11 @@
           <t>K2 "fpt" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L34" s="6" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên 2/3 ký tự — vế biên trên (đủ ngưỡng, khớp nhiều), đối chứng với `TC-USR-031`. · Căn cứ: BA chốt 2026-09-16; danh sách kỳ vọng đối chiếu `DOC-v1.1-04` cột `name`. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-026` cũ, không có ID cũ 1-1.</t>
@@ -10458,7 +10826,11 @@
           <t>K3 "Lê Thái Tổ" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng dương cho `TC-USR-028` — chọn từ gợi ý thì rời field vẫn giữ giá trị. · Căn cứ: BA chốt 2026-09-16 (chọn ⇒ điền chuỗi `name` của `DOC-v1.1-04`). · Đã sửa theo §10.4 (2026-09-17): bỏ dòng Expected ở step 6 (danh sách hiển thị 1 văn phòng) — việc chọn được đúng văn phòng ở step 7 đã ngầm xác nhận nó có trong danh sách; giữ đúng 1 điểm kiểm ở step cuối. · ID cũ: TC-USR-027.</t>
@@ -10537,7 +10909,11 @@
           <t>K4 "Cẩm Lệ" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L36" s="6" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 (không phân biệt dấu + hoa thường) — vế có dấu, đối chứng với `TC-USR-035`/`036` (không dấu thường/hoa). · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-028` cũ (3 biến thể gộp 1 TC) thành 3 TC riêng, mỗi biến thể 1 TC. · ID cũ: TC-USR-028 (một phần).</t>
@@ -10616,7 +10992,11 @@
           <t>K4 "cam le" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 (không phân biệt dấu + hoa thường) — vế chữ thường không dấu, đối chứng với `TC-USR-034`/`036`. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-028` cũ, không có ID cũ 1-1.</t>
@@ -10695,7 +11075,11 @@
           <t>K4 "CAM LE" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L38" s="6" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 (không phân biệt dấu + hoa thường) — vế chữ hoa không dấu, đối chứng với `TC-USR-034`/`035`. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-028` cũ, không có ID cũ 1-1.</t>
@@ -10774,7 +11158,11 @@
           <t>K8 "tan" — 36 văn phòng khớp (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Mục đích: "Tầng" chỉ khớp khi so kiểu chứa chuỗi — app khớp theo đầu từ sẽ thiếu mục này. · Căn cứ: BA chốt 2026-09-16 (chứa chuỗi); tổng 36 văn phòng theo `DOC-v1.1-04`. · ID cũ: TC-USR-029.</t>
@@ -10853,7 +11241,11 @@
           <t>K5 "xyz" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L40" s="6" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 ("không có thì không gợi ý"). · ID cũ: TC-USR-030.</t>
@@ -10932,7 +11324,11 @@
           <t>K6 "hcm" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
           <t>Mục đích: `DOC-v1.1-04` có cột `search_alias_text` chứa mã tỉnh ("hcm …") — app tìm nhầm cột này sẽ ra 34 văn phòng HCM ⇒ log bug. · Căn cứ: BA chốt 2026-09-16 (tìm theo tên văn phòng). · ID cũ: TC-USR-031.</t>
@@ -11019,7 +11415,11 @@
           <t>Tài khoản C = `FOXECO_STG_USER_C` (MNV 00041796); địa chỉ HRIS `HCM LôB3,E-Office,KCN TânThuận` ⇒ kỳ vọng prefill chuỗi `name` **`LôB3,E-Office,KCN TânThuận`** (`DOC-v1.1-04`) — `04_test-data/valid/USR-accounts.md`</t>
         </is>
       </c>
-      <c r="L43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 (mặc định load HRIS, cho sửa) + §8.15.2 "địa chỉ làm việc trong hồ sơ". ⛔ Chạy trước mọi TC lưu hồ sơ trên tài khoản C. · ✅ Test data đã có 2026-09-18 (`DOC-v1.1-05`). ⚠️ HRIS trả **mã tỉnh + tên VP** (`HCM LôB3,...`) còn catalog `name` không có tiền tố `HCM` — app hiện nguyên tiền tố thì **ghi nhận + hỏi BA**, ⛔ chưa kết luận bug. · Đã sửa theo §10.4 (2026-09-17): đổi thứ tự step 4/5 và gộp 2 điểm kiểm (giá trị HRIS + cho phép sửa) vào 1 Expected ở step cuối. · ID cũ: TC-USR-032.</t>
@@ -11188,7 +11588,11 @@
           <t>K3 "Tòa V-City, Lê Thái Tổ" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L45" s="6" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
           <t>✅ Tiền đề đã thoả 2026-09-18: HRIS của A = `HCM LôB3,E-Office,KCN TânThuận` ≠ `Tòa V-City, Lê Thái Tổ` (`DOC-v1.1-05`). · Mục đích: đối chứng với `TC-USR-040` — thứ tự ưu tiên "đã lưu &gt; HRIS &gt; rỗng"; thoát hẳn FoxEco để loại trừ giá trị còn trong phiên. · Căn cứ: BA chốt 2026-09-16 ("đã cập nhật trước đó vào lại sẽ thấy data cũ"). · ID cũ: TC-USR-034.</t>
@@ -11268,7 +11672,11 @@
           <t>Tài khoản C = `FOXECO_STG_USER_C`; SĐT HRIS đọc từ `00_input/v1.1/datatest` (`DOC-v1.1-05`, local — ⛔ không chép vào TC/evidence), định dạng 10 số đầu 0 ⇒ hợp lệ theo `BR15-02`</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 ("SĐT mặc định từ HRIS") + §8.15.2 "số điện thoại hiện tại". Có thể chạy cùng phiên với `TC-USR-040` trên tài khoản C. · ✅ Test data đã có 2026-09-18 (`DOC-v1.1-05`). 🕐 SĐT HRIS mới cập nhật 18/09, FoxEco có thể chỉ đồng bộ **sau** 18/09 ⇒ chạy từ 19/09; lệch đúng ngày 18/09 ⇒ ghi `BLOCKED`, ⛔ không log bug. · Đã sửa theo §10.4 (2026-09-17): đổi thứ tự step 4/5 và gộp 2 điểm kiểm vào 1 Expected ở step cuối. · ID cũ: TC-USR-035.</t>
@@ -11441,7 +11849,11 @@
           <t>SĐT "0987654321"; văn phòng "36 Nhơn Hòa 4, Cẩm Lệ" (04_test-data/valid/USR-office-catalog.md K4)</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 ("không lưu, không hiện xác nhận") — vế (1) không có hộp thoại chặn đường ra. · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-037` cũ — vế "giá trị chưa lưu bị bỏ" tách sang `TC-USR-046`. · ID cũ: TC-USR-037 (một phần).</t>
@@ -11525,7 +11937,11 @@
           <t>SĐT "0987654321"; văn phòng "36 Nhơn Hòa 4, Cẩm Lệ" (04_test-data/valid/USR-office-catalog.md K4)</t>
         </is>
       </c>
-      <c r="L50" s="6" t="inlineStr"/>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 — vế (2) giá trị chưa lưu không bị lưu ngầm/giữ nháp. Demo giữ bản nháp khi mở lại màn (đọc code `DOC-v1.1-02`) ⇒ STG giống demo thì log bug, ⛔ không dùng demo làm oracle. · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-037` cũ, giữ đúng 1 điểm kiểm ở step cuối. Nếu giá trị bước 4 trùng test data thì đổi giá trị khác. · ID cũ: TC-USR-037 (một phần — điểm kiểm chính).</t>
@@ -11999,7 +12415,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo BA trả lời `C-ACT-02` 2026-09-16: assert cứng bộ nhãn của app, thay vì chỉ assert "có đúng 2 tab" như bản v1.0. · Mục đích: nhãn tab xuất hiện trong Steps của rất nhiều TC ở `ACT` và các module khác, chốt sai là phải sửa rải rác. · Căn cứ: BA chốt **theo app**; PRD `EMP-05`/`EMP-06`/`AC-09.1.01` ghi "Đang chạy"/"Hoàn tất" là **PRD chưa cập nhật** — ⛔ không assert theo PRD, app hiện đúng bộ nhãn này thì PASS.</t>
@@ -12076,7 +12496,11 @@
           <t>1 đơn `COMPLETED` + 1 đơn `EXPIRED` + 1 đơn `RETURNED` của `SEED-ACT-03` (test_data_catalog §ACT — Bộ 3 đơn kết thúc)</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `AC-24.2.01` + BA trả lời `C-ACT-04(a)` 2026-09-17: bổ sung loại đơn thứ ba (`RETURNED`) vào danh sách phải có, bản v1.0 chỉ có 2 loại. · Mục đích: `RETURNED` là kết cục mới của v1.1, dev dễ quên xếp nó vào tab nào. · Căn cứ: chuỗi lý do của card "Hết hạn" verify ở `TC-ACT-008`, lý do hoàn hàng của card `RETURNED` verify ở `TC-ACT-015` — TC này chỉ chốt vị trí tab. Lô `DLV` chưa đẩy được đơn tới `RETURNED` ⇒ ghi `Blocked` phần đó, ⛔ không PASS cả TC.</t>
@@ -12153,7 +12577,11 @@
           <t>Tài khoản 0 đơn đang hoạt động = `SEED-ACT-02` (test_data_catalog §ACT — Text empty state tab đang-chạy)</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-06` Resolved 2026-09-15 (tài liệu đã phê duyệt, `EMP-05`): bản v1.0 chỉ assert "không có card nào" vì text empty state chưa có đặc tả; nay assert verbatim chuỗi + nhãn CTA. · Mục đích: cặp bất đối xứng với `TC-ACT-014` — tab này CÓ đúng 1 CTA, tab kia KHÔNG có; đây là nội dung phải assert, không phải chi tiết trình bày. · Căn cứ: `BR17-01` *"tối đa một CTA"* nên "không có" ở tab kia là lựa chọn thiết kế hợp lệ.</t>
@@ -12229,7 +12657,11 @@
           <t>Đơn `COMPLETED` của `SEED-ACT-03` (test_data_catalog §ACT)</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `DOC-v1.1-01 §8.14.1 BR14-03` + `§4 SCOPES` 2026-09-17: bản v1.0 chỉ assert "nhấn vào chuỗi sao không mở màn chấm điểm" và cố ý KHÔNG assert sự tồn tại của chuỗi leftover; nay **sự tồn tại của dấu vết đã là defect**. · Mục đích: kết quả phản trực giác so với bản cũ — người chạy quen v1.0 dễ cho PASS khi vẫn thấy ★ trên card. · Căn cứ: `§4` loại trừ vĩnh viễn ★/điểm/tier/chỉ số môi trường. Còn ★ ⇒ **log bug**, ⛔ KHÔNG diễn giải là "dấu vết phase sau". Chạy cùng lô với `SC-GIFT-011` để log 1 bug cho 2 bề mặt.</t>
@@ -12307,7 +12739,11 @@
           <t>Tài khoản 0 đơn kết thúc = `SEED-ACT-02` (test_data_catalog §ACT — Text empty state tab hoàn-tất)</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-06` Resolved 2026-09-15 (`EMP-06`): bản v1.0 chỉ assert "không có card nào"; nay assert verbatim chuỗi + KHÔNG CTA + ẩn hẳn khối lịch sử. · Mục đích: đối chứng âm cho `TC-ACT-012` — hai tab rỗng cạnh nhau nhưng khác nhau ở CTA và ở khối lịch sử; app hiện nút ở tab này là **sai spec**. · Căn cứ: `BR17-01` + `EMP-06`.</t>
@@ -12385,7 +12821,11 @@
           <t>Cặp đối chứng 1 đơn `RETURNED` + 1 đơn `CANCELLED` cùng tài khoản của `SEED-ACT-03` (test_data_catalog §ACT — Cặp đối chứng CANCELLED ⟷ RETURNED)</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
           <t>Đã sửa Expected theo app — QC GiangDC2 chốt 2026-09-21 (sau VR-017): đơn "Đã huỷ" hiện ở tab "Đang diễn ra" với badge "Đã huỷ" là hành vi ĐÚNG, không phải bug; thay kết luận BA `C-ACT-04(b)` 2026-09-17 (ẩn khỏi cả 2 tab). ⚠️ Title chưa sửa vì `§10.5` khoá Title (nợ #27 `03_test-cases/v1.1/CHANGELOG.md`). · Mục đích: hai kết cục bất thường nhưng hai cách xử lý ngược nhau — giá trị của TC nằm ở **phép đối chứng**, xem lẻ từng đơn thì không bắt được lỗi "gom chung mọi đơn bất thường vào một nhánh hiển thị". · Căn cứ: `AC-24.2.01` cho vế `RETURNED`; vế `CANCELLED` theo BA trả lời `C-ACT-04(b)` 2026-09-17 — đơn "Đã huỷ" **vẫn ẩn khỏi cả 2 tab**, rule v1.0 CÒN HIỆU LỰC, `§8.12.3` cho mọi vai *"Xem lý do"* đơn huỷ là **PRD chưa cập nhật**. · Phụ thuộc lô `DLV` để có đơn `RETURNED` — lô đó `BLOCKED` thì TC này `BLOCKED`.</t>
@@ -12461,7 +12901,11 @@
           <t>Đơn `EXPIRED` của `SEED-ACT-03` (test_data_catalog §ACT — Text lý do "Hết hạn", ⛔ không seed được qua UI)</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `DOC-v1.1-01 §8.5.1 BR05-03` + `AC-09.1.01` 2026-09-17: chuỗi lý do đổi sang bản **ngắn**, bỏ vế "— tin đã tự động đóng." mà bản v1.0 cùng ID đang assert. · Mục đích: 2 nguồn từng lệch phần đuôi câu; PRD v1.1 nay gọi tên chuỗi lần đầu nên thắng quan sát cũ `KB-ORD-07` (#4). App hiện bản dài ⇒ FAIL và log bug, ⛔ không hạ Expected về bản v1.0. · Chỉ ĐỌC card, ⛔ không tap — `C-ACT-03(c)` và `C-ORD-17` đang nói ngược nhau về việc card Hết hạn có tương tác được không.</t>
@@ -12540,7 +12984,11 @@
           <t>Tài khoản 0 đơn ở cả 2 tab = `SEED-ACT-02` (test_data_catalog §ACT — Tài khoản trắng)</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp với `TC-ACT-017` — che thanh tab dưới và khoá cuộn là hai lỗi layout khác bản chất, sửa được lỗi này không đảm bảo hết lỗi kia. · Căn cứ: `DOC-v1.1-01` §8.17.2 BR17-03 + `§6.2 AC-29.1.01`. `ACT` là màn duy nhất có 2 empty state cạnh nhau nên rule hình thức chung của `FR17` đặt home tại đây.</t>
@@ -12619,7 +13067,11 @@
           <t>Tài khoản 0 đơn ở cả 2 tab = `SEED-ACT-02` (test_data_catalog §ACT — Tài khoản trắng)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Đã sửa Expected + step 5 theo app — QC GiangDC2 chốt 2026-09-21 (sau VR-017): màn rỗng không cuộn/không phản hồi vuốt là hành vi ĐÚNG, không phải bug (`BUG-032` đã xoá). ⚠️ Title chưa sửa vì `§10.5` khoá Title (nợ #28 `03_test-cases/v1.1/CHANGELOG.md`). · Căn cứ gốc: `DOC-v1.1-01` §8.17.2 BR17-03 — QC hiểu "vẫn cuộn được" là màn không bị treo/khoá thao tác, không bắt buộc có phản hồi cuộn khi không có nội dung vượt màn.</t>
@@ -12699,7 +13151,11 @@
           <t>Tài khoản 0 đơn ở cả 2 tab = `SEED-ACT-02`; mạng throttle 3G chậm (test_data_catalog §ACT — Tốc độ mạng)</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
           <t>Mục đích: neo vào `[GAP]` của `SC-ACT-017` — điều kiện *"hiện empty state dựa cờ dữ liệu rỗng, không dựa null field"* là rule **backend**, ⛔ không verify được qua UI, nên TC chỉ assert phần quan sát được. · Căn cứ: `DOC-v1.1-01` §8.17 Pre-Conditions + §8.17.2 BR17-02. Bắt buộc throttle 3G chậm: mạng nhanh thì pha loading trôi qua quá nhanh, không phân biệt được hai trạng thái.</t>
@@ -12778,7 +13234,11 @@
           <t>2 người vận chuyển bấm gần đồng thời (test_data_catalog §ASN v1.1, biên)</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (a) — chỉ kiểm chứng được thứ tự tuần tự bằng 2 thiết bị thật; nhánh (b) automation ở `TC-ASN-024`. · Căn cứ: `DOC-v1.1-01 §8.3 BR03-02` · `§9 NFR-06`.</t>
@@ -12855,7 +13315,11 @@
           <t>1 tin NEED POSTED; 50 request đồng thời (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (b) của `SC-ASN-006` — ngưỡng `NFR-06`, chỉ kiểm chứng được bằng concurrency/backend test, không phải manual. · Căn cứ: `DOC-v1.1-01 §9 NFR-06`. ⚠️ Cần công cụ load/concurrency test gọi thẳng API — giao automation/backend, không nằm trong phạm vi vibe-test UI thuần. Đối chứng với `TC-ASN-006` (nhánh a, manual 2 thiết bị).</t>
@@ -12934,7 +13398,11 @@
           <t>3 phiên 3 vai trên 3 thiết bị; mốc đo ≤5 giây (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Mục đích: siết Expected từ định tính ("không cần làm mới", v1.0) sang định lượng **≤5 giây** theo `NFR-08`. · Căn cứ: `DOC-v1.1-01 §9 NFR-08` — "Cách đo: Integration test đa thiết bị". ⚠️ Đo bằng tay có sai số; ưu tiên automation nếu cần độ chính xác cao. · Đã sửa theo delta v1.1 (2026-09-15).</t>
@@ -13010,7 +13478,11 @@
           <t>Tin NEED lệch điểm giao, buổi "Sáng", dùng `SEED-ASN-01` (test_data_catalog §ASN v1.1, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (a) của `SC-ASN-011` v1.1 — vẫn là lệch điểm, không đổi bản chất so v1.0 nhưng đổi khuôn dữ liệu (Khoảng ngày + Buổi thay khung giờ đơn). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-01`. · Đã sửa theo delta v1.1 (2026-09-15): đổi test data từ "khung giờ" sang "khoảng ngày + tập buổi" theo form mới. · Nhãn buổi "Sáng" theo quan sát demo 3-role 2026-09-17 (QA-obs, chưa phải chốt chính thức).</t>
@@ -13086,7 +13558,11 @@
           <t>Tin NEED lệch khoảng ngày (không overlap), buổi "Giờ nào cũng được", dùng `SEED-ASN-01` (test_data_catalog §ASN v1.1, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (b) của `SC-ASN-011` v1.1 — thay "khung giờ tách rời hoàn toàn" (v1.0) bằng đúng định nghĩa "khoảng ngày KHÔNG overlap" chính thức; cố tình chọn buổi "Giờ nào cũng được" để khẳng định biến buổi KHÔNG cứu được khi ngày đã lệch (2 điều kiện độc lập). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-01`. · Đã sửa theo delta v1.1 (2026-09-15). · Nhãn buổi theo quan sát demo 3-role 2026-09-17 (QA-obs).</t>
@@ -13163,7 +13639,11 @@
           <t>3 tin NEED khớp tuyến, tự đăng qua UI (test_data_catalog §ASN v1.1, mốc dưới trần)</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
           <t>Mục đích: mốc dưới trần trong bộ ba 3/5/6 — xác nhận tài khoản B (người ĐĂNG TUYẾN) là người nhận thông báo và &lt;5 tin thì gửi đúng số đó, đúng kết luận `C-ASN-04(a)(c)`. · Căn cứ: `DOC-v1.1-01 §8.4 BR04-04` (dư) + kết luận BA `C-ASN-04` Resolved 2026-09-17. · Đã sửa theo delta v1.1: đổi test data OFFER sang khoảng ngày + tập buổi, giữ nguyên mốc số 3/5/6 đã BA chốt.</t>
@@ -13241,7 +13721,11 @@
           <t>5 tin NEED khớp tuyến, tự đăng qua UI; ghi baseline thông báo tồn của B (test_data_catalog §ASN v1.1, mốc đúng trần tài khoản)</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
           <t>Mục đích: mốc đúng trần — biên hợp lệ, cặp với `TC-ASN-017` (mốc vượt trần). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-04` (dư) + `C-ASN-04` Resolved 2026-09-17. · Đã sửa theo delta v1.1: đổi test data OFFER sang khoảng ngày + tập buổi. · ✏️ Sửa 2026-09-21 (QC GiangDC2 recheck — KHÔNG phải bug): trần 5 thông báo khớp tuyến tính theo TÀI KHOẢN, mọi tuyến cộng dồn, ⛔ không phải theo từng tuyến. Căn cứ đo: VR-010 (5 tin NEED khớp → 4 thông báo mới + 1 tồn = 5). ✅ BA đã xác nhận lại 2026-09-21 (QC GiangDC2 báo lại, chưa có văn bản): trần tính theo TÀI KHOẢN — thay kết luận cũ `C-ASN-04(e)` (2026-09-17: độc lập theo từng tuyến).</t>
@@ -13320,7 +13804,11 @@
           <t>6 tin NEED khớp cùng 1 tuyến OFFER, tự đăng qua UI (test_data_catalog §ASN v1.1, mốc vượt trần)</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
           <t>Mục đích: mốc vượt trần — xác nhận rule `C-ASN-04(d)`: tuyến ĐÃ đủ 5 thì KHÔNG gửi thêm cho tin mới. · Căn cứ: `DOC-v1.1-01 §8.4 BR04-04` (dư) + `C-ASN-04` Resolved 2026-09-17. ⛔ Trần KHÔNG cộng dồn theo ngày; nếu app chặn theo ngày ⇒ FAIL và log bug.</t>
@@ -13396,7 +13884,11 @@
           <t>Tin NEED ngày overlap nhưng buổi "Sau giờ làm" không chung với "Sáng"/"Chiều" của OFFER, dùng `SEED-ASN-01` (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (c) — case MỚI của `SC-ASN-011` v1.1, trước đây không tách được vì chưa có định nghĩa buổi độc lập với ngày; phân biệt với nhánh (b) "ngày không overlap". · Căn cứ: `DOC-v1.1-01 §8.4 BR04-01` · `BR04-02`. · Nhãn buổi "Sau giờ làm" theo quan sát demo 3-role 2026-09-17 (QA-obs, chưa phải chốt chính thức).</t>
@@ -13472,7 +13964,11 @@
           <t>Tin NEED khớp đầy đủ 3 điều kiện, buổi "Sáng", dùng `SEED-ASN-01`; ngưỡng đo ≤60s (NFR-04) (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr"/>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (d) — vế dương đối chứng với 3 nhánh âm (a)(b)(c), gắn thêm ngưỡng định lượng `NFR-04` ≤60s chưa từng assert ở `SC-ASN-009` (CARRIED, chỉ xác nhận CÓ thông báo, không đo thời gian). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-01/02` · `§9 NFR-04`. · Nhãn buổi "Sáng" theo quan sát demo 3-role 2026-09-17 (QA-obs). Demo cũng xác nhận trực tiếp cơ chế sync realtime tồn tại (dùng chéo làm evidence cho `TC-ASN-008`).</t>
@@ -13549,7 +14045,11 @@
           <t>2 tuyến OFFER của cùng tài khoản B, dùng chung 1 trần 5 theo tài khoản (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
           <t>Mục đích: xác nhận `C-ASN-04(e)` — trần ĐỘC LẬP theo từng tuyến (mỗi lần đăng "Tôi nhận giao hàng"); rủi ro thật nếu backend dùng chung 1 bộ đếm cho cả tài khoản. · Căn cứ: kết luận BA `C-ASN-04(e)`, `risk_assessment.md` Resolved 2026-09-17. · ✏️ Sửa 2026-09-21 (QC GiangDC2 recheck — KHÔNG phải bug): ĐẢO kỳ vọng — trần 5 tính theo TÀI KHOẢN nên tuyến thứ hai KHÔNG có slot riêng. Căn cứ đo: VR-010 (OFFER tuyến 2 + 1 tin NEED khớp, tổng vẫn 5, 0 thông báo mới). ✅ BA đã xác nhận lại 2026-09-21 (QC GiangDC2 báo lại, chưa có văn bản): trần tính theo TÀI KHOẢN — thay kết luận cũ `C-ASN-04(e)` (2026-09-17: độc lập theo từng tuyến). ⚠️ `Test Title` giữ nguyên (§10.5 không cho đổi tiêu đề) nên tiêu đề CŨ ('độc lập, không cộng dồn') mô tả rule BA cũ — đọc theo Expected.</t>
@@ -13625,7 +14125,11 @@
           <t>Tin OFFER của B; token tài khoản D không sở hữu tin đó (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
           <t>Mục đích: mở rộng `BR03-05`/`SC-ASN-007` (ẩn trên UI) sang tầng API — kiểm tra quyền phải ở tầng máy chủ, không chỉ ẩn giao diện. · Căn cứ: `DOC-v1.1-01 §9 NFR-11`. ⚠️ Cần công cụ gọi API trực tiếp (Postman/tương đương) — UI không có đường dẫn tới tin OFFER của người khác nên không chạy được bằng thao tác UI thuần. Giao automation/backend/security test.</t>
@@ -13703,7 +14207,11 @@
           <t>2 tin trùng tuyến ở 2 thời điểm + 1 tin không trùng tuyến đăng sớm nhất (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
           <t>Mục đích: làm rõ (không phải đảo) — độ gần tuyến vẫn là tầng ưu tiên số 1 (nhị phân), thời gian đăng chỉ là tầng 2 khi cùng trùng tuyến; v1.0 chỉ test được tầng 2, thiếu vế tầng 1 vs tin không trùng tuyến. · Căn cứ: `DOC-v1.1-01 §8.3 BR03-06`. · Đã sửa theo delta v1.1 (2026-09-15): thêm tin không-trùng-tuyến để kiểm chứng tầng 1.</t>
@@ -13778,7 +14286,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>9. Dòng "Ghép thành công" vẫn còn trong block LỊCH SỬ ở bước 8 (không bị xoá), có thêm 1 dòng log ghi hành động huỷ nhận kèm vai "Người vận chuyển" và lý do "Doi ca lam viec"; đơn chuyển về trạng thái "Chờ ghép" và hiện lại trên bảng tin.</t>
+          <t>9. Dòng "Ghép thành công" vẫn còn trong block LỊCH SỬ ở bước 8 (không bị xoá), có thêm 1 dòng log ghi đúng nhãn hành động huỷ nhận "Đã huỷ nhận đơn" kèm danh tính người thực hiện (app ghi tên người, không ghi vai trò — chấp nhận theo hành vi nhất quán toàn app) và lý do "Doi ca lam viec"; đơn chuyển về trạng thái "Chờ ghép" và hiện lại trên bảng tin.</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -13786,10 +14294,14 @@
           <t>Đơn `MATCHED`; block LỊCH SỬ có dòng "Ghép thành công" (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: log phải bất biến — xoá dòng cũ là phá tính bằng chứng của cả timeline; đồng thời đơn phải quay lại vòng đời bình thường, không mắc kẹt. · Căn cứ: `BR11-03` + `AC-25.1.02` (PRD phê duyệt, không còn là override QA — trước dựa `BR-INT-04` suy diễn). ⚠ Dự kiến FAIL — `KB-CNL-01` đã live-verify app XOÁ dòng "Ghép thành công" ⇒ log bug. · Cùng nhóm rule truy vết "bằng chứng đã ghi thì bất biến" — chạy cùng lô với `SC-USR-017`/`SC-ORD-065`/`SC-DLV-062`, cùng vỡ thì gộp 1 bug report. · Đã sửa theo §10.4 (2026-09-17): gộp 2 điểm kiểm (log giữ nguyên + đơn về POSTED/hiện lại bảng tin) vào 1 Expected ở step cuối; bỏ Expected ở step 4 (chỉ còn observation baseline, không phải case fail độc lập).</t>
+          <t>Mục đích: log phải bất biến — xoá dòng cũ là phá tính bằng chứng của cả timeline; đồng thời đơn phải quay lại vòng đời bình thường, không mắc kẹt. · Căn cứ: `BR11-03` + `AC-25.1.02` (PRD phê duyệt, không còn là override QA — trước dựa `BR-INT-04` suy diễn). ⚠ Dự kiến FAIL — `KB-CNL-01` đã live-verify app XOÁ dòng "Ghép thành công" ⇒ log bug. · Cùng nhóm rule truy vết "bằng chứng đã ghi thì bất biến" — chạy cùng lô với `SC-USR-017`/`SC-ORD-065`/`SC-DLV-062`, cùng vỡ thì gộp 1 bug report. · Đã sửa theo §10.4 (2026-09-17): gộp 2 điểm kiểm (log giữ nguyên + đơn về POSTED/hiện lại bảng tin) vào 1 Expected ở step cuối; bỏ Expected ở step 4 (chỉ còn observation baseline, không phải case fail độc lập). · 🔁 Đính chính 2026-09-22 (QC): vế "ghi vai trò" đổi thành "ghi tên người" (chấp nhận, nhất quán toàn app) — BUG-035 đã xoá. Không còn vướng mắc nào khác ⇒ verdict FAIL → PASS.</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
@@ -13854,7 +14366,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2. KHÔNG còn nút huỷ đơn thường nào; chỉ có đúng 2 nút hành động liên quan huỷ: "Yêu cầu hoàn hàng" và "Báo cáo sự cố".</t>
+          <t>2. KHÔNG còn nút huỷ đơn thường nào; chỉ còn đúng 1 nút hành động liên quan: "Báo cáo sự cố". KHÔNG có nút "hoàn hàng" nào ở màn này của Người gửi — hoàn hàng (RETURNING) là hành động do Người vận chuyển khởi tạo (FR09), Người gửi không có control kích hoạt trực tiếp.</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -13862,10 +14374,14 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `AC-25.2.01` + `BR11-04` ("bất kỳ vai trò nào"). · Đọc chéo `DLV` (`SC-DLV-053/054` — home của đường "hoàn hàng") và `TS` (`SC-TS-008..015` — home của form "báo sự cố"); TC này chỉ đếm đúng 2 nút tồn tại, KHÔNG lặp nội dung luồng con. · Đã sửa theo §10.4 (2026-09-17): tách theo vai — vai Người vận chuyển ở `TC-CNL-018`, vai Người nhận ở `TC-CNL-019`.</t>
+          <t>Căn cứ: `AC-25.2.01` + `BR11-04` ("bất kỳ vai trò nào") — chỉ đảm bảo ở MỨC TRẠNG THÁI (hoàn hàng vẫn là 1 trong 2 lối thoát hợp lệ của đơn), KHÔNG đặt tên nút UI. Đọc chéo `DLV` `FR09` §8.9 (trang 43) — trigger thật của RETURNING là Người vận chuyển chọn "Cầm hàng về" ở màn "Xử lý đơn hàng", không phải nút trên màn Theo dõi đơn của Sender/Receiver. Và `TS` (`SC-TS-008..015` — home của form "báo sự cố"). · Đã sửa theo §10.4 (2026-09-17): tách theo vai — vai Người vận chuyển ở `TC-CNL-018`, vai Người nhận ở `TC-CNL-019`. · 🔁 Đính chính 2026-09-22 (QC, sau khi đối chiếu PRD gốc): bỏ giả định nút "Yêu cầu hoàn hàng" trên màn Sender/Receiver — không tồn tại trong PRD, TC viết sai. BUG-033 đã xoá, verdict FAIL → PASS.</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -13930,7 +14446,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>2. KHÔNG còn nút huỷ đơn thường nào; chỉ có đúng 2 nút hành động liên quan huỷ: "Yêu cầu hoàn hàng" và "Báo cáo sự cố".</t>
+          <t>2. KHÔNG còn nút huỷ đơn thường nào; có nút "Báo cáo sự cố" VÀ đường vào luồng hoàn hàng đi qua màn giao hàng: bấm nút "Đã đến địa điểm giao hàng" → màn "Xử lý đơn hàng" → chọn chế độ "Cầm hàng về" (FR09). KHÔNG có một nút riêng tên "Yêu cầu hoàn hàng" trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -13938,10 +14454,14 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L27" s="6" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: vai độc lập với `TC-CNL-017`/`019` — `BR11-04` yêu cầu "bất kỳ vai trò nào". · Căn cứ: giống `TC-CNL-017`. · Đọc chéo `DLV`/`TS`, không lặp nội dung luồng con. TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1.</t>
+          <t>Mục đích: vai độc lập với `TC-CNL-017`/`019` — `BR11-04` yêu cầu "bất kỳ vai trò nào". · Căn cứ: giống `TC-CNL-017`. · Đọc chéo `DLV`/`TS`, không lặp nội dung luồng con. TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1. · 🔁 Đính chính 2026-09-22 (QC): chỉ vai Người vận chuyển mới có đường vào hoàn hàng (qua FR09 "Xử lý đơn hàng" → "Cầm hàng về"), không phải nút riêng "Yêu cầu hoàn hàng". BUG-033 đã xoá, verdict FAIL → PASS. · 🔁 Đính chính 2026-09-22 (QC, bổ sung): chốt tên chính thức nút vào luồng hoàn hàng ở v1.1 là "Đã đến địa điểm giao hàng" (đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện CHƯA đổi theo tên mới (evidence VR-018 2026-09-21), xem BUG-044.</t>
         </is>
       </c>
       <c r="N27" s="6" t="inlineStr">
@@ -14006,7 +14526,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2. KHÔNG còn nút huỷ đơn thường nào; chỉ có đúng 2 nút hành động liên quan huỷ: "Yêu cầu hoàn hàng" và "Báo cáo sự cố".</t>
+          <t>2. KHÔNG còn nút huỷ đơn thường nào; chỉ còn đúng 1 nút hành động liên quan: "Báo cáo sự cố". KHÔNG có nút "hoàn hàng" nào ở màn này của Người nhận — hoàn hàng (RETURNING) là hành động do Người vận chuyển khởi tạo (FR09), Người nhận không có control kích hoạt trực tiếp.</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -14014,10 +14534,14 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: vai độc lập với `TC-CNL-017`/`018` — `BR11-04` yêu cầu "bất kỳ vai trò nào". · Căn cứ: giống `TC-CNL-017`. · Đọc chéo `DLV`/`TS`, không lặp nội dung luồng con. TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1.</t>
+          <t>Mục đích: vai độc lập với `TC-CNL-017`/`018` — `BR11-04` yêu cầu "bất kỳ vai trò nào". · Căn cứ: giống `TC-CNL-017`. · Đọc chéo `DLV`/`TS`, không lặp nội dung luồng con. TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1. · 🔁 Đính chính 2026-09-22 (QC): bỏ giả định nút "Yêu cầu hoàn hàng" trên màn Người nhận — không tồn tại trong PRD. BUG-033 đã xoá, verdict FAIL → PASS.</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -14092,7 +14616,11 @@
           <t>Lý do 4 ký tự "abcd" (test_data_catalog §CNL v1.1, biên dưới)</t>
         </is>
       </c>
-      <c r="L29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
           <t>Mục đích: siết thêm 2 chi tiết Then mà v1.0 chưa có — nút vô hiệu hoá SẴN (không phải bấm rồi báo lỗi) và lỗi hiện đúng vị trí dưới ô lý do. · Căn cứ: `BR11-01` + `VAL-04` + `AC-25.1.03` (PRD phê duyệt, không còn là override QA). ⚠ Dự kiến FAIL — app hiện cho qua ⇒ log bug, ⛔ không hạ chuẩn TC theo hành vi app. · Đã sửa theo analyze v1.1 (2026-09-15): bỏ vế "5 ký tự được nhận" — đã có `TC-CNL-003` (CARRIED) cover, tránh trùng. · Đã sửa theo §10.4 (2026-09-17): gộp 3 điểm quan sát (nút khoá · lỗi đúng vị trí · trạng thái đơn) vào 1 Expected ở step cuối.</t>
@@ -14168,7 +14696,11 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
           <t>🔴 Bản v1.0 cùng ID assert KHÔNG có chức năng này — kỳ vọng ngược hoàn toàn, phải dùng bản v1.1. · Căn cứ: `§4 SCOPES` In-scope + `§8.16` + `AC-25.2.01`. ⚠ Dự kiến FAIL nếu STG chưa build `FR16` ⇒ log gap PRD↔app, ⛔ không diễn giải thành "vẫn out of scope". · Đọc chéo `TS` — chỉ kiểm nút tồn tại + mở được, KHÔNG lặp nội dung form/ảnh (home ở `SC-TS-008..015`). · Đã sửa theo §10.4 (2026-09-17): tách riêng theo vai — vai Người vận chuyển ở `TC-CNL-015`, vai Người nhận ở `TC-CNL-016` (mỗi vai độc lập, có thể fail riêng theo `BR11-04` "bất kỳ vai trò nào").</t>
@@ -14242,7 +14774,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>8. Block LỊCH SỬ có nhiều hơn số dòng đã ghi ở bước 3 đúng 1 dòng; dòng mới ghi đủ 3 thành phần: vai "Người gửi", lý do "Huy vi trung lich" và thời điểm (timestamp) huỷ.</t>
+          <t>8. Block LỊCH SỬ có nhiều hơn số dòng đã ghi ở bước 3 đúng 1 dòng; dòng mới ghi đúng nhãn hành động huỷ đơn của Người gửi (KHÔNG phải nhãn "Đã huỷ nhận đơn" của luồng huỷ nhận), kèm danh tính người thực hiện (app ghi tên người, không ghi vai trò — chấp nhận theo hành vi nhất quán toàn app), lý do "Huy vi trung lich" và thời điểm (timestamp) huỷ.</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -14250,10 +14782,14 @@
           <t>Đơn `MATCHED`; block LỊCH SỬ đã có mốc trước đó (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: `BR11-02` đòi đủ 3 thành phần (vai trò · lý do · thời điểm) — v1.0 chỉ assert 2, thiếu timestamp. · Căn cứ: `BR11-02` + `AC-25.1.01` (PRD phê duyệt, không còn là override QA). ⚠ Dự kiến FAIL — app hiện chỉ hiện banner, không ghi log ⇒ log bug. · Kiểm chéo cùng lô với `SC-TS-003` + `SC-DLV-062` — cùng vỡ thì gộp 1 bug report. · Đã sửa theo analyze v1.1 (2026-09-15): thêm assert thời điểm (timestamp) vào Expected.</t>
+          <t>Mục đích: `BR11-02` đòi đủ 3 thành phần (vai trò · lý do · thời điểm) — v1.0 chỉ assert 2, thiếu timestamp. · Căn cứ: `BR11-02` + `AC-25.1.01` (PRD phê duyệt, không còn là override QA). ⚠ Dự kiến FAIL — app hiện chỉ hiện banner, không ghi log ⇒ log bug. · Kiểm chéo cùng lô với `SC-TS-003` + `SC-DLV-062` — cùng vỡ thì gộp 1 bug report. · Đã sửa theo analyze v1.1 (2026-09-15): thêm assert thời điểm (timestamp) vào Expected. · 🔁 Đính chính 2026-09-22 (QC): vế "ghi vai trò" đổi thành "ghi tên người" (app nhất quán ghi tên ở mọi dòng LỊCH SỬ, không riêng dòng huỷ) — BUG-035 đã xoá, không phải bug. Vế nhãn hành động sai ("Đã huỷ nhận đơn" thay vì nhãn đúng của huỷ đơn) vẫn là lỗi độc lập, còn giữ ở BUG-034 — verdict TC này vẫn FAIL vì lý do này.</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
@@ -14326,7 +14862,11 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
           <t>Mục đích: vai độc lập với `TC-CNL-006` (vai Người gửi) — `BR11-04` yêu cầu "bất kỳ vai trò nào", mỗi vai có thể fail riêng. · Căn cứ: giống `TC-CNL-006`. · Đọc chéo `TS` — chỉ kiểm nút tồn tại, không lặp nội dung form (home `SC-TS-008..015`). TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1.</t>
@@ -14402,7 +14942,11 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L33" s="6" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
           <t>Mục đích: vai độc lập với `TC-CNL-006`/`015` — `BR11-04` yêu cầu "bất kỳ vai trò nào". · Căn cứ: giống `TC-CNL-006`. · Đọc chéo `TS` — chỉ kiểm nút tồn tại, không lặp nội dung form (home `SC-TS-008..015`). TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1.</t>
@@ -14478,7 +15022,11 @@
           <t>Đơn `INCIDENT` (test_data_catalog §CNL v1.1) — ⚠ có thể chưa seed được nếu STG chưa build `FR16`</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
           <t>⚠️ Verdict đúng khi STG chưa build `INCIDENT`/`FR16` là **BLOCKED**, ⛔ không đánh PASS vì "không thấy đơn tự chuyển". · Căn cứ: `AC-25.2.01`. · ⛔ Không assert trạng thái đích cụ thể sau khi admin xử lý — `C-CNL-03` chốt trạng thái đích tuỳ dev. · ⛔ Không assert banner/thông báo "đang được hỗ trợ" — BA xác nhận người dùng không nhận thông báo gì trong lúc chờ.</t>
@@ -14554,7 +15102,11 @@
           <t>2 phiên song song A (Người gửi) + B (Người vận chuyển); đơn `MATCHED`, popup "Tôi đã lấy hàng" đang mở ở phiên B (test_data_catalog §CNL v1.1, ô biên duy nhất của delta)</t>
         </is>
       </c>
-      <c r="L35" s="6" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
           <t>⭐ Vùng dễ có lỗi race thật — nếu backend chỉ kiểm `status == MATCHED` mà không kiểm hành động đã bấm thì huỷ sẽ lọt qua. · Căn cứ: PRD đổi cách phát biểu ngưỡng từ trạng thái sang hành động (`§8.11 Pre-Conditions` + `AC-25.1.01` — "MATCHED khi CHƯA bấm Tôi đã lấy hàng", không phải "MATCHED" đơn thuần). · Cần thao tác đồng thời 2 phiên trong cùng khoảnh khắc — không dựng được bằng 1 tài khoản.</t>
@@ -14632,7 +15184,11 @@
           <t>Lý do gồm 5 dấu cách (test_data_catalog §CNL v1.1, biên)</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
           <t>Mục đích: mốc thứ tư trong bộ boundary lý do (rỗng → 4 ký tự → 5 ký tự → 5 dấu cách). · Căn cứ: `VAL-03` (trim) + `VAL-04` (PRD phê duyệt, không còn là override QA). ⚠ Dự kiến FAIL — `KB-CNL-02` đã live-verify app cho qua ⇒ log bug. · ⚠️ Biên "5 dấu cách" dễ bị gõ nhầm thành "     x" khi nhập tay — ghi rõ trong Test Data để tester không tự ý gõ sai.</t>
@@ -14708,7 +15264,11 @@
           <t>Giá trị assert-absent: bề mặt "Admin vận hành" (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L37" s="6" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
           <t>`[GAP]` theo `Project_rule §10.1` — PRD nêu actor "Admin vận hành" nhưng không mô tả bề mặt nào ⇒ ghi nhận thiếu vắng, ⛔ không viết TC khẳng định hành vi Admin. · Căn cứ: `C-CNL-03` Resolved 2026-09-16 — dev xử lý tay qua Google Form ngoài app, không có tool/màn. · Gap nghiệp vụ cần nêu PM: nếu chỉ admin đóng được `INCIDENT` mà không có đường tới admin, đơn có thể treo vĩnh viễn.</t>
@@ -14773,7 +15333,7 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn nút mở màn "Xác nhận đã giao".
+3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
 4. Chọn "Người nhận" ở field "Giao cho".
 5. Đính 1 ảnh JPG từ thư viện thiết bị.
 6. Nhấn "Xác nhận đã giao hàng" và đồng ý ở popup xác nhận.
@@ -14790,10 +15350,14 @@
           <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02`; đối tượng nhận "Người nhận" + 1 ảnh bằng chứng (test_data_catalog §DLV — Đối tượng nhận, Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: luồng chính của `FR07` mở rộng — 3 nhánh còn lại (TC-DLV-044/045/046) đều rẽ từ đúng màn này. · Căn cứ: `DOC-v1.1-01` §8.7.2 + §8.12.4 mẫu câu 1. `RISK-DLV-08` đã Confirmed qua demo 2026-09-16 (luồng submit chạy đúng); vẫn double-check locator trên STG trước khi hardening.</t>
+          <t>Mục đích: luồng chính của `FR07` mở rộng — 3 nhánh còn lại (TC-DLV-044/045/046) đều rẽ từ đúng màn này. · Căn cứ: `DOC-v1.1-01` §8.7.2 + §8.12.4 mẫu câu 1. `RISK-DLV-08` đã Confirmed qua demo 2026-09-16 (luồng submit chạy đúng); vẫn double-check locator trên STG trước khi hardening. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
@@ -14855,7 +15419,7 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn nút mở màn "Xác nhận đã giao".
+3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
 4. Chọn "Người được uỷ quyền" ở field "Giao cho".
 5. Nhập "Nguyễn Văn Bảy" vào ô tên người nhận thay.
 6. Nhập "0912345678" vào ô số điện thoại người nhận thay.
@@ -14874,10 +15438,10 @@
           <t>Đơn `IN_TRANSIT` đơn #2 của `SEED-DLV-02`; tên 12 ký tự + SĐT hợp lệ (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr"/>
+      <c r="L39" s="6" t="n"/>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: chốt giá trị tự sinh của "Uỷ quyền bởi" theo MÀN VÀO chứ không theo loại đối tượng nhận — đối chứng âm là TC-DLV-051 (vào từ màn "Liên hệ người gửi" thì tự sinh "Người gửi"). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03/BR07-04/BR07-05 + §8.12.4 mẫu câu 2. Trường "Uỷ quyền bởi" chỉ đọc, không sửa được.</t>
+          <t>Mục đích: chốt giá trị tự sinh của "Uỷ quyền bởi" theo MÀN VÀO chứ không theo loại đối tượng nhận — đối chứng âm là TC-DLV-051 (vào từ màn "Liên hệ người gửi" thì tự sinh "Người gửi"). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03/BR07-04/BR07-05 + §8.12.4 mẫu câu 2. Trường "Uỷ quyền bởi" chỉ đọc, không sửa được. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
         </is>
       </c>
       <c r="N39" s="6" t="inlineStr">
@@ -14953,7 +15517,7 @@
           <t>Đơn `RETURNED` = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="n"/>
       <c r="M40" s="5" t="inlineStr">
         <is>
           <t>Mục đích: oracle bảo vệ ranh giới `RETURNED` ⟷ `COMPLETED` — lỗi hay gặp nhất là coi hoàn hàng như một dạng hoàn thành. Chạy sớm nhất trong nhóm hậu-hoàn-hàng. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06 + §8.14.1 (bước tặng quà chỉ mở ở đơn Hoàn thành). Cặp với TC-DLV-065.</t>
@@ -15033,7 +15597,7 @@
           <t>Đơn `RETURNED` = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L41" s="6" t="inlineStr"/>
+      <c r="L41" s="6" t="n"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
           <t>Mục đích: điểm fail độc lập với TC-DLV-064 — bước tặng quà và chỉ số đóng góp là hai bề mặt khác nhau, khoá một bề mặt không đảm bảo khoá bề mặt kia. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đơn vẫn phải xuất hiện trong tab "Đã hoàn thành" — verify ở TC-DLV-063.</t>
@@ -15112,7 +15676,11 @@
           <t>Transition `POSTED` → `DELIVERED` — ngoài bảng transition hợp lệ (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
           <t>Mục đích: tầng backend của rule đã có TC ở tầng UI (`TC-DLV-021` v1.0 chỉ verify màn hình không cho nhảy bước) — UI chặn không đảm bảo backend cũng chặn. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-01 + bảng §8.12.2. Dự án không có API spec/HTTP Status Contract nên assert theo hệ quả quan sát được trên app, không assert mã status.</t>
@@ -15192,7 +15760,11 @@
           <t>Transition `IN_TRANSIT` → `RETURNED` bỏ qua `RETURNING` (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh nhảy bậc nguy hiểm nhất — đóng đơn ở kết cục hoàn hàng mà không có bước người gửi xác nhận nhận lại, tức mất luôn oracle của TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02.</t>
@@ -15272,7 +15844,11 @@
           <t>Transition `IN_TRANSIT` → `COMPLETED` bỏ qua `DELIVERED` (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp với TC-DLV-075 — hai đích nhảy bậc khác nhau từ cùng một trạng thái nguồn, chặn được đích này không suy ra chặn được đích kia. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02. Bỏ qua "Đã giao" còn xoá luôn yêu cầu ảnh bằng chứng của `BR07-02`.</t>
@@ -15353,7 +15929,11 @@
           <t>Đơn `MATCHED` rồi bị huỷ nhận đơn (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L45" s="6" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
           <t>Mục đích: neo vào `RISK-DLV-09` — bug audit đã biết (`RISK-TS-01`: huỷ nhận đơn xoá dòng "Ghép thành công") vi phạm trực tiếp rule này, nên TC **dự kiến FAIL có chủ đích** cho tới khi bug được fix. · Căn cứ: `DOC-v1.1-01` §9 NFR-07 (log append-only, không API sửa/xoá). FAIL ⇒ log bug và cross-ref `RISK-TS-01`, ⛔ không hạ Expected theo hành vi hiện tại.</t>
@@ -15432,7 +16012,7 @@
           <t>Đơn `RESCHEDULED`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="n"/>
       <c r="M46" s="5" t="inlineStr">
         <is>
           <t>Mục đích: 1 trong 3 ô vai của nhóm trạng thái `RESCHEDULED` — mỗi vai fail độc lập. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. ⚠ Thanh timeline vẫn hiện đúng 5 mốc và mốc "Đang giao" đang active — đây là thiết kế đã chốt (`C-DLV-05(d)` Resolved 2026-09-17), ⛔ không FAIL vì thiếu mốc mới.</t>
@@ -15511,7 +16091,7 @@
           <t>Đơn `RESCHEDULED`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L47" s="6" t="inlineStr"/>
+      <c r="L47" s="6" t="n"/>
       <c r="M47" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED — đây là vai DUY NHẤT có nút hành động thật ở trạng thái này, 2 vai kia chỉ xem.</t>
@@ -15590,7 +16170,7 @@
           <t>Đơn `RESCHEDULED`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="n"/>
       <c r="M48" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với TC-DLV-032 — quyền giao lại chỉ thuộc người vận chuyển. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED.</t>
@@ -15669,7 +16249,7 @@
           <t>Đơn `RETURNING`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L49" s="6" t="inlineStr"/>
+      <c r="L49" s="6" t="n"/>
       <c r="M49" s="6" t="inlineStr">
         <is>
           <t>Mục đích: người gửi là vai DUY NHẤT đóng được đơn ở nhánh hoàn hàng — cặp với TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
@@ -15748,7 +16328,7 @@
           <t>Đơn `RETURNING`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="n"/>
       <c r="M50" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
@@ -15827,7 +16407,7 @@
           <t>Đơn `RETURNING`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L51" s="6" t="inlineStr"/>
+      <c r="L51" s="6" t="n"/>
       <c r="M51" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
@@ -15908,7 +16488,7 @@
           <t>Đơn `INCIDENT` đã vượt mốc 2h và 4h = `SEED-DLV-04` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="n"/>
       <c r="M52" s="5" t="inlineStr">
         <is>
           <t>Mục đích: chốt ranh giới nhánh sự cố ⟷ luồng tự đóng thường — dễ lập trình sai thành "quá giờ thì đóng". · Căn cứ: `DOC-v1.1-01` §8.10.1 BR10-04 (SC mới gắn REQ giữ ID, không sửa `SC-DLV-024` v1.0 vốn đúng cho nhánh thường). ⛔ Không assert vế "admin xử lý" — role admin out of scope v1.1 (`C-DLV-07` Resolved 2026-09-17).</t>
@@ -15973,7 +16553,7 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn nút mở màn "Xác nhận đã giao".
+3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
 4. Chọn "Quầy lễ tân" ở field "Giao cho".
 5. Đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" khi vẫn để trống cả hai ô của khối "NGƯỜI NHẬN TẠI QUẦY".
 6. Nhập "Trần Thị Lan" vào ô "Họ tên người trực quầy".
@@ -15992,10 +16572,10 @@
           <t>Đơn `IN_TRANSIT` đơn #3 của `SEED-DLV-02`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
-      <c r="L53" s="6" t="inlineStr"/>
+      <c r="L53" s="6" t="n"/>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: step 5 là vế âm gộp trong cùng TC — submit khi 2 ô trống phải không đi được, nên step 9 mới quan sát được kết quả dương. · Căn cứ: `C-DLV-06` Resolved 2026-09-17 (BA *"trên UI có dấu * bắt buộc mà"*, QA submit thử với 2 ô trống thì form không đi) + `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 3. ⛔ Chưa assert cờ "không liên lạc được" và `NTF-05`/`NTF-11` — `C-DLV-08` (a)(b) còn Partially, QA tự xác minh qua block "LỊCH SỬ" trước khi siết TC.</t>
+          <t>Mục đích: step 5 là vế âm gộp trong cùng TC — submit khi 2 ô trống phải không đi được, nên step 9 mới quan sát được kết quả dương. · Căn cứ: `C-DLV-06` Resolved 2026-09-17 (BA *"trên UI có dấu * bắt buộc mà"*, QA submit thử với 2 ô trống thì form không đi) + `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 3. ⛔ Chưa assert cờ "không liên lạc được" và `NTF-05`/`NTF-11` — `C-DLV-08` (a)(b) còn Partially, QA tự xác minh qua block "LỊCH SỬ" trước khi siết TC. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
         </is>
       </c>
       <c r="N53" s="6" t="inlineStr">
@@ -16057,7 +16637,7 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn nút mở màn "Xác nhận đã giao".
+3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
 4. Chọn "Quầy bảo vệ" ở field "Giao cho".
 5. Nhập "Lê Văn Tám" vào ô "Họ tên người trực quầy".
 6. Nhập "0901112223" vào ô "Số điện thoại".
@@ -16076,10 +16656,10 @@
           <t>Đơn `IN_TRANSIT` đơn #4 của `SEED-DLV-02`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="n"/>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-045 — hai quầy dùng hai mẫu câu nhật ký khác nhau, lập trình gộp 1 chuỗi là defect. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 4. ⛔ Chưa assert cờ/`NTF` — `C-DLV-08` (a)(b) còn Partially.</t>
+          <t>Mục đích: cặp với TC-DLV-045 — hai quầy dùng hai mẫu câu nhật ký khác nhau, lập trình gộp 1 chuỗi là defect. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 4. ⛔ Chưa assert cờ/`NTF` — `C-DLV-08` (a)(b) còn Partially. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr">
@@ -16141,7 +16721,7 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn nút mở màn "Xác nhận đã giao".
+3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
 4. Chọn "Người nhận" ở field "Giao cho" mà chưa đính ảnh nào.
 5. Check trạng thái nút "Xác nhận đã giao hàng".
 6. Đính 1 ảnh JPG từ thư viện thiết bị.
@@ -16158,10 +16738,10 @@
           <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02`; 0 ảnh (chặn) và 1 ảnh (biên dưới hợp lệ) (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
-      <c r="L55" s="6" t="inlineStr"/>
+      <c r="L55" s="6" t="n"/>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp biên dưới 0⟷1 của ảnh bằng chứng lúc giao — ngược hẳn ảnh lúc lấy hàng (TC-DLV-042, 0 ảnh vẫn hợp lệ). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-02. Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1 vì TC đó sẽ đẩy đơn sang "Đã giao".</t>
+          <t>Mục đích: cặp biên dưới 0⟷1 của ảnh bằng chứng lúc giao — ngược hẳn ảnh lúc lấy hàng (TC-DLV-042, 0 ảnh vẫn hợp lệ). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-02. Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1 vì TC đó sẽ đẩy đơn sang "Đã giao". · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
         </is>
       </c>
       <c r="N55" s="6" t="inlineStr">
@@ -16239,7 +16819,7 @@
           <t>Đơn `DELIVERED` có 1 ảnh bằng chứng = `SEED-DLV-05` (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="n"/>
       <c r="M56" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-07 — ảnh gắn vào mốc nhật ký là bất biến. Liên quan cùng nhóm bất biến với TC-DLV-078 (log append-only).</t>
@@ -16321,7 +16901,7 @@
           <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L57" s="6" t="inlineStr"/>
+      <c r="L57" s="6" t="n"/>
       <c r="M57" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng âm cho TC-DLV-043 — popup phải là gate thật, không phải thông báo trang trí. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-06 (popup nêu rõ hệ quả không thể hoàn tác trước khi ghi mốc). Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1.</t>
@@ -16403,7 +16983,11 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
           <t>Mục đích: `BR08-02` ghi thứ tự NGƯỢC (lễ tân trước bảo vệ) và mô tả 1 danh sách 4 bước — assert theo PRD sẽ FAIL oan. · Căn cứ: `C-DLV-06` **Resolved 2026-09-17** — cấu trúc 4 tầng (màn "Xác nhận đã giao" → màn "Liên hệ người gửi" → modal "Chưa liên lạc được?" → màn "Xử lý đơn hàng") và thứ tự bảo-vệ-trước là oracle chính thức, khớp `AC-17.1.01`/`§8.8.2`. App lệch bản này ⇒ log bug và dẫn `C-DLV-06`, ⛔ không sửa TC theo `BR08-02`.</t>
@@ -16482,7 +17066,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03` (test_data_catalog §DLV — Tên người nhận thay)</t>
         </is>
       </c>
-      <c r="L59" s="6" t="inlineStr"/>
+      <c r="L59" s="6" t="n"/>
       <c r="M59" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với TC-DLV-044 — cùng loại đối tượng nhận nhưng khác MÀN VÀO nên "Uỷ quyền bởi" phải ra giá trị ngược lại; và ở màn này ⛔ KHÔNG prefill người uỷ quyền người gửi đã khai. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-03 + §8.7.1 BR07-05. Gộp bốn quan sát vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả bốn thuộc cùng một trạng thái tĩnh của màn.</t>
@@ -16566,7 +17150,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
-      <c r="L60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="n"/>
       <c r="M60" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đường thứ hai tới cùng kết cục của TC-DLV-045 — hai đường phải cùng đòi tên người trực quầy, SĐT và ảnh. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-04 + §8.12.4 mẫu câu 3. ⛔ Chưa assert điểm phân biệt với TC-DLV-045 (cờ "không liên lạc được" / `NTF-05` ⟷ `NTF-11`) — `C-DLV-08` (a)(b) còn Partially, QA vibe-check block "LỊCH SỬ" xong mới siết. ⛔ Không assert hạn giữ hàng 4h/24h — out of scope v1.1.</t>
@@ -16645,7 +17229,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `retry` (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
-      <c r="L61" s="6" t="inlineStr"/>
+      <c r="L61" s="6" t="n"/>
       <c r="M61" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp với TC-DLV-059 — hai chế độ dùng chung một form nên rất dễ bị lập trình cứng một bộ nhãn. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02.</t>
@@ -16724,7 +17308,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `return` (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
-      <c r="L62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="n"/>
       <c r="M62" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02 + vibe-check demo 2026-09-17 (`C-DLV-05` — khối "Hẹn trả hàng" do chính Carrier nhập tại màn "Xử lý đơn hàng").</t>
@@ -16804,7 +17388,7 @@
           <t>Ngày hẹn +7 ngày (hợp lệ) và +8 ngày (chặn) (test_data_catalog §DLV — Ngày hẹn cầm hàng về, biên)</t>
         </is>
       </c>
-      <c r="L63" s="6" t="inlineStr"/>
+      <c r="L63" s="6" t="n"/>
       <c r="M63" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên trên của trần 7 ngày — hai giá trị liền kề fail độc lập nên phải nằm trong cùng 1 TC để so được. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-04.</t>
@@ -16885,7 +17469,7 @@
           <t>Giờ hẹn 30 phút (hợp lệ), 29 phút (chặn), giờ đến ≤ giờ từ (chặn) (test_data_catalog §DLV — Giờ hẹn từ–đến, biên)</t>
         </is>
       </c>
-      <c r="L64" s="5" t="inlineStr"/>
+      <c r="L64" s="5" t="n"/>
       <c r="M64" s="5" t="inlineStr">
         <is>
           <t>Mục đích: gộp ba giá trị vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả ba cùng thuộc một trạng thái tĩnh của form, không mất khả năng bắt lỗi riêng vì Expected nêu đích danh từng khoảng. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-03.</t>
@@ -16965,7 +17549,7 @@
           <t>Đơn `RESCHEDULED` = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L65" s="6" t="inlineStr"/>
+      <c r="L65" s="6" t="n"/>
       <c r="M65" s="6" t="inlineStr">
         <is>
           <t>Mục đích: `AC-18.1.01` viết *"theo lịch hẹn, đơn quay lại IN_TRANSIT"* — đọc được thành hệ thống tự chuyển, chạy TC theo cách hiểu đó sẽ treo chờ đúng giờ. · Căn cứ: `C-DLV-05` **Resolved 2026-09-17** — chính người vận chuyển bấm, không có gate chặn theo giờ nên bấm sớm hơn lịch hẹn vẫn đi được; không giới hạn số lần hẹn. App chặn theo giờ ⇒ log bug và dẫn `C-DLV-05`.</t>
@@ -17045,7 +17629,7 @@
           <t>Đơn `RETURNING` = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="n"/>
       <c r="M66" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đây là bước tạo trạng thái `RETURNED` dùng chung cho TC-DLV-037/038/039, TC-DLV-064/065, TC-DLV-073 và cho `GIFT`/`ACT` — chạy xong mới chạy nhóm đó.</t>
@@ -17126,7 +17710,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `return` + ghi chú lý do từ chối (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
-      <c r="L67" s="6" t="inlineStr"/>
+      <c r="L67" s="6" t="n"/>
       <c r="M67" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-07 — từ chối nhận hàng đi chung nhánh return, phân biệt với nhánh không liên lạc được chỉ bằng ghi chú.</t>
@@ -17205,7 +17789,11 @@
           <t>Đơn `DELIVERED` qua nhánh giao tận tay = `SEED-DLV-05` (test_data_catalog §DLV — Đối tượng nhận)</t>
         </is>
       </c>
-      <c r="L68" s="5" t="inlineStr"/>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
           <t>Mục đích: 1 trong 6 mẫu câu nhật ký của `§8.12.4` — mỗi mẫu câu là 1 chuỗi verbatim riêng, sai chữ nào là defect chữ đó. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 1 + dòng "Mọi dòng" (thời điểm + cờ không liên lạc nếu có + dấu hiệu có ảnh). Assert nguyên văn kể cả dấu gạch ngang, ⛔ không paraphrase.</t>
@@ -17284,7 +17872,7 @@
           <t>Đơn `DELIVERED` qua nhánh uỷ quyền; tên 12 ký tự + SĐT hợp lệ (test_data_catalog §DLV — Tên người nhận thay)</t>
         </is>
       </c>
-      <c r="L69" s="6" t="inlineStr"/>
+      <c r="L69" s="6" t="n"/>
       <c r="M69" s="6" t="inlineStr">
         <is>
           <t>Mục đích: mẫu câu phức tạp nhất trong 6 mẫu — có 2 biến nội dung và 1 biến nguồn uỷ quyền, dễ ghép sai thứ tự. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 2. Assert nguyên văn kể cả dấu gạch ngang và dấu chấm giữa tên với số điện thoại.</t>
@@ -17363,7 +17951,7 @@
           <t>Đơn `DELIVERED` qua nhánh quầy lễ tân (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
-      <c r="L70" s="5" t="inlineStr"/>
+      <c r="L70" s="5" t="n"/>
       <c r="M70" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 3. Assert nguyên văn, ⛔ không paraphrase.</t>
@@ -17442,7 +18030,7 @@
           <t>Đơn `DELIVERED` qua nhánh quầy bảo vệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
-      <c r="L71" s="6" t="inlineStr"/>
+      <c r="L71" s="6" t="n"/>
       <c r="M71" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp với TC-DLV-070 — hai quầy là hai mẫu câu tách biệt trong bảng `§8.12.4`, gộp 1 chuỗi có tham số là defect. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 4.</t>
@@ -17520,7 +18108,7 @@
           <t>Đơn `RESCHEDULED` = `SEED-DLV-03`; lịch hẹn hợp lệ + nơi hẹn (test_data_catalog §DLV — Ngày hẹn, Giờ hẹn từ–đến, Nơi hẹn)</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr"/>
+      <c r="L72" s="5" t="n"/>
       <c r="M72" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 5 — ba biến ngày/giờ/nơi hẹn phải khớp đúng giá trị vừa nhập ở form.</t>
@@ -17599,7 +18187,7 @@
           <t>Đơn `RETURNED` = `SEED-DLV-03` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L73" s="6" t="inlineStr"/>
+      <c r="L73" s="6" t="n"/>
       <c r="M73" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 6 — mẫu câu duy nhất do người gửi kích hoạt, 5 mẫu còn lại do người vận chuyển.</t>
@@ -17679,7 +18267,7 @@
           <t>Đơn `RETURNED`, `CANCELLED`, `EXPIRED`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr"/>
+      <c r="L74" s="5" t="n"/>
       <c r="M74" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhóm ba trạng thái đóng phải cho CÙNG một nhãn — lệch giữa ba đơn mới là defect. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng (PRD chỉ mô tả cấp danh mục, không có microcopy riêng cho từng trạng thái).</t>
@@ -17759,7 +18347,7 @@
           <t>Đơn `RETURNED`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L75" s="6" t="inlineStr"/>
+      <c r="L75" s="6" t="n"/>
       <c r="M75" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với TC-DLV-037 — quyền đăng lại chỉ thuộc người gửi. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng.</t>
@@ -17839,7 +18427,7 @@
           <t>Đơn `RETURNED`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L76" s="5" t="inlineStr"/>
+      <c r="L76" s="5" t="n"/>
       <c r="M76" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng.</t>
@@ -17920,7 +18508,11 @@
           <t>1 ảnh JPG ≤5MB (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
         </is>
       </c>
-      <c r="L77" s="6" t="inlineStr"/>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 — `C-DLV-04` Resolved 2026-09-15 (ảnh lúc lấy hàng có tồn tại). ⚠ `RISK-DLV-11`: popup "Tôi đã lấy hàng" trên demo chưa thấy field ảnh — không thấy ô đính ảnh trên STG ⇒ log bug, ⛔ không sửa TC theo demo.</t>
@@ -17999,7 +18591,11 @@
           <t>0 ảnh — biên dưới hợp lệ (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
         </is>
       </c>
-      <c r="L78" s="5" t="inlineStr"/>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên dưới với TC-DLV-041 — ảnh lúc lấy hàng là tuỳ chọn, khác hẳn ảnh lúc giao hàng (bắt buộc ≥1, xem TC-DLV-047). · Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 *"tuỳ chọn nhưng được khuyến nghị mạnh"*.</t>
@@ -18081,7 +18677,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; ô tên người trực quầy rỗng (test_data_catalog §DLV — Tên người trực quầy, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L79" s="6" t="inlineStr"/>
+      <c r="L79" s="6" t="n"/>
       <c r="M79" s="6" t="inlineStr">
         <is>
           <t>Mục đích: chốt đường thoát khi không có người trực quầy — nhánh gửi quầy phải đóng lại chứ không được cho qua với tên rỗng. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-07 + `C-DLV-06` Resolved 2026-09-17 (2 ô quầy là ràng buộc thật, QA đã submit thử với ô trống và form không đi).</t>
@@ -18161,7 +18757,7 @@
           <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L80" s="5" t="inlineStr"/>
+      <c r="L80" s="5" t="n"/>
       <c r="M80" s="5" t="inlineStr">
         <is>
           <t>Mục đích: 1 trong 3 ô vai — cảnh báo phải hiện cho CẢ 3 bên, ẩn với 1 vai là defect. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
@@ -18241,7 +18837,7 @@
           <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L81" s="6" t="inlineStr"/>
+      <c r="L81" s="6" t="n"/>
       <c r="M81" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
@@ -18321,7 +18917,7 @@
           <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L82" s="5" t="inlineStr"/>
+      <c r="L82" s="5" t="n"/>
       <c r="M82" s="5" t="inlineStr">
         <is>
           <t>Mục đích: vai nhạy cảm nhất của bộ ba — chính người nhận là bên bị ghi "không liên lạc được" nên dễ bị ẩn cảnh báo nhất. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
@@ -18401,14 +18997,10 @@
           <t>Đơn gửi quầy chưa xác nhận, đã vượt mốc 4h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L83" s="6" t="inlineStr">
-        <is>
-          <t>🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-067 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
-        </is>
-      </c>
+      <c r="L83" s="6" t="n"/>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: `§8.13.1` liệt kê 15 loại thông báo và KHÔNG có loại "nhắc" nào — TC này chính là điểm đối chiếu danh mục với hành vi thật. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-06 + `C-DLV-07` Resolved 2026-09-17 (hệ thống CHỈ gửi remind). ⛔ Không assert giờ cụ thể của "cuối ngày" và không FAIL vì kênh push hay in-app — BA không đặc tả, giới hạn đã chấp nhận. ⛔ Không assert vế "sau 24h chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy.</t>
+          <t>Mục đích: `§8.13.1` liệt kê 15 loại thông báo và KHÔNG có loại "nhắc" nào — TC này chính là điểm đối chiếu danh mục với hành vi thật. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-06 + `C-DLV-07` Resolved 2026-09-17 (hệ thống CHỈ gửi remind). ⛔ Không assert giờ cụ thể của "cuối ngày" và không FAIL vì kênh push hay in-app — BA không đặc tả, giới hạn đã chấp nhận. ⛔ Không assert vế "sau 24h chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-067 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
         </is>
       </c>
       <c r="N83" s="6" t="inlineStr">
@@ -18486,14 +19078,10 @@
           <t>Đơn `RESCHEDULED` đã quá lịch hẹn 24h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L84" s="5" t="inlineStr">
-        <is>
-          <t>🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-057 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
-        </is>
-      </c>
+      <c r="L84" s="5" t="n"/>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: vế duy nhất còn assert được của `BR09-04` sau khi BA cắt scope — dễ bị bỏ sót vì cả câu rule đã bị coi là out of scope. · Căn cứ: `AC-23.2.01` câu cuối + `C-DLV-07` Resolved 2026-09-17 (chỉ gửi remind, đơn không đổi trạng thái/nhãn/cờ). ⛔ Không assert vế "chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy.</t>
+          <t>Mục đích: vế duy nhất còn assert được của `BR09-04` sau khi BA cắt scope — dễ bị bỏ sót vì cả câu rule đã bị coi là out of scope. · Căn cứ: `AC-23.2.01` câu cuối + `C-DLV-07` Resolved 2026-09-17 (chỉ gửi remind, đơn không đổi trạng thái/nhãn/cờ). ⛔ Không assert vế "chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-057 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
         </is>
       </c>
       <c r="N84" s="5" t="inlineStr">
@@ -18574,7 +19162,7 @@
           <t>5 ảnh JPG đúng 5MB, mạng 4G (test_data_catalog §DLV — Upload ảnh hiệu năng)</t>
         </is>
       </c>
-      <c r="L85" s="6" t="inlineStr"/>
+      <c r="L85" s="6" t="n"/>
       <c r="M85" s="6" t="inlineStr">
         <is>
           <t>Mục đích: `NFR-03` phát biểu theo p95 nên 1 lần đo không kết luận được — 10 lần đo là mẫu tối thiểu chạy tay được, cho phép đúng 1 lần vượt ngưỡng. · Căn cứ: `DOC-v1.1-01` §9 NFR-03. Chạy trên 10 đơn khác nhau vì ảnh đã ghi mốc thì không xoá để tải lại được (`BR07-07`, xem TC-DLV-048).</t>
@@ -18654,7 +19242,7 @@
           <t>Tên và SĐT người nhận thay đã ghi vào nhật ký (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
         </is>
       </c>
-      <c r="L86" s="5" t="inlineStr"/>
+      <c r="L86" s="5" t="n"/>
       <c r="M86" s="5" t="inlineStr">
         <is>
           <t>Mục đích: dữ liệu người nhận thay là dữ liệu cá nhân của bên thứ ba ngoài 3 vai của đơn — rò ra bề mặt khác là vi phạm quyền riêng tư, không chỉ lỗi hiển thị. · Căn cứ: `DOC-v1.1-01` §9 NFR-12. Phạm vi rà giới hạn ở các màn end-user; dự án không có bề mặt báo cáo hay Admin Portal trong scope v1.1.</t>
@@ -18734,7 +19322,11 @@
           <t>Số điện thoại liên hệ trên màn Theo dõi đơn (test_data_catalog §DLV — SĐT người nhận thay)</t>
         </is>
       </c>
-      <c r="L87" s="6" t="inlineStr"/>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp với TC-DLV-081 — hai instance icon copy nằm ở hai vùng khác nhau của cùng màn, hỏng độc lập. · Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04. Rule ghi 1,8 giây nhưng đây là hiệu ứng thị giác — chấp nhận dung sai quanh 2 giây, ⛔ không bấm giờ đòi đúng 1,8 giây. Instance ở màn Chi tiết tin thuộc `FEED`, không rà ở đây.</t>
@@ -18814,7 +19406,11 @@
           <t>Địa chỉ giao trên màn Theo dõi đơn (test_data_catalog §DLV — Nơi hẹn)</t>
         </is>
       </c>
-      <c r="L88" s="5" t="inlineStr"/>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04 — rule đặt icon copy cạnh CẢ địa chỉ giao và số điện thoại.</t>
@@ -18890,7 +19486,11 @@
           <t>1 tin NEED `POSTED` có khung giờ, loại hàng "Tài liệu" (test_data_catalog §FEED)</t>
         </is>
       </c>
-      <c r="L89" s="6" t="inlineStr"/>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
           <t>Mục đích: hết gap CTA — đổi từ "cố ý không assert vị trí CTA" (v1.0) sang assert cứng phủ định "card KHÔNG có CTA". · Căn cứ: `C-FEED-01(a)` Resolved 2026-09-16 — vibe-check demo xác nhận CTA chỉ có ở màn Chi tiết tin. Badge "Tin của bạn" verify riêng ở `TC-FEED-003/004` (thành phần có điều kiện). · Đã sửa tại chỗ 2026-09-16: thêm assert phủ định CTA vào Expected.</t>
@@ -18967,7 +19567,11 @@
           <t>1 tin NEED `POSTED` của tài khoản khác (test_data_catalog §FEED)</t>
         </is>
       </c>
-      <c r="L90" s="5" t="inlineStr"/>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
           <t>Mục đích: bổ sung assert tên người gửi hiển thị trước ghép (thành phần tồn tại) — phân biệt với `TC-FEED-010` (cùng cụm nhưng assert SĐT KHÔNG hiển thị). · Căn cứ: `C-FEED-04` Resolved 2026-09-17 — trước ghép chỉ ẩn SĐT, tên + địa chỉ đầy đủ hiện bình thường. ⛔ KHÔNG log bug nếu tên/địa chỉ hiện đầy đủ trước ghép — đó là hành vi ĐÚNG. · Đã sửa tại chỗ 2026-09-17: thêm "có đúng họ tên" + "điểm Lấy/Giao đầy đủ như data đã đăng" vào Expected.</t>
@@ -19043,7 +19647,11 @@
           <t>Tin NEED có điểm lấy/giao thuộc văn phòng đủ toạ độ (test_data_catalog §FEED)</t>
         </is>
       </c>
-      <c r="L91" s="6" t="inlineStr"/>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
           <t>Mục đích: ĐẢO kết luận v1.0 — trước assert "placeholder tĩnh, không có bản đồ" (`C-FEED-01(b)` Open), nay assert "CÓ bản đồ thật, ảnh tĩnh vẽ tuyến". · Căn cứ: `C-FEED-01(b)` + `C-FEED-02(c)` Resolved 2026-09-17. ⛔ Không test zoom/pan — ảnh tĩnh, không phải bản đồ tương tác. · Đã sửa tại chỗ 2026-09-17: đảo hoàn toàn Expected + Pre-condition (cần văn phòng có toạ độ hợp lệ, khác v1.0 không cần điều kiện gì), bỏ 2 bước test zoom/pan của v1.0.</t>
@@ -19119,7 +19727,11 @@
           <t>0 tin cộng đồng (test_data_catalog §FEED, biên)</t>
         </is>
       </c>
-      <c r="L92" s="5" t="inlineStr"/>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M92" s="5" t="inlineStr">
         <is>
           <t>Mục đích: hết `[GAP]` — text empty state đã chốt (`EMP-04`, home ở `ACT`) + xác nhận cấu trúc 1 danh sách (không phải 2 tab như nghi vấn cũ). · Căn cứ: `C-FEED-03` Resolved 2026-09-17 (1 danh sách, không tab/lọc) + `DOC-v1.1-01 §8.17.1 EMP-04` + `C-HOME-04` Resolved vòng 3 2026-09-17 (BA: *"giữ nguyên nhé"* ⇒ `EMP-04` giữ nguyên chữ PRD dù Bảng tin load toàn quốc). ℹ️ PRD không nói "gợi ý mở rộng khu vực" là nút hay chữ ⇒ assert **nội dung chữ**, ghi nhận dạng hiển thị thực tế, không FAIL vì hình thức. · Đã sửa tại chỗ 2026-09-17: thay "chỉ assert phần suy được" bằng assert cứng text + cấu trúc 1 danh sách; bổ sung assert câu gợi ý mở rộng khu vực sau khi `C-HOME-04` đóng.</t>
@@ -19277,7 +19889,11 @@
           <t>Tập đóng 4 tên quà chính thức, dùng đơn của `SEED-GIFT-01` (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L94" s="5" t="inlineStr"/>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
           <t>Mục đích: siết Expected từ "đúng 4 loại quà" (chỉ đếm số lượng, v1.0) sang assert đúng TÊN từng loại theo `BR14-01`. · Căn cứ: `DOC-v1.1-01 §8.14.1 BR14-01`. · Đã sửa theo delta v1.1 (2026-09-15): đổi Expected, giữ nguyên Steps/Pre-condition/Test Data so với v1.0.</t>
@@ -19356,7 +19972,11 @@
           <t>Đơn Hoàn thành của `SEED-GIFT-02`; loại quà "Bông hoa" (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L95" s="6" t="inlineStr"/>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
           <t>Mục đích: siết đúng chuỗi popup theo `BR14-02`/`AC-24.1.01` — thay chuỗi "Đã gửi lời cảm ơn!" (v1.0, dựa nguồn thua `US-D15` theo `C-GIFT-03` Resolved) bằng chuỗi chính thức + thêm assert nút về trang chủ. · Căn cứ: `DOC-v1.1-01 §8.14.1 BR14-02` · `§6.2 AC-24.1.01`. ⚠ TC này tiêu 1 đơn Hoàn thành (`SEED-GIFT-02`, không tái dùng được). · Đã sửa theo delta v1.1 (2026-09-15).</t>
@@ -19432,7 +20052,11 @@
           <t>Tài khoản B đã nhận 5 quà (3 Bông hoa + 2 Gấu bông) từ `SEED-GIFT-05` (test_data_catalog §GIFT v1.1, biên)</t>
         </is>
       </c>
-      <c r="L96" s="5" t="inlineStr"/>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M96" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cập nhật bộ số mẫu theo `AC-26.1.01` (5 quà, ≥2 loại) — thay bộ 2 quà/2 loại của v1.0; rule "loại count=0 không hiện card" (`KB-GIFT-03`) vẫn không có nguồn PRD, giữ nguyên như v1.0. · Căn cứ: `DOC-v1.1-01 §6.2 AC-26.1.01`. · Đã sửa theo delta v1.1 (2026-09-15): đổi Test Data từ 2 quà/2 loại sang 5 quà/2 loại.</t>
@@ -19508,7 +20132,11 @@
           <t>Tài khoản B đã nhận quà nhiều lần từ `SEED-GIFT-05` (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L97" s="6" t="inlineStr"/>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
           <t>Mục đích: hết `[GAP]` của `C-GIFT-03` vế (b) — Resolved: xác nhận CÓ danh sách lịch sử (v1.0 dự kiến FAIL vì chưa thấy trên app, khi đó chỉ ghi nhận); nay assert khẳng định, nâng Priority P3 → P2. · Căn cứ: `DOC-v1.1-01 §6.2 AC-26.1.01` "kèm lịch sử nhận quà". ⚠ Lệch app → log bug, ⛔ không hạ Expected theo hành vi app hiện tại. · Đã sửa theo delta v1.1 (2026-09-15): đổi Expected từ ghi-nhận sang assert cứng + nâng priority.</t>
@@ -19585,7 +20213,11 @@
           <t>Đơn `RETURNED` của `SEED-GIFT-08` (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L98" s="5" t="inlineStr"/>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
           <t>Mục đích: vế (a) — lỗi NHÌN THẤY ĐƯỢC của `AC-24.2.01`; đối chứng với vế (b) âm thầm ở `TC-GIFT-014`. · Căn cứ: `DOC-v1.1-01 §8.14 Pre-Conditions` · `§8.14.1 BR14-04` · `§6.2 AC-24.2.01`. ⛔ Không seed được đơn `RETURNED` (STG chưa build `FR09`) → verdict BLOCKED, ⛔ không PASS ("không thấy nút" không chứng minh gì nếu không có đơn RETURNED thật để thử). · Cross-ref: không nhân bản SC bộ đếm "Đơn đã giúp" sang `USR`/`HOME` — chỉ dùng ở `TC-GIFT-014`. ⚠️ Giả định đơn `RETURNED` nằm trong tab con "Đã hoàn thành" (cùng nhóm với `COMPLETED`, vì cả hai đều là trạng thái đóng) — chưa có nguồn PRD/BA xác nhận rõ tab hiển thị; nếu STG đặt đơn `RETURNED` ở tab khác thì sửa lại step 1, không phải lỗi TC.</t>
@@ -19663,7 +20295,11 @@
           <t>N đơn `COMPLETED` có sẵn (ví dụ PRD: 7 — `AC-26.1.01`) + 1 đơn `RETURNED` mới; **bắt buộc ghi số N ở bước 2 TRƯỚC khi đơn RETURNED phát sinh ở bước 3** (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L99" s="6" t="inlineStr"/>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
           <t>Mục đích: vế (b) ÂM THẦM của `AC-24.2.01`/`BR14-04` — sai lệch 1 đơn không nhìn ra được bằng mắt nếu không ghi số trước rồi so sau. · Căn cứ: `DOC-v1.1-01 §8.14.1 BR14-04` · `§6.2 AC-24.2.01`/`AC-26.1.01`. ⛔ Không seed được đơn `RETURNED` (STG chưa build `FR09`) → verdict BLOCKED, ⛔ không PASS. · Cross-ref: cùng bộ đếm với `USR` (2 chỉ số đóng góp) và `HOME`/`ACT` (card "Đóng góp của bạn") — ⛔ không nhân bản SC/TC sang các module đó.</t>
@@ -19740,7 +20376,7 @@
           <t>Tài khoản 0 đơn/0 quà (test_data_catalog §GIFT v1.1, biên)</t>
         </is>
       </c>
-      <c r="L100" s="5" t="inlineStr"/>
+      <c r="L100" s="5" t="n"/>
       <c r="M100" s="5" t="inlineStr">
         <is>
           <t>Mục đích: hết `[GAP]` của `C-ORD-06` phần GIFT (`EMP-08`) — Resolved bằng tài liệu phê duyệt, không còn dựa suy diễn `KB-GIFT-03` như v1.0. · Căn cứ: `DOC-v1.1-01 §8.17.1 EMP-08` · `§6.2 AC-26.2.01`. ⚠️ Cột CTA của `EMP-08` = "—" là assert thật theo `BR17-01` (tối đa 1 CTA) — không phải thiếu sót. · Đã sửa theo delta v1.1 (2026-09-15): đổi Expected từ "KHÔNG hiển thị loại quà nào" (v1.0, suy diễn) sang assert verbatim text + thống kê 0/0 + không CTA (theo tài liệu chính thức).</t>
@@ -19820,7 +20456,7 @@
           <t>Bộ giá trị assert-absent: sao/điểm/tier/chỉ số môi trường, dùng đơn của `SEED-GIFT-06` (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L101" s="6" t="inlineStr"/>
+      <c r="L101" s="6" t="n"/>
       <c r="M101" s="6" t="inlineStr">
         <is>
           <t>Mục đích: `BR14-03` v1.1 liệt kê đủ 4 bề mặt (màn Tặng quà · popup cảm ơn · "Quà đã nhận" · Trang cá nhân) và bổ sung "không chỉ số môi trường" — loại trừ nay là VĨNH VIỄN, không phải "out of scope v1.0" như trước. · Căn cứ: `DOC-v1.1-01 §8.14.1 BR14-03` · `§4 SCOPES`. ⚠️ Cross-ref: `SC-ACT-013` (★ leftover ở `ACT`) nay là defect xác nhận, không còn diễn giải "dấu vết phase sau". · Đã sửa theo delta v1.1 (2026-09-15): mở rộng phạm vi rà từ 3 bề mặt (v1.0: Theo dõi đơn/Tặng quà/Cá nhân) sang đúng 4 bề mặt theo `BR14-03` (thêm popup cảm ơn + "Quà đã nhận") — TC giờ tiêu 1 đơn Hoàn thành riêng (`SEED-GIFT-06`), khác v1.0 (dùng chung `SEED-GIFT-01`, không tiêu đơn).</t>
@@ -19900,7 +20536,7 @@
           <t>1 đơn Hoàn thành mà A đóng vai người vận chuyển = `SEED-HOME-03` (test_data_catalog §HOME — Số đơn đã giúp theo vai)</t>
         </is>
       </c>
-      <c r="L102" s="5" t="inlineStr"/>
+      <c r="L102" s="5" t="n"/>
       <c r="M102" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo BA trả lời `C-HOME-06` 2026-09-17: hero chỉ đếm đơn **Hoàn thành ở vai người vận chuyển**, bản v1.0 chưa có công thức nên chỉ assert "có hiện số". · Mục đích: đo bằng phép tăng 1 thay vì so với con số tuyệt đối — tài khoản dùng chung trên STG không có con số gốc tin cậy. · Căn cứ: `BR14-04` (đơn Đã trả người gửi KHÔNG tính — verify ở `TC-DLV-065`). ⛔ Không assert số người ở dòng cộng đồng: BA đề nghị bỏ qua định nghĩa "người tham gia".</t>
@@ -19979,7 +20615,7 @@
           <t>Số đơn cộng đồng trước và sau 1 đơn Hoàn thành (test_data_catalog §HOME — "[x] đơn · [y] người" cộng đồng)</t>
         </is>
       </c>
-      <c r="L103" s="6" t="inlineStr"/>
+      <c r="L103" s="6" t="n"/>
       <c r="M103" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đồng thời chốt hai vế của `C-HOME-06(b)(c)` — x đếm **toàn hệ thống** (đơn do tài khoản khác hoàn thành vẫn cộng vào số A nhìn thấy) và cập nhật **realtime** (tăng ngay lần mở lại, không chờ chu kỳ). · Căn cứ: BA trả lời `C-HOME-06(b)(c)` 2026-09-17. ⛔ Không assert số người ở dòng này — định nghĩa "người tham gia" BA đề nghị bỏ qua.</t>
@@ -20059,12 +20695,12 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>🚫 Deferred — cần công cụ load-test, ⛔ không test tay được (QC GiangDC2, 2026-09-17)</t>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: giữ traceability cho `NFR01` thay vì bỏ hẳn SC — `test_data_catalog §HOME` ghi rõ *"không viết TC manual assert số đo"*, nên TC tồn tại để `execute-maintain` biết cần defer cho automation/load-test. · Căn cứ: `DOC-v1.1-01` §9 NFR01. ⛔ Loại khỏi mẫu số pass-rate cho tới khi có môi trường load-test.</t>
+          <t>Mục đích: giữ traceability cho `NFR01` thay vì bỏ hẳn SC — `test_data_catalog §HOME` ghi rõ *"không viết TC manual assert số đo"*, nên TC tồn tại để `execute-maintain` biết cần defer cho automation/load-test. · Căn cứ: `DOC-v1.1-01` §9 NFR01. ⛔ Loại khỏi mẫu số pass-rate cho tới khi có môi trường load-test. · 🚫 Deferred — cần công cụ load-test, ⛔ không test tay được (QC GiangDC2, 2026-09-17)</t>
         </is>
       </c>
       <c r="N104" s="5" t="inlineStr">
@@ -20138,7 +20774,11 @@
           <t>≥6 tin NEED `POSTED` hợp lệ = `SEED-HOME-02` (test_data_catalog §HOME — Số tin NEED section "Tin mới")</t>
         </is>
       </c>
-      <c r="L105" s="6" t="inlineStr"/>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-HOME-03` Resolved 2026-09-15 (`AC-11.1.01`): đổi từ *"hiển thị nhiều nhất 5 tin"* của bản v1.0 sang **đúng 5 tin** — PRD v1.1 thắng cả `DOC-v1.0-02` (1 tin) lẫn BRD `US-D06`. · Mục đích: app từng hiện đúng 1 tin; "nhiều nhất 5" khiến 1 tin cũng PASS, đó là lý do phải siết thành số chính xác. · Căn cứ: 3 lớp loại trừ verify riêng ở `TC-HOME-030` — TC này chỉ chốt số lượng.</t>
@@ -20217,7 +20857,11 @@
           <t>&gt;5 tin NEED hợp lệ = `SEED-HOME-02` (test_data_catalog §HOME — Tổng tin hợp lệ, biên trên)</t>
         </is>
       </c>
-      <c r="L106" s="5" t="inlineStr"/>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M106" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `AC-11.1.01` 2026-09-17: bổ sung điều kiện hiện nút (**&gt;5 tin hợp lệ**) mà bản v1.0 cố ý bỏ trống vì khi đó không có nguồn tài liệu (`RISK-HOME-03`). · Mục đích: cặp biên với `TC-HOME-025` — chiều dương của cùng ngưỡng 5.</t>
@@ -20296,7 +20940,11 @@
           <t>Đúng 5 tin NEED hợp lệ toàn hệ thống — biên dưới (test_data_catalog §HOME — Tổng tin hợp lệ, biên)</t>
         </is>
       </c>
-      <c r="L107" s="6" t="inlineStr"/>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M107" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên âm với `TC-HOME-021` — ngưỡng 5 phải phân định được hai chiều, chỉ chạy chiều dương thì nút luôn-hiện cũng PASS. · Căn cứ: `AC-11.1.01`. ⚠️ **Không dựng được trên STG dùng chung**: `C-HOME-04` Resolved 2026-09-17 chốt tin load **toàn quốc** nên phải khống chế dữ liệu toàn hệ thống, không chỉ dữ liệu tài khoản test. Không có môi trường riêng ⇒ ghi **`Blocked` kèm lý do**, ⛔ KHÔNG đánh PASS cho xong.</t>
@@ -20374,7 +21022,11 @@
           <t>Tài khoản "sạch" + 0 tin hợp lệ toàn hệ thống (test_data_catalog §HOME — Tài khoản "sạch" cho empty state)</t>
         </is>
       </c>
-      <c r="L108" s="5" t="inlineStr"/>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M108" s="5" t="inlineStr">
         <is>
           <t>Mục đích: kết quả phản trực giác — `C-HOME-04` chốt tin load **toàn quốc** nên chữ *"trong khu vực của bạn"* KHÔNG còn khớp hành vi, nhưng BA trả lời vòng 3 *"giữ nguyên nhé"* ⇒ **assert cứng chuỗi PRD**, ⛔ không sửa Expected theo logic. · Căn cứ: `EMP-01` + `AC-11.2.01`. App đổi chữ ⇒ FAIL và dẫn `C-HOME-04`. ⚠️ Cùng ràng buộc môi trường với `TC-HOME-025`; không dựng được ⇒ ghi `Blocked` kèm lý do.</t>
@@ -20451,7 +21103,11 @@
           <t>Tài khoản 0 đơn đang chạy = `SEED-HOME-01` (test_data_catalog §HOME — Tài khoản "sạch")</t>
         </is>
       </c>
-      <c r="L109" s="6" t="inlineStr"/>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
           <t>Mục đích: thay thế `TC-HOME-010` đã gỡ — TC cũ assert **NGƯỢC HẲN** (*"Trang chủ KHÔNG có section Đơn của tôi"*). Người chạy quen bản v1.0 rất dễ cho FAIL nhầm khi thấy section hiện ra. · Căn cứ: `C-HOME-05` **Resolved 2026-09-17** — BA chốt HIỆN `EMP-02`, không ẩn; ảnh demo `HOME_03` (không có section) nay là **lệch demo ↔ rule**, ⛔ không còn là oracle. Section bị ẩn ⇒ FAIL và log bug.</t>
@@ -20529,7 +21185,11 @@
           <t>Tài khoản "sạch" + hệ thống 0 đơn Hoàn thành (test_data_catalog §HOME — Tài khoản "sạch")</t>
         </is>
       </c>
-      <c r="L110" s="5" t="inlineStr"/>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M110" s="5" t="inlineStr">
         <is>
           <t>Mục đích: `EMP-03` là empty state duy nhất của Trang chủ **KHÔNG có CTA** — bất đối xứng với `EMP-01` và `EMP-02` (đều có 1 CTA); app hiện nút ở đây là **sai spec**. · Căn cứ: `AC-26.2.01` + `EMP-03` + `BR17-01` (*"tối đa một CTA"*).</t>
@@ -20609,7 +21269,7 @@
           <t>Tài khoản chỉ làm người gửi, có ≥1 đơn Hoàn thành (test_data_catalog §HOME — Số đơn đã giúp theo vai, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L111" s="6" t="inlineStr"/>
+      <c r="L111" s="6" t="n"/>
       <c r="M111" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng âm cho `TC-HOME-008` — cùng 1 đơn Hoàn thành nhưng đếm cho vai người vận chuyển chứ không cho vai người gửi; lỗi hay gặp là đếm mọi đơn Hoàn thành mà tài khoản có liên quan. · Căn cứ: BA trả lời `C-HOME-06(a)` 2026-09-17 + `AC-26.2.01`.</t>
@@ -20689,7 +21349,7 @@
           <t>1 tin đã ghép + 1 tin hết hạn + 1 tin của chính tài khoản quan sát = `SEED-HOME-02` (test_data_catalog §HOME — Số tin NEED section "Tin mới")</t>
         </is>
       </c>
-      <c r="L112" s="5" t="inlineStr"/>
+      <c r="L112" s="5" t="n"/>
       <c r="M112" s="5" t="inlineStr">
         <is>
           <t>Mục đích: fail độc lập với `TC-HOME-019` — đếm đúng 5 tin không đảm bảo lọc đúng; app có thể trả đủ 5 nhưng lẫn tin đã ghép. · Căn cứ: `AC-11.1.01` — 3 lớp loại trừ là phần PRD v1.1 bổ sung, không nguồn v1.0 nào có. ✅ TC này **dựng được trên STG dùng chung** vì chỉ cần chứng minh 3 tin CỤ THỂ vắng mặt, ⛔ không cần khống chế toàn bộ danh sách như `TC-HOME-025`/`026`.</t>
@@ -20766,7 +21426,7 @@
           <t>Đủ 15 sự kiện, kiểm cả in-app và push (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L113" s="6" t="inlineStr"/>
+      <c r="L113" s="6" t="n"/>
       <c r="M113" s="6" t="inlineStr">
         <is>
           <t>Mục đích: mở rộng phạm vi P1 từ 9/9 (v1.0) sang **đủ 15/15 sự kiện** — bỏ sót 1 trong 6 sự kiện mới là bỏ sót đúng chỗ nhạy cảm nhất (uỷ quyền/quầy/không liên lạc được). · Căn cứ: `DOC-v1.1-01 §8.13.1` (đối chiếu toàn bộ 15 dòng "Nội dung (mẫu)"). Có thông báo chứa số ⇒ FAIL và log bug mức cao (rò rỉ dữ liệu cá nhân).</t>
@@ -20842,7 +21502,7 @@
           <t>Đơn `COMPLETED` đủ 3 vai của `SEED-DLV-01` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L114" s="5" t="inlineStr"/>
+      <c r="L114" s="5" t="n"/>
       <c r="M114" s="5" t="inlineStr">
         <is>
           <t>Mục đích: PRD chính thức `DOC-v1.1-01` chốt dứt điểm text `NTF-06`, thay bản BRD "nguồn thắng có điều kiện" của v1.0 — hết rủi ro phải dẫn `C-NTF-01` nếu app lệch, vì `C-NTF-01` đã Resolved 2026-09-15. · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-06`. · Đã sửa theo delta v1.1 (2026-09-15): bỏ hedge "App hiện bản PRD ⇒ FAIL và dẫn C-NTF-01" ở Notes v1.0, nay assert dứt khoát không còn đường thoát CL.</t>
@@ -20918,7 +21578,7 @@
           <t>Đơn trọn vòng đời chính + 1 lượt qua mỗi nhánh phụ FR08/FR09, đối chiếu 15 loại chính thức (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L115" s="6" t="inlineStr"/>
+      <c r="L115" s="6" t="n"/>
       <c r="M115" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đảo vai trò từ `[GAP]` ghi-nhận (v1.0) sang **assert đủ-danh-mục** — thiếu 1 trong 15 loại là bằng chứng cụ thể để log finding, không còn coi "có SC chạy qua" là đủ coverage. · Căn cứ: `DOC-v1.1-01 §8.13.1` bảng 15 dòng, `C-NTF-01` Resolved 2026-09-15. Tiền đề tốn thời gian nhất module — gộp chạy chung lô vibe-test `DLV` (`RISK-NTF-05`). · Đã sửa theo delta v1.1 (2026-09-15): bỏ 2 assert-absent cũ (đánh giá 5 sao, CO₂) — nay gộp vào phép đối chiếu đủ-danh-mục (loại đó không có trong 15 loại chính thức nên tự động không xuất hiện nếu quan sát đúng đủ 15/15).</t>
@@ -20994,7 +21654,7 @@
           <t>Đơn giao qua uỷ quyền, tái dùng từ luồng `SC-DLV-038` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L116" s="5" t="inlineStr"/>
+      <c r="L116" s="5" t="n"/>
       <c r="M116" s="5" t="inlineStr">
         <is>
           <t>Mục đích: SC hoàn toàn mới — chỉ test đúng bắn thông báo/người nhận/nội dung, KHÔNG lặp nghiệp vụ giao nhận (đã có SC bên `DLV` delta v1.1). · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-10`. Tiền đề phụ thuộc vibe-test nhánh FR08 bên `DLV` (`RISK-NTF-07`), chưa có TC-DLV-v1.1 tại thời điểm generate — cập nhật tham chiếu khi có.</t>
@@ -21070,7 +21730,7 @@
           <t>Đơn giao qua quầy, tái dùng từ luồng `SC-DLV-039` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L117" s="6" t="inlineStr"/>
+      <c r="L117" s="6" t="n"/>
       <c r="M117" s="6" t="inlineStr">
         <is>
           <t>Mục đích: SC hoàn toàn mới, chỉ test bắn thông báo/người nhận/nội dung. · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-11`. Tiền đề phụ thuộc vibe-test nhánh FR08 bên `DLV`, chưa có TC-DLV-v1.1 tại thời điểm generate.</t>
@@ -21145,7 +21805,7 @@
           <t>Đơn ở nhánh không liên lạc được, tái dùng từ luồng `SC-DLV-044` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L118" s="5" t="inlineStr"/>
+      <c r="L118" s="5" t="n"/>
       <c r="M118" s="5" t="inlineStr">
         <is>
           <t>Mục đích: SC hoàn toàn mới; chỉ 1 vai (người gửi) nhận theo đúng danh mục `§8.13.1` dòng `NTF-12`, khác `NTF-10`/`11` có 2 vai. · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-12`. Tiền đề phụ thuộc vibe-test nhánh FR08 bên `DLV`, chưa có TC-DLV-v1.1 tại thời điểm generate.</t>
@@ -21221,7 +21881,7 @@
           <t>Đơn `RESCHEDULED`, tái dùng từ luồng `SC-DLV-049` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L119" s="6" t="inlineStr"/>
+      <c r="L119" s="6" t="n"/>
       <c r="M119" s="6" t="inlineStr">
         <is>
           <t>Mục đích: SC hoàn toàn mới, chỉ test đúng biến `{ngày · giờ}`/`{nơi hẹn}` được thay đúng giá trị runtime, không lặp validate field lịch hẹn (đã có ở `SC-DLV-049`). · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-13`. Tiền đề phụ thuộc vibe-test nhánh FR09 bên `DLV`, chưa có TC-DLV-v1.1 tại thời điểm generate.</t>
@@ -21297,7 +21957,7 @@
           <t>Đơn `RETURNING`, tái dùng từ luồng `SC-DLV-049` chế độ `return` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L120" s="5" t="inlineStr"/>
+      <c r="L120" s="5" t="n"/>
       <c r="M120" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với `TC-NTF-020` — cùng field lịch hẹn nhưng khác chế độ (`return` thay `retry`), nội dung/đích thông báo khác hẳn (`NTF-14` thay `NTF-13`). · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-14`. Tiền đề phụ thuộc vibe-test nhánh FR09 bên `DLV`, chưa có TC-DLV-v1.1 tại thời điểm generate.</t>
@@ -21374,7 +22034,7 @@
           <t>Đơn `RETURNED`, tái dùng từ `TC-NTF-021` (test_data_catalog §NTF v1.1)</t>
         </is>
       </c>
-      <c r="L121" s="6" t="inlineStr"/>
+      <c r="L121" s="6" t="n"/>
       <c r="M121" s="6" t="inlineStr">
         <is>
           <t>Mục đích: SC cuối cùng của nhánh hoàn hàng — đóng đúng vòng đời `RETURNING → RETURNED`, cross-ref `SC-GIFT-013/014` (module `GIFT`) cùng phụ thuộc trạng thái `RETURNED` này. · Căn cứ: `DOC-v1.1-01 §8.13.1` dòng `NTF-15`.</t>
@@ -21454,7 +22114,11 @@
           <t>3 chip đã chọn + 0 ảnh — nhánh chặn (test_data_catalog §ORD — Ảnh món hàng, biên 0)</t>
         </is>
       </c>
-      <c r="L122" s="5" t="inlineStr"/>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
           <t>Mục đích: **P1 chặn luồng chính** — `BR01-01` biến ảnh từ *không rõ* thành **bắt buộc**, đây là oracle của cả cụm ảnh. · Căn cứ: `BR01-01` *"Thiếu ảnh thì chặn sang bước 2"* + `AC-03.1.02`. Tầng UI đã build (`DOC-v1.1-03`: dấu `*` + "0/5" + helper) nên TC này verify **hành vi chặn thật**; app cho qua ⇒ FAIL và log bug. ⚠ Ảnh demo cho thấy nút "Tiếp theo" vẫn cam khi chưa đủ điều kiện — nghi giới hạn ảnh tĩnh, ⛔ không log bug dựa trên mỗi ảnh đó.</t>
@@ -21534,7 +22198,11 @@
           <t>Email `stag_anhdc4@fpt.com` — có trên HRIS, đang làm việc = `SEED-ORD-02` ① (test_data_catalog §ORD — Email công ty người nhận)</t>
         </is>
       </c>
-      <c r="L123" s="6" t="inlineStr"/>
+      <c r="L123" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M123" s="6" t="inlineStr">
         <is>
           <t>Mục đích: **P1** — đây là tích hợp hệ thống ngoài được nêu tên lần đầu ở v1.1, không có nó thì cả cụm `TC-ORD-074..077` vô nghĩa. · Căn cứ: `BR01-09` + `AC-04.1.01` + BA `C-ORD-13` Resolved 2026-09-17. Ô bị khoá không sửa được ⇒ FAIL — `BR01-09` nói rõ *"vẫn sửa được"*.</t>
@@ -21611,7 +22279,11 @@
           <t>8 giá trị Loại hàng, mặc định "Tài liệu" (test_data_catalog §ORD — Loại hàng)</t>
         </is>
       </c>
-      <c r="L124" s="5" t="inlineStr"/>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo BA trả lời `C-ORD-09` 2026-09-16: assert nhãn **"Tài liệu"** theo PRD. Ràng buộc cũ của v1.0 *"⛔ không dùng nhãn Tài liệu, ghi theo app STG"* **HẾT HIỆU LỰC**. · Mục đích: kết quả phản trực giác — app STG hiện "Giấy tờ, hồ sơ", người chạy quen v1.0 sẽ cho PASS nhầm. App hiện nhãn khác ⇒ **FAIL và log bug**, ⛔ không sửa TC theo app. · `Thuốc/Y tế` giữ trong danh mục (`C-ORD-04` Resolved 2026-09-17), ⛔ không assert banner hàng cấm — v1.1 không có.</t>
@@ -21689,7 +22361,11 @@
           <t>1 ảnh JPG nhỏ của `SEED-ORD-01` (test_data_catalog §ORD — Ảnh món hàng)</t>
         </is>
       </c>
-      <c r="L125" s="6" t="inlineStr"/>
+      <c r="L125" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M125" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `BR01-01` 2026-09-17: bổ sung assert bộ đếm `n/5` — bản v1.0 chưa có vì khi đó không rõ ảnh có bắt buộc không. · Căn cứ: dấu bắt buộc và hành vi chặn verify ở `TC-ORD-013`/`TC-ORD-063`.</t>
@@ -21765,7 +22441,11 @@
           <t>Trạng thái 0 ảnh — biên dưới (test_data_catalog §ORD — Ảnh món hàng)</t>
         </is>
       </c>
-      <c r="L126" s="5" t="inlineStr"/>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `BR01-01`/`BR18-02` 2026-09-17: v1.0 TC này kiểm ảnh quá dung lượng/sai định dạng, nay chuyển sang chốt **dấu hiệu bắt buộc ở tầng UI**; 2 nhánh từ chối file chuyển sang `TC-ORD-066/067`. · Mục đích: tách tầng UI (có dấu `*`) khỏi tầng hành vi (chặn thật ở `TC-ORD-063`) — app có thể vẽ dấu `*` mà không chặn. · Căn cứ: ảnh `DOC-v1.1-03` xác nhận tầng UI đã build (thu hẹp `RISK-ORD-09`).</t>
@@ -21843,7 +22523,11 @@
           <t>Địa chỉ mặc định của hồ sơ = `SEED-ORD-03` (test_data_catalog §ORD — Địa chỉ lấy hàng)</t>
         </is>
       </c>
-      <c r="L127" s="6" t="inlineStr"/>
+      <c r="L127" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-10` Resolved 2026-09-15: prefill là **hành vi đặc tả**, không còn là "chưa rõ bug hay tài khoản chưa cấu hình" như v1.0. · Mục đích: ô trống ⇒ **BUG**, ⛔ không diễn giải là tài khoản chưa cấu hình. · Căn cứ: `AC-30.1.01` + `§8.1.4`. ⛔ Không chạy trên tài khoản không rõ trạng thái hồ sơ.</t>
@@ -21921,7 +22605,11 @@
           <t>Ngày liền trước ngày hiện tại — tính tương đối (test_data_catalog §ORD — Khoảng ngày)</t>
         </is>
       </c>
-      <c r="L128" s="5" t="inlineStr"/>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-15(a)` Resolved 2026-09-17: tách riêng nhánh ngày quá khứ khỏi phần mặc định mà v1.0 gộp chung, để mỗi nhánh có 1 điểm kiểm chứng ở step cuối. · Căn cứ: `BR01-04` + `AC-06.1.02`. ⛔ Không hardcode ngày — tính tương đối so với hiện tại.</t>
@@ -21999,7 +22687,11 @@
           <t>Từ = hiện tại +3 ngày, Đến = hiện tại +1 ngày (test_data_catalog §ORD — Khoảng ngày, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L129" s="6" t="inlineStr"/>
+      <c r="L129" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M129" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `Project_rule §Custom Rules §10.4` 2026-09-17: thu hẹp phạm vi còn **đúng 1 điểm kiểm chứng** ở step cuối — bản v1.0 gộp chung với nhánh ngày quá khứ (nay tách sang `TC-ORD-030`). Expected không đảo chiều. · Căn cứ: `BR01-04` *"Đến ≥ Từ"* + `AC-06.1.02`. ⛔ Không hardcode ngày.</t>
@@ -22078,7 +22770,11 @@
           <t>4 buổi mong muốn (test_data_catalog §ORD — Buổi mong muốn)</t>
         </is>
       </c>
-      <c r="L130" s="5" t="inlineStr"/>
+      <c r="L130" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `Project_rule §Custom Rules §10.4` 2026-09-17: tách vế **giá trị mặc định** ra `TC-ORD-058` để mỗi TC chỉ còn 1 điểm kiểm chứng ở step cuối; bản v1.0 gộp cả hai. Expected không đảo chiều. · Căn cứ: `BR01-04` + `AC-06.2.01` — quan hệ loại trừ giữa "Giờ nào cũng được" và 3 buổi cụ thể.</t>
@@ -22157,7 +22853,11 @@
           <t>Dữ liệu hợp lệ đủ 3 bước + 1 ảnh của `SEED-ORD-01` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L131" s="6" t="inlineStr"/>
+      <c r="L131" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-05` Resolved 2026-09-15: chốt **KHÔNG có mã đơn**, v1.0 còn để ngỏ. · Mục đích: kết quả phản trực giác — người chạy quen app thương mại sẽ đi tìm mã đơn rồi báo thiếu. · Căn cứ: `AC-07.1.01` + `§8.1.3` bước 8. Vế *"tin xuất hiện ngay ở Tin mới và Đơn của tôi"* thuộc `HOME`/`ACT`, ⛔ không nhân bản ở đây.</t>
@@ -22235,7 +22935,11 @@
           <t>1 tin OFFER của tài khoản khác (test_data_catalog §ORD — Tin OFFER của tài khoản khác)</t>
         </is>
       </c>
-      <c r="L132" s="5" t="inlineStr"/>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `AC-20.1.01`/`AC-20.1.02` 2026-09-17: siết Steps rà **cả hai tab con** + dùng ô tìm kiếm, bản v1.0 chỉ rà danh sách. · Mục đích: đây là kiểm soát truy cập — PASS giả làm cả một lớp bảo vệ chưa từng được kiểm. · Căn cứ: `BR02-01`. ⛔ Vế *"mở link trực tiếp"* của `AC-20.1.02` **không có đường thử trên mobile** (không có URL) — ⛔ KHÔNG PASS chỉ vì không thử được; ghi nợ ở header §0.4.</t>
@@ -22316,7 +23020,11 @@
           <t>1 tin `POSTED` của chính mình = `SEED-ORD-04` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L133" s="6" t="inlineStr"/>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M133" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-16` Resolved 2026-09-17: bổ sung assert **giữ nguyên trạng thái** sau khi cập nhật. · Căn cứ: `BR05-01`/`BR05-02` + `AC-08.1.01`. Nhánh "Huỷ chỉnh sửa" tách sang `TC-ORD-060`.</t>
@@ -22394,7 +23102,11 @@
           <t>Tin đã chuyển `MATCHED` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L134" s="5" t="inlineStr"/>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-16` Resolved 2026-09-17: **Expected giữ nguyên bản v1.0** (nút "Chỉnh sửa" không hiển thị); phần thêm ở SC MODIFIED là 2 vế backend nên chỉ ghi giới hạn phạm vi, không đổi assert. · Căn cứ: `BR05-01` + `AC-08.1.02`. ⛔ Vế *"request sửa bị từ chối"* và *"không ghi mốc vào nhật ký"* là **backend**, không verify được qua UI — ghi nợ ở header §0.4, ⛔ không viết Expected cho phần đó.</t>
@@ -22475,7 +23187,11 @@
           <t>Tin `POSTED` quá "Đến ngày", chưa ai ghép = `SEED-ORD-05` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L135" s="6" t="inlineStr"/>
+      <c r="L135" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
           <t>✅ **Gỡ phụ thuộc dev 2026-09-18 (QC chốt):** tin cũ trên STG đã tự quá hạn ⇒ dùng luôn, ⛔ không cần nhờ lùi "Đến ngày". Xem `SEED-ORD-05` §0.5 cho 3 lối theo thứ tự ưu tiên. ⚠️ Dùng tin cũ thì chỉ quan sát **trạng thái kết quả**, không thấy lúc job chuyển trạng thái — vẫn đủ cho Expected. · Đã sửa theo `C-ORD-15(c)` Resolved 2026-09-17: bổ sung điều kiện **job chạy cuối ngày** vào setup — v1.0 chỉ ghi "sau khi hết ngày cuối", khiến người chạy kiểm quá sớm rồi báo lỗi sai. · Căn cứ: `BR05-03` + `AC-09.1.01`. Nhánh đối chứng (tin đã `MATCHED` thì KHÔNG hết hạn) tách sang `TC-ORD-061`.</t>
@@ -22555,7 +23271,11 @@
           <t>Dữ liệu nhập dở ở bước 2 (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L136" s="5" t="inlineStr"/>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-08` Resolved 2026-09-15: assert **verbatim** chuỗi popup, v1.0 chỉ assert có popup. · Căn cứ: `AC-01.2.01`. Nhánh chọn thoát tách sang `TC-ORD-062`.</t>
@@ -22633,7 +23353,11 @@
           <t>Khoảng đúng 7 ngày — biên trên hợp lệ (test_data_catalog §ORD — Khoảng ngày, biên)</t>
         </is>
       </c>
-      <c r="L137" s="6" t="inlineStr"/>
+      <c r="L137" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên với `TC-ORD-057` — chỉ chạy chiều chặn thì rule "chặn mọi khoảng" cũng PASS. · Căn cứ: `C-ORD-15(a)` Resolved 2026-09-17 — BA chốt *"Từ X → Đến tối đa X+7"*, tức 7 ngày là **hợp lệ**.</t>
@@ -22711,7 +23435,11 @@
           <t>Khoảng 8 ngày — vượt biên (test_data_catalog §ORD — Khoảng ngày, biên)</t>
         </is>
       </c>
-      <c r="L138" s="5" t="inlineStr"/>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `BR01-04` + `C-ORD-15(a)`. ⛔ Không hardcode ngày.</t>
@@ -22787,7 +23515,11 @@
           <t>Giá trị mặc định của field buổi (test_data_catalog §ORD — Buổi mong muốn)</t>
         </is>
       </c>
-      <c r="L139" s="6" t="inlineStr"/>
+      <c r="L139" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M139" s="6" t="inlineStr">
         <is>
           <t>Mục đích: v1.0 cố ý **KHÔNG** assert mặc định vì 3 nguồn cho 3 giá trị khác nhau; PRD v1.1 `§8.1.4` nay gọi tên rõ nên assert được. · Căn cứ: `§8.1.4` — nguồn mới nhất thắng các nguồn v1.0. App hiện buổi khác ⇒ FAIL và log bug.</t>
@@ -22866,7 +23598,11 @@
           <t>Buổi đã qua trong ngày hiện tại (test_data_catalog §ORD — Buổi mong muốn)</t>
         </is>
       </c>
-      <c r="L140" s="5" t="inlineStr"/>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
           <t>Mục đích: neo vào `C-ORD-15(b)` Resolved 2026-09-17 — BA chốt *"app CHẶN chọn buổi đã qua trong ngày"*, rule này **không có trong PRD**, chưa SC nào phủ trước lượt này. · Căn cứ: câu trả lời BA là nguồn chốt duy nhất; app cho chọn ⇒ FAIL và dẫn `C-ORD-15`. ⛔ Không hardcode giờ — điều kiện thời điểm chạy ghi ở Pre-condition.</t>
@@ -22946,7 +23682,11 @@
           <t>1 tin `POSTED` của chính mình = `SEED-ORD-04` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L141" s="6" t="inlineStr"/>
+      <c r="L141" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M141" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng âm cho `TC-ORD-046` — lưu được không suy ra huỷ được; lỗi hay gặp là "Huỷ" vẫn ghi đè dữ liệu. · Căn cứ: `VAL-05` + `AC-08.1.01`.</t>
@@ -23025,7 +23765,11 @@
           <t>Tin `MATCHED` quá "Đến ngày" = `SEED-ORD-05` (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L142" s="5" t="inlineStr"/>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
           <t>✅ **Gỡ phụ thuộc dev 2026-09-18 (QC chốt):** dùng tin đã ghép cũ đã quá hạn trên STG (`SEED-ORD-05` §0.5). · Mục đích: đối chứng âm cho `TC-ORD-048` — vế *"vẫn POSTED"* của `BR05-03` là điều kiện **v1.0 chưa nêu**; dev hay chỉ kiểm mỗi ngày hết hạn rồi đóng luôn cả đơn đã ghép. · Căn cứ: `BR05-03`.</t>
@@ -23105,7 +23849,11 @@
           <t>Dữ liệu nhập dở đã bị bỏ (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L143" s="6" t="inlineStr"/>
+      <c r="L143" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M143" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với `TC-ORD-053` — cùng một popup nhưng hai lựa chọn cho hai hệ quả ngược nhau; step 4 chốt thêm vế **⛔ không có DRAFT** mà `AC-01.2.01` nêu. · Căn cứ: `AC-01.2.01`.</t>
@@ -23186,7 +23934,11 @@
           <t>3 chip Trọng lượng, trạng thái chưa chọn (test_data_catalog §ORD — Trọng lượng)</t>
         </is>
       </c>
-      <c r="L144" s="5" t="inlineStr"/>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
           <t>🔑 Áp `C-ORD-18` Resolved 2026-09-17 — BA *"lấy UI làm chuẩn"*: assert cứng nhãn **"Trọng lượng"** và nhãn phụ Nhẹ/Trung bình/Nặng. **PRD `§8.1.4` ghi "Khối lượng" + kiểu Dropdown đã HẾT HIỆU LỰC** — app hiện "Khối lượng" hoặc dropdown ⇒ **defect UI**, ⛔ không phải TC sai. · Mục đích: rào *"ghi nhận nhãn, không FAIL vì tên nhãn"* của bản phân tích trước đã gỡ.</t>
@@ -23266,7 +24018,11 @@
           <t>Chip "Trên 10 kg (Nặng)" — mức cao nhất (test_data_catalog §ORD — Trọng lượng)</t>
         </is>
       </c>
-      <c r="L145" s="6" t="inlineStr"/>
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M145" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng dương cho `TC-ORD-064` — bắt buộc chọn KHÁC với chặn theo ngưỡng; lỗi hay gặp là lập trình chặn luôn mức nặng nhất. · Căn cứ: `BR01-02` *"không chặn theo ngưỡng"*.</t>
@@ -23346,7 +24102,11 @@
           <t>3 chip Kích thước, trạng thái chưa chọn (test_data_catalog §ORD — Kích thước)</t>
         </is>
       </c>
-      <c r="L146" s="5" t="inlineStr"/>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `BR01-02` *"không cho để trống"* + `C-ORD-18` (kiểu control là **chip**, ⛔ không phải Dropdown như PRD ghi).</t>
@@ -23426,7 +24186,7 @@
           <t>Chip "Lớn · &gt; 20×20 cm" — mức cao nhất (test_data_catalog §ORD — Kích thước)</t>
         </is>
       </c>
-      <c r="L147" s="6" t="inlineStr"/>
+      <c r="L147" s="6" t="n"/>
       <c r="M147" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng dương cho `TC-ORD-066`, cùng cặp với `TC-ORD-065`. · Căn cứ: `BR01-02`.</t>
@@ -23504,7 +24264,11 @@
           <t>1 ảnh &gt; 5MB của `SEED-ORD-01` (test_data_catalog §ORD — Ảnh món hàng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L148" s="5" t="inlineStr"/>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M148" s="5" t="inlineStr">
         <is>
           <t>Mục đích: assert thêm vế **"bộ đếm không tăng"** — từ chối hiển thị mà vẫn đếm là lỗi hay gặp, và làm hỏng luôn trần 5 ở `TC-ORD-070`. · Căn cứ: `BR01-01` + `BR18-02` + `AC-03.2.02`.</t>
@@ -23582,7 +24346,11 @@
           <t>1 file `.pdf` của `SEED-ORD-01` (test_data_catalog §ORD — Ảnh món hàng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L149" s="6" t="inlineStr"/>
+      <c r="L149" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh khác bản chất với `TC-ORD-068` — lọc theo định dạng và lọc theo dung lượng là hai lớp kiểm độc lập, chặn được lớp này không suy ra lớp kia. · Căn cứ: `VAL-07` + `BR18-02`.</t>
@@ -23661,7 +24429,11 @@
           <t>5 ảnh hợp lệ (biên trên) + 1 ảnh thứ 6 (chặn) của `SEED-ORD-01` (test_data_catalog §ORD — Ảnh món hàng, biên)</t>
         </is>
       </c>
-      <c r="L150" s="5" t="inlineStr"/>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M150" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên trên của trần 5 — hai giá trị liền kề phải quan sát trong cùng 1 TC để so được. · Căn cứ: `BR18-02` + `VAL-07` + `AC-03.2.01`. Trần 5 ở đây dùng chung rule với `DLV` và `TS` nhưng là **form khác**, ⛔ không dùng chung state. · 🔑 **Sửa Expected 2026-09-18 (QC GiangDC2 chốt sau recheck VR-002):** bộ đếm `n/5` được vẽ **bên trong ô thêm ảnh** ở cuối dải, nên vế *"ẩn nút thêm khi đủ 5"* của `BR18-02` tất yếu làm bộ đếm biến mất ở mức 5/5 — **hành vi hiện tại là ĐÚNG**. Expected cũ đòi đồng thời `5/5` + ẩn nút là **tự mâu thuẫn**, đã bỏ vế `5/5` và chuyển mốc assert bộ đếm về `4/5`. ⛔ Không log bug cho việc mất bộ đếm ở 5/5. · ⚠️ Dải ảnh là **danh sách cuộn ngang lazy**: phần tử ngoài viewport KHÔNG có trong accessibility tree ⇒ phải cuộn rồi mới assert (đã gây 1 ứng viên bug ma ở VR-002, xem bẫy `T10`).</t>
@@ -23740,7 +24512,11 @@
           <t>5 ảnh rồi xoá 1 (test_data_catalog §ORD — Ảnh món hàng)</t>
         </is>
       </c>
-      <c r="L151" s="6" t="inlineStr"/>
+      <c r="L151" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
           <t>Mục đích: fail độc lập với `TC-ORD-070` — chặn được ảnh thứ 6 không đảm bảo bộ đếm giảm đúng khi xoá; lỗi hay gặp là xoá nhầm ảnh cuối thay vì ảnh được chọn. · Căn cứ: `BR18-02` *"xoá được từng ảnh"*.</t>
@@ -23818,7 +24594,11 @@
           <t>Email `@fpt.com` không tồn tại trên HRIS (test_data_catalog §ORD — Email công ty người nhận ②)</t>
         </is>
       </c>
-      <c r="L152" s="5" t="inlineStr"/>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
           <t>🔑 **ĐẢO PRD.** `BR01-09` và `AC-04.1.02` ghi *"không thấy thì cho nhập thủ công"*; BA `C-ORD-14` **Resolved 2026-09-17** chốt ngược: **nút "Tiếp theo" DISABLE, không cho tạo đơn**. Lấy câu trả lời BA làm nguồn chốt. · Mục đích: kết quả phản trực giác — người đọc PRD sẽ cho rằng mở ô nhập tay là đúng. STG cho nhập tay và tạo được đơn ⇒ **FAIL và log bug**, ⛔ không sửa Expected về `BR01-09`.</t>
@@ -23897,7 +24677,11 @@
           <t>Email `stag_binhnt23@fpt.com` — người đã nghỉ việc, MNV 00026682 = `SEED-ORD-02` ② (`DOC-v1.1-05` · test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L153" s="6" t="inlineStr"/>
+      <c r="L153" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh thứ tư của tra danh bạ — HRIS **chỉ nhận nhân sự đang làm việc** (BA `C-ORD-13`), nên "có trong hệ thống" vẫn có thể ra kết quả chặn; đây là ca dễ bị lập trình sót nhất. · Căn cứ: BA `C-ORD-14` — cùng kết quả với `TC-ORD-075` nhưng khác dữ liệu đầu vào. ⚠️ Chưa có email mẫu ⇒ ghi **`Blocked` kèm lý do**, ⛔ không PASS cho xong.</t>
@@ -23975,7 +24759,11 @@
           <t>Email sai định dạng "stag_anhdc4@" (test_data_catalog §ORD — Email công ty người nhận ③)</t>
         </is>
       </c>
-      <c r="L154" s="5" t="inlineStr"/>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M154" s="5" t="inlineStr">
         <is>
           <t>Mục đích: chốt thứ tự hai lớp kiểm — validate định dạng phải chạy TRƯỚC và chặn luôn việc gọi danh bạ; gọi danh bạ với chuỗi rác là lãng phí và có thể lộ lỗi hệ thống ngoài. · Căn cứ: `§8.1.4` + `AC-04.2.01`.</t>
@@ -24053,7 +24841,11 @@
           <t>Email `@gmail.com` — ngoài tên miền công ty (test_data_catalog §ORD — Email công ty người nhận ④)</t>
         </is>
       </c>
-      <c r="L155" s="6" t="inlineStr"/>
+      <c r="L155" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M155" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh khác bản chất với `TC-ORD-077` — email **đúng định dạng** nhưng sai tên miền, dễ bị lập trình bỏ qua vì regex đã pass. · Căn cứ: tên miền hợp lệ duy nhất là **`@fpt.com`** (QC GiangDC2 chốt 2026-09-17, đính chính câu trả lời BA cũ). ⛔ `@fpt.vn` chưa xác nhận lại, không dùng làm test data cho bất kỳ nhánh nào.</t>
@@ -24133,7 +24925,11 @@
           <t>SĐT "123" — sai định dạng (test_data_catalog §ORD — SĐT người được uỷ quyền)</t>
         </is>
       </c>
-      <c r="L156" s="5" t="inlineStr"/>
+      <c r="L156" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
           <t>Mục đích: rule chỉ validate **khi được nhập** — ⛔ KHÔNG viết TC "bỏ trống thì lỗi", khối uỷ quyền là **không bắt buộc** (verify ở `TC-ORD-082`). · Căn cứ: `BR01-06` + `AC-05.1.02`.</t>
@@ -24213,10 +25009,10 @@
           <t>Tên 14 ký tự + SĐT hợp lệ (test_data_catalog §ORD — Tên người được uỷ quyền, SĐT người được uỷ quyền)</t>
         </is>
       </c>
-      <c r="L157" s="6" t="inlineStr"/>
+      <c r="L157" s="6" t="n"/>
       <c r="M157" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: nhãn "Người gửi chỉ định" là thứ phân biệt người uỷ quyền khai **lúc đăng tin** với người uỷ quyền khai **lúc giao hàng** (`TC-DLV-044`, nhãn "uỷ quyền bởi Người nhận") — lẫn hai nguồn này là lỗi truy vết nghiêm trọng. · Căn cứ: `BR01-06` + `AC-05.1.01`.</t>
+          <t>Mục đích: nhãn "Người gửi chỉ định" là thứ phân biệt người uỷ quyền khai **lúc đăng tin** với người uỷ quyền khai **lúc giao hàng** (`TC-DLV-044`, nhãn "uỷ quyền bởi Người nhận") — lẫn hai nguồn này là lỗi truy vết nghiêm trọng. · Căn cứ: `BR01-06` + `AC-05.1.01`. · ⚠️ Đã chạy nhưng THIẾU EVIDENCE hợp lệ ⇒ không được ghi PASS, tính là Not Run (gate verify_evidence.py).</t>
         </is>
       </c>
       <c r="N157" s="6" t="inlineStr">
@@ -24294,7 +25090,11 @@
           <t>Tên 1 / 2 / 60 / 61 ký tự (test_data_catalog §ORD — Tên người được uỷ quyền, biên)</t>
         </is>
       </c>
-      <c r="L158" s="5" t="inlineStr"/>
+      <c r="L158" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
           <t>Mục đích: gộp 4 giá trị vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cùng một ô, một loại rule, Expected nêu đích danh từng giá trị nên không mất khả năng bắt lỗi riêng. · Căn cứ: `§8.1.4` biên 2-60.</t>
@@ -24373,7 +25173,11 @@
           <t>Hai địa chỉ trùng hệt (test_data_catalog §ORD — Địa chỉ giao hàng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L159" s="6" t="inlineStr"/>
+      <c r="L159" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `§8.1.4` *"Địa chỉ giao phải khác địa chỉ lấy"*. Nhánh biên gần nhất (chỉ khác khoảng trắng) tách sang `TC-ORD-084` vì PRD không định nghĩa phép so sánh.</t>
@@ -24452,7 +25256,11 @@
           <t>Chuỗi chỉ khác khoảng trắng đầu/cuối — biên gần nhất (test_data_catalog §ORD — Địa chỉ giao hàng, biên)</t>
         </is>
       </c>
-      <c r="L160" s="5" t="inlineStr"/>
+      <c r="L160" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
           <t>Mục đích: biên gần nhất của phép so sánh — `VAL-03` có **trim** nên chuỗi này phải bị coi là trùng. · Căn cứ: `VAL-03`. ⛔ **KHÔNG mở rộng sang hoa/thường hay dấu tiếng Việt** — PRD không định nghĩa phép so sánh cho hai chiều đó (`RISK-ORD-12`); app xử lý bất nhất thì nêu với BA, ⛔ không viết TC assert.</t>
@@ -24530,7 +25338,11 @@
           <t>Chuỗi địa chỉ tự do (test_data_catalog §ORD — Địa chỉ giao hàng)</t>
         </is>
       </c>
-      <c r="L161" s="6" t="inlineStr"/>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-11` Resolved 2026-09-15: chốt **ô văn bản tự do**, bản v1.0 còn để ngỏ 3 khả năng (preset 6 văn phòng / chip gợi ý / autocomplete). · Căn cứ: `§8.1.4`. Biên 200/201 ký tự tách sang `TC-ORD-055`.</t>
@@ -24608,7 +25420,11 @@
           <t>Chuỗi 200 ký tự (hợp lệ) và 201 ký tự (chặn) (test_data_catalog §ORD — Địa chỉ giao hàng, biên)</t>
         </is>
       </c>
-      <c r="L162" s="5" t="inlineStr"/>
+      <c r="L162" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên trên của trần 200 — hai giá trị liền kề phải quan sát trong cùng 1 TC để so được. · Căn cứ: `§8.1.4`.</t>
@@ -24686,7 +25502,11 @@
           <t>1 tin `POSTED` có 5 ảnh = `SEED-ORD-04` (test_data_catalog §ORD — Tin đã đăng có ≥2 ảnh)</t>
         </is>
       </c>
-      <c r="L163" s="6" t="inlineStr"/>
+      <c r="L163" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `BR18-03` + `AC-03.1.01`. Lightbox tách sang `TC-ORD-073` vì là màn khác.</t>
@@ -24767,7 +25587,11 @@
           <t>1 tin `POSTED` có 5 ảnh = `SEED-ORD-04` (test_data_catalog §ORD — Tin đã đăng có ≥2 ảnh)</t>
         </is>
       </c>
-      <c r="L164" s="5" t="inlineStr"/>
+      <c r="L164" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M164" s="5" t="inlineStr">
         <is>
           <t>Mục đích: xác nhận cách đóng lightbox của app — chỉ đóng bằng nút (×), chạm nền tối không đóng. · Căn cứ: `BR18-03`. · ♻️ Sửa 2026-09-21 (QC GiangDC2, theo `BUG-024` đã huỷ): QC kiểm lại — app đúng, chạm nền không đóng lightbox; Expected đổi theo app (`BR18-03` không còn được hiểu là "chạm nền để đóng"). ⚠️ Title còn ghi *"cả nút đóng lẫn chạm nền"* — `§10.5` không cho sửa Title (xem CHANGELOG §3). VR-013: ✅ PASS.</t>
@@ -24847,7 +25671,7 @@
           <t>Dữ liệu uỷ quyền đã nhập rồi xoá (test_data_catalog §ORD — SĐT người được uỷ quyền)</t>
         </is>
       </c>
-      <c r="L165" s="6" t="inlineStr"/>
+      <c r="L165" s="6" t="n"/>
       <c r="M165" s="6" t="inlineStr">
         <is>
           <t>Mục đích: khối uỷ quyền là **không bắt buộc** — lỗi hay gặp là sau khi mở khối thì validate bắt buộc luôn, khiến người dùng không thoát ra được. · Căn cứ: `AC-05.2.01` + `BR01-06`.</t>
@@ -24926,7 +25750,11 @@
           <t>Địa chỉ giao trên màn chi tiết tin (test_data_catalog §ORD — Địa chỉ giao hàng)</t>
         </is>
       </c>
-      <c r="L166" s="5" t="inlineStr"/>
+      <c r="L166" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp với `TC-ORD-086` — hai instance icon copy ở hai vùng khác nhau của cùng màn, hỏng độc lập. · Căn cứ: `BR18-04`. Rule ghi 1,8 giây nhưng đây là hiệu ứng thị giác — chấp nhận dung sai quanh 2 giây, ⛔ không bấm giờ đòi đúng 1,8 giây. Instance ở màn Theo dõi đơn thuộc `DLV` (`TC-DLV-080/081`), ⛔ không nhân bản.</t>
@@ -25005,7 +25833,11 @@
           <t>Số điện thoại người nhận trên màn chi tiết tin (test_data_catalog §ORD)</t>
         </is>
       </c>
-      <c r="L167" s="6" t="inlineStr"/>
+      <c r="L167" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M167" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `BR18-04` — rule đặt icon copy cạnh CẢ địa chỉ giao và số điện thoại.</t>
@@ -25084,7 +25916,11 @@
           <t>2 ảnh đang soạn, chưa đăng tin (test_data_catalog §ORD — Ảnh món hàng)</t>
         </is>
       </c>
-      <c r="L168" s="5" t="inlineStr"/>
+      <c r="L168" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M168" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp với `TC-ORD-088` — ranh giới xoá được ⟷ không xoá được là **thời điểm ghi mốc**, không phải loại ảnh; chạy lẻ một vế thì không chốt được ranh giới. · Căn cứ: `BR18-02`.</t>
@@ -25164,7 +26000,11 @@
           <t>1 tin `POSTED` có 5 ảnh = `SEED-ORD-04` (test_data_catalog §ORD — Tin đã đăng có ≥2 ảnh)</t>
         </is>
       </c>
-      <c r="L169" s="6" t="inlineStr"/>
+      <c r="L169" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
           <t>Mục đích: ghi nhận hành vi thật của app — form sửa tin đã đăng vẫn cho xoá ảnh bằng nút ×; đối chiếu `TC-ORD-087`. Tin phải còn `POSTED` để vào được form sửa (`BR05-01`). · ♻️ Sửa 2026-09-21 (QC GiangDC2, theo `BUG-023` đã huỷ): QC kiểm lại — app đúng, cho xoá ảnh của tin đã đăng (đơn đã có mốc `Đăng tin` vẫn xoá được); Expected/Steps đổi theo app. ⚠️ Title còn ghi *"không xoá được"* — `§10.5` không cho sửa Title (xem CHANGELOG §3). ⚠️ `SC-CNL-010`/`SC-DLV-062` (nhóm "ảnh bất biến truy vết" `BR11-03`/`NFR-07`) chưa chạy — cân nhắc kiểm cùng cách hiểu. VR-013: ✅ PASS.</t>
@@ -25243,7 +26083,11 @@
           <t>Đơn `IN_TRANSIT` = `SEED-TS-01` CP2; mã đơn prefill (test_data_catalog §TS — Mã đơn hàng prefill)</t>
         </is>
       </c>
-      <c r="L170" s="5" t="inlineStr"/>
+      <c r="L170" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M170" s="5" t="inlineStr">
         <is>
           <t>🔴 Áp bản Resolved `C-TS-03(a)` 2026-09-17 thay vì Then của `SC-TS-008`: form prefill **đúng 1 trường**, ⛔ KHÔNG phải 9 trường như `AC-31.1.01` liệt kê — `BR16-02` mới là bản đúng, `AC-31.1.01` là PRD sai/thừa. · Mục đích: kết quả phản trực giác so với PRD — người chạy đọc `AC-31.1.01` sẽ tưởng thiếu 8 trường là bug. App prefill thêm trường ⇒ FAIL và dẫn `C-TS-03` để BA cập nhật PRD.</t>
@@ -25327,7 +26171,11 @@
           <t>Loại yêu cầu "Sự cố đơn hàng" + mô tả không rỗng + SĐT hợp lệ + 2 ảnh (test_data_catalog §TS)</t>
         </is>
       </c>
-      <c r="L171" s="6" t="inlineStr"/>
+      <c r="L171" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
           <t>Mục đích: chuỗi cam kết 24 giờ là **thứ duy nhất verify được** của quy trình hỗ trợ — hành động thật của Admin nằm ngoài app, ⛔ không mở rộng phạm vi sang đó. · Căn cứ: `AC-31.1.01` + vibe-check demo 2026-09-15 (ảnh `TS_05`, chuỗi verbatim). Màn xác nhận và nút "Quay lại đơn hàng" do **APP** vẽ chứ không phải trang xác nhận của Google Form (`C-TS-03(d)` Resolved 2026-09-17).</t>
@@ -25399,7 +26247,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>6. Nút "Gửi" ở trạng thái vô hiệu hoá và cạnh nút hiện chữ "Điền các mục bắt buộc".</t>
+          <t>6. Nút "Gửi" vẫn ở trạng thái bấm được (không disable); ngay sau khi bấm, form KHÔNG được gửi đi, tự cuộn tới câu hỏi "Loại yêu cầu" và hiện lỗi inline "Câu hỏi này là bắt buộc." ngay dưới câu hỏi đó.</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr">
@@ -25407,7 +26255,11 @@
           <t>Loại yêu cầu chưa chọn — nhánh invalid (test_data_catalog §TS — Loại yêu cầu)</t>
         </is>
       </c>
-      <c r="L172" s="5" t="inlineStr"/>
+      <c r="L172" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M172" s="5" t="inlineStr">
         <is>
           <t>Mục đích: 1 trong 3 nhánh OR của điều kiện bắt buộc — mỗi nhánh fail độc lập, khoá được nhánh này không suy ra khoá được 2 nhánh kia. · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.1.02 + vibe-check demo 2026-09-15 (ảnh `TS_04`, chiều dương của cùng rule).</t>
@@ -25479,7 +26331,7 @@
       </c>
       <c r="J173" s="7" t="inlineStr">
         <is>
-          <t>6. Nút "Gửi" ở trạng thái vô hiệu hoá và cạnh nút hiện chữ "Điền các mục bắt buộc".</t>
+          <t>6. Nút "Gửi" vẫn ở trạng thái bấm được (không disable); ngay sau khi bấm, form KHÔNG được gửi đi, tự cuộn tới câu hỏi "Mô tả chi tiết" và hiện lỗi inline "Câu hỏi này là bắt buộc." ngay dưới câu hỏi đó.</t>
         </is>
       </c>
       <c r="K173" s="6" t="inlineStr">
@@ -25487,7 +26339,11 @@
           <t>Mô tả chi tiết rỗng — nhánh invalid (test_data_catalog §TS — Mô tả chi tiết)</t>
         </is>
       </c>
-      <c r="L173" s="6" t="inlineStr"/>
+      <c r="L173" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §6.2 AC-31.1.02 — `test_data_catalog §TS` ghi rõ trường này **không có giới hạn ký tự công bố** nên chỉ có nhánh rỗng ⟷ không rỗng, ⛔ không viết TC biên độ dài.</t>
@@ -25560,7 +26416,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>7. Nút "Gửi" ở trạng thái vô hiệu hoá và cạnh nút hiện chữ "Điền các mục bắt buộc".</t>
+          <t>7. Nút "Gửi" vẫn ở trạng thái bấm được (không disable — cơ chế thật của form là inline error, xem TC-TS-010/TC-TS-011); tuy nhiên SĐT sai định dạng vẫn phải bị chặn không cho gửi (báo lỗi định dạng hoặc tương đương) trước khi form được submit.</t>
         </is>
       </c>
       <c r="K174" s="5" t="inlineStr">
@@ -25568,7 +26424,11 @@
           <t>SĐT sai định dạng "0912abc" (test_data_catalog §TS — Số điện thoại liên hệ lại, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L174" s="5" t="inlineStr"/>
+      <c r="L174" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M174" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhánh khác bản chất với 2 TC kia — ô CÓ dữ liệu nhưng sai định dạng, dễ bị lập trình thành "chỉ kiểm rỗng". · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.1.02 + §8.16.2. Dùng loại yêu cầu thứ ba để đồng thời phủ đủ 3 giá trị enum của ô "Loại yêu cầu" trong cụm này.</t>
@@ -25649,7 +26509,11 @@
           <t>Trạng thái mất kết nối mạng (test_data_catalog §TS — Trạng thái kết nối mạng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L175" s="6" t="inlineStr"/>
+      <c r="L175" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §6.2 AC-31.2.01 + **Dev trả lời `C-TS-03(c)` 2026-09-17** (*"App hiển thị nhé"*) — nút "Thử lại" do CHÍNH APP vẽ, tách biệt khỏi khung nhúng, nên assert được dù `BR16-01` dùng Custom Tabs. ⛔ Không assert công nghệ nhúng cụ thể (WebView trần hay Custom Tabs) — không quan sát được từ UI.</t>
@@ -25731,7 +26595,11 @@
           <t>Mã đơn của `SEED-TS-01`; chuyển từ mất mạng sang có mạng (test_data_catalog §TS — Trạng thái kết nối mạng)</t>
         </is>
       </c>
-      <c r="L176" s="5" t="inlineStr"/>
+      <c r="L176" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M176" s="5" t="inlineStr">
         <is>
           <t>Mục đích: fail độc lập với `TC-TS-016` — hiện được nút "Thử lại" không đảm bảo app còn giữ ngữ cảnh đơn; lỗi hay gặp là thử lại xong mở form trắng, mất mã đơn. · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.2.01 (*"KHÔNG mất ngữ cảnh đơn"*).</t>
@@ -25812,7 +26680,11 @@
           <t>Đơn `POSTED` = `SEED-TS-01` CP0 (test_data_catalog §TS — Mã đơn hàng prefill)</t>
         </is>
       </c>
-      <c r="L177" s="6" t="inlineStr"/>
+      <c r="L177" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
           <t>Mục đích: neo vào `C-TS-02(b)` Resolved 2026-09-17 — BA: *"ver hiện tại không chuyển trạng thái gì"*. `§8.12.2` định nghĩa `INCIDENT` = *"có báo cáo sự cố sau khi đơn đã sang IN_TRANSIT"*, đọc được là **tự chuyển**, nên TC này là oracle chặn đúng cách đọc sai đó. · Căn cứ: form Google không gọi được API app ⇒ `INCIDENT` chỉ vào được qua Dev xử lý tay; đơn tự đổi trạng thái ⇒ FAIL và dẫn `C-TS-02`. Kết luận này là căn cứ để `SC-CNL-015`/`SC-DLV-034` out of scope test qua UI.</t>
@@ -25892,7 +26764,11 @@
           <t>Đơn qua 3 trạng thái `POSTED` · `MATCHED` · `IN_TRANSIT` = `SEED-TS-01`; vai người gửi (test_data_catalog §TS)</t>
         </is>
       </c>
-      <c r="L178" s="5" t="inlineStr"/>
+      <c r="L178" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
           <t>🔑 Áp `C-TS-02(a)` Resolved 2026-09-17: nút hiện ở **MỌI trạng thái**, ⛔ KHÔNG giới hạn `IN_TRANSIT`/`DELIVERED` như `§8.12.3` liệt kê — `AC-31.1.01` (*"vai trò bất kỳ"*) là bản đúng, `§8.12.3` là PRD thiếu. · Mục đích: 1 trong 3 ô vai — nút ẩn với 1 vai hoặc ở 1 trạng thái là defect. Nút không hiện ở trạng thái nào ⇒ FAIL và dẫn `C-TS-02`.</t>
@@ -25971,7 +26847,11 @@
           <t>Đơn qua 2 trạng thái `MATCHED` · `IN_TRANSIT` = `SEED-TS-01`; vai người vận chuyển (test_data_catalog §TS)</t>
         </is>
       </c>
-      <c r="L179" s="6" t="inlineStr"/>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
           <t>Mục đích: vai này chỉ thấy đơn từ khi nhận nên chỉ quan sát được 2 trạng thái — ⛔ không ghép chung TC với vai người gửi (3 trạng thái) để tránh Expected gộp hai phạm vi khác nhau. · Căn cứ: `DOC-v1.1-01` §8.16 Trigger + `C-TS-02(a)` Resolved 2026-09-17.</t>
@@ -26051,7 +26931,11 @@
           <t>Đơn `IN_TRANSIT` = `SEED-TS-01` CP2; vai người nhận (test_data_catalog §TS — Mã đơn hàng prefill)</t>
         </is>
       </c>
-      <c r="L180" s="5" t="inlineStr"/>
+      <c r="L180" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M180" s="5" t="inlineStr">
         <is>
           <t>Mục đích: vai này thụ động nhất trong luồng nên dễ bị bỏ quên quyền báo sự cố; TC đi thêm một bước mở form để chốt hành vi giống nhau cho cả 3 vai, không chỉ chốt nút có hiện. · Căn cứ: `DOC-v1.1-01` §8.16 Actor + `AC-31.1.01` (*"vai trò bất kỳ"*).</t>
@@ -26133,7 +27017,11 @@
           <t>0 ảnh — biên dưới hợp lệ (test_data_catalog §TS — Hình ảnh đính kèm)</t>
         </is>
       </c>
-      <c r="L181" s="6" t="inlineStr"/>
+      <c r="L181" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên dưới với `TC-TS-014` — ảnh KHÔNG nằm trong điều kiện bật nút "Gửi", khác hẳn ảnh bằng chứng giao hàng của `DLV` (bắt buộc ≥1). · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.1.02 + §8.16.2.</t>
@@ -26214,7 +27102,11 @@
           <t>5 ảnh — biên trên hợp lệ, ảnh thứ 6 bị chặn (test_data_catalog §TS — Hình ảnh đính kèm, biên)</t>
         </is>
       </c>
-      <c r="L182" s="5" t="inlineStr"/>
+      <c r="L182" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M182" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên trên của trần 5 — hai giá trị liền kề nên phải quan sát trong cùng 1 TC để so được. · Căn cứ: `DOC-v1.1-01` §8.16.2 + vibe-check demo 2026-09-15 (ảnh `TS_03`, nút tự disable ở ảnh thứ 5). Trần 5 ở đây **độc lập** với trần ảnh bằng chứng của `DLV` — 2 form khác nhau, không dùng chung state dù cùng số 5.</t>
@@ -26295,7 +27187,11 @@
           <t>5 ảnh rồi xoá 1 (test_data_catalog §TS — Hình ảnh đính kèm)</t>
         </is>
       </c>
-      <c r="L183" s="6" t="inlineStr"/>
+      <c r="L183" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M183" s="6" t="inlineStr">
         <is>
           <t>Mục đích: fail độc lập với `TC-TS-014` — chặn được ảnh thứ 6 không đảm bảo bộ đếm giảm đúng khi xoá; lỗi hay gặp là xoá nhầm ảnh cuối thay vì ảnh được chọn. · Căn cứ: `DOC-v1.1-01` §8.16.2 (*"xoá được từng ảnh"*).</t>
@@ -26376,7 +27272,11 @@
           <t>Đơn `IN_TRANSIT` = `SEED-TS-01` CP2 (test_data_catalog §TS)</t>
         </is>
       </c>
-      <c r="L184" s="5" t="inlineStr"/>
+      <c r="L184" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M184" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.16.1 BR16-04 — đóng WebView ⛔ KHÔNG reset ngăn xếp điều hướng về trang chủ.</t>
@@ -26456,7 +27356,11 @@
           <t>Dữ liệu nhập dở ở phiên trước (test_data_catalog §TS — Loại yêu cầu, Mô tả chi tiết)</t>
         </is>
       </c>
-      <c r="L185" s="6" t="inlineStr"/>
+      <c r="L185" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M185" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với `TC-TS-018` — cùng một thao tác đóng nhưng hai hệ quả khác nhau: ngăn xếp điều hướng phải GIỮ, còn dữ liệu form phải MẤT. · Căn cứ: `DOC-v1.1-01` §8.16.1 BR16-06 (*"mở lại là một phiên mới"*).</t>
@@ -26535,7 +27439,11 @@
           <t>Mã đơn prefill chỉ đọc (test_data_catalog §TS — Mã đơn hàng prefill)</t>
         </is>
       </c>
-      <c r="L186" s="5" t="inlineStr"/>
+      <c r="L186" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M186" s="5" t="inlineStr">
         <is>
           <t>🔴 Áp bản Resolved `C-TS-03(b)` 2026-09-17 — **ĐẢO HẲN Then của `SC-TS-014`** (*"trường prefill CHO PHÉP sửa"*). `§8.16.2` (*"Chỉ đọc · Không sửa"*) là bản đúng, **`BR16-03` là PRD sai**; demo cho thấy ô là nhãn tĩnh, không phải câu trả lời ngắn của Google Form. · Mục đích: kết quả phản trực giác — người chạy đọc `BR16-03` sẽ tưởng "không sửa được" là bug. Sửa được ⇒ FAIL và dẫn `C-TS-03` để BA cập nhật PRD.</t>
@@ -26617,7 +27525,11 @@
           <t>SĐT hợp lệ "0987654321"; văn phòng K3 "Lê Thái Tổ" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L187" s="6" t="inlineStr"/>
+      <c r="L187" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M187" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `AC-30.1.01` + `BR15-05`. Nếu giá trị ghi ở bước 4 trùng test data thì đổi sang SĐT/văn phòng khác trong catalog. · Đã sửa theo §10.4 (2026-09-17): thu hẹp — chỉ giữ điểm kiểm banner ở step cuối; điểm kiểm persist (mở lại xem giá trị) tách sang `TC-USR-016` mới. · 🔄 **SỬA EXPECTED 2026-09-18 (QC GiangDC2 chốt): hành vi app là ĐÚNG, ⛔ KHÔNG phải bug.** Expected cũ (*"banner xanh 'Đã lưu thông tin của bạn' + màn vẫn ở lại"*) **HẾT HIỆU LỰC**. Hành vi chốt: bấm "Lưu thay đổi" với dữ liệu hợp lệ ⇒ **không có banner**, app **điều hướng về màn "Cá nhân"**; dữ liệu lưu đúng (phủ bởi `TC-USR-016`). VR-001 từng ghi FAIL (ứng viên bug **B1**) — verdict đã đổi sang **PASS**, B1 **rút lại**. ⚠️ Nợ upstream: `SC-USR-014` THEN + `DOC-v1.1-01 §8.15.1 BR15-05`/`§6.2 AC-30.1.01` vẫn ghi "banner xanh + ở lại màn" ⇒ cần `/analyze-requirements --module USR` + clarification với BA. ⚠️ `Test Title` vẫn còn chữ *"hiển thị đúng banner xanh"* (Title không thuộc danh sách field được sửa ở `Project_rule §10.5`) ⇒ chờ QC chốt riêng.</t>
@@ -26702,7 +27614,11 @@
           <t>SĐT hợp lệ "0987654321"; văn phòng K3 "Lê Thái Tổ" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L188" s="5" t="inlineStr"/>
+      <c r="L188" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M188" s="5" t="inlineStr">
         <is>
           <t>Technique: N/A — happy schema assert · Mục đích: tách khỏi `TC-USR-015` theo §10.4 (2026-09-17) — điểm kiểm persist thật (không tin banner) là lý do TC này tồn tại, giữ đúng ở step cuối. Căn cứ: Analyst Note `SC-USR-014` — "TC-USR-014 bắt buộc có bước mở lại màn để kiểm giá trị đã persist". Nếu giá trị ghi ở bước 4 trùng test data thì đổi sang SĐT/văn phòng khác trong catalog. TC mới, không có ID cũ 1-1.</t>
@@ -26789,7 +27705,11 @@
           <t>SĐT mới "0987654321"; văn phòng K4 "363 Nguyễn Hữu Thọ,Cẩm Lệ" (04_test-data/valid/USR-office-catalog.md); đơn tạo TRƯỚC khi sửa hồ sơ (test_data_catalog §USR v1.1)</t>
         </is>
       </c>
-      <c r="L189" s="6" t="inlineStr"/>
+      <c r="L189" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M189" s="6" t="inlineStr">
         <is>
           <t>Mục đích: `RISK-USR-07` — nhóm rule truy vết mà app đã vi phạm 1 lần; chạy cùng lô với `SC-CNL-010` · `SC-ORD-065` · `SC-DLV-062`, cùng vỡ ⇒ 1 bug report cho nguyên nhân gốc. · Căn cứ: `BR15-03` + `AC-30.2.02`. Nếu SĐT người gửi hoặc giá trị bước 4 trùng test data thì đổi giá trị khác trong catalog. Giả định màn Theo dõi đơn hiển thị SĐT người gửi cho chính người đăng — nếu không hiển thị thì đối chiếu ở màn chi tiết tin, không coi là FAIL của TC này. · Đã sửa theo §10.4 (2026-09-17): bỏ steps mở wizard mới để check giá trị điền sẵn (vế thứ 2 của `AC-30.2.02`) — vế đó trùng phạm vi "wizard nhận đúng giá trị prefill" đã có home ở `SC-ORD-025` (Analyst Note gốc: ⛔ không nhân bản SC). TC này giữ đúng 1 điểm kiểm ở step cuối: đơn cũ không bị ghi đè. · ID cũ: TC-USR-022.</t>
@@ -26866,7 +27786,11 @@
           <t>Tên tài khoản A + chữ viết tắt kỳ vọng (test_data_catalog §USR v1.1 — Avatar)</t>
         </is>
       </c>
-      <c r="L190" s="5" t="inlineStr"/>
+      <c r="L190" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M190" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo analyze v1.1 (2026-09-16): 4 trường có ảnh avatar → avatar chữ viết tắt; thêm assert vắng SĐT/email/địa chỉ. · Căn cứ: BA chốt `C-USR-05(a)`; SĐT/email/địa chỉ chỉ ở màn "Cập nhật thông tin" (`C-USR-04`). Demo trang Cá nhân hiện icon người ⇒ STG giống demo thì log bug.</t>
@@ -26946,7 +27870,11 @@
           <t>Hồ sơ nhân viên đầy đủ (test_data_catalog §USR)</t>
         </is>
       </c>
-      <c r="L191" s="6" t="inlineStr"/>
+      <c r="L191" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M191" s="6" t="inlineStr">
         <is>
           <t>Mục đích: bản v1.0 cùng ID assert "không có bất kỳ control sửa nào" — kỳ vọng ngược, phải dùng bản v1.1. · Đã sửa theo `C-USR-03` đảo (2026-09-15): trang Cá nhân nay có mục "Cập nhật thông tin" hợp lệ nên chỉ assert không sửa trực tiếp trên từng trường. · Căn cứ: `BR15-01`. · Đã sửa theo §10.4 (2026-09-17): gộp 3 điểm kiểm avatar/tên/phòng ban·MNV vào 1 step Check cuối + 1 Expected duy nhất (Expected chỉ ghi ở step cuối).</t>
@@ -27023,7 +27951,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L192" s="5" t="inlineStr"/>
+      <c r="L192" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M192" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `DOC-v1.1-01` §8.15 Trigger (2026-09-15): hết dạng GAP 3 nhãn, assert được nhãn + vị trí; priority P3 → P2 theo `SC-USR-012`.</t>
@@ -27100,7 +28032,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L193" s="6" t="inlineStr"/>
+      <c r="L193" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M193" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: §8.15 Trigger; nút "←" và việc ẩn bottom nav lấy theo ảnh `USR_02` (`DOC-v1.1-03`) + code demo — PRD không mô tả, STG lệch thì mở CL.</t>
@@ -27179,7 +28115,11 @@
           <t>SĐT để trống (test_data_catalog §USR v1.1 — Số điện thoại mặc định)</t>
         </is>
       </c>
-      <c r="L194" s="5" t="inlineStr"/>
+      <c r="L194" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M194" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `BR15-02` + `AC-30.1.02`. PRD không có chuỗi thông báo. Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức (PRD không đặc tả); STG hiện chuỗi khác ⇒ log bug, ⛔ không sửa TC. · ID cũ: TC-USR-016.</t>
@@ -27258,7 +28198,11 @@
           <t>SĐT 9 chữ số "091234567" (test_data_catalog §USR v1.1, biên dưới)</t>
         </is>
       </c>
-      <c r="L195" s="6" t="inlineStr"/>
+      <c r="L195" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M195" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên với TC-USR-020 quanh mốc đúng 10 chữ số (giá trị hợp lệ đối chứng ở TC-USR-015). · Căn cứ: BA chốt 2026-09-16 "bắt đầu bằng 0, đúng 10 ký tự số" + `BR15-02`. · Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức. · ID cũ: TC-USR-017.</t>
@@ -27340,7 +28284,11 @@
           <t>SĐT 11 chữ số "09123456789" (test_data_catalog §USR v1.1, biên trên)</t>
         </is>
       </c>
-      <c r="L196" s="5" t="inlineStr"/>
+      <c r="L196" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M196" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên với TC-USR-018. · Căn cứ: BA chốt 2026-09-16 "đúng 10 ký tự số" + `BR15-02`. Chưa đặc tả app chặn nhập ở chữ số thứ 11 hay báo lỗi khi lưu ⇒ chỉ assert kết quả cuối: không lưu được chuỗi 11 chữ số. · Đã sửa theo §10.4 (2026-09-17): bỏ dòng Expected ở step 5 ("KHÔNG hiển thị banner") — hành vi block ngay hay ở persist chưa rõ theo doc, chỉ assert chắc điểm cuối. · ID cũ: TC-USR-018.</t>
@@ -27419,7 +28367,11 @@
           <t>SĐT 10 chữ số không bắt đầu bằng 0 "1912345678" (test_data_catalog §USR v1.1)</t>
         </is>
       </c>
-      <c r="L197" s="6" t="inlineStr"/>
+      <c r="L197" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M197" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `AC-30.1.02` "10 số, đầu 0" + BA chốt 2026-09-16. · Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức. · ID cũ: TC-USR-019.</t>
@@ -27498,7 +28450,11 @@
           <t>"0912 345 678" (test_data_catalog §USR v1.1 — Invalid)</t>
         </is>
       </c>
-      <c r="L198" s="5" t="inlineStr"/>
+      <c r="L198" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M198" s="5" t="inlineStr">
         <is>
           <t>Mục đích: "10 ký tự là số" loại cả dạng hiển thị có khoảng trắng mà demo dùng — dễ bị coi là hợp lệ. · Căn cứ: BA chốt 2026-09-16. · Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức. · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-020` cũ (3 định dạng invalid gộp 1 TC) thành 3 TC riêng, mỗi TC 1 định dạng ở step cuối. · ID cũ: TC-USR-020 (một phần).</t>
@@ -27577,7 +28533,11 @@
           <t>"+84912345678" (test_data_catalog §USR v1.1 — Invalid)</t>
         </is>
       </c>
-      <c r="L199" s="6" t="inlineStr"/>
+      <c r="L199" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M199" s="6" t="inlineStr">
         <is>
           <t>Mục đích: định dạng quốc tế +84 không đúng "10 số, đầu 0" — dễ nhầm là hợp lệ vì đúng số quốc gia VN. · Căn cứ: BA chốt 2026-09-16. · Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-020` cũ, không có ID cũ 1-1.</t>
@@ -27656,7 +28616,11 @@
           <t>"09123a5678" (test_data_catalog §USR v1.1 — Invalid)</t>
         </is>
       </c>
-      <c r="L200" s="5" t="inlineStr"/>
+      <c r="L200" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M200" s="5" t="inlineStr">
         <is>
           <t>Mục đích: chuỗi lẫn ký tự chữ vào dãy số — kiểm field không chỉ validate độ dài mà cả kiểu ký tự. · Căn cứ: BA chốt 2026-09-16. · Chuỗi thông báo theo demo `DOC-v1.1-02` — BA xác nhận 2026-09-17 là chuỗi chính thức. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-020` cũ, không có ID cũ 1-1.</t>
@@ -27738,7 +28702,11 @@
           <t>Trường SSO của tài khoản A (test_data_catalog §USR v1.1 — Trường SSO)</t>
         </is>
       </c>
-      <c r="L201" s="6" t="inlineStr"/>
+      <c r="L201" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M201" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `BR15-01` + `AC-30.2.01`; avatar theo `C-USR-05(a)`. Icon khiên theo UI — BA chốt 2026-09-16; PRD ghi "icon khoá" ⇒ lệch chữ PRD, báo BA sửa PRD, ⛔ không đổi TC. · Đã sửa theo §10.4 (2026-09-17): gộp 5 điểm kiểm (4 field chỉ đọc + icon khiên) vào 1 step Check cuối + 1 Expected duy nhất. · ID cũ: TC-USR-021.</t>
@@ -27823,7 +28791,11 @@
           <t>SĐT/địa chỉ nhập trong đơn khác hồ sơ (test_data_catalog §USR v1.1 — Cặp giá trị TRƯỚC/SAU)</t>
         </is>
       </c>
-      <c r="L202" s="5" t="inlineStr"/>
+      <c r="L202" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M202" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `BR15-04` + `AC-30.1.01` "sửa trong từng đơn mà không ghi lại hồ sơ". Vế "wizard nhận đúng giá trị điền sẵn" kiểm ở `SC-ORD-025`, không lặp ở đây. Nếu field địa chỉ lấy hàng chỉ cho chọn từ danh sách thì chọn "Tòa V-City, Lê Thái Tổ" trong danh sách gợi ý. Nếu giá trị bước 4 trùng test data thì đổi giá trị khác.</t>
@@ -27903,7 +28875,11 @@
           <t>Văn phòng K3 "Tòa V-City, Lê Thái Tổ" (setup) · chuỗi gõ tay K7 "asdfghjkl1" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L203" s="6" t="inlineStr"/>
+      <c r="L203" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M203" s="6" t="inlineStr">
         <is>
           <t>Mục đích: kết quả phản trực giác — gõ tay không chọn thì bị xoá thay vì giữ chuỗi đã gõ. · Căn cứ: BA chốt 2026-09-16 (rời field không chọn ⇒ rỗng). Demo cho gõ tự do ⇒ STG giống demo thì log bug. · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-025` cũ (4 điểm kiểm gộp 1 TC) — TC này giữ điểm "rời field ⇒ rỗng"; điểm "lưu rỗng thành công" và "mở lại vẫn rỗng" tách sang `TC-USR-029`/`030`. · ID cũ: TC-USR-025 (một phần).</t>
@@ -27984,7 +28960,11 @@
           <t>Văn phòng K3 "Tòa V-City, Lê Thái Tổ" (setup) · chuỗi gõ tay K7 "asdfghjkl1" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L204" s="5" t="inlineStr"/>
+      <c r="L204" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M204" s="5" t="inlineStr">
         <is>
           <t>Mục đích: BA chốt "cho phép để trống" — TC này chứng minh rỗng không bị chặn lưu như SĐT. · Căn cứ: BA chốt 2026-09-16. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-025` cũ, không có ID cũ 1-1.</t>
@@ -28068,7 +29048,11 @@
           <t>Văn phòng K3 "Tòa V-City, Lê Thái Tổ" (setup) · chuỗi gõ tay K7 "asdfghjkl1" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L205" s="6" t="inlineStr"/>
+      <c r="L205" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M205" s="6" t="inlineStr">
         <is>
           <t>Mục đích: kết quả phản trực giác — lưu rỗng xong mở lại vẫn rỗng, không tự lấy lại HRIS; đây là bẫy dễ bỏ sót nhất trong nhóm (Analyst Note `SC-USR-020`). Demo cho gõ tự do ⇒ STG giống demo thì log bug. · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-025` cũ, giữ đúng điểm kiểm quan trọng nhất của cả nhóm ở step cuối. · ID cũ: TC-USR-025 (một phần — điểm kiểm chính).</t>
@@ -28147,7 +29131,11 @@
           <t>K1 "fp" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L206" s="5" t="inlineStr"/>
+      <c r="L206" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M206" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên 2/3 ký tự — vế biên dưới (2 ký tự, chưa đủ ngưỡng), đối chứng với `TC-USR-032`. · Căn cứ: BA chốt 2026-09-16 (gợi ý từ 3 ký tự). · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-026` cũ thành 2 TC theo từng vế biên. · ID cũ: TC-USR-026 (một phần).</t>
@@ -28226,7 +29214,11 @@
           <t>K2 "fpt" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L207" s="6" t="inlineStr"/>
+      <c r="L207" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M207" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên 2/3 ký tự — vế biên trên (đủ ngưỡng, khớp nhiều), đối chứng với `TC-USR-031`. · Căn cứ: BA chốt 2026-09-16; danh sách kỳ vọng đối chiếu `DOC-v1.1-04` cột `name`. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-026` cũ, không có ID cũ 1-1.</t>
@@ -28308,7 +29300,11 @@
           <t>K3 "Lê Thái Tổ" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L208" s="5" t="inlineStr"/>
+      <c r="L208" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M208" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng dương cho `TC-USR-028` — chọn từ gợi ý thì rời field vẫn giữ giá trị. · Căn cứ: BA chốt 2026-09-16 (chọn ⇒ điền chuỗi `name` của `DOC-v1.1-04`). · Đã sửa theo §10.4 (2026-09-17): bỏ dòng Expected ở step 6 (danh sách hiển thị 1 văn phòng) — việc chọn được đúng văn phòng ở step 7 đã ngầm xác nhận nó có trong danh sách; giữ đúng 1 điểm kiểm ở step cuối. · ID cũ: TC-USR-027.</t>
@@ -28387,7 +29383,11 @@
           <t>K4 "Cẩm Lệ" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L209" s="6" t="inlineStr"/>
+      <c r="L209" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M209" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 (không phân biệt dấu + hoa thường) — vế có dấu, đối chứng với `TC-USR-035`/`036` (không dấu thường/hoa). · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-028` cũ (3 biến thể gộp 1 TC) thành 3 TC riêng, mỗi biến thể 1 TC. · ID cũ: TC-USR-028 (một phần).</t>
@@ -28466,7 +29466,11 @@
           <t>K4 "cam le" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L210" s="5" t="inlineStr"/>
+      <c r="L210" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M210" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 (không phân biệt dấu + hoa thường) — vế chữ thường không dấu, đối chứng với `TC-USR-034`/`036`. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-028` cũ, không có ID cũ 1-1.</t>
@@ -28545,7 +29549,11 @@
           <t>K4 "CAM LE" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L211" s="6" t="inlineStr"/>
+      <c r="L211" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M211" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 (không phân biệt dấu + hoa thường) — vế chữ hoa không dấu, đối chứng với `TC-USR-034`/`035`. · TC mới tách theo §10.4 (2026-09-17) từ `TC-USR-028` cũ, không có ID cũ 1-1.</t>
@@ -28624,7 +29632,11 @@
           <t>K8 "tan" — 36 văn phòng khớp (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L212" s="5" t="inlineStr"/>
+      <c r="L212" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M212" s="5" t="inlineStr">
         <is>
           <t>Mục đích: "Tầng" chỉ khớp khi so kiểu chứa chuỗi — app khớp theo đầu từ sẽ thiếu mục này. · Căn cứ: BA chốt 2026-09-16 (chứa chuỗi); tổng 36 văn phòng theo `DOC-v1.1-04`. · ID cũ: TC-USR-029.</t>
@@ -28703,7 +29715,11 @@
           <t>K5 "xyz" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L213" s="6" t="inlineStr"/>
+      <c r="L213" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M213" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 ("không có thì không gợi ý"). · ID cũ: TC-USR-030.</t>
@@ -28782,7 +29798,11 @@
           <t>K6 "hcm" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L214" s="5" t="inlineStr"/>
+      <c r="L214" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M214" s="5" t="inlineStr">
         <is>
           <t>Mục đích: `DOC-v1.1-04` có cột `search_alias_text` chứa mã tỉnh ("hcm …") — app tìm nhầm cột này sẽ ra 34 văn phòng HCM ⇒ log bug. · Căn cứ: BA chốt 2026-09-16 (tìm theo tên văn phòng). · ID cũ: TC-USR-031.</t>
@@ -28862,7 +29882,11 @@
           <t>Tài khoản C = `FOXECO_STG_USER_C` (MNV 00041796); địa chỉ HRIS `HCM LôB3,E-Office,KCN TânThuận` ⇒ kỳ vọng prefill chuỗi `name` **`LôB3,E-Office,KCN TânThuận`** (`DOC-v1.1-04`) — `04_test-data/valid/USR-accounts.md`</t>
         </is>
       </c>
-      <c r="L215" s="6" t="inlineStr"/>
+      <c r="L215" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M215" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 (mặc định load HRIS, cho sửa) + §8.15.2 "địa chỉ làm việc trong hồ sơ". ⛔ Chạy trước mọi TC lưu hồ sơ trên tài khoản C. · ✅ Test data đã có 2026-09-18 (`DOC-v1.1-05`). ⚠️ HRIS trả **mã tỉnh + tên VP** (`HCM LôB3,...`) còn catalog `name` không có tiền tố `HCM` — app hiện nguyên tiền tố thì **ghi nhận + hỏi BA**, ⛔ chưa kết luận bug. · Đã sửa theo §10.4 (2026-09-17): đổi thứ tự step 4/5 và gộp 2 điểm kiểm (giá trị HRIS + cho phép sửa) vào 1 Expected ở step cuối. · ID cũ: TC-USR-032.</t>
@@ -29031,7 +30055,11 @@
           <t>K3 "Tòa V-City, Lê Thái Tổ" (04_test-data/valid/USR-office-catalog.md)</t>
         </is>
       </c>
-      <c r="L217" s="6" t="inlineStr"/>
+      <c r="L217" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M217" s="6" t="inlineStr">
         <is>
           <t>✅ Tiền đề đã thoả 2026-09-18: HRIS của A = `HCM LôB3,E-Office,KCN TânThuận` ≠ `Tòa V-City, Lê Thái Tổ` (`DOC-v1.1-05`). · Mục đích: đối chứng với `TC-USR-040` — thứ tự ưu tiên "đã lưu &gt; HRIS &gt; rỗng"; thoát hẳn FoxEco để loại trừ giá trị còn trong phiên. · Căn cứ: BA chốt 2026-09-16 ("đã cập nhật trước đó vào lại sẽ thấy data cũ"). · ID cũ: TC-USR-034.</t>
@@ -29111,7 +30139,11 @@
           <t>Tài khoản C = `FOXECO_STG_USER_C`; SĐT HRIS đọc từ `00_input/v1.1/datatest` (`DOC-v1.1-05`, local — ⛔ không chép vào TC/evidence), định dạng 10 số đầu 0 ⇒ hợp lệ theo `BR15-02`</t>
         </is>
       </c>
-      <c r="L218" s="5" t="inlineStr"/>
+      <c r="L218" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M218" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 ("SĐT mặc định từ HRIS") + §8.15.2 "số điện thoại hiện tại". Có thể chạy cùng phiên với `TC-USR-040` trên tài khoản C. · ✅ Test data đã có 2026-09-18 (`DOC-v1.1-05`). 🕐 SĐT HRIS mới cập nhật 18/09, FoxEco có thể chỉ đồng bộ **sau** 18/09 ⇒ chạy từ 19/09; lệch đúng ngày 18/09 ⇒ ghi `BLOCKED`, ⛔ không log bug. · Đã sửa theo §10.4 (2026-09-17): đổi thứ tự step 4/5 và gộp 2 điểm kiểm vào 1 Expected ở step cuối. · ID cũ: TC-USR-035.</t>
@@ -29272,7 +30304,11 @@
           <t>Giá trị assert-absent: badge "Hạng Đồng hành" (test_data_catalog §USR)</t>
         </is>
       </c>
-      <c r="L220" s="5" t="inlineStr"/>
+      <c r="L220" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M220" s="5" t="inlineStr">
         <is>
           <t>Mục đích: bản v1.0 cùng ID assert badge TỒN TẠI — kỳ vọng ngược, phải dùng bản v1.1. · Đã sửa theo BA 2026-09-16 (`C-USR-06` Resolved — badge không hiện). · Căn cứ: `BR14-03` cấm mọi tier/xếp hạng. Demo còn badge ⇒ STG còn badge thì log bug.</t>
@@ -29349,7 +30385,11 @@
           <t>Hồ sơ nhân viên đầy đủ (test_data_catalog §USR)</t>
         </is>
       </c>
-      <c r="L221" s="6" t="inlineStr"/>
+      <c r="L221" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M221" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo analyze v1.1 (2026-09-16): bỏ badge hạng, 2 → 3 mục menu, avatar chữ viết tắt; bỏ tiền đề 2 chỉ số &gt; 0 vì chỉ đối chiếu thành phần và thứ tự; priority P2 → P3 theo `SC-USR-011`. · Căn cứ: §8.15 Trigger + `C-USR-05(a)` + `C-USR-06`.</t>
@@ -29432,7 +30472,11 @@
           <t>SĐT hợp lệ "0987654321" / "0987654322" (test_data_catalog §USR v1.1)</t>
         </is>
       </c>
-      <c r="L222" s="5" t="inlineStr"/>
+      <c r="L222" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M222" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: BR15-05 + AC-30.1.01 "tự ẩn khi người dùng sửa tiếp". Không assert ẩn theo thời gian và không assert trường hợp chỉ chạm vào field mà không đổi nội dung — PRD không có mốc. · Đã sửa theo §10.4 (2026-09-17): bỏ dòng Expected ở step 6 (banner đang hiển thị) — điểm này đã có TC-USR-015 assert riêng (chuỗi banner đúng); TC này chỉ giữ đúng 1 điểm kiểm ở step cuối: banner tự ẩn khi sửa tiếp. · ID cũ: TC-USR-024. · 🔄 SỬA STEPS + EXPECTED 2026-09-18 (QC GiangDC2 chốt): tiền đề gốc "có banner, kiểm banner tự ẩn khi sửa tiếp" KHÔNG còn đúng sau khi bug B1 rút lại — app KHÔNG hề hiện banner ở bất kỳ lần lưu nào và tự điều hướng về "Cá nhân" (xem TC-USR-015). Viết lại Steps/Expected theo hướng kiểm tính nhất quán của hành vi không-banner qua 2 lần lưu liên tiếp, thay vì kiểm banner tự ẩn (không còn banner để mà ẩn). ⚠️ Nợ upstream: SC-USR-019 + BR15-05/AC-30.1.01 ("banner tự ẩn khi sửa tiếp") cần /analyze-requirements --module USR cập nhật lại cho khớp việc bỏ hẳn banner — chưa sửa ở đây vì ngoài phạm vi field được phép sửa của TC (Project_rule §10.5). 🔄 SỬA TEST TITLE 2026-09-18 (QC GiangDC2 chốt trực tiếp): Title cũ "Check banner đã lưu tự ẩn khi sửa tiếp nội dung field" → "Check hai lần lưu liên tiếp đều không hiện banner và đều về màn Cá nhân". Lý do: Steps + Expected đã đổi hẳn sang kiểm tính nhất quán của hành vi không-banner, Title cũ mô tả NGƯỢC nội dung TC ⇒ người đọc Title sẽ hiểu sai. §10.5 FREEZE vẫn giữ nguyên với thêm/xoá/tách/gộp TC — Σ TC không đổi (223 · USR 38). Đã verify PASS ở VR-003 theo đúng bản Steps/Expected này. ⚠️ TC-USR-015 vẫn còn Title cũ ("hiển thị đúng banner xanh") — việc còn treo riêng, chưa được chốt sửa.</t>
@@ -29514,7 +30558,11 @@
           <t>SĐT "0987654321"; văn phòng "36 Nhơn Hòa 4, Cẩm Lệ" (04_test-data/valid/USR-office-catalog.md K4)</t>
         </is>
       </c>
-      <c r="L223" s="6" t="inlineStr"/>
+      <c r="L223" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M223" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 ("không lưu, không hiện xác nhận") — vế (1) không có hộp thoại chặn đường ra. · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-037` cũ — vế "giá trị chưa lưu bị bỏ" tách sang `TC-USR-046`. · ID cũ: TC-USR-037 (một phần).</t>
@@ -29598,7 +30646,11 @@
           <t>SĐT "0987654321"; văn phòng "36 Nhơn Hòa 4, Cẩm Lệ" (04_test-data/valid/USR-office-catalog.md K4)</t>
         </is>
       </c>
-      <c r="L224" s="5" t="inlineStr"/>
+      <c r="L224" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M224" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: BA chốt 2026-09-16 — vế (2) giá trị chưa lưu không bị lưu ngầm/giữ nháp. Demo giữ bản nháp khi mở lại màn (đọc code `DOC-v1.1-02`) ⇒ STG giống demo thì log bug, ⛔ không dùng demo làm oracle. · Đã sửa theo §10.4 (2026-09-17): tách khỏi `TC-USR-037` cũ, giữ đúng 1 điểm kiểm ở step cuối. Nếu giá trị bước 4 trùng test data thì đổi giá trị khác. · ID cũ: TC-USR-037 (một phần — điểm kiểm chính).</t>
@@ -29797,7 +30849,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo BA trả lời `C-ACT-02` 2026-09-16: assert cứng bộ nhãn của app, thay vì chỉ assert "có đúng 2 tab" như bản v1.0. · Mục đích: nhãn tab xuất hiện trong Steps của rất nhiều TC ở `ACT` và các module khác, chốt sai là phải sửa rải rác. · Căn cứ: BA chốt **theo app**; PRD `EMP-05`/`EMP-06`/`AC-09.1.01` ghi "Đang chạy"/"Hoàn tất" là **PRD chưa cập nhật** — ⛔ không assert theo PRD, app hiện đúng bộ nhãn này thì PASS.</t>
@@ -29881,7 +30937,11 @@
           <t>1 đơn `COMPLETED` + 1 đơn `EXPIRED` + 1 đơn `RETURNED` của `SEED-ACT-03` (test_data_catalog §ACT — Bộ 3 đơn kết thúc)</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `AC-24.2.01` + BA trả lời `C-ACT-04(a)` 2026-09-17: bổ sung loại đơn thứ ba (`RETURNED`) vào danh sách phải có, bản v1.0 chỉ có 2 loại. · Mục đích: `RETURNED` là kết cục mới của v1.1, dev dễ quên xếp nó vào tab nào. · Căn cứ: chuỗi lý do của card "Hết hạn" verify ở `TC-ACT-008`, lý do hoàn hàng của card `RETURNED` verify ở `TC-ACT-015` — TC này chỉ chốt vị trí tab. Lô `DLV` chưa đẩy được đơn tới `RETURNED` ⇒ ghi `Blocked` phần đó, ⛔ không PASS cả TC.</t>
@@ -29959,7 +31019,11 @@
           <t>Cặp đối chứng 1 đơn `RETURNED` + 1 đơn `CANCELLED` cùng tài khoản của `SEED-ACT-03` (test_data_catalog §ACT — Cặp đối chứng CANCELLED ⟷ RETURNED)</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Đã sửa Expected theo app — QC GiangDC2 chốt 2026-09-21 (sau VR-017): đơn "Đã huỷ" hiện ở tab "Đang diễn ra" với badge "Đã huỷ" là hành vi ĐÚNG, không phải bug; thay kết luận BA `C-ACT-04(b)` 2026-09-17 (ẩn khỏi cả 2 tab). ⚠️ Title chưa sửa vì `§10.5` khoá Title (nợ #27 `03_test-cases/v1.1/CHANGELOG.md`). · Mục đích: hai kết cục bất thường nhưng hai cách xử lý ngược nhau — giá trị của TC nằm ở **phép đối chứng**, xem lẻ từng đơn thì không bắt được lỗi "gom chung mọi đơn bất thường vào một nhánh hiển thị". · Căn cứ: `AC-24.2.01` cho vế `RETURNED`; vế `CANCELLED` theo BA trả lời `C-ACT-04(b)` 2026-09-17 — đơn "Đã huỷ" **vẫn ẩn khỏi cả 2 tab**, rule v1.0 CÒN HIỆU LỰC, `§8.12.3` cho mọi vai *"Xem lý do"* đơn huỷ là **PRD chưa cập nhật**. · Phụ thuộc lô `DLV` để có đơn `RETURNED` — lô đó `BLOCKED` thì TC này `BLOCKED`.</t>
@@ -30042,7 +31106,11 @@
           <t>Đơn `EXPIRED` của `SEED-ACT-03` (test_data_catalog §ACT — Text lý do "Hết hạn", ⛔ không seed được qua UI)</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `DOC-v1.1-01 §8.5.1 BR05-03` + `AC-09.1.01` 2026-09-17: chuỗi lý do đổi sang bản **ngắn**, bỏ vế "— tin đã tự động đóng." mà bản v1.0 cùng ID đang assert. · Mục đích: 2 nguồn từng lệch phần đuôi câu; PRD v1.1 nay gọi tên chuỗi lần đầu nên thắng quan sát cũ `KB-ORD-07` (#4). App hiện bản dài ⇒ FAIL và log bug, ⛔ không hạ Expected về bản v1.0. · Chỉ ĐỌC card, ⛔ không tap — `C-ACT-03(c)` và `C-ORD-17` đang nói ngược nhau về việc card Hết hạn có tương tác được không.</t>
@@ -30126,7 +31194,11 @@
           <t>Tài khoản 0 đơn đang hoạt động = `SEED-ACT-02` (test_data_catalog §ACT — Text empty state tab đang-chạy)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-06` Resolved 2026-09-15 (tài liệu đã phê duyệt, `EMP-05`): bản v1.0 chỉ assert "không có card nào" vì text empty state chưa có đặc tả; nay assert verbatim chuỗi + nhãn CTA. · Mục đích: cặp bất đối xứng với `TC-ACT-014` — tab này CÓ đúng 1 CTA, tab kia KHÔNG có; đây là nội dung phải assert, không phải chi tiết trình bày. · Căn cứ: `BR17-01` *"tối đa một CTA"* nên "không có" ở tab kia là lựa chọn thiết kế hợp lệ.</t>
@@ -30204,7 +31276,11 @@
           <t>Tài khoản 0 đơn kết thúc = `SEED-ACT-02` (test_data_catalog §ACT — Text empty state tab hoàn-tất)</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
           <t>Đã sửa theo `C-ORD-06` Resolved 2026-09-15 (`EMP-06`): bản v1.0 chỉ assert "không có card nào"; nay assert verbatim chuỗi + KHÔNG CTA + ẩn hẳn khối lịch sử. · Mục đích: đối chứng âm cho `TC-ACT-012` — hai tab rỗng cạnh nhau nhưng khác nhau ở CTA và ở khối lịch sử; app hiện nút ở tab này là **sai spec**. · Căn cứ: `BR17-01` + `EMP-06`.</t>
@@ -30287,7 +31363,11 @@
           <t>Đơn `COMPLETED` của `SEED-ACT-03` (test_data_catalog §ACT)</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Đã sửa theo `DOC-v1.1-01 §8.14.1 BR14-03` + `§4 SCOPES` 2026-09-17: bản v1.0 chỉ assert "nhấn vào chuỗi sao không mở màn chấm điểm" và cố ý KHÔNG assert sự tồn tại của chuỗi leftover; nay **sự tồn tại của dấu vết đã là defect**. · Mục đích: kết quả phản trực giác so với bản cũ — người chạy quen v1.0 dễ cho PASS khi vẫn thấy ★ trên card. · Căn cứ: `§4` loại trừ vĩnh viễn ★/điểm/tier/chỉ số môi trường. Còn ★ ⇒ **log bug**, ⛔ KHÔNG diễn giải là "dấu vết phase sau". Chạy cùng lô với `SC-GIFT-011` để log 1 bug cho 2 bề mặt.</t>
@@ -30373,7 +31453,11 @@
           <t>Tài khoản 0 đơn ở cả 2 tab = `SEED-ACT-02` (test_data_catalog §ACT — Tài khoản trắng)</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp với `TC-ACT-017` — che thanh tab dưới và khoá cuộn là hai lỗi layout khác bản chất, sửa được lỗi này không đảm bảo hết lỗi kia. · Căn cứ: `DOC-v1.1-01` §8.17.2 BR17-03 + `§6.2 AC-29.1.01`. `ACT` là màn duy nhất có 2 empty state cạnh nhau nên rule hình thức chung của `FR17` đặt home tại đây.</t>
@@ -30452,7 +31536,11 @@
           <t>Tài khoản 0 đơn ở cả 2 tab = `SEED-ACT-02` (test_data_catalog §ACT — Tài khoản trắng)</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Đã sửa Expected + step 5 theo app — QC GiangDC2 chốt 2026-09-21 (sau VR-017): màn rỗng không cuộn/không phản hồi vuốt là hành vi ĐÚNG, không phải bug (`BUG-032` đã xoá). ⚠️ Title chưa sửa vì `§10.5` khoá Title (nợ #28 `03_test-cases/v1.1/CHANGELOG.md`). · Căn cứ gốc: `DOC-v1.1-01` §8.17.2 BR17-03 — QC hiểu "vẫn cuộn được" là màn không bị treo/khoá thao tác, không bắt buộc có phản hồi cuộn khi không có nội dung vượt màn.</t>
@@ -30532,7 +31620,11 @@
           <t>Tài khoản 0 đơn ở cả 2 tab = `SEED-ACT-02`; mạng throttle 3G chậm (test_data_catalog §ACT — Tốc độ mạng)</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
           <t>Mục đích: neo vào `[GAP]` của `SC-ACT-017` — điều kiện *"hiện empty state dựa cờ dữ liệu rỗng, không dựa null field"* là rule **backend**, ⛔ không verify được qua UI, nên TC chỉ assert phần quan sát được. · Căn cứ: `DOC-v1.1-01` §8.17 Pre-Conditions + §8.17.2 BR17-02. Bắt buộc throttle 3G chậm: mạng nhanh thì pha loading trôi qua quá nhanh, không phân biệt được hai trạng thái.</t>
@@ -30741,7 +31833,11 @@
           <t>2 người vận chuyển bấm gần đồng thời (test_data_catalog §ASN v1.1, biên)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (a) — chỉ kiểm chứng được thứ tự tuần tự bằng 2 thiết bị thật; nhánh (b) automation ở `TC-ASN-024`. · Căn cứ: `DOC-v1.1-01 §8.3 BR03-02` · `§9 NFR-06`.</t>
@@ -30818,7 +31914,11 @@
           <t>1 tin NEED POSTED; 50 request đồng thời (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (b) của `SC-ASN-006` — ngưỡng `NFR-06`, chỉ kiểm chứng được bằng concurrency/backend test, không phải manual. · Căn cứ: `DOC-v1.1-01 §9 NFR-06`. ⚠️ Cần công cụ load/concurrency test gọi thẳng API — giao automation/backend, không nằm trong phạm vi vibe-test UI thuần. Đối chứng với `TC-ASN-006` (nhánh a, manual 2 thiết bị).</t>
@@ -30904,7 +32004,11 @@
           <t>3 phiên 3 vai trên 3 thiết bị; mốc đo ≤5 giây (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Mục đích: siết Expected từ định tính ("không cần làm mới", v1.0) sang định lượng **≤5 giây** theo `NFR-08`. · Căn cứ: `DOC-v1.1-01 §9 NFR-08` — "Cách đo: Integration test đa thiết bị". ⚠️ Đo bằng tay có sai số; ưu tiên automation nếu cần độ chính xác cao. · Đã sửa theo delta v1.1 (2026-09-15).</t>
@@ -30987,7 +32091,11 @@
           <t>Tin NEED lệch điểm giao, buổi "Sáng", dùng `SEED-ASN-01` (test_data_catalog §ASN v1.1, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (a) của `SC-ASN-011` v1.1 — vẫn là lệch điểm, không đổi bản chất so v1.0 nhưng đổi khuôn dữ liệu (Khoảng ngày + Buổi thay khung giờ đơn). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-01`. · Đã sửa theo delta v1.1 (2026-09-15): đổi test data từ "khung giờ" sang "khoảng ngày + tập buổi" theo form mới. · Nhãn buổi "Sáng" theo quan sát demo 3-role 2026-09-17 (QA-obs, chưa phải chốt chính thức).</t>
@@ -31063,7 +32171,11 @@
           <t>Tin NEED lệch khoảng ngày (không overlap), buổi "Giờ nào cũng được", dùng `SEED-ASN-01` (test_data_catalog §ASN v1.1, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (b) của `SC-ASN-011` v1.1 — thay "khung giờ tách rời hoàn toàn" (v1.0) bằng đúng định nghĩa "khoảng ngày KHÔNG overlap" chính thức; cố tình chọn buổi "Giờ nào cũng được" để khẳng định biến buổi KHÔNG cứu được khi ngày đã lệch (2 điều kiện độc lập). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-01`. · Đã sửa theo delta v1.1 (2026-09-15). · Nhãn buổi theo quan sát demo 3-role 2026-09-17 (QA-obs).</t>
@@ -31139,7 +32251,11 @@
           <t>Tin NEED ngày overlap nhưng buổi "Sau giờ làm" không chung với "Sáng"/"Chiều" của OFFER, dùng `SEED-ASN-01` (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (c) — case MỚI của `SC-ASN-011` v1.1, trước đây không tách được vì chưa có định nghĩa buổi độc lập với ngày; phân biệt với nhánh (b) "ngày không overlap". · Căn cứ: `DOC-v1.1-01 §8.4 BR04-01` · `BR04-02`. · Nhãn buổi "Sau giờ làm" theo quan sát demo 3-role 2026-09-17 (QA-obs, chưa phải chốt chính thức).</t>
@@ -31215,7 +32331,11 @@
           <t>Tin NEED khớp đầy đủ 3 điều kiện, buổi "Sáng", dùng `SEED-ASN-01`; ngưỡng đo ≤60s (NFR-04) (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhánh (d) — vế dương đối chứng với 3 nhánh âm (a)(b)(c), gắn thêm ngưỡng định lượng `NFR-04` ≤60s chưa từng assert ở `SC-ASN-009` (CARRIED, chỉ xác nhận CÓ thông báo, không đo thời gian). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-01/02` · `§9 NFR-04`. · Nhãn buổi "Sáng" theo quan sát demo 3-role 2026-09-17 (QA-obs). Demo cũng xác nhận trực tiếp cơ chế sync realtime tồn tại (dùng chéo làm evidence cho `TC-ASN-008`).</t>
@@ -31299,7 +32419,11 @@
           <t>3 tin NEED khớp tuyến, tự đăng qua UI (test_data_catalog §ASN v1.1, mốc dưới trần)</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
           <t>Mục đích: mốc dưới trần trong bộ ba 3/5/6 — xác nhận tài khoản B (người ĐĂNG TUYẾN) là người nhận thông báo và &lt;5 tin thì gửi đúng số đó, đúng kết luận `C-ASN-04(a)(c)`. · Căn cứ: `DOC-v1.1-01 §8.4 BR04-04` (dư) + kết luận BA `C-ASN-04` Resolved 2026-09-17. · Đã sửa theo delta v1.1: đổi test data OFFER sang khoảng ngày + tập buổi, giữ nguyên mốc số 3/5/6 đã BA chốt.</t>
@@ -31377,7 +32501,11 @@
           <t>5 tin NEED khớp tuyến, tự đăng qua UI; ghi baseline thông báo tồn của B (test_data_catalog §ASN v1.1, mốc đúng trần tài khoản)</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Mục đích: mốc đúng trần — biên hợp lệ, cặp với `TC-ASN-017` (mốc vượt trần). · Căn cứ: `DOC-v1.1-01 §8.4 BR04-04` (dư) + `C-ASN-04` Resolved 2026-09-17. · Đã sửa theo delta v1.1: đổi test data OFFER sang khoảng ngày + tập buổi. · ✏️ Sửa 2026-09-21 (QC GiangDC2 recheck — KHÔNG phải bug): trần 5 thông báo khớp tuyến tính theo TÀI KHOẢN, mọi tuyến cộng dồn, ⛔ không phải theo từng tuyến. Căn cứ đo: VR-010 (5 tin NEED khớp → 4 thông báo mới + 1 tồn = 5). ✅ BA đã xác nhận lại 2026-09-21 (QC GiangDC2 báo lại, chưa có văn bản): trần tính theo TÀI KHOẢN — thay kết luận cũ `C-ASN-04(e)` (2026-09-17: độc lập theo từng tuyến).</t>
@@ -31456,7 +32584,11 @@
           <t>6 tin NEED khớp cùng 1 tuyến OFFER, tự đăng qua UI (test_data_catalog §ASN v1.1, mốc vượt trần)</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
           <t>Mục đích: mốc vượt trần — xác nhận rule `C-ASN-04(d)`: tuyến ĐÃ đủ 5 thì KHÔNG gửi thêm cho tin mới. · Căn cứ: `DOC-v1.1-01 §8.4 BR04-04` (dư) + `C-ASN-04` Resolved 2026-09-17. ⛔ Trần KHÔNG cộng dồn theo ngày; nếu app chặn theo ngày ⇒ FAIL và log bug.</t>
@@ -31533,7 +32665,11 @@
           <t>2 tuyến OFFER của cùng tài khoản B, dùng chung 1 trần 5 theo tài khoản (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Mục đích: xác nhận `C-ASN-04(e)` — trần ĐỘC LẬP theo từng tuyến (mỗi lần đăng "Tôi nhận giao hàng"); rủi ro thật nếu backend dùng chung 1 bộ đếm cho cả tài khoản. · Căn cứ: kết luận BA `C-ASN-04(e)`, `risk_assessment.md` Resolved 2026-09-17. · ✏️ Sửa 2026-09-21 (QC GiangDC2 recheck — KHÔNG phải bug): ĐẢO kỳ vọng — trần 5 tính theo TÀI KHOẢN nên tuyến thứ hai KHÔNG có slot riêng. Căn cứ đo: VR-010 (OFFER tuyến 2 + 1 tin NEED khớp, tổng vẫn 5, 0 thông báo mới). ✅ BA đã xác nhận lại 2026-09-21 (QC GiangDC2 báo lại, chưa có văn bản): trần tính theo TÀI KHOẢN — thay kết luận cũ `C-ASN-04(e)` (2026-09-17: độc lập theo từng tuyến). ⚠️ `Test Title` giữ nguyên (§10.5 không cho đổi tiêu đề) nên tiêu đề CŨ ('độc lập, không cộng dồn') mô tả rule BA cũ — đọc theo Expected.</t>
@@ -31618,7 +32754,11 @@
           <t>2 tin trùng tuyến ở 2 thời điểm + 1 tin không trùng tuyến đăng sớm nhất (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
           <t>Mục đích: làm rõ (không phải đảo) — độ gần tuyến vẫn là tầng ưu tiên số 1 (nhị phân), thời gian đăng chỉ là tầng 2 khi cùng trùng tuyến; v1.0 chỉ test được tầng 2, thiếu vế tầng 1 vs tin không trùng tuyến. · Căn cứ: `DOC-v1.1-01 §8.3 BR03-06`. · Đã sửa theo delta v1.1 (2026-09-15): thêm tin không-trùng-tuyến để kiểm chứng tầng 1.</t>
@@ -31701,7 +32841,11 @@
           <t>Tin OFFER của B; token tài khoản D không sở hữu tin đó (test_data_catalog §ASN v1.1)</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
           <t>Mục đích: mở rộng `BR03-05`/`SC-ASN-007` (ẩn trên UI) sang tầng API — kiểm tra quyền phải ở tầng máy chủ, không chỉ ẩn giao diện. · Căn cứ: `DOC-v1.1-01 §9 NFR-11`. ⚠️ Cần công cụ gọi API trực tiếp (Postman/tương đương) — UI không có đường dẫn tới tin OFFER của người khác nên không chạy được bằng thao tác UI thuần. Giao automation/backend/security test.</t>
@@ -31909,7 +33053,11 @@
           <t>Lý do 4 ký tự "abcd" (test_data_catalog §CNL v1.1, biên dưới)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Mục đích: siết thêm 2 chi tiết Then mà v1.0 chưa có — nút vô hiệu hoá SẴN (không phải bấm rồi báo lỗi) và lỗi hiện đúng vị trí dưới ô lý do. · Căn cứ: `BR11-01` + `VAL-04` + `AC-25.1.03` (PRD phê duyệt, không còn là override QA). ⚠ Dự kiến FAIL — app hiện cho qua ⇒ log bug, ⛔ không hạ chuẩn TC theo hành vi app. · Đã sửa theo analyze v1.1 (2026-09-15): bỏ vế "5 ký tự được nhận" — đã có `TC-CNL-003` (CARRIED) cover, tránh trùng. · Đã sửa theo §10.4 (2026-09-17): gộp 3 điểm quan sát (nút khoá · lỗi đúng vị trí · trạng thái đơn) vào 1 Expected ở step cuối.</t>
@@ -31987,7 +33135,11 @@
           <t>Lý do gồm 5 dấu cách (test_data_catalog §CNL v1.1, biên)</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Mục đích: mốc thứ tư trong bộ boundary lý do (rỗng → 4 ký tự → 5 ký tự → 5 dấu cách). · Căn cứ: `VAL-03` (trim) + `VAL-04` (PRD phê duyệt, không còn là override QA). ⚠ Dự kiến FAIL — `KB-CNL-02` đã live-verify app cho qua ⇒ log bug. · ⚠️ Biên "5 dấu cách" dễ bị gõ nhầm thành "     x" khi nhập tay — ghi rõ trong Test Data để tester không tự ý gõ sai.</t>
@@ -32070,7 +33222,11 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
           <t>🔴 Bản v1.0 cùng ID assert KHÔNG có chức năng này — kỳ vọng ngược hoàn toàn, phải dùng bản v1.1. · Căn cứ: `§4 SCOPES` In-scope + `§8.16` + `AC-25.2.01`. ⚠ Dự kiến FAIL nếu STG chưa build `FR16` ⇒ log gap PRD↔app, ⛔ không diễn giải thành "vẫn out of scope". · Đọc chéo `TS` — chỉ kiểm nút tồn tại + mở được, KHÔNG lặp nội dung form/ảnh (home ở `SC-TS-008..015`). · Đã sửa theo §10.4 (2026-09-17): tách riêng theo vai — vai Người vận chuyển ở `TC-CNL-015`, vai Người nhận ở `TC-CNL-016` (mỗi vai độc lập, có thể fail riêng theo `BR11-04` "bất kỳ vai trò nào").</t>
@@ -32146,7 +33302,11 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
           <t>Mục đích: vai độc lập với `TC-CNL-006` (vai Người gửi) — `BR11-04` yêu cầu "bất kỳ vai trò nào", mỗi vai có thể fail riêng. · Căn cứ: giống `TC-CNL-006`. · Đọc chéo `TS` — chỉ kiểm nút tồn tại, không lặp nội dung form (home `SC-TS-008..015`). TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1.</t>
@@ -32222,7 +33382,11 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Mục đích: vai độc lập với `TC-CNL-006`/`015` — `BR11-04` yêu cầu "bất kỳ vai trò nào". · Căn cứ: giống `TC-CNL-006`. · Đọc chéo `TS` — chỉ kiểm nút tồn tại, không lặp nội dung form (home `SC-TS-008..015`). TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1.</t>
@@ -32303,7 +33467,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>8. Block LỊCH SỬ có nhiều hơn số dòng đã ghi ở bước 3 đúng 1 dòng; dòng mới ghi đủ 3 thành phần: vai "Người gửi", lý do "Huy vi trung lich" và thời điểm (timestamp) huỷ.</t>
+          <t>8. Block LỊCH SỬ có nhiều hơn số dòng đã ghi ở bước 3 đúng 1 dòng; dòng mới ghi đúng nhãn hành động huỷ đơn của Người gửi (KHÔNG phải nhãn "Đã huỷ nhận đơn" của luồng huỷ nhận), kèm danh tính người thực hiện (app ghi tên người, không ghi vai trò — chấp nhận theo hành vi nhất quán toàn app), lý do "Huy vi trung lich" và thời điểm (timestamp) huỷ.</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -32311,10 +33475,14 @@
           <t>Đơn `MATCHED`; block LỊCH SỬ đã có mốc trước đó (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: `BR11-02` đòi đủ 3 thành phần (vai trò · lý do · thời điểm) — v1.0 chỉ assert 2, thiếu timestamp. · Căn cứ: `BR11-02` + `AC-25.1.01` (PRD phê duyệt, không còn là override QA). ⚠ Dự kiến FAIL — app hiện chỉ hiện banner, không ghi log ⇒ log bug. · Kiểm chéo cùng lô với `SC-TS-003` + `SC-DLV-062` — cùng vỡ thì gộp 1 bug report. · Đã sửa theo analyze v1.1 (2026-09-15): thêm assert thời điểm (timestamp) vào Expected.</t>
+          <t>Mục đích: `BR11-02` đòi đủ 3 thành phần (vai trò · lý do · thời điểm) — v1.0 chỉ assert 2, thiếu timestamp. · Căn cứ: `BR11-02` + `AC-25.1.01` (PRD phê duyệt, không còn là override QA). ⚠ Dự kiến FAIL — app hiện chỉ hiện banner, không ghi log ⇒ log bug. · Kiểm chéo cùng lô với `SC-TS-003` + `SC-DLV-062` — cùng vỡ thì gộp 1 bug report. · Đã sửa theo analyze v1.1 (2026-09-15): thêm assert thời điểm (timestamp) vào Expected. · 🔁 Đính chính 2026-09-22 (QC): vế "ghi vai trò" đổi thành "ghi tên người" (app nhất quán ghi tên ở mọi dòng LỊCH SỬ, không riêng dòng huỷ) — BUG-035 đã xoá, không phải bug. Vế nhãn hành động sai ("Đã huỷ nhận đơn" thay vì nhãn đúng của huỷ đơn) vẫn là lỗi độc lập, còn giữ ở BUG-034 — verdict TC này vẫn FAIL vì lý do này.</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
@@ -32386,7 +33554,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9. Dòng "Ghép thành công" vẫn còn trong block LỊCH SỬ ở bước 8 (không bị xoá), có thêm 1 dòng log ghi hành động huỷ nhận kèm vai "Người vận chuyển" và lý do "Doi ca lam viec"; đơn chuyển về trạng thái "Chờ ghép" và hiện lại trên bảng tin.</t>
+          <t>9. Dòng "Ghép thành công" vẫn còn trong block LỊCH SỬ ở bước 8 (không bị xoá), có thêm 1 dòng log ghi đúng nhãn hành động huỷ nhận "Đã huỷ nhận đơn" kèm danh tính người thực hiện (app ghi tên người, không ghi vai trò — chấp nhận theo hành vi nhất quán toàn app) và lý do "Doi ca lam viec"; đơn chuyển về trạng thái "Chờ ghép" và hiện lại trên bảng tin.</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -32394,10 +33562,14 @@
           <t>Đơn `MATCHED`; block LỊCH SỬ có dòng "Ghép thành công" (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: log phải bất biến — xoá dòng cũ là phá tính bằng chứng của cả timeline; đồng thời đơn phải quay lại vòng đời bình thường, không mắc kẹt. · Căn cứ: `BR11-03` + `AC-25.1.02` (PRD phê duyệt, không còn là override QA — trước dựa `BR-INT-04` suy diễn). ⚠ Dự kiến FAIL — `KB-CNL-01` đã live-verify app XOÁ dòng "Ghép thành công" ⇒ log bug. · Cùng nhóm rule truy vết "bằng chứng đã ghi thì bất biến" — chạy cùng lô với `SC-USR-017`/`SC-ORD-065`/`SC-DLV-062`, cùng vỡ thì gộp 1 bug report. · Đã sửa theo §10.4 (2026-09-17): gộp 2 điểm kiểm (log giữ nguyên + đơn về POSTED/hiện lại bảng tin) vào 1 Expected ở step cuối; bỏ Expected ở step 4 (chỉ còn observation baseline, không phải case fail độc lập).</t>
+          <t>Mục đích: log phải bất biến — xoá dòng cũ là phá tính bằng chứng của cả timeline; đồng thời đơn phải quay lại vòng đời bình thường, không mắc kẹt. · Căn cứ: `BR11-03` + `AC-25.1.02` (PRD phê duyệt, không còn là override QA — trước dựa `BR-INT-04` suy diễn). ⚠ Dự kiến FAIL — `KB-CNL-01` đã live-verify app XOÁ dòng "Ghép thành công" ⇒ log bug. · Cùng nhóm rule truy vết "bằng chứng đã ghi thì bất biến" — chạy cùng lô với `SC-USR-017`/`SC-ORD-065`/`SC-DLV-062`, cùng vỡ thì gộp 1 bug report. · Đã sửa theo §10.4 (2026-09-17): gộp 2 điểm kiểm (log giữ nguyên + đơn về POSTED/hiện lại bảng tin) vào 1 Expected ở step cuối; bỏ Expected ở step 4 (chỉ còn observation baseline, không phải case fail độc lập). · 🔁 Đính chính 2026-09-22 (QC): vế "ghi vai trò" đổi thành "ghi tên người" (chấp nhận, nhất quán toàn app) — BUG-035 đã xoá. Không còn vướng mắc nào khác ⇒ verdict FAIL → PASS.</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -32469,7 +33641,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>2. KHÔNG còn nút huỷ đơn thường nào; chỉ có đúng 2 nút hành động liên quan huỷ: "Yêu cầu hoàn hàng" và "Báo cáo sự cố".</t>
+          <t>2. KHÔNG còn nút huỷ đơn thường nào; chỉ còn đúng 1 nút hành động liên quan: "Báo cáo sự cố". KHÔNG có nút "hoàn hàng" nào ở màn này của Người gửi — hoàn hàng (RETURNING) là hành động do Người vận chuyển khởi tạo (FR09), Người gửi không có control kích hoạt trực tiếp.</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -32477,10 +33649,14 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `AC-25.2.01` + `BR11-04` ("bất kỳ vai trò nào"). · Đọc chéo `DLV` (`SC-DLV-053/054` — home của đường "hoàn hàng") và `TS` (`SC-TS-008..015` — home của form "báo sự cố"); TC này chỉ đếm đúng 2 nút tồn tại, KHÔNG lặp nội dung luồng con. · Đã sửa theo §10.4 (2026-09-17): tách theo vai — vai Người vận chuyển ở `TC-CNL-018`, vai Người nhận ở `TC-CNL-019`.</t>
+          <t>Căn cứ: `AC-25.2.01` + `BR11-04` ("bất kỳ vai trò nào") — chỉ đảm bảo ở MỨC TRẠNG THÁI (hoàn hàng vẫn là 1 trong 2 lối thoát hợp lệ của đơn), KHÔNG đặt tên nút UI. Đọc chéo `DLV` `FR09` §8.9 (trang 43) — trigger thật của RETURNING là Người vận chuyển chọn "Cầm hàng về" ở màn "Xử lý đơn hàng", không phải nút trên màn Theo dõi đơn của Sender/Receiver. Và `TS` (`SC-TS-008..015` — home của form "báo sự cố"). · Đã sửa theo §10.4 (2026-09-17): tách theo vai — vai Người vận chuyển ở `TC-CNL-018`, vai Người nhận ở `TC-CNL-019`. · 🔁 Đính chính 2026-09-22 (QC, sau khi đối chiếu PRD gốc): bỏ giả định nút "Yêu cầu hoàn hàng" trên màn Sender/Receiver — không tồn tại trong PRD, TC viết sai. BUG-033 đã xoá, verdict FAIL → PASS.</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
@@ -32545,7 +33721,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2. KHÔNG còn nút huỷ đơn thường nào; chỉ có đúng 2 nút hành động liên quan huỷ: "Yêu cầu hoàn hàng" và "Báo cáo sự cố".</t>
+          <t>2. KHÔNG còn nút huỷ đơn thường nào; có nút "Báo cáo sự cố" VÀ đường vào luồng hoàn hàng đi qua màn giao hàng: bấm nút "Đã đến địa điểm giao hàng" → màn "Xử lý đơn hàng" → chọn chế độ "Cầm hàng về" (FR09). KHÔNG có một nút riêng tên "Yêu cầu hoàn hàng" trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -32553,10 +33729,14 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: vai độc lập với `TC-CNL-017`/`019` — `BR11-04` yêu cầu "bất kỳ vai trò nào". · Căn cứ: giống `TC-CNL-017`. · Đọc chéo `DLV`/`TS`, không lặp nội dung luồng con. TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1.</t>
+          <t>Mục đích: vai độc lập với `TC-CNL-017`/`019` — `BR11-04` yêu cầu "bất kỳ vai trò nào". · Căn cứ: giống `TC-CNL-017`. · Đọc chéo `DLV`/`TS`, không lặp nội dung luồng con. TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1. · 🔁 Đính chính 2026-09-22 (QC): chỉ vai Người vận chuyển mới có đường vào hoàn hàng (qua FR09 "Xử lý đơn hàng" → "Cầm hàng về"), không phải nút riêng "Yêu cầu hoàn hàng". BUG-033 đã xoá, verdict FAIL → PASS. · 🔁 Đính chính 2026-09-22 (QC, bổ sung): chốt tên chính thức nút vào luồng hoàn hàng ở v1.1 là "Đã đến địa điểm giao hàng" (đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện CHƯA đổi theo tên mới (evidence VR-018 2026-09-21), xem BUG-044.</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -32621,7 +33801,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>2. KHÔNG còn nút huỷ đơn thường nào; chỉ có đúng 2 nút hành động liên quan huỷ: "Yêu cầu hoàn hàng" và "Báo cáo sự cố".</t>
+          <t>2. KHÔNG còn nút huỷ đơn thường nào; chỉ còn đúng 1 nút hành động liên quan: "Báo cáo sự cố". KHÔNG có nút "hoàn hàng" nào ở màn này của Người nhận — hoàn hàng (RETURNING) là hành động do Người vận chuyển khởi tạo (FR09), Người nhận không có control kích hoạt trực tiếp.</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -32629,10 +33809,14 @@
           <t>Đơn `IN_TRANSIT` của `SEED-DLV-01` (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: vai độc lập với `TC-CNL-017`/`018` — `BR11-04` yêu cầu "bất kỳ vai trò nào". · Căn cứ: giống `TC-CNL-017`. · Đọc chéo `DLV`/`TS`, không lặp nội dung luồng con. TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1.</t>
+          <t>Mục đích: vai độc lập với `TC-CNL-017`/`018` — `BR11-04` yêu cầu "bất kỳ vai trò nào". · Căn cứ: giống `TC-CNL-017`. · Đọc chéo `DLV`/`TS`, không lặp nội dung luồng con. TC mới tách theo §10.4 (2026-09-17), không có ID cũ 1-1. · 🔁 Đính chính 2026-09-22 (QC): bỏ giả định nút "Yêu cầu hoàn hàng" trên màn Người nhận — không tồn tại trong PRD. BUG-033 đã xoá, verdict FAIL → PASS.</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
@@ -32705,7 +33889,11 @@
           <t>Đơn `INCIDENT` (test_data_catalog §CNL v1.1) — ⚠ có thể chưa seed được nếu STG chưa build `FR16`</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
           <t>⚠️ Verdict đúng khi STG chưa build `INCIDENT`/`FR16` là **BLOCKED**, ⛔ không đánh PASS vì "không thấy đơn tự chuyển". · Căn cứ: `AC-25.2.01`. · ⛔ Không assert trạng thái đích cụ thể sau khi admin xử lý — `C-CNL-03` chốt trạng thái đích tuỳ dev. · ⛔ Không assert banner/thông báo "đang được hỗ trợ" — BA xác nhận người dùng không nhận thông báo gì trong lúc chờ.</t>
@@ -32788,7 +33976,11 @@
           <t>2 phiên song song A (Người gửi) + B (Người vận chuyển); đơn `MATCHED`, popup "Tôi đã lấy hàng" đang mở ở phiên B (test_data_catalog §CNL v1.1, ô biên duy nhất của delta)</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
           <t>⭐ Vùng dễ có lỗi race thật — nếu backend chỉ kiểm `status == MATCHED` mà không kiểm hành động đã bấm thì huỷ sẽ lọt qua. · Căn cứ: PRD đổi cách phát biểu ngưỡng từ trạng thái sang hành động (`§8.11 Pre-Conditions` + `AC-25.1.01` — "MATCHED khi CHƯA bấm Tôi đã lấy hàng", không phải "MATCHED" đơn thuần). · Cần thao tác đồng thời 2 phiên trong cùng khoảnh khắc — không dựng được bằng 1 tài khoản.</t>
@@ -32871,7 +34063,11 @@
           <t>Giá trị assert-absent: bề mặt "Admin vận hành" (test_data_catalog §CNL v1.1)</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
           <t>`[GAP]` theo `Project_rule §10.1` — PRD nêu actor "Admin vận hành" nhưng không mô tả bề mặt nào ⇒ ghi nhận thiếu vắng, ⛔ không viết TC khẳng định hành vi Admin. · Căn cứ: `C-CNL-03` Resolved 2026-09-16 — dev xử lý tay qua Google Form ngoài app, không có tool/màn. · Gap nghiệp vụ cần nêu PM: nếu chỉ admin đóng được `INCIDENT` mà không có đường tới admin, đơn có thể treo vĩnh viễn.</t>
@@ -33080,7 +34276,7 @@
           <t>Đơn `RESCHEDULED`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="n"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Mục đích: 1 trong 3 ô vai của nhóm trạng thái `RESCHEDULED` — mỗi vai fail độc lập. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. ⚠ Thanh timeline vẫn hiện đúng 5 mốc và mốc "Đang giao" đang active — đây là thiết kế đã chốt (`C-DLV-05(d)` Resolved 2026-09-17), ⛔ không FAIL vì thiếu mốc mới.</t>
@@ -33159,7 +34355,7 @@
           <t>Đơn `RESCHEDULED`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="n"/>
       <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED — đây là vai DUY NHẤT có nút hành động thật ở trạng thái này, 2 vai kia chỉ xem.</t>
@@ -33238,7 +34434,7 @@
           <t>Đơn `RESCHEDULED`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với TC-DLV-032 — quyền giao lại chỉ thuộc người vận chuyển. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED.</t>
@@ -33317,7 +34513,7 @@
           <t>Đơn `RETURNING`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="inlineStr">
         <is>
           <t>Mục đích: người gửi là vai DUY NHẤT đóng được đơn ở nhánh hoàn hàng — cặp với TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
@@ -33396,7 +34592,7 @@
           <t>Đơn `RETURNING`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="n"/>
       <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
@@ -33475,7 +34671,7 @@
           <t>Đơn `RETURNING`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="n"/>
       <c r="M8" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
@@ -33555,7 +34751,7 @@
           <t>Đơn `RETURNED`, `CANCELLED`, `EXPIRED`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhóm ba trạng thái đóng phải cho CÙNG một nhãn — lệch giữa ba đơn mới là defect. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng (PRD chỉ mô tả cấp danh mục, không có microcopy riêng cho từng trạng thái).</t>
@@ -33635,7 +34831,7 @@
           <t>Đơn `RETURNED`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="n"/>
       <c r="M10" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với TC-DLV-037 — quyền đăng lại chỉ thuộc người gửi. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng.</t>
@@ -33715,7 +34911,7 @@
           <t>Đơn `RETURNED`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="n"/>
       <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng.</t>
@@ -33803,7 +34999,7 @@
           <t>Đơn `INCIDENT` đã vượt mốc 2h và 4h = `SEED-DLV-04` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="n"/>
       <c r="M13" s="6" t="inlineStr">
         <is>
           <t>Mục đích: chốt ranh giới nhánh sự cố ⟷ luồng tự đóng thường — dễ lập trình sai thành "quá giờ thì đóng". · Căn cứ: `DOC-v1.1-01` §8.10.1 BR10-04 (SC mới gắn REQ giữ ID, không sửa `SC-DLV-024` v1.0 vốn đúng cho nhánh thường). ⛔ Không assert vế "admin xử lý" — role admin out of scope v1.1 (`C-DLV-07` Resolved 2026-09-17).</t>
@@ -33891,7 +35087,11 @@
           <t>1 ảnh JPG ≤5MB (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 — `C-DLV-04` Resolved 2026-09-15 (ảnh lúc lấy hàng có tồn tại). ⚠ `RISK-DLV-11`: popup "Tôi đã lấy hàng" trên demo chưa thấy field ảnh — không thấy ô đính ảnh trên STG ⇒ log bug, ⛔ không sửa TC theo demo.</t>
@@ -33970,7 +35170,11 @@
           <t>0 ảnh — biên dưới hợp lệ (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên dưới với TC-DLV-041 — ảnh lúc lấy hàng là tuỳ chọn, khác hẳn ảnh lúc giao hàng (bắt buộc ≥1, xem TC-DLV-047). · Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 *"tuỳ chọn nhưng được khuyến nghị mạnh"*.</t>
@@ -34042,7 +35246,7 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn nút mở màn "Xác nhận đã giao".
+3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
 4. Chọn "Người nhận" ở field "Giao cho".
 5. Đính 1 ảnh JPG từ thư viện thiết bị.
 6. Nhấn "Xác nhận đã giao hàng" và đồng ý ở popup xác nhận.
@@ -34059,10 +35263,14 @@
           <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02`; đối tượng nhận "Người nhận" + 1 ảnh bằng chứng (test_data_catalog §DLV — Đối tượng nhận, Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: luồng chính của `FR07` mở rộng — 3 nhánh còn lại (TC-DLV-044/045/046) đều rẽ từ đúng màn này. · Căn cứ: `DOC-v1.1-01` §8.7.2 + §8.12.4 mẫu câu 1. `RISK-DLV-08` đã Confirmed qua demo 2026-09-16 (luồng submit chạy đúng); vẫn double-check locator trên STG trước khi hardening.</t>
+          <t>Mục đích: luồng chính của `FR07` mở rộng — 3 nhánh còn lại (TC-DLV-044/045/046) đều rẽ từ đúng màn này. · Căn cứ: `DOC-v1.1-01` §8.7.2 + §8.12.4 mẫu câu 1. `RISK-DLV-08` đã Confirmed qua demo 2026-09-16 (luồng submit chạy đúng); vẫn double-check locator trên STG trước khi hardening. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -34124,7 +35332,7 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn nút mở màn "Xác nhận đã giao".
+3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
 4. Chọn "Người được uỷ quyền" ở field "Giao cho".
 5. Nhập "Nguyễn Văn Bảy" vào ô tên người nhận thay.
 6. Nhập "0912345678" vào ô số điện thoại người nhận thay.
@@ -34143,10 +35351,10 @@
           <t>Đơn `IN_TRANSIT` đơn #2 của `SEED-DLV-02`; tên 12 ký tự + SĐT hợp lệ (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr"/>
+      <c r="L19" s="6" t="n"/>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: chốt giá trị tự sinh của "Uỷ quyền bởi" theo MÀN VÀO chứ không theo loại đối tượng nhận — đối chứng âm là TC-DLV-051 (vào từ màn "Liên hệ người gửi" thì tự sinh "Người gửi"). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03/BR07-04/BR07-05 + §8.12.4 mẫu câu 2. Trường "Uỷ quyền bởi" chỉ đọc, không sửa được.</t>
+          <t>Mục đích: chốt giá trị tự sinh của "Uỷ quyền bởi" theo MÀN VÀO chứ không theo loại đối tượng nhận — đối chứng âm là TC-DLV-051 (vào từ màn "Liên hệ người gửi" thì tự sinh "Người gửi"). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03/BR07-04/BR07-05 + §8.12.4 mẫu câu 2. Trường "Uỷ quyền bởi" chỉ đọc, không sửa được. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
@@ -34208,7 +35416,7 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn nút mở màn "Xác nhận đã giao".
+3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
 4. Chọn "Quầy lễ tân" ở field "Giao cho".
 5. Đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" khi vẫn để trống cả hai ô của khối "NGƯỜI NHẬN TẠI QUẦY".
 6. Nhập "Trần Thị Lan" vào ô "Họ tên người trực quầy".
@@ -34227,10 +35435,10 @@
           <t>Đơn `IN_TRANSIT` đơn #3 của `SEED-DLV-02`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: step 5 là vế âm gộp trong cùng TC — submit khi 2 ô trống phải không đi được, nên step 9 mới quan sát được kết quả dương. · Căn cứ: `C-DLV-06` Resolved 2026-09-17 (BA *"trên UI có dấu * bắt buộc mà"*, QA submit thử với 2 ô trống thì form không đi) + `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 3. ⛔ Chưa assert cờ "không liên lạc được" và `NTF-05`/`NTF-11` — `C-DLV-08` (a)(b) còn Partially, QA tự xác minh qua block "LỊCH SỬ" trước khi siết TC.</t>
+          <t>Mục đích: step 5 là vế âm gộp trong cùng TC — submit khi 2 ô trống phải không đi được, nên step 9 mới quan sát được kết quả dương. · Căn cứ: `C-DLV-06` Resolved 2026-09-17 (BA *"trên UI có dấu * bắt buộc mà"*, QA submit thử với 2 ô trống thì form không đi) + `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 3. ⛔ Chưa assert cờ "không liên lạc được" và `NTF-05`/`NTF-11` — `C-DLV-08` (a)(b) còn Partially, QA tự xác minh qua block "LỊCH SỬ" trước khi siết TC. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -34292,7 +35500,7 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn nút mở màn "Xác nhận đã giao".
+3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
 4. Chọn "Quầy bảo vệ" ở field "Giao cho".
 5. Nhập "Lê Văn Tám" vào ô "Họ tên người trực quầy".
 6. Nhập "0901112223" vào ô "Số điện thoại".
@@ -34311,10 +35519,10 @@
           <t>Đơn `IN_TRANSIT` đơn #4 của `SEED-DLV-02`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr"/>
+      <c r="L21" s="6" t="n"/>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-045 — hai quầy dùng hai mẫu câu nhật ký khác nhau, lập trình gộp 1 chuỗi là defect. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 4. ⛔ Chưa assert cờ/`NTF` — `C-DLV-08` (a)(b) còn Partially.</t>
+          <t>Mục đích: cặp với TC-DLV-045 — hai quầy dùng hai mẫu câu nhật ký khác nhau, lập trình gộp 1 chuỗi là defect. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 4. ⛔ Chưa assert cờ/`NTF` — `C-DLV-08` (a)(b) còn Partially. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
@@ -34376,7 +35584,7 @@
         <is>
           <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
 2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn nút mở màn "Xác nhận đã giao".
+3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
 4. Chọn "Người nhận" ở field "Giao cho" mà chưa đính ảnh nào.
 5. Check trạng thái nút "Xác nhận đã giao hàng".
 6. Đính 1 ảnh JPG từ thư viện thiết bị.
@@ -34393,10 +35601,10 @@
           <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02`; 0 ảnh (chặn) và 1 ảnh (biên dưới hợp lệ) (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="n"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: cặp biên dưới 0⟷1 của ảnh bằng chứng lúc giao — ngược hẳn ảnh lúc lấy hàng (TC-DLV-042, 0 ảnh vẫn hợp lệ). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-02. Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1 vì TC đó sẽ đẩy đơn sang "Đã giao".</t>
+          <t>Mục đích: cặp biên dưới 0⟷1 của ảnh bằng chứng lúc giao — ngược hẳn ảnh lúc lấy hàng (TC-DLV-042, 0 ảnh vẫn hợp lệ). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-02. Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1 vì TC đó sẽ đẩy đơn sang "Đã giao". · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -34474,7 +35682,7 @@
           <t>Đơn `DELIVERED` có 1 ảnh bằng chứng = `SEED-DLV-05` (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
-      <c r="L23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="n"/>
       <c r="M23" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-07 — ảnh gắn vào mốc nhật ký là bất biến. Liên quan cùng nhóm bất biến với TC-DLV-078 (log append-only).</t>
@@ -34556,7 +35764,7 @@
           <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="n"/>
       <c r="M24" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng âm cho TC-DLV-043 — popup phải là gate thật, không phải thông báo trang trí. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-06 (popup nêu rõ hệ quả không thể hoàn tác trước khi ghi mốc). Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1.</t>
@@ -34645,7 +35853,11 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
           <t>Mục đích: `BR08-02` ghi thứ tự NGƯỢC (lễ tân trước bảo vệ) và mô tả 1 danh sách 4 bước — assert theo PRD sẽ FAIL oan. · Căn cứ: `C-DLV-06` **Resolved 2026-09-17** — cấu trúc 4 tầng (màn "Xác nhận đã giao" → màn "Liên hệ người gửi" → modal "Chưa liên lạc được?" → màn "Xử lý đơn hàng") và thứ tự bảo-vệ-trước là oracle chính thức, khớp `AC-17.1.01`/`§8.8.2`. App lệch bản này ⇒ log bug và dẫn `C-DLV-06`, ⛔ không sửa TC theo `BR08-02`.</t>
@@ -34724,7 +35936,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03` (test_data_catalog §DLV — Tên người nhận thay)</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="n"/>
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t>Mục đích: đối chứng với TC-DLV-044 — cùng loại đối tượng nhận nhưng khác MÀN VÀO nên "Uỷ quyền bởi" phải ra giá trị ngược lại; và ở màn này ⛔ KHÔNG prefill người uỷ quyền người gửi đã khai. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-03 + §8.7.1 BR07-05. Gộp bốn quan sát vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả bốn thuộc cùng một trạng thái tĩnh của màn.</t>
@@ -34808,7 +36020,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
-      <c r="L28" s="6" t="inlineStr"/>
+      <c r="L28" s="6" t="n"/>
       <c r="M28" s="6" t="inlineStr">
         <is>
           <t>Mục đích: đường thứ hai tới cùng kết cục của TC-DLV-045 — hai đường phải cùng đòi tên người trực quầy, SĐT và ảnh. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-04 + §8.12.4 mẫu câu 3. ⛔ Chưa assert điểm phân biệt với TC-DLV-045 (cờ "không liên lạc được" / `NTF-05` ⟷ `NTF-11`) — `C-DLV-08` (a)(b) còn Partially, QA vibe-check block "LỊCH SỬ" xong mới siết. ⛔ Không assert hạn giữ hàng 4h/24h — out of scope v1.1.</t>
@@ -34890,7 +36102,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; ô tên người trực quầy rỗng (test_data_catalog §DLV — Tên người trực quầy, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="n"/>
       <c r="M29" s="5" t="inlineStr">
         <is>
           <t>Mục đích: chốt đường thoát khi không có người trực quầy — nhánh gửi quầy phải đóng lại chứ không được cho qua với tên rỗng. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-07 + `C-DLV-06` Resolved 2026-09-17 (2 ô quầy là ràng buộc thật, QA đã submit thử với ô trống và form không đi).</t>
@@ -34970,7 +36182,7 @@
           <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L30" s="6" t="inlineStr"/>
+      <c r="L30" s="6" t="n"/>
       <c r="M30" s="6" t="inlineStr">
         <is>
           <t>Mục đích: 1 trong 3 ô vai — cảnh báo phải hiện cho CẢ 3 bên, ẩn với 1 vai là defect. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
@@ -35050,7 +36262,7 @@
           <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="n"/>
       <c r="M31" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
@@ -35130,7 +36342,7 @@
           <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr"/>
+      <c r="L32" s="6" t="n"/>
       <c r="M32" s="6" t="inlineStr">
         <is>
           <t>Mục đích: vai nhạy cảm nhất của bộ ba — chính người nhận là bên bị ghi "không liên lạc được" nên dễ bị ẩn cảnh báo nhất. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
@@ -35210,14 +36422,10 @@
           <t>Đơn gửi quầy chưa xác nhận, đã vượt mốc 4h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-067 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
-        </is>
-      </c>
+      <c r="L33" s="5" t="n"/>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: `§8.13.1` liệt kê 15 loại thông báo và KHÔNG có loại "nhắc" nào — TC này chính là điểm đối chiếu danh mục với hành vi thật. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-06 + `C-DLV-07` Resolved 2026-09-17 (hệ thống CHỈ gửi remind). ⛔ Không assert giờ cụ thể của "cuối ngày" và không FAIL vì kênh push hay in-app — BA không đặc tả, giới hạn đã chấp nhận. ⛔ Không assert vế "sau 24h chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy.</t>
+          <t>Mục đích: `§8.13.1` liệt kê 15 loại thông báo và KHÔNG có loại "nhắc" nào — TC này chính là điểm đối chiếu danh mục với hành vi thật. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-06 + `C-DLV-07` Resolved 2026-09-17 (hệ thống CHỈ gửi remind). ⛔ Không assert giờ cụ thể của "cuối ngày" và không FAIL vì kênh push hay in-app — BA không đặc tả, giới hạn đã chấp nhận. ⛔ Không assert vế "sau 24h chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-067 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
@@ -35300,7 +36508,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `retry` (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
-      <c r="L35" s="6" t="inlineStr"/>
+      <c r="L35" s="6" t="n"/>
       <c r="M35" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp với TC-DLV-059 — hai chế độ dùng chung một form nên rất dễ bị lập trình cứng một bộ nhãn. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02.</t>
@@ -35379,7 +36587,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `return` (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="n"/>
       <c r="M36" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02 + vibe-check demo 2026-09-17 (`C-DLV-05` — khối "Hẹn trả hàng" do chính Carrier nhập tại màn "Xử lý đơn hàng").</t>
@@ -35459,7 +36667,7 @@
           <t>Ngày hẹn +7 ngày (hợp lệ) và +8 ngày (chặn) (test_data_catalog §DLV — Ngày hẹn cầm hàng về, biên)</t>
         </is>
       </c>
-      <c r="L37" s="6" t="inlineStr"/>
+      <c r="L37" s="6" t="n"/>
       <c r="M37" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp biên trên của trần 7 ngày — hai giá trị liền kề fail độc lập nên phải nằm trong cùng 1 TC để so được. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-04.</t>
@@ -35540,7 +36748,7 @@
           <t>Giờ hẹn 30 phút (hợp lệ), 29 phút (chặn), giờ đến ≤ giờ từ (chặn) (test_data_catalog §DLV — Giờ hẹn từ–đến, biên)</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="n"/>
       <c r="M38" s="5" t="inlineStr">
         <is>
           <t>Mục đích: gộp ba giá trị vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả ba cùng thuộc một trạng thái tĩnh của form, không mất khả năng bắt lỗi riêng vì Expected nêu đích danh từng khoảng. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-03.</t>
@@ -35620,7 +36828,7 @@
           <t>Đơn `RESCHEDULED` = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr"/>
+      <c r="L39" s="6" t="n"/>
       <c r="M39" s="6" t="inlineStr">
         <is>
           <t>Mục đích: `AC-18.1.01` viết *"theo lịch hẹn, đơn quay lại IN_TRANSIT"* — đọc được thành hệ thống tự chuyển, chạy TC theo cách hiểu đó sẽ treo chờ đúng giờ. · Căn cứ: `C-DLV-05` **Resolved 2026-09-17** — chính người vận chuyển bấm, không có gate chặn theo giờ nên bấm sớm hơn lịch hẹn vẫn đi được; không giới hạn số lần hẹn. App chặn theo giờ ⇒ log bug và dẫn `C-DLV-05`.</t>
@@ -35700,7 +36908,7 @@
           <t>Đơn `RETURNING` = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="n"/>
       <c r="M40" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đây là bước tạo trạng thái `RETURNED` dùng chung cho TC-DLV-037/038/039, TC-DLV-064/065, TC-DLV-073 và cho `GIFT`/`ACT` — chạy xong mới chạy nhóm đó.</t>
@@ -35779,7 +36987,7 @@
           <t>Đơn `RETURNED` = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L41" s="6" t="inlineStr"/>
+      <c r="L41" s="6" t="n"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
           <t>Mục đích: oracle bảo vệ ranh giới `RETURNED` ⟷ `COMPLETED` — lỗi hay gặp nhất là coi hoàn hàng như một dạng hoàn thành. Chạy sớm nhất trong nhóm hậu-hoàn-hàng. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06 + §8.14.1 (bước tặng quà chỉ mở ở đơn Hoàn thành). Cặp với TC-DLV-065.</t>
@@ -35859,7 +37067,7 @@
           <t>Đơn `RETURNED` = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="n"/>
       <c r="M42" s="5" t="inlineStr">
         <is>
           <t>Mục đích: điểm fail độc lập với TC-DLV-064 — bước tặng quà và chỉ số đóng góp là hai bề mặt khác nhau, khoá một bề mặt không đảm bảo khoá bề mặt kia. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đơn vẫn phải xuất hiện trong tab "Đã hoàn thành" — verify ở TC-DLV-063.</t>
@@ -35940,7 +37148,7 @@
           <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `return` + ghi chú lý do từ chối (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
-      <c r="L43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="n"/>
       <c r="M43" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-07 — từ chối nhận hàng đi chung nhánh return, phân biệt với nhánh không liên lạc được chỉ bằng ghi chú.</t>
@@ -36021,14 +37229,10 @@
           <t>Đơn `RESCHEDULED` đã quá lịch hẹn 24h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-057 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
-        </is>
-      </c>
+      <c r="L44" s="5" t="n"/>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: vế duy nhất còn assert được của `BR09-04` sau khi BA cắt scope — dễ bị bỏ sót vì cả câu rule đã bị coi là out of scope. · Căn cứ: `AC-23.2.01` câu cuối + `C-DLV-07` Resolved 2026-09-17 (chỉ gửi remind, đơn không đổi trạng thái/nhãn/cờ). ⛔ Không assert vế "chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy.</t>
+          <t>Mục đích: vế duy nhất còn assert được của `BR09-04` sau khi BA cắt scope — dễ bị bỏ sót vì cả câu rule đã bị coi là out of scope. · Căn cứ: `AC-23.2.01` câu cuối + `C-DLV-07` Resolved 2026-09-17 (chỉ gửi remind, đơn không đổi trạng thái/nhãn/cờ). ⛔ Không assert vế "chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-057 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
@@ -36111,7 +37315,11 @@
           <t>Đơn `DELIVERED` qua nhánh giao tận tay = `SEED-DLV-05` (test_data_catalog §DLV — Đối tượng nhận)</t>
         </is>
       </c>
-      <c r="L46" s="6" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
           <t>Mục đích: 1 trong 6 mẫu câu nhật ký của `§8.12.4` — mỗi mẫu câu là 1 chuỗi verbatim riêng, sai chữ nào là defect chữ đó. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 1 + dòng "Mọi dòng" (thời điểm + cờ không liên lạc nếu có + dấu hiệu có ảnh). Assert nguyên văn kể cả dấu gạch ngang, ⛔ không paraphrase.</t>
@@ -36190,7 +37398,7 @@
           <t>Đơn `DELIVERED` qua nhánh uỷ quyền; tên 12 ký tự + SĐT hợp lệ (test_data_catalog §DLV — Tên người nhận thay)</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="n"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
           <t>Mục đích: mẫu câu phức tạp nhất trong 6 mẫu — có 2 biến nội dung và 1 biến nguồn uỷ quyền, dễ ghép sai thứ tự. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 2. Assert nguyên văn kể cả dấu gạch ngang và dấu chấm giữa tên với số điện thoại.</t>
@@ -36269,7 +37477,7 @@
           <t>Đơn `DELIVERED` qua nhánh quầy lễ tân (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
-      <c r="L48" s="6" t="inlineStr"/>
+      <c r="L48" s="6" t="n"/>
       <c r="M48" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 3. Assert nguyên văn, ⛔ không paraphrase.</t>
@@ -36348,7 +37556,7 @@
           <t>Đơn `DELIVERED` qua nhánh quầy bảo vệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr"/>
+      <c r="L49" s="5" t="n"/>
       <c r="M49" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cặp với TC-DLV-070 — hai quầy là hai mẫu câu tách biệt trong bảng `§8.12.4`, gộp 1 chuỗi có tham số là defect. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 4.</t>
@@ -36426,7 +37634,7 @@
           <t>Đơn `RESCHEDULED` = `SEED-DLV-03`; lịch hẹn hợp lệ + nơi hẹn (test_data_catalog §DLV — Ngày hẹn, Giờ hẹn từ–đến, Nơi hẹn)</t>
         </is>
       </c>
-      <c r="L50" s="6" t="inlineStr"/>
+      <c r="L50" s="6" t="n"/>
       <c r="M50" s="6" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 5 — ba biến ngày/giờ/nơi hẹn phải khớp đúng giá trị vừa nhập ở form.</t>
@@ -36505,7 +37713,7 @@
           <t>Đơn `RETURNED` = `SEED-DLV-03` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="n"/>
       <c r="M51" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 6 — mẫu câu duy nhất do người gửi kích hoạt, 5 mẫu còn lại do người vận chuyển.</t>
@@ -36591,7 +37799,11 @@
           <t>Transition `POSTED` → `DELIVERED` — ngoài bảng transition hợp lệ (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L53" s="6" t="inlineStr"/>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
           <t>Mục đích: tầng backend của rule đã có TC ở tầng UI (`TC-DLV-021` v1.0 chỉ verify màn hình không cho nhảy bước) — UI chặn không đảm bảo backend cũng chặn. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-01 + bảng §8.12.2. Dự án không có API spec/HTTP Status Contract nên assert theo hệ quả quan sát được trên app, không assert mã status.</t>
@@ -36671,7 +37883,11 @@
           <t>Transition `IN_TRANSIT` → `RETURNED` bỏ qua `RETURNING` (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
           <t>Mục đích: nhánh nhảy bậc nguy hiểm nhất — đóng đơn ở kết cục hoàn hàng mà không có bước người gửi xác nhận nhận lại, tức mất luôn oracle của TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02.</t>
@@ -36751,7 +37967,11 @@
           <t>Transition `IN_TRANSIT` → `COMPLETED` bỏ qua `DELIVERED` (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
-      <c r="L55" s="6" t="inlineStr"/>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp với TC-DLV-075 — hai đích nhảy bậc khác nhau từ cùng một trạng thái nguồn, chặn được đích này không suy ra chặn được đích kia. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02. Bỏ qua "Đã giao" còn xoá luôn yêu cầu ảnh bằng chứng của `BR07-02`.</t>
@@ -36842,7 +38062,7 @@
           <t>5 ảnh JPG đúng 5MB, mạng 4G (test_data_catalog §DLV — Upload ảnh hiệu năng)</t>
         </is>
       </c>
-      <c r="L57" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="n"/>
       <c r="M57" s="5" t="inlineStr">
         <is>
           <t>Mục đích: `NFR-03` phát biểu theo p95 nên 1 lần đo không kết luận được — 10 lần đo là mẫu tối thiểu chạy tay được, cho phép đúng 1 lần vượt ngưỡng. · Căn cứ: `DOC-v1.1-01` §9 NFR-03. Chạy trên 10 đơn khác nhau vì ảnh đã ghi mốc thì không xoá để tải lại được (`BR07-07`, xem TC-DLV-048).</t>
@@ -36923,7 +38143,11 @@
           <t>Đơn `MATCHED` rồi bị huỷ nhận đơn (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
-      <c r="L58" s="6" t="inlineStr"/>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
           <t>Mục đích: neo vào `RISK-DLV-09` — bug audit đã biết (`RISK-TS-01`: huỷ nhận đơn xoá dòng "Ghép thành công") vi phạm trực tiếp rule này, nên TC **dự kiến FAIL có chủ đích** cho tới khi bug được fix. · Căn cứ: `DOC-v1.1-01` §9 NFR-07 (log append-only, không API sửa/xoá). FAIL ⇒ log bug và cross-ref `RISK-TS-01`, ⛔ không hạ Expected theo hành vi hiện tại.</t>
@@ -37003,7 +38227,7 @@
           <t>Tên và SĐT người nhận thay đã ghi vào nhật ký (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr"/>
+      <c r="L59" s="5" t="n"/>
       <c r="M59" s="5" t="inlineStr">
         <is>
           <t>Mục đích: dữ liệu người nhận thay là dữ liệu cá nhân của bên thứ ba ngoài 3 vai của đơn — rò ra bề mặt khác là vi phạm quyền riêng tư, không chỉ lỗi hiển thị. · Căn cứ: `DOC-v1.1-01` §9 NFR-12. Phạm vi rà giới hạn ở các màn end-user; dự án không có bề mặt báo cáo hay Admin Portal trong scope v1.1.</t>
@@ -37090,7 +38314,11 @@
           <t>Số điện thoại liên hệ trên màn Theo dõi đơn (test_data_catalog §DLV — SĐT người nhận thay)</t>
         </is>
       </c>
-      <c r="L61" s="6" t="inlineStr"/>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
           <t>Mục đích: cặp với TC-DLV-081 — hai instance icon copy nằm ở hai vùng khác nhau của cùng màn, hỏng độc lập. · Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04. Rule ghi 1,8 giây nhưng đây là hiệu ứng thị giác — chấp nhận dung sai quanh 2 giây, ⛔ không bấm giờ đòi đúng 1,8 giây. Instance ở màn Chi tiết tin thuộc `FEED`, không rà ở đây.</t>
@@ -37170,7 +38398,11 @@
           <t>Địa chỉ giao trên màn Theo dõi đơn (test_data_catalog §DLV — Nơi hẹn)</t>
         </is>
       </c>
-      <c r="L62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
           <t>Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04 — rule đặt icon copy cạnh CẢ địa chỉ giao và số điện thoại.</t>
@@ -37380,7 +38612,11 @@
           <t>1 tin NEED `POSTED` có khung giờ, loại hàng "Tài liệu" (test_data_catalog §FEED)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Mục đích: hết gap CTA — đổi từ "cố ý không assert vị trí CTA" (v1.0) sang assert cứng phủ định "card KHÔNG có CTA". · Căn cứ: `C-FEED-01(a)` Resolved 2026-09-16 — vibe-check demo xác nhận CTA chỉ có ở màn Chi tiết tin. Badge "Tin của bạn" verify riêng ở `TC-FEED-003/004` (thành phần có điều kiện). · Đã sửa tại chỗ 2026-09-16: thêm assert phủ định CTA vào Expected.</t>
@@ -37464,7 +38700,11 @@
           <t>1 tin NEED `POSTED` của tài khoản khác (test_data_catalog §FEED)</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Mục đích: bổ sung assert tên người gửi hiển thị trước ghép (thành phần tồn tại) — phân biệt với `TC-FEED-010` (cùng cụm nhưng assert SĐT KHÔNG hiển thị). · Căn cứ: `C-FEED-04` Resolved 2026-09-17 — trước ghép chỉ ẩn SĐT, tên + địa chỉ đầy đủ hiện bình thường. ⛔ KHÔNG log bug nếu tên/địa chỉ hiện đầy đủ trước ghép — đó là hành vi ĐÚNG. · Đã sửa tại chỗ 2026-09-17: thêm "có đúng họ tên" + "điểm Lấy/Giao đầy đủ như data đã đăng" vào Expected.</t>
@@ -37547,7 +38787,11 @@
           <t>Tin NEED có điểm lấy/giao thuộc văn phòng đủ toạ độ (test_data_catalog §FEED)</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Mục đích: ĐẢO kết luận v1.0 — trước assert "placeholder tĩnh, không có bản đồ" (`C-FEED-01(b)` Open), nay assert "CÓ bản đồ thật, ảnh tĩnh vẽ tuyến". · Căn cứ: `C-FEED-01(b)` + `C-FEED-02(c)` Resolved 2026-09-17. ⛔ Không test zoom/pan — ảnh tĩnh, không phải bản đồ tương tác. · Đã sửa tại chỗ 2026-09-17: đảo hoàn toàn Expected + Pre-condition (cần văn phòng có toạ độ hợp lệ, khác v1.0 không cần điều kiện gì), bỏ 2 bước test zoom/pan của v1.0.</t>
@@ -37710,7 +38954,11 @@
           <t>0 tin cộng đồng (test_data_catalog §FEED, biên)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Mục đích: hết `[GAP]` — text empty state đã chốt (`EMP-04`, home ở `ACT`) + xác nhận cấu trúc 1 danh sách (không phải 2 tab như nghi vấn cũ). · Căn cứ: `C-FEED-03` Resolved 2026-09-17 (1 danh sách, không tab/lọc) + `DOC-v1.1-01 §8.17.1 EMP-04` + `C-HOME-04` Resolved vòng 3 2026-09-17 (BA: *"giữ nguyên nhé"* ⇒ `EMP-04` giữ nguyên chữ PRD dù Bảng tin load toàn quốc). ℹ️ PRD không nói "gợi ý mở rộng khu vực" là nút hay chữ ⇒ assert **nội dung chữ**, ghi nhận dạng hiển thị thực tế, không FAIL vì hình thức. · Đã sửa tại chỗ 2026-09-17: thay "chỉ assert phần suy được" bằng assert cứng text + cấu trúc 1 danh sách; bổ sung assert câu gợi ý mở rộng khu vực sau khi `C-HOME-04` đóng.</t>
@@ -37916,7 +39164,11 @@
           <t>Tập đóng 4 tên quà chính thức, dùng đơn của `SEED-GIFT-01` (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Mục đích: siết Expected từ "đúng 4 loại quà" (chỉ đếm số lượng, v1.0) sang assert đúng TÊN từng loại theo `BR14-01`. · Căn cứ: `DOC-v1.1-01 §8.14.1 BR14-01`. · Đã sửa theo delta v1.1 (2026-09-15): đổi Expected, giữ nguyên Steps/Pre-condition/Test Data so với v1.0.</t>
@@ -38002,7 +39254,11 @@
           <t>Đơn Hoàn thành của `SEED-GIFT-02`; loại quà "Bông hoa" (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Mục đích: siết đúng chuỗi popup theo `BR14-02`/`AC-24.1.01` — thay chuỗi "Đã gửi lời cảm ơn!" (v1.0, dựa nguồn thua `US-D15` theo `C-GIFT-03` Resolved) bằng chuỗi chính thức + thêm assert nút về trang chủ. · Căn cứ: `DOC-v1.1-01 §8.14.1 BR14-02` · `§6.2 AC-24.1.01`. ⚠ TC này tiêu 1 đơn Hoàn thành (`SEED-GIFT-02`, không tái dùng được). · Đã sửa theo delta v1.1 (2026-09-15).</t>
@@ -38085,7 +39341,11 @@
           <t>Tài khoản B đã nhận 5 quà (3 Bông hoa + 2 Gấu bông) từ `SEED-GIFT-05` (test_data_catalog §GIFT v1.1, biên)</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Mục đích: cập nhật bộ số mẫu theo `AC-26.1.01` (5 quà, ≥2 loại) — thay bộ 2 quà/2 loại của v1.0; rule "loại count=0 không hiện card" (`KB-GIFT-03`) vẫn không có nguồn PRD, giữ nguyên như v1.0. · Căn cứ: `DOC-v1.1-01 §6.2 AC-26.1.01`. · Đã sửa theo delta v1.1 (2026-09-15): đổi Test Data từ 2 quà/2 loại sang 5 quà/2 loại.</t>
@@ -38161,7 +39421,11 @@
           <t>Tài khoản B đã nhận quà nhiều lần từ `SEED-GIFT-05` (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
           <t>Mục đích: hết `[GAP]` của `C-GIFT-03` vế (b) — Resolved: xác nhận CÓ danh sách lịch sử (v1.0 dự kiến FAIL vì chưa thấy trên app, khi đó chỉ ghi nhận); nay assert khẳng định, nâng Priority P3 → P2. · Căn cứ: `DOC-v1.1-01 §6.2 AC-26.1.01` "kèm lịch sử nhận quà". ⚠ Lệch app → log bug, ⛔ không hạ Expected theo hành vi app hiện tại. · Đã sửa theo delta v1.1 (2026-09-15): đổi Expected từ ghi-nhận sang assert cứng + nâng priority.</t>
@@ -38245,7 +39509,7 @@
           <t>Tài khoản 0 đơn/0 quà (test_data_catalog §GIFT v1.1, biên)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="n"/>
       <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Mục đích: hết `[GAP]` của `C-ORD-06` phần GIFT (`EMP-08`) — Resolved bằng tài liệu phê duyệt, không còn dựa suy diễn `KB-GIFT-03` như v1.0. · Căn cứ: `DOC-v1.1-01 §8.17.1 EMP-08` · `§6.2 AC-26.2.01`. ⚠️ Cột CTA của `EMP-08` = "—" là assert thật theo `BR17-01` (tối đa 1 CTA) — không phải thiếu sót. · Đã sửa theo delta v1.1 (2026-09-15): đổi Expected từ "KHÔNG hiển thị loại quà nào" (v1.0, suy diễn) sang assert verbatim text + thống kê 0/0 + không CTA (theo tài liệu chính thức).</t>
@@ -38332,7 +39596,7 @@
           <t>Bộ giá trị assert-absent: sao/điểm/tier/chỉ số môi trường, dùng đơn của `SEED-GIFT-06` (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr"/>
+      <c r="L12" s="6" t="n"/>
       <c r="M12" s="6" t="inlineStr">
         <is>
           <t>Mục đích: `BR14-03` v1.1 liệt kê đủ 4 bề mặt (màn Tặng quà · popup cảm ơn · "Quà đã nhận" · Trang cá nhân) và bổ sung "không chỉ số môi trường" — loại trừ nay là VĨNH VIỄN, không phải "out of scope v1.0" như trước. · Căn cứ: `DOC-v1.1-01 §8.14.1 BR14-03` · `§4 SCOPES`. ⚠️ Cross-ref: `SC-ACT-013` (★ leftover ở `ACT`) nay là defect xác nhận, không còn diễn giải "dấu vết phase sau". · Đã sửa theo delta v1.1 (2026-09-15): mở rộng phạm vi rà từ 3 bề mặt (v1.0: Theo dõi đơn/Tặng quà/Cá nhân) sang đúng 4 bề mặt theo `BR14-03` (thêm popup cảm ơn + "Quà đã nhận") — TC giờ tiêu 1 đơn Hoàn thành riêng (`SEED-GIFT-06`), khác v1.0 (dùng chung `SEED-GIFT-01`, không tiêu đơn).</t>
@@ -38416,7 +39680,11 @@
           <t>Đơn `RETURNED` của `SEED-GIFT-08` (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Mục đích: vế (a) — lỗi NHÌN THẤY ĐƯỢC của `AC-24.2.01`; đối chứng với vế (b) âm thầm ở `TC-GIFT-014`. · Căn cứ: `DOC-v1.1-01 §8.14 Pre-Conditions` · `§8.14.1 BR14-04` · `§6.2 AC-24.2.01`. ⛔ Không seed được đơn `RETURNED` (STG chưa build `FR09`) → verdict BLOCKED, ⛔ không PASS ("không thấy nút" không chứng minh gì nếu không có đơn RETURNED thật để thử). · Cross-ref: không nhân bản SC bộ đếm "Đơn đã giúp" sang `USR`/`HOME` — chỉ dùng ở `TC-GIFT-014`. ⚠️ Giả định đơn `RETURNED` nằm trong tab con "Đã hoàn thành" (cùng nhóm với `COMPLETED`, vì cả hai đều là trạng thái đóng) — chưa có nguồn PRD/BA xác nhận rõ tab hiển thị; nếu STG đặt đơn `RETURNED` ở tab khác thì sửa lại step 1, không phải lỗi TC.</t>
@@ -38494,7 +39762,11 @@
           <t>N đơn `COMPLETED` có sẵn (ví dụ PRD: 7 — `AC-26.1.01`) + 1 đơn `RETURNED` mới; **bắt buộc ghi số N ở bước 2 TRƯỚC khi đơn RETURNED phát sinh ở bước 3** (test_data_catalog §GIFT v1.1)</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
           <t>Mục đích: vế (b) ÂM THẦM của `AC-24.2.01`/`BR14-04` — sai lệch 1 đơn không nhìn ra được bằng mắt nếu không ghi số trước rồi so sau. · Căn cứ: `DOC-v1.1-01 §8.14.1 BR14-04` · `§6.2 AC-24.2.01`/`AC-26.1.01`. ⛔ Không seed được đơn `RETURNED` (STG chưa build `FR09`) → verdict BLOCKED, ⛔ không PASS. · Cross-ref: cùng bộ đếm với `USR` (2 chỉ số đóng góp) và `HOME`/`ACT` (card "Đóng góp của bạn") — ⛔ không nhân bản SC/TC sang các module đó.</t>

--- a/03_test-cases/TC-MASTER-LATEST.xlsx
+++ b/03_test-cases/TC-MASTER-LATEST.xlsx
@@ -12117,26 +12117,48 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SEED-DLV-02 · SEED-DLV-03 · SEED-DLV-04 · SEED-DLV-05</t>
+          <t>SEED-DLV-02 · SEED-DLV-03-A (= SEED-DLV-03) · SEED-DLV-03-B · SEED-DLV-04 · SEED-DLV-05 · SEED-DLV-06</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>⚠️ **Trạng thái đơn một chiều, không lùi được.** Chạy đủ TC tại 1 checkpoint rồi mới đẩy sang checkpoint kế; lỡ đẩy sớm phải tạo đơn mới từ checkpoint 0. A = người gửi · B = người vận chuyển · C = người nhận.
-**`SEED-DLV-02` — bộ 4 đơn tới "Đang giao", mỗi đơn cho 1 nhánh "Giao cho"** (tạo hoàn toàn qua UI thật, ⛔ không nhờ dev seed DB):
-- CP0 `POSTED` — A đăng 1 tin NEED khai C là người nhận (đơn #4 khai thêm người nhận uỷ quyền lúc đăng tin).
-- CP1 `MATCHED` — B nhấn "Tôi mang giúp được" và xác nhận.
-- CP2 `IN_TRANSIT` — B nhấn "Tôi đã lấy hàng" → dùng cho `TC-DLV-041..049`.
-- Đơn #1 → `TC-DLV-043` (Người nhận) · đơn #2 → `TC-DLV-044` (Người được uỷ quyền) · đơn #3 → `TC-DLV-045` (Quầy lễ tân) · đơn #4 → `TC-DLV-046` (Quầy bảo vệ). `TC-DLV-047/048/049` bám theo đơn #1 trước khi submit.
-**`SEED-DLV-03` — 1 đơn đi hết nhánh "không liên lạc được" → "cầm hàng về"** (nguồn trạng thái duy nhất cho nhóm hậu-`FR09`):
-- CP2 `IN_TRANSIT` như trên → CP3 B nhấn "Không thể liên lạc cho người nhận?" → dùng cho `TC-DLV-050..056`.
-- CP4 `RESCHEDULED` — "Cầm hàng về" → "Tôi sẽ giao lại sau" + nhập lịch hẹn → dùng cho `TC-DLV-031/032/033`, `058..062`, `072`.
-- CP5 `RETURNING` — "Cầm hàng về" → "Tôi sẽ trả về cho người gửi" → dùng cho `TC-DLV-034/035/036`, `066`.
-- CP6 `RETURNED` — A nhấn "Xác nhận đã nhận lại hàng" → dùng cho `TC-DLV-037/038/039`, `063/064/065`, `073`.
-- ⚠️ **Dùng chung với `GIFT` (`TC-GIFT-013/014`) và `ACT` (`SC-ACT-015`)** — 3 module cùng cần đúng 1 đơn `RETURNED`; chạy chung lô để seed 1 lần.
-**`SEED-DLV-04` — 1 đơn ở `INCIDENT`** (B báo sự cố sau khi đã lấy hàng) → dùng cho `TC-DLV-040`.
-**`SEED-DLV-05` — 1 đơn đã "Đã giao" qua nhánh giao tận tay** → dùng cho `TC-DLV-048` (ảnh bất biến), `TC-DLV-068`, `TC-DLV-078/079/080/081`.
-⛔ **Không seed được qua UI — cần dev/QA lùi timestamp hoặc chờ thời gian thật:** `TC-DLV-057` (mốc 4h + cuối ngày) · `TC-DLV-067` (quá lịch hẹn 24h). Hai TC này đánh `Deferred` ở cột Status, chạy chung lô với `TC-DLV-024` (v1.0) và `SC-TS-006` để chỉ chờ 1 lần.</t>
+          <t>⚠️ **Trạng thái đơn một chiều, không lùi được.** Chạy đúng THỨ TỰ ghi dưới đây; lỡ đẩy sớm phải tạo đơn mới từ đầu. A = người gửi · B = người vận chuyển · C = người nhận (tài khoản: `04_test-data/valid/USR-accounts.md §2`). *(Viết lại 2026-09-23 — bản cũ gán 1 đơn cho cả nhánh giao lại lẫn trả hàng, không chạy được.)*
+**Thao tác dùng chung — đọc 1 lần:**
+- **Lấy hàng (2 lớp):** "Tôi đã lấy hàng" → popup lớp 1 nhấn **"Xác nhận"** → màn "Xác nhận đã lấy hàng" (có ô ảnh tuỳ chọn) → "Xác nhận" → popup "Đã lấy hàng" nhấn "Đồng ý".
+- **Mở màn "Xác nhận đã giao" (2 lớp):** nút chính "Đã đến địa điểm giao hàng" (STG hiện tên cũ **"Đã giao cho người nhận"** — BUG-044) → popup lớp 1 "Bạn xác nhận đã giao hàng tận tay người nhận?" nhấn **"Xác nhận"** — ⛔ KHÔNG nhấn "Huỷ" (VR-020/021 từng chấm BLOCKED sai vì nhấn Huỷ). Nhấn "Xác nhận" ở lớp 1 **chưa** giao đơn.
+- **Tới màn "Xử lý đơn hàng":** trên màn "Xác nhận đã giao" nhấn link "Không thể liên lạc cho người nhận?" → STG hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" (lệch cấu trúc 4 tầng BA chốt — FE-333, chờ BA).
+- **Lịch hẹn chuẩn:** Ngày hẹn = ngày mai · 09:00–10:00 · nơi "Sảnh toà FPT Tower".
+**`SEED-DLV-02` — 4 đơn A→B, mỗi đơn 1 nhánh "Giao cho"** (A đăng tin NEED khai C là người nhận, ⛔ không khai người nhận uỷ quyền; B nhấn "Tôi mang giúp được" ⇒ "Đã ghép"):
+- Đơn #1: "Đã ghép" → **TC-041** (lấy hàng có ảnh) → "Đang giao" → **047 → 049 → 043 + 068** (1 lần submit, 2 evidence) → "Đã giao" = `SEED-DLV-05` → **048**.
+- Đơn #2: "Đã ghép" → **TC-042** (lấy hàng 0 ảnh) → **044 + 069** → **079**.
+- Đơn #3: lấy hàng thường → **077** (không submit) → **045 + 070**.
+- Đơn #4: lấy hàng thường → **046 + 071**.
+**`SEED-DLV-03-A` — 1 đơn đi hết nhánh giao lại → trả hàng → đã trả người gửi** (A đăng, B nhận + lấy hàng ⇒ "Đang giao"):
+1. "Đang giao", không submit: **050 → 051 → 058 → 059 → 060 → 061**
+2. **072** submit "Tôi sẽ giao lại sau" + lịch hẹn chuẩn ⇒ **"Giao lại"** (RESCHEDULED) → **031 · 032 · 033** (chỉ xem)
+3. **062** B nhấn nút giao lại ⇒ quay về "Đang giao"
+4. **066** submit "Tôi sẽ trả về cho người gửi" + ghi chú + lịch hẹn ⇒ **"Trả hàng"** (RETURNING) → **034 · 035 · 036** (chỉ xem)
+5. **065 step 1** (B ghi số "đơn đã giúp") → **063 + 064** (A xác nhận đã nhận lại hàng) ⇒ RETURNED → **065 · 073 · 037 · 038 · 039**
+- ⚠️ Dùng chung với `GIFT` (`TC-GIFT-013/014`) và `ACT` (`TC-ACT-015`) — cùng cần đúng đơn RETURNED này; chạy chung lô.
+&gt; Mã cũ `SEED-DLV-03` (module ACT/GIFT còn trỏ) = `SEED-DLV-03-A`.
+**`SEED-DLV-03-B` — 1 đơn nhánh "không liên lạc được" → gửi quầy** (A đăng, B nhận + lấy hàng ⇒ "Đang giao"): **053** (tên trống, không đi được) → **052** (gửi quầy lễ tân ⇒ "Đã giao") → **054 · 055 · 056**.
+**`SEED-DLV-04` — 1 đơn có sự cố** (B báo sự cố sau khi lấy hàng) → **040** — 🚫 cần dev lùi timestamp.
+**`SEED-DLV-05`** = đơn #1 của `SEED-DLV-02` sau TC-043 ("Đã giao") → **048**.
+**`SEED-DLV-06` — 1 đơn "Đã ghép"** (A đăng, B nhận): **080 → 081** (chỉ xem/copy) → **078** (B huỷ nhận đơn — tiêu đơn, chạy cuối).
+**Đơn riêng, không dùng chung:** 057 · 067 (🚫 cần dev lùi timestamp — chạy chung lô với TC-DLV-024 v1.0 và SC-TS-006) · 074 · 075 · 076 (cần proxy — Skipped).
+**Bảng mã trạng thái ↔ nhãn hiển thị** (Test Data ghi cả hai):
+| Mã | Nhãn badge | Nguồn |
+|---|---|---|
+| POSTED | Chờ ghép | Figma v1.0 + demo |
+| MATCHED | Đã ghép | Figma v1.0 + demo |
+| IN_TRANSIT | Đang giao | Figma v1.0 + demo |
+| DELIVERED | Đã giao | Figma v1.0 + demo |
+| COMPLETED | Hoàn thành | Figma v1.0 + demo |
+| CANCELLED | Đã huỷ | demo |
+| RESCHEDULED | Giao lại | chỉ demo — PRD không đặc tả chữ |
+| RETURNING | Trả hàng | chỉ demo — PRD không đặc tả chữ |
+| RETURNED | ⚠ chưa có nguồn — demo gộp vào "Hoàn thành" (lệch BR09-06) | ghi nguyên văn STG vào Notes TC-063 |
+| EXPIRED · INCIDENT | chưa có nguồn | ghi nguyên văn STG khi gặp |</t>
         </is>
       </c>
     </row>
@@ -15324,30 +15346,29 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
-4. Chọn "Người nhận" ở field "Giao cho".
-5. Đính 1 ảnh JPG từ thư viện thiết bị.
-6. Nhấn "Xác nhận đã giao hàng" và đồng ý ở popup xác nhận.
-7. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Dùng đơn #1 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Chạy sau TC-DLV-049.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Người nhận" ở field "Giao cho".
+4. Đính 1 ảnh JPG từ thư viện thiết bị.
+5. Nhấn "Xác nhận đã giao hàng" và nhấn "Xác nhận" ở popup cảnh báo không thể hoàn tác.
+6. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>7. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã giao tận tay người nhận" kèm thời điểm.</t>
+          <t>6. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã giao tận tay người nhận" kèm thời điểm.</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02`; đối tượng nhận "Người nhận" + 1 ảnh bằng chứng (test_data_catalog §DLV — Đối tượng nhận, Ảnh bằng chứng giao hàng)</t>
+          <t>Đơn #1 `SEED-DLV-02` ở "Đang giao"; "Người nhận" + 1 ảnh (test_data_catalog §DLV — Đối tượng nhận, Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -15357,7 +15378,7 @@
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: luồng chính của `FR07` mở rộng — 3 nhánh còn lại (TC-DLV-044/045/046) đều rẽ từ đúng màn này. · Căn cứ: `DOC-v1.1-01` §8.7.2 + §8.12.4 mẫu câu 1. `RISK-DLV-08` đã Confirmed qua demo 2026-09-16 (luồng submit chạy đúng); vẫn double-check locator trên STG trước khi hardening. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
+          <t>Mục đích: luồng chính của `FR07` mở rộng — 3 nhánh còn lại (TC-DLV-044/045/046) đều rẽ từ đúng màn này. · Căn cứ: `DOC-v1.1-01` §8.7.2 + §8.12.4 mẫu câu 1. `RISK-DLV-08` đã Confirmed qua demo 2026-09-16 (luồng submit chạy đúng); vẫn double-check locator trên STG trước khi hardening. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-068: 1 lần submit, chụp 2 ảnh evidence riêng. Popup lớp 1 phải nhấn "Xác nhận" — VR-020 nhấn "Huỷ" nên từng chấm BLOCKED sai.</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
@@ -15410,38 +15431,37 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
-4. Chọn "Người được uỷ quyền" ở field "Giao cho".
-5. Nhập "Nguyễn Văn Bảy" vào ô tên người nhận thay.
-6. Nhập "0912345678" vào ô số điện thoại người nhận thay.
-7. Đính 1 ảnh JPG từ thư viện thiết bị.
-8. Nhấn "Xác nhận đã giao hàng" và đồng ý ở popup xác nhận.
-9. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Dùng đơn #2 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Người được uỷ quyền" ở field "Giao cho"; nếu 2 ô tên/SĐT người nhận thay đã được điền sẵn thì xoá trắng trước.
+4. Nhập "Nguyễn Văn Bảy" vào ô tên người nhận thay.
+5. Nhập "0912345678" vào ô số điện thoại người nhận thay.
+6. Đính 1 ảnh JPG từ thư viện thiết bị.
+7. Nhấn "Xác nhận đã giao hàng" và nhấn "Xác nhận" ở popup.
+8. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>9. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã giao cho người được uỷ quyền — Nguyễn Văn Bảy · 0912345678 — uỷ quyền bởi Người nhận".</t>
+          <t>8. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã giao cho người được uỷ quyền — Nguyễn Văn Bảy · 0912345678 — uỷ quyền bởi Người nhận".</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #2 của `SEED-DLV-02`; tên 12 ký tự + SĐT hợp lệ (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
+          <t>Đơn #2 `SEED-DLV-02` ở "Đang giao"; tên 12 ký tự + SĐT hợp lệ (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
         </is>
       </c>
       <c r="L39" s="6" t="n"/>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: chốt giá trị tự sinh của "Uỷ quyền bởi" theo MÀN VÀO chứ không theo loại đối tượng nhận — đối chứng âm là TC-DLV-051 (vào từ màn "Liên hệ người gửi" thì tự sinh "Người gửi"). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03/BR07-04/BR07-05 + §8.12.4 mẫu câu 2. Trường "Uỷ quyền bởi" chỉ đọc, không sửa được. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
+          <t>Mục đích: chốt giá trị tự sinh của "Uỷ quyền bởi" theo MÀN VÀO chứ không theo loại đối tượng nhận — đối chứng âm là TC-DLV-051 (vào từ màn "Liên hệ người gửi" thì tự sinh "Người gửi"). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03/BR07-04/BR07-05 + §8.12.4 mẫu câu 2. Trường "Uỷ quyền bởi" chỉ đọc, không sửa được. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-069 (1 lần submit, 2 evidence). ⚠ Demo tách dòng: tiêu đề "Đã giao cho người được uỷ quyền" + dòng phụ "Nguyễn Văn Bảy · 0912345678 · uỷ quyền bởi người nhận · &lt;tên C&gt;" — STG lệch đúng kiểu này (đủ 3 thành phần, chỉ khác cách xuống dòng/dấu nối) ⇒ ghi Notes, hỏi BA, chưa log bug.</t>
         </is>
       </c>
       <c r="N39" s="6" t="inlineStr">
@@ -15494,33 +15514,32 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, mở đơn đó và nhấn "Xác nhận đã nhận lại hàng". (setup)
-5. Check màn Theo dõi đơn ngay sau khi xác nhận và các nút trên đơn ở tab "Đã hoàn thành".</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Trả hàng" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Nhấn "Xác nhận đã nhận lại hàng" và đồng ý ở popup (chính là step 3 của TC-DLV-063 — chạy chung).
+4. Check màn hiện ra ngay sau khi xác nhận, rồi mở đơn ở tab "Đã hoàn thành" và check các nút trên đơn.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>5. KHÔNG có bước tặng quà nào mở ra và đơn KHÔNG có nút tặng quà.</t>
+          <t>4. KHÔNG có bước tặng quà nào mở ra và đơn KHÔNG có nút "Cảm ơn người vận chuyển" hay nút tặng quà nào.</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED` = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` → RETURNED; vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: oracle bảo vệ ranh giới `RETURNED` ⟷ `COMPLETED` — lỗi hay gặp nhất là coi hoàn hàng như một dạng hoàn thành. Chạy sớm nhất trong nhóm hậu-hoàn-hàng. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06 + §8.14.1 (bước tặng quà chỉ mở ở đơn Hoàn thành). Cặp với TC-DLV-065.</t>
+          <t>Mục đích: oracle bảo vệ ranh giới `RETURNED` ⟷ `COMPLETED` — lỗi hay gặp nhất là coi hoàn hàng như một dạng hoàn thành. Chạy sớm nhất trong nhóm hậu-hoàn-hàng. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06 + §8.14.1 (bước tặng quà chỉ mở ở đơn Hoàn thành). Cặp với TC-DLV-065. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-063 (1 lần xác nhận, 2 evidence). Demo có nút "Cảm ơn người vận chuyển" ở đơn trả hàng — gặp trên STG ⇒ FAIL.</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
@@ -15573,34 +15592,31 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, mở Trang chủ và ghi lại con số "đơn đã giúp" ở khối hero. (setup)
-3. Nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-4. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-5. Đăng nhập bằng tài khoản A, mở đơn đó, nhấn "Xác nhận đã nhận lại hàng" rồi đăng xuất. (setup)
-6. Đăng nhập lại bằng tài khoản B, mở Trang chủ và check con số "đơn đã giúp" ở khối hero.</t>
+          <t>1. (setup) TRƯỚC khi chạy TC-DLV-063: đăng nhập B, mở Trang chủ và ghi lại con số "đơn đã giúp" ở khối hero.
+2. (setup) Chạy TC-DLV-063 (A xác nhận đã nhận lại hàng trên `SEED-DLV-03-A`).
+3. Đăng nhập lại tài khoản B, mở Trang chủ và check con số "đơn đã giúp" ở khối hero.</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>6. Con số "đơn đã giúp" bằng đúng con số đã ghi ở step 2, không tăng.</t>
+          <t>3. Con số "đơn đã giúp" bằng đúng con số đã ghi ở step 1, không tăng.</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED` = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` trước/sau khi thành RETURNED; vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L41" s="6" t="n"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: điểm fail độc lập với TC-DLV-064 — bước tặng quà và chỉ số đóng góp là hai bề mặt khác nhau, khoá một bề mặt không đảm bảo khoá bề mặt kia. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đơn vẫn phải xuất hiện trong tab "Đã hoàn thành" — verify ở TC-DLV-063.</t>
+          <t>Mục đích: điểm fail độc lập với TC-DLV-064 — bước tặng quà và chỉ số đóng góp là hai bề mặt khác nhau, khoá một bề mặt không đảm bảo khoá bề mặt kia. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đơn vẫn phải xuất hiện trong tab "Đã hoàn thành" — verify ở TC-DLV-063. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
@@ -15653,15 +15669,15 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Có sẵn công cụ proxy chặn và phát lại request trỏ vào app FoxEco trên STG.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận. (setup)
-2. Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác. (setup)
+          <t>1. (setup) Đăng nhập A, đăng 1 tin NEED khai C là người nhận (đơn ở "Chờ ghép").
+2. (setup) Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác.
 3. Sửa request đã ghi thành yêu cầu chuyển đơn đang ở "Chờ ghép" sang "Đã giao" và phát lại request đó.
 4. Mở lại đơn đó trên app và check trạng thái đơn cùng số dòng ở block "LỊCH SỬ".</t>
         </is>
@@ -15673,7 +15689,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Transition `POSTED` → `DELIVERED` — ngoài bảng transition hợp lệ (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
+          <t>Chuyển "Chờ ghép" → "Đã giao" (POSTED → DELIVERED) — ngoài bảng transition hợp lệ (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -15683,7 +15699,7 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: tầng backend của rule đã có TC ở tầng UI (`TC-DLV-021` v1.0 chỉ verify màn hình không cho nhảy bước) — UI chặn không đảm bảo backend cũng chặn. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-01 + bảng §8.12.2. Dự án không có API spec/HTTP Status Contract nên assert theo hệ quả quan sát được trên app, không assert mã status.</t>
+          <t>Mục đích: tầng backend của rule đã có TC ở tầng UI (`TC-DLV-021` v1.0 chỉ verify màn hình không cho nhảy bước) — UI chặn không đảm bảo backend cũng chặn. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-01 + bảng §8.12.2. Dự án không có API spec/HTTP Status Contract nên assert theo hệ quả quan sát được trên app, không assert mã status. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
@@ -15736,28 +15752,27 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Có sẵn công cụ proxy chặn và phát lại request trỏ vào app FoxEco trên STG.</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác. (setup)
-4. Sửa request đã ghi thành yêu cầu chuyển đơn đang ở "Đang giao" thẳng sang trạng thái đã trả người gửi, bỏ qua bước hoàn hàng, và phát lại request đó.
-5. Mở lại đơn đó trên app và check trạng thái đơn cùng số dòng ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Tạo 1 đơn riêng: đăng nhập A, đăng 1 tin NEED khai C là người nhận, đăng xuất; đăng nhập B, nhấn "Tôi mang giúp được" và xác nhận, rồi nhấn "Tôi đã lấy hàng" → ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" → tại màn "Xác nhận đã lấy hàng" nhấn "Xác nhận" → ở popup "Đã lấy hàng" nhấn "Đồng ý".
+2. (setup) Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác.
+3. Sửa request đã ghi thành yêu cầu chuyển đơn đang ở "Đang giao" thẳng sang trạng thái đã trả người gửi, bỏ qua bước trả hàng, và phát lại request đó.
+4. Mở lại đơn đó trên app và check trạng thái đơn cùng số dòng ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>5. Đơn vẫn ở trạng thái "Đang giao" và block "LỊCH SỬ" KHÔNG có dòng mốc mới nào được thêm.</t>
+          <t>4. Đơn vẫn ở trạng thái "Đang giao" và block "LỊCH SỬ" KHÔNG có dòng mốc mới nào được thêm.</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>Transition `IN_TRANSIT` → `RETURNED` bỏ qua `RETURNING` (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
+          <t>Chuyển "Đang giao" → đã trả người gửi (IN_TRANSIT → RETURNED) bỏ qua RETURNING (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -15767,7 +15782,7 @@
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: nhánh nhảy bậc nguy hiểm nhất — đóng đơn ở kết cục hoàn hàng mà không có bước người gửi xác nhận nhận lại, tức mất luôn oracle của TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02.</t>
+          <t>Mục đích: nhánh nhảy bậc nguy hiểm nhất — đóng đơn ở kết cục hoàn hàng mà không có bước người gửi xác nhận nhận lại, tức mất luôn oracle của TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N43" s="6" t="inlineStr">
@@ -15820,28 +15835,27 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Có sẵn công cụ proxy chặn và phát lại request trỏ vào app FoxEco trên STG.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác. (setup)
-4. Sửa request đã ghi thành yêu cầu chuyển đơn đang ở "Đang giao" thẳng sang "Hoàn thành", bỏ qua bước "Đã giao", và phát lại request đó.
-5. Mở lại đơn đó trên app và check trạng thái đơn cùng số dòng ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Tạo 1 đơn riêng: đăng nhập A, đăng 1 tin NEED khai C là người nhận, đăng xuất; đăng nhập B, nhấn "Tôi mang giúp được" và xác nhận, rồi nhấn "Tôi đã lấy hàng" → ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" → tại màn "Xác nhận đã lấy hàng" nhấn "Xác nhận" → ở popup "Đã lấy hàng" nhấn "Đồng ý".
+2. (setup) Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác.
+3. Sửa request đã ghi thành yêu cầu chuyển đơn đang ở "Đang giao" thẳng sang "Hoàn thành", bỏ qua bước "Đã giao", và phát lại request đó.
+4. Mở lại đơn đó trên app và check trạng thái đơn cùng số dòng ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>5. Đơn vẫn ở trạng thái "Đang giao" và block "LỊCH SỬ" KHÔNG có dòng mốc mới nào được thêm.</t>
+          <t>4. Đơn vẫn ở trạng thái "Đang giao" và block "LỊCH SỬ" KHÔNG có dòng mốc mới nào được thêm.</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Transition `IN_TRANSIT` → `COMPLETED` bỏ qua `DELIVERED` (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
+          <t>Chuyển "Đang giao" → "Hoàn thành" (IN_TRANSIT → COMPLETED) bỏ qua DELIVERED (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -15851,7 +15865,7 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-075 — hai đích nhảy bậc khác nhau từ cùng một trạng thái nguồn, chặn được đích này không suy ra chặn được đích kia. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02. Bỏ qua "Đã giao" còn xoá luôn yêu cầu ảnh bằng chứng của `BR07-02`.</t>
+          <t>Mục đích: cặp với TC-DLV-075 — hai đích nhảy bậc khác nhau từ cùng một trạng thái nguồn, chặn được đích này không suy ra chặn được đích kia. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02. Bỏ qua "Đã giao" còn xoá luôn yêu cầu ảnh bằng chứng của `BR07-02`. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
@@ -15904,39 +15918,34 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
-- Host app FoxPro đã cài trên thiết bị Android/iOS.
-- Có sẵn công cụ proxy chặn và phát lại request trỏ vào app FoxEco trên STG.</t>
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó và xác nhận. (setup)
-3. Mở block "LỊCH SỬ" và ghi lại toàn bộ các dòng mốc hiện có.
-4. Nhấn "Huỷ nhận đơn" và xác nhận.
-5. Bật proxy, ghi lại request app gửi đi khi thao tác trên đơn, rồi sửa thành yêu cầu sửa hoặc xoá một dòng nhật ký đã có và phát lại request đó.
-6. Mở lại block "LỊCH SỬ" của đơn đó và check toàn bộ các dòng mốc.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-06` đang ở trạng thái "Đã ghép" — xem sheet Seed, ⛔ không tạo đơn mới. Chạy SAU TC-DLV-080/081 vì TC này tiêu đơn.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và ghi lại (chụp ảnh) toàn bộ các dòng mốc hiện có, gồm dòng "Ghép thành công".
+4. Nhấn "Huỷ nhận đơn", nhập lý do và xác nhận.
+5. Đăng nhập tài khoản A, nhấn tab "Hoạt động", mở đơn đó và mở block "LỊCH SỬ".
+6. Check toàn bộ các dòng mốc so với ảnh đã chụp ở step 3.</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>6. Block "LỊCH SỬ" vẫn giữ đủ mọi dòng mốc đã ghi ở step 3, gồm cả dòng ghép thành công, và KHÔNG dòng nào bị sửa hay biến mất.</t>
+          <t>6. Block "LỊCH SỬ" vẫn giữ đủ mọi dòng mốc đã ghi ở step 3, gồm cả dòng "Ghép thành công", và KHÔNG dòng nào bị sửa hay biến mất.</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>Đơn `MATCHED` rồi bị huỷ nhận đơn (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
+          <t>`SEED-DLV-06` ở "Đã ghép" rồi bị B huỷ nhận đơn (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="n"/>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: neo vào `RISK-DLV-09` — bug audit đã biết (`RISK-TS-01`: huỷ nhận đơn xoá dòng "Ghép thành công") vi phạm trực tiếp rule này, nên TC **dự kiến FAIL có chủ đích** cho tới khi bug được fix. · Căn cứ: `DOC-v1.1-01` §9 NFR-07 (log append-only, không API sửa/xoá). FAIL ⇒ log bug và cross-ref `RISK-TS-01`, ⛔ không hạ Expected theo hành vi hiện tại.</t>
+          <t>Mục đích: neo vào `RISK-DLV-09` — bug audit đã biết (`RISK-TS-01`: huỷ nhận đơn xoá dòng "Ghép thành công") vi phạm trực tiếp rule này, nên TC **dự kiến FAIL có chủ đích** cho tới khi bug được fix. · Căn cứ: `DOC-v1.1-01` §9 NFR-07 (log append-only, không API sửa/xoá). FAIL ⇒ log bug và cross-ref `RISK-TS-01`, ⛔ không hạ Expected theo hành vi hiện tại. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Bỏ phụ thuộc proxy: vế UI (huỷ nhận đơn không được xoá dòng) chạy được bằng thao tác thường nên Status Skipped → chạy được. Vế "không có API sửa/xoá dòng nhật ký" cần proxy — ghi nợ, chưa phủ. Vẫn 🔴 dự kiến FAIL có chủ đích theo `RISK-TS-01`.</t>
         </is>
       </c>
       <c r="N45" s="6" t="inlineStr">
@@ -15989,33 +15998,31 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Giao lại" (đã chạy xong TC-DLV-072) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn nút hành động chính ở cuối màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Xem lịch hẹn giao lại".</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn giao lại".</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Giao lại" (RESCHEDULED); vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: 1 trong 3 ô vai của nhóm trạng thái `RESCHEDULED` — mỗi vai fail độc lập. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. ⚠ Thanh timeline vẫn hiện đúng 5 mốc và mốc "Đang giao" đang active — đây là thiết kế đã chốt (`C-DLV-05(d)` Resolved 2026-09-17), ⛔ không FAIL vì thiếu mốc mới.</t>
+          <t>Mục đích: 1 trong 3 ô vai của nhóm trạng thái `RESCHEDULED` — mỗi vai fail độc lập. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. ⚠ Thanh timeline vẫn hiện đúng 5 mốc và mốc "Đang giao" đang active — đây là thiết kế đã chốt (`C-DLV-05(d)` Resolved 2026-09-17), ⛔ không FAIL vì thiếu mốc mới. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Người vận chuyển đang giữ hàng · sẽ giao lại theo lịch hẹn").</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
@@ -16068,33 +16075,31 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau", nhập lịch hẹn hợp lệ và xác nhận. (setup)
-4. Nhấn tab "Hoạt động" và mở lại đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Giao lại" (đã chạy xong TC-DLV-072) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn và trạng thái nút hành động chính — ⛔ KHÔNG nhấn (nhấn sẽ đẩy đơn về "Đang giao", thuộc TC-DLV-062).</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Giao lại theo lịch" và nhấn được để mở lại màn giao hàng.</t>
+          <t>3. Nhãn hành động chính hiển thị "Giao lại theo lịch" ở trạng thái enable.</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Giao lại" (RESCHEDULED); vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L47" s="6" t="n"/>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED — đây là vai DUY NHẤT có nút hành động thật ở trạng thái này, 2 vai kia chỉ xem.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED — đây là vai DUY NHẤT có nút hành động thật ở trạng thái này, 2 vai kia chỉ xem. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Bỏ vế "nhấn được để mở lại màn giao hàng" khỏi Expected vì nhấn sẽ tiêu trạng thái của TC-DLV-031/033/072 — vế này đã do TC-DLV-062 phủ. Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Giao lại cho người nhận").</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -16147,33 +16152,31 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản C, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Giao lại" (đã chạy xong TC-DLV-072) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản C, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn nút hành động chính và các nút khác trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Xem lịch hẹn" và KHÔNG có nút giao lại nào.</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn" và KHÔNG có nút giao lại nào.</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Giao lại" (RESCHEDULED); vai người nhận C (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng với TC-DLV-032 — quyền giao lại chỉ thuộc người vận chuyển. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED.</t>
+          <t>Mục đích: đối chứng với TC-DLV-032 — quyền giao lại chỉ thuộc người vận chuyển. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Người vận chuyển sẽ giao lại theo lịch hẹn").</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
@@ -16226,33 +16229,31 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Trả hàng" (đã chạy xong TC-DLV-066) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn, trạng thái nút hành động chính và mục lịch hẹn trả hàng trên màn — ⛔ KHÔNG nhấn nút (thuộc TC-DLV-063).</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Xác nhận đã nhận lại hàng" ở trạng thái enable và màn có mục xem lịch hẹn trả hàng.</t>
+          <t>3. Nhãn hành động chính hiển thị "Xác nhận đã nhận lại hàng" ở trạng thái enable và màn có mục xem lịch hẹn trả hàng.</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RETURNING`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Trả hàng" (RETURNING); vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L49" s="6" t="n"/>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: người gửi là vai DUY NHẤT đóng được đơn ở nhánh hoàn hàng — cặp với TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
+          <t>Mục đích: người gửi là vai DUY NHẤT đóng được đơn ở nhánh hoàn hàng — cặp với TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Đã lấy lại hàng từ người giao").</t>
         </is>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -16305,33 +16306,31 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận. (setup)
-4. Nhấn tab "Hoạt động" và mở lại đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Trả hàng" (đã chạy xong TC-DLV-066) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn nút hành động chính và các nút khác trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Xem lịch hẹn trả hàng" và KHÔNG có nút xác nhận đóng đơn.</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn trả hàng" và KHÔNG có nút xác nhận đóng đơn.</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNING`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Trả hàng" (RETURNING); vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. ⚠ Demo cho B nút "Đã trả hàng cho người gửi" (ngược Expected) — gặp trên STG ⇒ FAIL + log bug dẫn §8.12.3.</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr">
@@ -16384,33 +16383,31 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản C, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Trả hàng" (đã chạy xong TC-DLV-066) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản C, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn nút hành động chính trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Xem lý do hoàn hàng".</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lý do hoàn hàng".</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RETURNING`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Trả hàng" (RETURNING); vai người nhận C (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L51" s="6" t="n"/>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Không giao được · hàng đang được trả lại người gửi").</t>
         </is>
       </c>
       <c r="N51" s="6" t="inlineStr">
@@ -16463,35 +16460,34 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Dev/QA hỗ trợ lùi timestamp đơn để vượt mốc 2 giờ và 4 giờ — ⛔ không tái tạo được qua UI.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Báo cáo sự cố", gửi form báo sự cố cho đơn này, rồi đăng xuất. (setup)
-4. Nhờ dev/QA lùi timestamp của đơn để vượt qua cả mốc 2 giờ và mốc 4 giờ. (setup)
-5. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-6. Check trạng thái đơn và tab chứa đơn.</t>
+          <t>1. (setup) Tạo 1 đơn riêng: đăng nhập A, đăng 1 tin NEED khai C là người nhận, đăng xuất; đăng nhập B, nhấn "Tôi mang giúp được" và xác nhận, rồi nhấn "Tôi đã lấy hàng" → ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" → tại màn "Xác nhận đã lấy hàng" nhấn "Xác nhận" → ở popup "Đã lấy hàng" nhấn "Đồng ý".
+2. Nhấn "Báo cáo sự cố", gửi form báo sự cố cho đơn này, rồi đăng xuất. (setup)
+3. Nhờ dev/QA lùi timestamp của đơn để vượt qua cả mốc 2 giờ và mốc 4 giờ. (setup)
+4. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+5. Check trạng thái đơn và tab chứa đơn.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>6. Đơn KHÔNG ở trạng thái "Hoàn thành" và vẫn nằm ở tab "Đang diễn ra".</t>
+          <t>5. Đơn KHÔNG ở trạng thái "Hoàn thành" và vẫn nằm ở tab "Đang diễn ra".</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>Đơn `INCIDENT` đã vượt mốc 2h và 4h = `SEED-DLV-04` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-04` — đơn có sự cố (INCIDENT) đã vượt mốc 2h và 4h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L52" s="5" t="n"/>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: chốt ranh giới nhánh sự cố ⟷ luồng tự đóng thường — dễ lập trình sai thành "quá giờ thì đóng". · Căn cứ: `DOC-v1.1-01` §8.10.1 BR10-04 (SC mới gắn REQ giữ ID, không sửa `SC-DLV-024` v1.0 vốn đúng cho nhánh thường). ⛔ Không assert vế "admin xử lý" — role admin out of scope v1.1 (`C-DLV-07` Resolved 2026-09-17).</t>
+          <t>Mục đích: chốt ranh giới nhánh sự cố ⟷ luồng tự đóng thường — dễ lập trình sai thành "quá giờ thì đóng". · Căn cứ: `DOC-v1.1-01` §8.10.1 BR10-04 (SC mới gắn REQ giữ ID, không sửa `SC-DLV-024` v1.0 vốn đúng cho nhánh thường). ⛔ Không assert vế "admin xử lý" — role admin out of scope v1.1 (`C-DLV-07` Resolved 2026-09-17). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). 🚫 Deferred — cần dev lùi timestamp, chạy chung lô với TC-DLV-057/067, TC-DLV-024 (v1.0) và SC-TS-006.</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr">
@@ -16544,38 +16540,37 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
-4. Chọn "Quầy lễ tân" ở field "Giao cho".
-5. Đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" khi vẫn để trống cả hai ô của khối "NGƯỜI NHẬN TẠI QUẦY".
-6. Nhập "Trần Thị Lan" vào ô "Họ tên người trực quầy".
-7. Nhập "0987654321" vào ô "Số điện thoại".
-8. Nhấn "Xác nhận đã giao hàng" và đồng ý ở popup xác nhận.
-9. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Dùng đơn #3 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Chạy sau TC-DLV-077 (nếu chạy 077).
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Quầy lễ tân" ở field "Giao cho".
+4. Đính 1 ảnh JPG, để TRỐNG cả hai ô của khối "NGƯỜI NHẬN TẠI QUẦY" rồi nhấn "Xác nhận đã giao hàng" — form phải không đi tiếp.
+5. Nhập "Trần Thị Lan" vào ô "Họ tên người trực quầy".
+6. Nhập "0987654321" vào ô "Số điện thoại".
+7. Nhấn "Xác nhận đã giao hàng" và nhấn "Xác nhận" ở popup.
+8. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>9. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã gửi tại quầy lễ tân — Trần Thị Lan".</t>
+          <t>8. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã gửi tại quầy lễ tân — Trần Thị Lan".</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #3 của `SEED-DLV-02`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
+          <t>Đơn #3 `SEED-DLV-02` ở "Đang giao"; tên người trực quầy + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
       <c r="L53" s="6" t="n"/>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: step 5 là vế âm gộp trong cùng TC — submit khi 2 ô trống phải không đi được, nên step 9 mới quan sát được kết quả dương. · Căn cứ: `C-DLV-06` Resolved 2026-09-17 (BA *"trên UI có dấu * bắt buộc mà"*, QA submit thử với 2 ô trống thì form không đi) + `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 3. ⛔ Chưa assert cờ "không liên lạc được" và `NTF-05`/`NTF-11` — `C-DLV-08` (a)(b) còn Partially, QA tự xác minh qua block "LỊCH SỬ" trước khi siết TC. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
+          <t>Mục đích: step 5 là vế âm gộp trong cùng TC — submit khi 2 ô trống phải không đi được, nên step 9 mới quan sát được kết quả dương. · Căn cứ: `C-DLV-06` Resolved 2026-09-17 (BA *"trên UI có dấu * bắt buộc mà"*, QA submit thử với 2 ô trống thì form không đi) + `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 3. ⛔ Chưa assert cờ "không liên lạc được" và `NTF-05`/`NTF-11` — `C-DLV-08` (a)(b) còn Partially, QA tự xác minh qua block "LỊCH SỬ" trước khi siết TC. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-070 (1 lần submit, 2 evidence). Step 4 mà form đi tiếp được ⇒ FAIL ngay tại step 4.</t>
         </is>
       </c>
       <c r="N53" s="6" t="inlineStr">
@@ -16628,38 +16623,37 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
-4. Chọn "Quầy bảo vệ" ở field "Giao cho".
-5. Nhập "Lê Văn Tám" vào ô "Họ tên người trực quầy".
-6. Nhập "0901112223" vào ô "Số điện thoại".
-7. Đính 1 ảnh JPG từ thư viện thiết bị.
-8. Nhấn "Xác nhận đã giao hàng" và đồng ý ở popup xác nhận.
-9. Check dòng mới nhất ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Dùng đơn #4 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Quầy bảo vệ" ở field "Giao cho".
+4. Nhập "Lê Văn Tám" vào ô "Họ tên người trực quầy".
+5. Nhập "0901112223" vào ô "Số điện thoại".
+6. Đính 1 ảnh JPG từ thư viện thiết bị.
+7. Nhấn "Xác nhận đã giao hàng" và nhấn "Xác nhận" ở popup.
+8. Check dòng mới nhất ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>9. Block "LỊCH SỬ" có dòng mới "Đã gửi tại quầy bảo vệ — Lê Văn Tám", ⛔ KHÔNG dùng chữ "quầy lễ tân".</t>
+          <t>8. Block "LỊCH SỬ" có dòng mới "Đã gửi tại quầy bảo vệ — Lê Văn Tám", ⛔ KHÔNG dùng chữ "quầy lễ tân".</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #4 của `SEED-DLV-02`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
+          <t>Đơn #4 `SEED-DLV-02` ở "Đang giao"; tên người trực quầy + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-045 — hai quầy dùng hai mẫu câu nhật ký khác nhau, lập trình gộp 1 chuỗi là defect. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 4. ⛔ Chưa assert cờ/`NTF` — `C-DLV-08` (a)(b) còn Partially. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
+          <t>Mục đích: cặp với TC-DLV-045 — hai quầy dùng hai mẫu câu nhật ký khác nhau, lập trình gộp 1 chuỗi là defect. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 4. ⛔ Chưa assert cờ/`NTF` — `C-DLV-08` (a)(b) còn Partially. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-071 (1 lần submit, 2 evidence).</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr">
@@ -16712,36 +16706,35 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
-4. Chọn "Người nhận" ở field "Giao cho" mà chưa đính ảnh nào.
-5. Check trạng thái nút "Xác nhận đã giao hàng".
-6. Đính 1 ảnh JPG từ thư viện thiết bị.
-7. Check lại trạng thái nút "Xác nhận đã giao hàng".</t>
+          <t>1. (setup) Dùng đơn #1 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Người nhận" ở field "Giao cho" mà chưa đính ảnh nào.
+4. Check trạng thái nút "Xác nhận đã giao hàng".
+5. Đính 1 ảnh JPG từ thư viện thiết bị.
+6. Check lại trạng thái nút "Xác nhận đã giao hàng", rồi nhấn Back thoát màn — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>7. Nút "Xác nhận đã giao hàng" ở trạng thái disable tại step 5 khi chưa có ảnh, và chuyển sang enable ngay sau khi đính ảnh đầu tiên.</t>
+          <t>6. Nút "Xác nhận đã giao hàng" disable khi chưa có ảnh (quan sát ở step 4) và chuyển sang enable ngay sau khi đính ảnh đầu tiên.</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02`; 0 ảnh (chặn) và 1 ảnh (biên dưới hợp lệ) (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
+          <t>Đơn #1 `SEED-DLV-02` ở "Đang giao"; 0 ảnh (chặn) và 1 ảnh (biên dưới hợp lệ) (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
       <c r="L55" s="6" t="n"/>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp biên dưới 0⟷1 của ảnh bằng chứng lúc giao — ngược hẳn ảnh lúc lấy hàng (TC-DLV-042, 0 ảnh vẫn hợp lệ). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-02. Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1 vì TC đó sẽ đẩy đơn sang "Đã giao". · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
+          <t>Mục đích: cặp biên dưới 0⟷1 của ảnh bằng chứng lúc giao — ngược hẳn ảnh lúc lấy hàng (TC-DLV-042, 0 ảnh vẫn hợp lệ). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-02. Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1 vì TC đó sẽ đẩy đơn sang "Đã giao". · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Thứ tự trên đơn #1: TC-DLV-047 → 049 → 043 (+068) → 048.</t>
         </is>
       </c>
       <c r="N55" s="6" t="inlineStr">
@@ -16794,35 +16787,34 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Người nhận", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở block "LỊCH SỬ" và mở ảnh bằng chứng vừa ghi.
-5. Nhấn giữ vào ảnh và tìm thao tác xoá ảnh.
-6. Check ảnh bằng chứng ở mốc "Đã giao" sau khi đã thử xoá.</t>
+          <t>1. (setup) Dùng đơn #1 `SEED-DLV-02` đã "Đã giao" sau TC-DLV-043 (= `SEED-DLV-05`) — ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và nhấn vào ảnh bằng chứng ở mốc giao hàng để mở màn xem ảnh.
+4. Nhấn giữ ảnh ~2 giây, rồi rà đủ 3 vị trí: menu vừa hiện (nếu có) · icon/nút trên màn xem ảnh (thùng rác, "Xoá", menu ⋮) · vuốt ảnh sang trái. Rà xong 3 vị trí thì dừng.
+5. Đóng màn xem ảnh và check ảnh bằng chứng ở mốc "Đã giao".</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>6. KHÔNG có thao tác xoá nào khả dụng và ảnh bằng chứng vẫn còn nguyên ở mốc nhật ký.</t>
+          <t>5. KHÔNG có thao tác xoá nào khả dụng ở cả 3 vị trí và ảnh bằng chứng vẫn còn nguyên ở mốc nhật ký.</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>Đơn `DELIVERED` có 1 ảnh bằng chứng = `SEED-DLV-05` (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
+          <t>`SEED-DLV-05` = đơn #1 `SEED-DLV-02` sau TC-DLV-043 (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
       <c r="L56" s="5" t="n"/>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-07 — ảnh gắn vào mốc nhật ký là bất biến. Liên quan cùng nhóm bất biến với TC-DLV-078 (log append-only).</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-07 — ảnh gắn vào mốc nhật ký là bất biến. Liên quan cùng nhóm bất biến với TC-DLV-078 (log append-only). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr">
@@ -16875,19 +16867,19 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Người nhận" và đính 1 ảnh JPG. (setup)
+          <t>1. (setup) Dùng đơn #1 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Chạy sau TC-DLV-047.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Người nhận" ở field "Giao cho" và đính 1 ảnh JPG. (setup)
 4. Nhấn "Xác nhận đã giao hàng".
-5. Check nội dung popup xác nhận.
-6. Nhấn nút huỷ ở popup.
+5. Check nội dung popup xác nhận (có nêu thao tác không thể hoàn tác).
+6. Nhấn "Huỷ" ở popup.
 7. Check trạng thái đơn và số dòng ở block "LỊCH SỬ".</t>
         </is>
       </c>
@@ -16898,13 +16890,13 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>Đơn #1 `SEED-DLV-02` ở "Đang giao" (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L57" s="6" t="n"/>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng âm cho TC-DLV-043 — popup phải là gate thật, không phải thông báo trang trí. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-06 (popup nêu rõ hệ quả không thể hoàn tác trước khi ghi mốc). Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1.</t>
+          <t>Mục đích: đối chứng âm cho TC-DLV-043 — popup phải là gate thật, không phải thông báo trang trí. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-06 (popup nêu rõ hệ quả không thể hoàn tác trước khi ghi mốc). Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N57" s="6" t="inlineStr">
@@ -16957,20 +16949,20 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao" và nhấn "Không thể liên lạc cho người nhận?".
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Đây là TC ĐẦU TIÊN của chuỗi 03-A.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Nhấn link "Không thể liên lạc cho người nhận?".
 4. Check tên màn vừa mở và các thành phần trên màn đó.
 5. Nhấn "Không thể liên lạc với người gửi và người nhận?".
 6. Check tiêu đề và hai lựa chọn của modal vừa hiện.
 7. Nhấn "Xử lý đơn hàng".
-8. Check tên màn vừa mở và thứ tự các phương án trên màn đó.</t>
+8. Check tên màn vừa mở và thứ tự các phương án trên màn đó, rồi nhấn Back — ⛔ không chọn phương án nào.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -16980,17 +16972,17 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao" (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: `BR08-02` ghi thứ tự NGƯỢC (lễ tân trước bảo vệ) và mô tả 1 danh sách 4 bước — assert theo PRD sẽ FAIL oan. · Căn cứ: `C-DLV-06` **Resolved 2026-09-17** — cấu trúc 4 tầng (màn "Xác nhận đã giao" → màn "Liên hệ người gửi" → modal "Chưa liên lạc được?" → màn "Xử lý đơn hàng") và thứ tự bảo-vệ-trước là oracle chính thức, khớp `AC-17.1.01`/`§8.8.2`. App lệch bản này ⇒ log bug và dẫn `C-DLV-06`, ⛔ không sửa TC theo `BR08-02`.</t>
+          <t>Mục đích: `BR08-02` ghi thứ tự NGƯỢC (lễ tân trước bảo vệ) và mô tả 1 danh sách 4 bước — assert theo PRD sẽ FAIL oan. · Căn cứ: `C-DLV-06` **Resolved 2026-09-17** — cấu trúc 4 tầng (màn "Xác nhận đã giao" → màn "Liên hệ người gửi" → modal "Chưa liên lạc được?" → màn "Xử lý đơn hàng") và thứ tự bảo-vệ-trước là oracle chính thức, khớp `AC-17.1.01`/`§8.8.2`. App lệch bản này ⇒ log bug và dẫn `C-DLV-06`, ⛔ không sửa TC theo `BR08-02`. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Steps giữ ĐÚNG cấu trúc 4 tầng BA chốt (`C-DLV-06`) vì đó chính là điểm kiểm. STG hiện hiện bottom sheet 2 lựa chọn ("Liên hệ người gửi"/"Xử lý đơn hàng") ngay sau step 3 ⇒ lệch từ step 4 — đã log FE-333 (chờ BA). Status đổi Pass → Fail: verdict Pass của VR-021 chỉ quan sát tới bottom sheet, chưa từng thấy màn ở step 8. Chạy lại khi FE-333 có kết luận.</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr">
@@ -17043,17 +17035,17 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao" và nhấn "Không thể liên lạc cho người nhận?". (setup)
-4. Chọn "Người được uỷ quyền" ở field "Giao cho" trên màn "Liên hệ người gửi".
-5. Check giá trị hai ô tên và số điện thoại người nhận thay, dòng "Uỷ quyền bởi", khu vực liên hệ người gửi và dấu bắt buộc của ô ảnh.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-050) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Nhấn link "Không thể liên lạc cho người nhận?" để mở màn "Liên hệ người gửi" (STG hiện: chọn "Liên hệ người gửi" ở bottom sheet — FE-333).
+4. Chọn "Người được uỷ quyền" ở field "Giao cho".
+5. Check giá trị hai ô tên và số điện thoại người nhận thay, dòng "Uỷ quyền bởi", khu vực liên hệ người gửi và dấu bắt buộc của ô ảnh; rồi nhấn Back — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
@@ -17063,13 +17055,13 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03` (test_data_catalog §DLV — Tên người nhận thay)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao" (test_data_catalog §DLV — Tên người nhận thay)</t>
         </is>
       </c>
       <c r="L59" s="6" t="n"/>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng với TC-DLV-044 — cùng loại đối tượng nhận nhưng khác MÀN VÀO nên "Uỷ quyền bởi" phải ra giá trị ngược lại; và ở màn này ⛔ KHÔNG prefill người uỷ quyền người gửi đã khai. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-03 + §8.7.1 BR07-05. Gộp bốn quan sát vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả bốn thuộc cùng một trạng thái tĩnh của màn.</t>
+          <t>Mục đích: đối chứng với TC-DLV-044 — cùng loại đối tượng nhận nhưng khác MÀN VÀO nên "Uỷ quyền bởi" phải ra giá trị ngược lại; và ở màn này ⛔ KHÔNG prefill người uỷ quyền người gửi đã khai. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-03 + §8.7.1 BR07-05. Gộp bốn quan sát vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả bốn thuộc cùng một trạng thái tĩnh của màn. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N59" s="6" t="inlineStr">
@@ -17122,16 +17114,16 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", nhấn "Không thể liên lạc với người gửi và người nhận?" rồi nhấn "Xử lý đơn hàng". (setup)
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-B` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-053) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
 4. Nhấn "Gửi tại quầy lễ tân".
 5. Nhập "Phạm Thị Hoa" vào ô "Họ tên người trực quầy".
 6. Nhập "0933444555" vào ô "Số điện thoại".
@@ -17147,13 +17139,13 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
+          <t>`SEED-DLV-03-B` ở "Đang giao" → "Đã giao"; tên người trực quầy + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
       <c r="L60" s="5" t="n"/>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: đường thứ hai tới cùng kết cục của TC-DLV-045 — hai đường phải cùng đòi tên người trực quầy, SĐT và ảnh. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-04 + §8.12.4 mẫu câu 3. ⛔ Chưa assert điểm phân biệt với TC-DLV-045 (cờ "không liên lạc được" / `NTF-05` ⟷ `NTF-11`) — `C-DLV-08` (a)(b) còn Partially, QA vibe-check block "LỊCH SỬ" xong mới siết. ⛔ Không assert hạn giữ hàng 4h/24h — out of scope v1.1.</t>
+          <t>Mục đích: đường thứ hai tới cùng kết cục của TC-DLV-045 — hai đường phải cùng đòi tên người trực quầy, SĐT và ảnh. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-04 + §8.12.4 mẫu câu 3. ⛔ Chưa assert điểm phân biệt với TC-DLV-045 (cờ "không liên lạc được" / `NTF-05` ⟷ `NTF-11`) — `C-DLV-08` (a)(b) còn Partially, QA vibe-check block "LỊCH SỬ" xong mới siết. ⛔ Không assert hạn giữ hàng 4h/24h — out of scope v1.1. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr">
@@ -17206,17 +17198,17 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng" rồi nhấn "Cầm hàng về". (setup)
-4. Chọn "Tôi sẽ giao lại sau".
-5. Check tiêu đề khối lịch hẹn và nhãn ô địa điểm.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-051) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau".
+5. Check tiêu đề khối lịch hẹn và nhãn ô địa điểm — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
@@ -17226,13 +17218,13 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `retry` (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao"; chế độ giao lại (retry) (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
       <c r="L61" s="6" t="n"/>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-059 — hai chế độ dùng chung một form nên rất dễ bị lập trình cứng một bộ nhãn. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02.</t>
+          <t>Mục đích: cặp với TC-DLV-059 — hai chế độ dùng chung một form nên rất dễ bị lập trình cứng một bộ nhãn. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N61" s="6" t="inlineStr">
@@ -17285,17 +17277,17 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng" rồi nhấn "Cầm hàng về". (setup)
-4. Chọn "Tôi sẽ trả về cho người gửi".
-5. Check tiêu đề khối lịch hẹn và nhãn ô địa điểm.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-058) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi".
+5. Check tiêu đề khối lịch hẹn và nhãn ô địa điểm, rồi nhấn Back — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -17305,13 +17297,13 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `return` (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao"; chế độ trả hàng (return) (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
       <c r="L62" s="5" t="n"/>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02 + vibe-check demo 2026-09-17 (`C-DLV-05` — khối "Hẹn trả hàng" do chính Carrier nhập tại màn "Xử lý đơn hàng").</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02 + vibe-check demo 2026-09-17 (`C-DLV-05` — khối "Hẹn trả hàng" do chính Carrier nhập tại màn "Xử lý đơn hàng"). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr">
@@ -17364,34 +17356,35 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau". (setup)
-4. Chọn ngày hẹn là ngày hiện tại cộng 7 ngày.
-5. Chọn lại ngày hẹn là ngày hiện tại cộng 8 ngày.
-6. Check trạng thái ô "Ngày hẹn" và thông báo lỗi nếu có.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-059) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau". (setup)
+5. Chọn "Ngày hẹn" = ngày hiện tại + 7 ngày và quan sát ô "Ngày hẹn".
+6. Chọn lại "Ngày hẹn" = ngày hiện tại + 8 ngày.
+7. Check trạng thái ô "Ngày hẹn" và thông báo lỗi nếu có — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>6. Ngày cộng 7 được nhận không báo lỗi, còn ngày cộng 8 bị chặn kèm thông báo lỗi ở ô "Ngày hẹn".</t>
+          <t>7. Ngày +7 được nhận không báo lỗi (quan sát ở step 5), còn ngày +8 bị chặn (không chọn được hoặc báo lỗi ở ô "Ngày hẹn").</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>Ngày hẹn +7 ngày (hợp lệ) và +8 ngày (chặn) (test_data_catalog §DLV — Ngày hẹn cầm hàng về, biên)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao"; ngày hẹn +7 (hợp lệ) và +8 (chặn) (test_data_catalog §DLV — Ngày hẹn cầm hàng về, biên)</t>
         </is>
       </c>
       <c r="L63" s="6" t="n"/>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp biên trên của trần 7 ngày — hai giá trị liền kề fail độc lập nên phải nằm trong cùng 1 TC để so được. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-04.</t>
+          <t>Mục đích: cặp biên trên của trần 7 ngày — hai giá trị liền kề fail độc lập nên phải nằm trong cùng 1 TC để so được. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-04. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N63" s="6" t="inlineStr">
@@ -17444,35 +17437,36 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ giao lại sau" và chọn ngày hẹn hợp lệ. (setup)
-4. Chọn giờ từ "09:00" và giờ đến "09:30".
-5. Chọn lại giờ đến "09:29".
-6. Chọn lại giờ đến "08:30".
-7. Check trạng thái hai ô giờ và thông báo lỗi nếu có.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-060) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về", chọn "Tôi sẽ giao lại sau" và chọn "Ngày hẹn" = ngày mai. (setup)
+5. Chọn giờ từ "09:00" và giờ đến "09:30", quan sát hai ô giờ.
+6. Chọn lại giờ đến "09:29".
+7. Chọn lại giờ đến "08:30".
+8. Check trạng thái hai ô giờ và thông báo lỗi nếu có — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>7. Khoảng 09:00–09:30 được nhận không báo lỗi, còn khoảng 09:00–09:29 và khoảng có giờ đến nhỏ hơn giờ từ đều bị chặn kèm thông báo lỗi.</t>
+          <t>8. Khoảng 09:00–09:30 được nhận không báo lỗi, còn khoảng 09:00–09:29 và khoảng có giờ đến nhỏ hơn giờ từ đều bị chặn kèm thông báo lỗi.</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>Giờ hẹn 30 phút (hợp lệ), 29 phút (chặn), giờ đến ≤ giờ từ (chặn) (test_data_catalog §DLV — Giờ hẹn từ–đến, biên)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao"; giờ hẹn 30 phút (hợp lệ), 29 phút (chặn), giờ đến ≤ giờ từ (chặn) (test_data_catalog §DLV — Giờ hẹn từ–đến, biên)</t>
         </is>
       </c>
       <c r="L64" s="5" t="n"/>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: gộp ba giá trị vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả ba cùng thuộc một trạng thái tĩnh của form, không mất khả năng bắt lỗi riêng vì Expected nêu đích danh từng khoảng. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-03.</t>
+          <t>Mục đích: gộp ba giá trị vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả ba cùng thuộc một trạng thái tĩnh của form, không mất khả năng bắt lỗi riêng vì Expected nêu đích danh từng khoảng. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-03. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr">
@@ -17525,34 +17519,32 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ giao lại sau", nhập lịch hẹn hợp lệ và xác nhận. (setup)
-4. Nhấn tab "Hoạt động" và mở lại đơn đó.
-5. Nhấn "Giao lại theo lịch".
-6. Check màn vừa mở và trạng thái đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Giao lại" (đã chạy xong TC-DLV-031/032/033) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Nhấn nút hành động chính (tài liệu: "Giao lại theo lịch"; demo: "Giao lại cho người nhận").
+4. Check màn vừa mở và trạng thái đơn (nhấn Back về màn Theo dõi đơn nếu cần) — ⛔ không submit giao hàng.</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>6. Màn giao hàng mở lại được và đơn trở về trạng thái "Đang giao".</t>
+          <t>4. Màn giao hàng mở lại được và đơn trở về trạng thái "Đang giao".</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED` = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở "Giao lại" (RESCHEDULED); vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L65" s="6" t="n"/>
       <c r="M65" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: `AC-18.1.01` viết *"theo lịch hẹn, đơn quay lại IN_TRANSIT"* — đọc được thành hệ thống tự chuyển, chạy TC theo cách hiểu đó sẽ treo chờ đúng giờ. · Căn cứ: `C-DLV-05` **Resolved 2026-09-17** — chính người vận chuyển bấm, không có gate chặn theo giờ nên bấm sớm hơn lịch hẹn vẫn đi được; không giới hạn số lần hẹn. App chặn theo giờ ⇒ log bug và dẫn `C-DLV-05`.</t>
+          <t>Mục đích: `AC-18.1.01` viết *"theo lịch hẹn, đơn quay lại IN_TRANSIT"* — đọc được thành hệ thống tự chuyển, chạy TC theo cách hiểu đó sẽ treo chờ đúng giờ. · Căn cứ: `C-DLV-05` **Resolved 2026-09-17** — chính người vận chuyển bấm, không có gate chặn theo giờ nên bấm sớm hơn lịch hẹn vẫn đi được; không giới hạn số lần hẹn. App chặn theo giờ ⇒ log bug và dẫn `C-DLV-05`. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Không cần chờ tới giờ hẹn (không có gate theo giờ — `C-DLV-05`).</t>
         </is>
       </c>
       <c r="N65" s="6" t="inlineStr">
@@ -17605,34 +17597,32 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Nhấn "Xác nhận đã nhận lại hàng" và đồng ý ở popup xác nhận.
-6. Check trạng thái đơn và tab chứa đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Trả hàng" (đã chạy xong TC-DLV-034/035/036 và step 1 của TC-DLV-065) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Nhấn "Xác nhận đã nhận lại hàng" và đồng ý ở popup xác nhận.
+4. Check nhãn trạng thái đơn, nút hành động chính và tab chứa đơn.</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>6. Đơn chuyển sang trạng thái đã trả lại người gửi và nằm ở tab "Đã hoàn thành".</t>
+          <t>4. Đơn nằm ở tab "Đã hoàn thành", nhãn trạng thái KHÔNG phải "Hoàn thành" (đơn trả người gửi khác đơn hoàn thành — BR09-06) và nút "Xác nhận đã nhận lại hàng" không còn.</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNING` = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở "Trả hàng" (RETURNING) → RETURNED; vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đây là bước tạo trạng thái `RETURNED` dùng chung cho TC-DLV-037/038/039, TC-DLV-064/065, TC-DLV-073 và cho `GIFT`/`ACT` — chạy xong mới chạy nhóm đó.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đây là bước tạo trạng thái `RETURNED` dùng chung cho TC-DLV-037/038/039, TC-DLV-064/065, TC-DLV-073 và cho `GIFT`/`ACT` — chạy xong mới chạy nhóm đó. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Ghi nguyên văn nhãn trạng thái STG hiển thị vào Notes (PRD không đặc tả chữ). ⚠ Demo 2026-09-23 lệch PRD: cần CẢ B bấm "Đã trả hàng cho người gửi" và A bấm "Đã lấy lại hàng từ người giao", rồi đơn thành "Hoàn thành" — STG làm như demo ⇒ FAIL + log bug dẫn BR09-06.</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr">
@@ -17685,18 +17675,18 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng" rồi nhấn "Cầm hàng về". (setup)
-4. Chọn "Tôi sẽ trả về cho người gửi".
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-062) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi".
 5. Nhập "Người nhận từ chối nhận hàng" vào ô ghi chú.
-6. Nhập lịch hẹn hợp lệ và nhấn xác nhận.
+6. Nhập "Ngày hẹn" = ngày mai, giờ từ "09:00" đến "10:00", "Nơi nhận lại hàng" = "Sảnh toà FPT Tower", nhấn nút xác nhận và đồng ý ở popup.
 7. Mở block "LỊCH SỬ" và check ghi chú kèm mốc cầm hàng về.</t>
         </is>
       </c>
@@ -17707,13 +17697,13 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `return` + ghi chú lý do từ chối (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao" → sau TC này thành "Trả hàng" (RETURNING); ghi chú lý do từ chối (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
       <c r="L67" s="6" t="n"/>
       <c r="M67" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-07 — từ chối nhận hàng đi chung nhánh return, phân biệt với nhánh không liên lạc được chỉ bằng ghi chú.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-07 — từ chối nhận hàng đi chung nhánh return, phân biệt với nhánh không liên lạc được chỉ bằng ghi chú. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). TC này là bước đẩy chuỗi 03-A sang "Trả hàng" — chạy xong mới chạy TC-DLV-034/035/036.</t>
         </is>
       </c>
       <c r="N67" s="6" t="inlineStr">
@@ -17766,27 +17756,25 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Người nhận", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
+          <t>1. (setup) Dùng đơn #1 `SEED-DLV-02` ngay sau khi TC-DLV-043 submit xong — chạy chung, ⛔ không tạo đơn mới.
+2. Trên màn Theo dõi đơn (vai B), mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>4. Dòng mốc giao hàng ghi đúng nguyên văn "Đã giao tận tay người nhận", kèm thời điểm và dấu hiệu có ảnh bằng chứng.</t>
+          <t>2. Dòng mốc giao hàng có tiêu đề đúng nguyên văn "Đã giao tận tay người nhận", kèm thời điểm và chữ "có ảnh bằng chứng".</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>Đơn `DELIVERED` qua nhánh giao tận tay = `SEED-DLV-05` (test_data_catalog §DLV — Đối tượng nhận)</t>
+          <t>Đơn #1 `SEED-DLV-02` vừa "Đã giao" qua nhánh giao tận tay (test_data_catalog §DLV — Đối tượng nhận)</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
@@ -17796,7 +17784,7 @@
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: 1 trong 6 mẫu câu nhật ký của `§8.12.4` — mỗi mẫu câu là 1 chuỗi verbatim riêng, sai chữ nào là defect chữ đó. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 1 + dòng "Mọi dòng" (thời điểm + cờ không liên lạc nếu có + dấu hiệu có ảnh). Assert nguyên văn kể cả dấu gạch ngang, ⛔ không paraphrase.</t>
+          <t>Mục đích: 1 trong 6 mẫu câu nhật ký của `§8.12.4` — mỗi mẫu câu là 1 chuỗi verbatim riêng, sai chữ nào là defect chữ đó. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 1 + dòng "Mọi dòng" (thời điểm + cờ không liên lạc nếu có + dấu hiệu có ảnh). Assert nguyên văn kể cả dấu gạch ngang, ⛔ không paraphrase. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chữ "có ảnh bằng chứng" lấy từ demo 2026-09-23 (PRD §8.12.4 chỉ nói "dấu hiệu có ảnh") — STG dùng icon thay chữ ⇒ vẫn PASS, ghi Notes.</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr">
@@ -17849,33 +17837,31 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Người được uỷ quyền", nhập tên "Nguyễn Văn Bảy" và số điện thoại "0912345678", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
+          <t>1. (setup) Dùng đơn #2 `SEED-DLV-02` ngay sau khi TC-DLV-044 submit xong — chạy chung, ⛔ không tạo đơn mới.
+2. Trên màn Theo dõi đơn (vai B), mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>4. Dòng mốc giao hàng ghi đúng nguyên văn "Đã giao cho người được uỷ quyền — Nguyễn Văn Bảy · 0912345678 — uỷ quyền bởi Người nhận", kèm thời điểm và dấu hiệu có ảnh bằng chứng.</t>
+          <t>2. Dòng mốc giao hàng ghi đúng nguyên văn "Đã giao cho người được uỷ quyền — Nguyễn Văn Bảy · 0912345678 — uỷ quyền bởi Người nhận", kèm thời điểm và chữ "có ảnh bằng chứng".</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>Đơn `DELIVERED` qua nhánh uỷ quyền; tên 12 ký tự + SĐT hợp lệ (test_data_catalog §DLV — Tên người nhận thay)</t>
+          <t>Đơn #2 `SEED-DLV-02` vừa "Đã giao" qua nhánh uỷ quyền (test_data_catalog §DLV — Tên người nhận thay)</t>
         </is>
       </c>
       <c r="L69" s="6" t="n"/>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: mẫu câu phức tạp nhất trong 6 mẫu — có 2 biến nội dung và 1 biến nguồn uỷ quyền, dễ ghép sai thứ tự. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 2. Assert nguyên văn kể cả dấu gạch ngang và dấu chấm giữa tên với số điện thoại.</t>
+          <t>Mục đích: mẫu câu phức tạp nhất trong 6 mẫu — có 2 biến nội dung và 1 biến nguồn uỷ quyền, dễ ghép sai thứ tự. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 2. Assert nguyên văn kể cả dấu gạch ngang và dấu chấm giữa tên với số điện thoại. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Xem ghi chú định dạng demo ở TC-DLV-044.</t>
         </is>
       </c>
       <c r="N69" s="6" t="inlineStr">
@@ -17928,33 +17914,31 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Quầy lễ tân", nhập tên "Trần Thị Lan" và số điện thoại "0987654321", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
+          <t>1. (setup) Dùng đơn #3 `SEED-DLV-02` ngay sau khi TC-DLV-045 submit xong — chạy chung, ⛔ không tạo đơn mới.
+2. Trên màn Theo dõi đơn (vai B), mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>4. Dòng mốc giao hàng ghi đúng nguyên văn "Đã gửi tại quầy lễ tân — Trần Thị Lan", kèm thời điểm và dấu hiệu có ảnh bằng chứng.</t>
+          <t>2. Dòng mốc giao hàng ghi đúng nguyên văn "Đã gửi tại quầy lễ tân — Trần Thị Lan", kèm thời điểm và chữ "có ảnh bằng chứng".</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>Đơn `DELIVERED` qua nhánh quầy lễ tân (test_data_catalog §DLV — Tên người trực quầy)</t>
+          <t>Đơn #3 `SEED-DLV-02` vừa "Đã giao" qua nhánh quầy lễ tân (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
       <c r="L70" s="5" t="n"/>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 3. Assert nguyên văn, ⛔ không paraphrase.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 3. Assert nguyên văn, ⛔ không paraphrase. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr">
@@ -18007,33 +17991,31 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Quầy bảo vệ", nhập tên "Lê Văn Tám" và số điện thoại "0901112223", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
+          <t>1. (setup) Dùng đơn #4 `SEED-DLV-02` ngay sau khi TC-DLV-046 submit xong — chạy chung, ⛔ không tạo đơn mới.
+2. Trên màn Theo dõi đơn (vai B), mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>4. Dòng mốc giao hàng ghi đúng nguyên văn "Đã gửi tại quầy bảo vệ — Lê Văn Tám", kèm thời điểm và dấu hiệu có ảnh bằng chứng.</t>
+          <t>2. Dòng mốc giao hàng ghi đúng nguyên văn "Đã gửi tại quầy bảo vệ — Lê Văn Tám", kèm thời điểm và chữ "có ảnh bằng chứng".</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Đơn `DELIVERED` qua nhánh quầy bảo vệ (test_data_catalog §DLV — Tên người trực quầy)</t>
+          <t>Đơn #4 `SEED-DLV-02` vừa "Đã giao" qua nhánh quầy bảo vệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
       <c r="L71" s="6" t="n"/>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-070 — hai quầy là hai mẫu câu tách biệt trong bảng `§8.12.4`, gộp 1 chuỗi có tham số là defect. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 4.</t>
+          <t>Mục đích: cặp với TC-DLV-070 — hai quầy là hai mẫu câu tách biệt trong bảng `§8.12.4`, gộp 1 chuỗi có tham số là defect. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 4. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N71" s="6" t="inlineStr">
@@ -18086,32 +18068,33 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ giao lại sau", nhập ngày hẹn hợp lệ, giờ "09:00" đến "10:00", nơi hẹn "Sảnh toà FPT Tower" rồi xác nhận. (setup)
-4. Mở block "LỊCH SỬ" và check dòng mốc cầm hàng về.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-061) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về". Chọn "Tôi sẽ giao lại sau", nhập "Ngày hẹn" = ngày mai, giờ từ "09:00" đến "10:00", "Nơi giao lại" = "Sảnh toà FPT Tower", nhấn nút xác nhận và đồng ý ở popup.
+5. Mở block "LỊCH SỬ" và check dòng mốc cầm hàng về.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>4. Dòng mốc ghi đúng nguyên văn "Cầm hàng về — hẹn giao lại" kèm đúng ngày hẹn, khoảng giờ 09:00–10:00 và nơi hẹn "Sảnh toà FPT Tower" đã nhập.</t>
+          <t>5. Dòng mốc ghi đúng nguyên văn "Cầm hàng về — hẹn giao lại" kèm đúng ngày hẹn (ngày mai), khoảng giờ 09:00–10:00 và nơi hẹn "Sảnh toà FPT Tower".</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED` = `SEED-DLV-03`; lịch hẹn hợp lệ + nơi hẹn (test_data_catalog §DLV — Ngày hẹn, Giờ hẹn từ–đến, Nơi hẹn)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao" → sau TC này thành "Giao lại" (RESCHEDULED); ngày mai · 09:00–10:00 · "Sảnh toà FPT Tower" (test_data_catalog §DLV — Ngày hẹn, Giờ hẹn từ–đến, Nơi hẹn)</t>
         </is>
       </c>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 5 — ba biến ngày/giờ/nơi hẹn phải khớp đúng giá trị vừa nhập ở form.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 5 — ba biến ngày/giờ/nơi hẹn phải khớp đúng giá trị vừa nhập ở form. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). TC này là bước đẩy chuỗi 03-A sang "Giao lại" — chạy xong mới chạy TC-DLV-031/032/033. ⚠ Demo ghi 2 dòng "Người vận chuyển giữ hàng để giao lại" + "Hẹn giao lại · &lt;ngày&gt; · 09:00 – 10:00 / Sảnh toà FPT Tower" — khác nguyên văn PRD §8.12.4; STG lệch kiểu này ⇒ ghi Notes, hỏi BA.</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr">
@@ -18164,33 +18147,31 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, mở đơn đó và nhấn "Xác nhận đã nhận lại hàng". (setup)
-5. Mở block "LỊCH SỬ" và check dòng mốc cuối cùng.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "đã trả người gửi" (đã chạy xong TC-DLV-063) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và check dòng mốc cuối cùng.</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>5. Dòng mốc cuối cùng ghi đúng nguyên văn "Đã trả lại người gửi", kèm thời điểm.</t>
+          <t>3. Dòng mốc cuối cùng ghi đúng nguyên văn "Đã trả lại người gửi", kèm thời điểm.</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED` = `SEED-DLV-03` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` (RETURNED) (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L73" s="6" t="n"/>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 6 — mẫu câu duy nhất do người gửi kích hoạt, 5 mẫu còn lại do người vận chuyển.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 6 — mẫu câu duy nhất do người gửi kích hoạt, 5 mẫu còn lại do người vận chuyển. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ⚠ Demo ghi "Người gửi xác nhận đã nhận lại hàng" / "Đơn đóng · hàng đã về người gửi" — khác PRD §8.12.4; STG lệch ⇒ log bug.</t>
         </is>
       </c>
       <c r="N73" s="6" t="inlineStr">
@@ -18243,34 +18224,32 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động", mở đơn đó và nhấn "Xác nhận đã nhận lại hàng". (setup)
-5. Đăng 1 tin NEED khác rồi huỷ đơn đó, và để 1 tin NEED thứ ba quá "Đến ngày" mà không ai nhận. (setup)
-6. Mở lần lượt cả ba đơn ở tab "Đã hoàn thành" và check nhãn hành động chính của từng đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "đã trả người gửi" (đã chạy xong TC-DLV-063) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. (setup) Đăng nhập A, đăng 1 tin NEED mới rồi nhấn "Huỷ đơn", nhập lý do và xác nhận ⇒ có 1 đơn "Đã huỷ".
+3. (setup) Trong tab "Hoạt động" của A, tìm 1 tin CŨ đã quá "Đến ngày" mà chưa ai ghép (cách 1 của `SEED-ORD-05`). Không có ⇒ ghi Notes "thiếu đơn hết hạn", vẫn chạy 2 đơn còn lại.
+4. Mở lần lượt 3 đơn ở tab chứa đơn (dự kiến "Đã hoàn thành") và check nhãn hành động chính của từng đơn.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>6. Cả ba đơn đều hiển thị nhãn "Xem lý do" kèm lựa chọn "Đăng lại".</t>
+          <t>4. Cả ba đơn đều hiển thị nhãn "Xem lý do" kèm lựa chọn "Đăng lại".</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED`, `CANCELLED`, `EXPIRED`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` (RETURNED) + 1 đơn A tự huỷ (CANCELLED) + 1 tin cũ quá hạn (EXPIRED, theo `SEED-ORD-05` cách 1); vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: nhóm ba trạng thái đóng phải cho CÙNG một nhãn — lệch giữa ba đơn mới là defect. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng (PRD chỉ mô tả cấp danh mục, không có microcopy riêng cho từng trạng thái).</t>
+          <t>Mục đích: nhóm ba trạng thái đóng phải cho CÙNG một nhãn — lệch giữa ba đơn mới là defect. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng (PRD chỉ mô tả cấp danh mục, không có microcopy riêng cho từng trạng thái). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Đơn hết hạn lấy từ tin cũ có sẵn trên STG, ⛔ không chờ dev. Thiếu đơn hết hạn ⇒ verdict chỉ dựa trên 2 đơn, ghi rõ trong Notes.</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr">
@@ -18323,34 +18302,31 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận. (setup)
-4. Đăng nhập bằng tài khoản A, mở đơn đó và nhấn "Xác nhận đã nhận lại hàng", rồi đăng xuất. (setup)
-5. Đăng nhập lại bằng tài khoản B, nhấn tab "Hoạt động" và mở đơn đó ở tab "Đã hoàn thành". (setup)
-6. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "đã trả người gửi" (đã chạy xong TC-DLV-063) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó. (tìm ở tab "Đã hoàn thành")
+3. Check nhãn nút hành động chính trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>6. Nhãn hành động chính hiển thị "Xem lý do" và KHÔNG có lựa chọn "Đăng lại".</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lý do" và KHÔNG có lựa chọn "Đăng lại".</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` (RETURNED); vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L75" s="6" t="n"/>
       <c r="M75" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng với TC-DLV-037 — quyền đăng lại chỉ thuộc người gửi. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng.</t>
+          <t>Mục đích: đối chứng với TC-DLV-037 — quyền đăng lại chỉ thuộc người gửi. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N75" s="6" t="inlineStr">
@@ -18403,34 +18379,31 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, mở đơn đó và nhấn "Xác nhận đã nhận lại hàng", rồi đăng xuất. (setup)
-5. Đăng nhập bằng tài khoản C, nhấn tab "Hoạt động" và mở đơn đó ở tab "Đã hoàn thành". (setup)
-6. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "đã trả người gửi" (đã chạy xong TC-DLV-063) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản C, nhấn tab "Hoạt động" và mở đơn đó. (tìm ở tab "Đã hoàn thành")
+3. Check nhãn nút hành động chính trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>6. Nhãn hành động chính hiển thị "Xem lý do" và KHÔNG có lựa chọn "Đăng lại".</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lý do" và KHÔNG có lựa chọn "Đăng lại".</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` (RETURNED); vai người nhận C (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr">
@@ -18483,29 +18456,29 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó và xác nhận. (setup)
-3. Nhấn "Tôi đã lấy hàng".
-4. Đính 1 ảnh JPG từ thư viện thiết bị.
-5. Nhấn "Xác nhận".
+          <t>1. (setup) Dùng đơn #1 của `SEED-DLV-02` đang ở trạng thái "Đã ghép" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó. (setup)
+3. Nhấn "Tôi đã lấy hàng", ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" để mở màn "Xác nhận đã lấy hàng".
+4. Đính 1 ảnh JPG từ thư viện thiết bị vào khối "ẢNH BẰNG CHỨNG (TÙY CHỌN)".
+5. Nhấn "Xác nhận" và nhấn "Đồng ý" ở popup "Đã lấy hàng".
 6. Mở lại đơn đó và check trạng thái đơn cùng nội dung block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>6. Đơn ở trạng thái "Đang giao"; block "LỊCH SỬ" có mốc "Tôi đã lấy hàng" kèm dấu hiệu có ảnh bằng chứng và mở xem được đúng ảnh vừa đính.</t>
+          <t>6. Đơn ở trạng thái "Đang giao"; block "LỊCH SỬ" có mốc lấy hàng kèm dấu hiệu có ảnh bằng chứng (chữ "có ảnh bằng chứng" hoặc icon ảnh) và mở xem được đúng ảnh vừa đính.</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>1 ảnh JPG ≤5MB (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
+          <t>Đơn #1 `SEED-DLV-02` ở "Đã ghép"; 1 ảnh JPG ≤5MB (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
@@ -18515,7 +18488,7 @@
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 — `C-DLV-04` Resolved 2026-09-15 (ảnh lúc lấy hàng có tồn tại). ⚠ `RISK-DLV-11`: popup "Tôi đã lấy hàng" trên demo chưa thấy field ảnh — không thấy ô đính ảnh trên STG ⇒ log bug, ⛔ không sửa TC theo demo.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 — `C-DLV-04` Resolved 2026-09-15 (ảnh lúc lấy hàng có tồn tại). ⚠ `RISK-DLV-11`: popup "Tôi đã lấy hàng" trên demo chưa thấy field ảnh — không thấy ô đính ảnh trên STG ⇒ log bug, ⛔ không sửa TC theo demo. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Ô ảnh nằm ở màn thứ 2 "Xác nhận đã lấy hàng", KHÔNG ở popup lớp 1 (VR-021 — `RISK-DLV-11` đã đính chính).</t>
         </is>
       </c>
       <c r="N77" s="6" t="inlineStr">
@@ -18568,16 +18541,16 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó và xác nhận. (setup)
-3. Nhấn "Tôi đã lấy hàng".
-4. Nhấn "Xác nhận" mà KHÔNG đính ảnh nào.
+          <t>1. (setup) Dùng đơn #2 của `SEED-DLV-02` đang ở trạng thái "Đã ghép" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó. (setup)
+3. Nhấn "Tôi đã lấy hàng", ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" để mở màn "Xác nhận đã lấy hàng".
+4. Nhấn "Xác nhận" mà KHÔNG đính ảnh nào, rồi nhấn "Đồng ý" ở popup "Đã lấy hàng".
 5. Check trạng thái đơn trên màn Theo dõi đơn.</t>
         </is>
       </c>
@@ -18588,7 +18561,7 @@
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>0 ảnh — biên dưới hợp lệ (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
+          <t>Đơn #2 `SEED-DLV-02` ở "Đã ghép"; 0 ảnh — biên dưới hợp lệ (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
         </is>
       </c>
       <c r="L78" s="5" t="inlineStr">
@@ -18598,7 +18571,7 @@
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: cặp biên dưới với TC-DLV-041 — ảnh lúc lấy hàng là tuỳ chọn, khác hẳn ảnh lúc giao hàng (bắt buộc ≥1, xem TC-DLV-047). · Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 *"tuỳ chọn nhưng được khuyến nghị mạnh"*.</t>
+          <t>Mục đích: cặp biên dưới với TC-DLV-041 — ảnh lúc lấy hàng là tuỳ chọn, khác hẳn ảnh lúc giao hàng (bắt buộc ≥1, xem TC-DLV-047). · Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 *"tuỳ chọn nhưng được khuyến nghị mạnh"*. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr">
@@ -18651,36 +18624,36 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", nhấn "Không thể liên lạc với người gửi và người nhận?" rồi nhấn "Xử lý đơn hàng". (setup)
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-B` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Đây là TC ĐẦU TIÊN của chuỗi 03-B.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
 4. Nhấn "Gửi tại chốt bảo vệ".
-5. Đính 1 ảnh JPG và để TRỐNG ô "Họ tên người trực quầy".
+5. Đính 1 ảnh JPG và để TRỐNG ô "Họ tên người trực quầy" và ô "Số điện thoại".
 6. Nhấn nút xác nhận.
-7. Check trạng thái đơn và các phương án còn khả dụng trên màn.</t>
+7. Check nút xác nhận, màn đang đứng và trạng thái đơn.</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>7. Đơn vẫn ở trạng thái "Đang giao" và màn vẫn còn phương án "Cầm hàng về" để chọn tiếp.</t>
+          <t>7. Không submit được (nút xác nhận disable hoặc báo lỗi bắt buộc ở ô "Họ tên người trực quầy"), không có popup xác nhận; màn vẫn là "Xử lý đơn hàng" với phương án "Cầm hàng về" chọn được; đơn vẫn "Đang giao".</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; ô tên người trực quầy rỗng (test_data_catalog §DLV — Tên người trực quầy, nhánh invalid)</t>
+          <t>`SEED-DLV-03-B` ở "Đang giao"; ô tên người trực quầy rỗng (test_data_catalog §DLV — Tên người trực quầy, nhánh invalid)</t>
         </is>
       </c>
       <c r="L79" s="6" t="n"/>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: chốt đường thoát khi không có người trực quầy — nhánh gửi quầy phải đóng lại chứ không được cho qua với tên rỗng. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-07 + `C-DLV-06` Resolved 2026-09-17 (2 ô quầy là ràng buộc thật, QA đã submit thử với ô trống và form không đi).</t>
+          <t>Mục đích: chốt đường thoát khi không có người trực quầy — nhánh gửi quầy phải đóng lại chứ không được cho qua với tên rỗng. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-07 + `C-DLV-06` Resolved 2026-09-17 (2 ô quầy là ràng buộc thật, QA đã submit thử với ô trống và form không đi). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ⚠ Demo không bắt buộc ô tên ở màn "Xử lý đơn hàng" — lệch `C-DLV-06` (2 ô bắt buộc đã chốt); STG cho submit ⇒ FAIL + log bug dẫn C-DLV-06.</t>
         </is>
       </c>
       <c r="N79" s="6" t="inlineStr">
@@ -18733,34 +18706,32 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Gửi tại quầy lễ tân", nhập tên người trực quầy và số điện thoại, đính 1 ảnh rồi xác nhận, sau đó đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-B` đang ở trạng thái "Đã giao" (đã chạy xong TC-DLV-052) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>5. Block "LỊCH SỬ" hiển thị cảnh báo không liên lạc được người nhận gắn đúng mốc gửi quầy.</t>
+          <t>3. Block "LỊCH SỬ" có dòng cảnh báo chứa chữ "Không liên lạc được người nhận" (màu cảnh báo) gắn với lần giao này, và dòng mốc gửi quầy có chú thích "không liên lạc được người nhận tại thời điểm giao".</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-B` sau TC-DLV-052; vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: 1 trong 3 ô vai — cảnh báo phải hiện cho CẢ 3 bên, ẩn với 1 vai là defect. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
+          <t>Mục đích: 1 trong 3 ô vai — cảnh báo phải hiện cho CẢ 3 bên, ẩn với 1 vai là defect. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chữ cảnh báo lấy từ demo 2026-09-23 — PRD BR08-05 chỉ nói "hiện cảnh báo", không đặc tả chữ: so khớp theo nghĩa (không phân biệt hoa thường/dấu nối); STG có cảnh báo nhưng khác chữ ⇒ vẫn PASS, ghi nguyên văn vào Notes; KHÔNG có cảnh báo ⇒ FAIL.</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr">
@@ -18813,34 +18784,32 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Gửi tại quầy lễ tân", nhập tên người trực quầy và số điện thoại, đính 1 ảnh rồi xác nhận. (setup)
-4. Nhấn tab "Hoạt động" và mở lại đơn đó. (setup)
-5. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-B` đang ở trạng thái "Đã giao" (đã chạy xong TC-DLV-052) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>5. Block "LỊCH SỬ" hiển thị cảnh báo không liên lạc được người nhận gắn đúng mốc gửi quầy.</t>
+          <t>3. Block "LỊCH SỬ" có dòng cảnh báo chứa chữ "Không liên lạc được người nhận" (màu cảnh báo) gắn với lần giao này, và dòng mốc gửi quầy có chú thích "không liên lạc được người nhận tại thời điểm giao".</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-B` sau TC-DLV-052; vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L81" s="6" t="n"/>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chữ cảnh báo lấy từ demo 2026-09-23 — PRD BR08-05 chỉ nói "hiện cảnh báo", không đặc tả chữ: so khớp theo nghĩa (không phân biệt hoa thường/dấu nối); STG có cảnh báo nhưng khác chữ ⇒ vẫn PASS, ghi nguyên văn vào Notes; KHÔNG có cảnh báo ⇒ FAIL.</t>
         </is>
       </c>
       <c r="N81" s="6" t="inlineStr">
@@ -18893,34 +18862,32 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Gửi tại quầy lễ tân", nhập tên người trực quầy và số điện thoại, đính 1 ảnh rồi xác nhận, sau đó đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản C, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-B` đang ở trạng thái "Đã giao" (đã chạy xong TC-DLV-052) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản C, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>5. Block "LỊCH SỬ" hiển thị cảnh báo không liên lạc được người nhận gắn đúng mốc gửi quầy.</t>
+          <t>3. Block "LỊCH SỬ" có dòng cảnh báo chứa chữ "Không liên lạc được người nhận" (màu cảnh báo) gắn với lần giao này, và dòng mốc gửi quầy có chú thích "không liên lạc được người nhận tại thời điểm giao".</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-B` sau TC-DLV-052; vai người nhận C (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: vai nhạy cảm nhất của bộ ba — chính người nhận là bên bị ghi "không liên lạc được" nên dễ bị ẩn cảnh báo nhất. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
+          <t>Mục đích: vai nhạy cảm nhất của bộ ba — chính người nhận là bên bị ghi "không liên lạc được" nên dễ bị ẩn cảnh báo nhất. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chữ cảnh báo lấy từ demo 2026-09-23 — PRD BR08-05 chỉ nói "hiện cảnh báo", không đặc tả chữ: so khớp theo nghĩa (không phân biệt hoa thường/dấu nối); STG có cảnh báo nhưng khác chữ ⇒ vẫn PASS, ghi nguyên văn vào Notes; KHÔNG có cảnh báo ⇒ FAIL.</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr">
@@ -18973,18 +18940,18 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Dev/QA hỗ trợ lùi timestamp đơn để vượt mốc 4 giờ — ⛔ không tái tạo được qua UI.</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Quầy lễ tân", nhập tên người trực quầy và số điện thoại, đính 1 ảnh rồi xác nhận, sau đó đăng xuất. (setup)
-4. Nhờ dev/QA lùi timestamp của mốc gửi quầy để vượt mốc 4 giờ, rồi chờ tới hết ngày làm việc mà tài khoản C không xác nhận đã nhận hàng. (setup)
-5. Đăng nhập bằng tài khoản C, nhấn tab "Thông báo" và check các thông báo của đơn này.</t>
+          <t>1. (setup) Tạo 1 đơn riêng: đăng nhập A, đăng 1 tin NEED khai C là người nhận, đăng xuất; đăng nhập B, nhấn "Tôi mang giúp được" và xác nhận, rồi nhấn "Tôi đã lấy hàng" → ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" → tại màn "Xác nhận đã lấy hàng" nhấn "Xác nhận" → ở popup "Đã lấy hàng" nhấn "Đồng ý". Đăng xuất.
+2. Đăng nhập lại tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao". (setup)
+3. Chọn "Quầy lễ tân", nhập tên "Trần Thị Lan" và số "0987654321", đính 1 ảnh rồi nhấn "Xác nhận đã giao hàng" và xác nhận ở popup, sau đó đăng xuất. (setup)
+4. Nhờ dev/QA lùi timestamp của mốc gửi quầy để vượt mốc 4 giờ, rồi chờ tới hết ngày làm việc mà C không xác nhận đã nhận hàng. (setup)
+5. Đăng nhập tài khoản C, nhấn tab "Thông báo" và check các thông báo của đơn này.</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
@@ -18994,13 +18961,13 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>Đơn gửi quầy chưa xác nhận, đã vượt mốc 4h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>1 đơn riêng gửi quầy lễ tân, chưa xác nhận, đã vượt mốc 4h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L83" s="6" t="n"/>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: `§8.13.1` liệt kê 15 loại thông báo và KHÔNG có loại "nhắc" nào — TC này chính là điểm đối chiếu danh mục với hành vi thật. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-06 + `C-DLV-07` Resolved 2026-09-17 (hệ thống CHỈ gửi remind). ⛔ Không assert giờ cụ thể của "cuối ngày" và không FAIL vì kênh push hay in-app — BA không đặc tả, giới hạn đã chấp nhận. ⛔ Không assert vế "sau 24h chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-067 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
+          <t>Mục đích: `§8.13.1` liệt kê 15 loại thông báo và KHÔNG có loại "nhắc" nào — TC này chính là điểm đối chiếu danh mục với hành vi thật. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-06 + `C-DLV-07` Resolved 2026-09-17 (hệ thống CHỈ gửi remind). ⛔ Không assert giờ cụ thể của "cuối ngày" và không FAIL vì kênh push hay in-app — BA không đặc tả, giới hạn đã chấp nhận. ⛔ Không assert vế "sau 24h chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-067 và SC-TS-006 (QC GiangDC2, 2026-09-17) · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N83" s="6" t="inlineStr">
@@ -19053,35 +19020,36 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Dev/QA hỗ trợ lùi timestamp lịch hẹn để vượt mốc 24 giờ — ⛔ không tái tạo được qua UI.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ giao lại sau", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Nhờ dev/QA lùi timestamp lịch hẹn để vượt mốc 24 giờ mà không ai đóng đơn. (setup)
-5. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-6. Check trạng thái đơn, nhãn trên đơn và tab chứa đơn.</t>
+          <t>1. (setup) Tạo 1 đơn riêng: đăng nhập A, đăng 1 tin NEED khai C là người nhận, đăng xuất; đăng nhập B, nhấn "Tôi mang giúp được" và xác nhận, rồi nhấn "Tôi đã lấy hàng" → ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" → tại màn "Xác nhận đã lấy hàng" nhấn "Xác nhận" → ở popup "Đã lấy hàng" nhấn "Đồng ý". Đăng xuất.
+2. Đăng nhập lại tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao". (setup)
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333). (setup)
+4. Nhấn "Cầm hàng về". Chọn "Tôi sẽ giao lại sau", nhập "Ngày hẹn" = ngày mai, giờ từ "09:00" đến "10:00", "Nơi giao lại" = "Sảnh toà FPT Tower", nhấn nút xác nhận và đồng ý ở popup. Rồi đăng xuất. (setup)
+5. Nhờ dev/QA lùi timestamp lịch hẹn để vượt mốc 24 giờ mà không ai đóng đơn. (setup)
+6. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+7. Check trạng thái đơn, nhãn trên đơn và tab chứa đơn.</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>6. Đơn KHÔNG ở trạng thái "Hoàn thành", KHÔNG có nhãn hay cờ mới nào so với trước mốc, và vẫn nằm ở tab "Đang diễn ra".</t>
+          <t>7. Đơn KHÔNG ở trạng thái "Hoàn thành", KHÔNG có nhãn hay cờ mới nào so với trước mốc, và vẫn nằm ở tab "Đang diễn ra".</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED` đã quá lịch hẹn 24h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>1 đơn riêng ở "Giao lại" (RESCHEDULED) đã quá lịch hẹn 24h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: vế duy nhất còn assert được của `BR09-04` sau khi BA cắt scope — dễ bị bỏ sót vì cả câu rule đã bị coi là out of scope. · Căn cứ: `AC-23.2.01` câu cuối + `C-DLV-07` Resolved 2026-09-17 (chỉ gửi remind, đơn không đổi trạng thái/nhãn/cờ). ⛔ Không assert vế "chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-057 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
+          <t>Mục đích: vế duy nhất còn assert được của `BR09-04` sau khi BA cắt scope — dễ bị bỏ sót vì cả câu rule đã bị coi là out of scope. · Căn cứ: `AC-23.2.01` câu cuối + `C-DLV-07` Resolved 2026-09-17 (chỉ gửi remind, đơn không đổi trạng thái/nhãn/cờ). ⛔ Không assert vế "chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-057 và SC-TS-006 (QC GiangDC2, 2026-09-17) · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N84" s="5" t="inlineStr">
@@ -19134,7 +19102,7 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thiết bị đang dùng mạng 4G, đã tắt Wi-Fi.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh đúng 5MB.
@@ -19143,12 +19111,12 @@
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao" và chọn "Người nhận". (setup)
+          <t>1. (setup) Dùng đơn #3 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Chạy TRƯỚC TC-DLV-045 — TC này không submit nên không tiêu đơn.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Người nhận" ở field "Giao cho".
 4. Khởi động đồng hồ bấm giờ rồi đính cùng lúc 5 ảnh JPG 5MB từ thư viện thiết bị.
-5. Dừng đồng hồ bấm giờ khi cả 5 ảnh hiện đủ trong ô ảnh.
-6. Lặp lại step 3 đến step 5 thêm 9 lần trên 9 đơn khác nhau và ghi lại 10 số đo.
+5. Dừng đồng hồ khi cả 5 ảnh hiện đủ trong ô ảnh; ghi lại số đo.
+6. Nhấn Back thoát màn (⛔ không submit), mở lại màn "Xác nhận đã giao" như step 2 và lặp step 3–5 thêm 9 lần.
 7. Check 10 số đo đã ghi và chỉ báo tiến trình quan sát được trong lúc tải.</t>
         </is>
       </c>
@@ -19159,13 +19127,13 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>5 ảnh JPG đúng 5MB, mạng 4G (test_data_catalog §DLV — Upload ảnh hiệu năng)</t>
+          <t>Đơn #3 `SEED-DLV-02` ở "Đang giao"; 5 ảnh JPG đúng 5MB, mạng 4G (test_data_catalog §DLV — Upload ảnh hiệu năng)</t>
         </is>
       </c>
       <c r="L85" s="6" t="n"/>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: `NFR-03` phát biểu theo p95 nên 1 lần đo không kết luận được — 10 lần đo là mẫu tối thiểu chạy tay được, cho phép đúng 1 lần vượt ngưỡng. · Căn cứ: `DOC-v1.1-01` §9 NFR-03. Chạy trên 10 đơn khác nhau vì ảnh đã ghi mốc thì không xoá để tải lại được (`BR07-07`, xem TC-DLV-048).</t>
+          <t>Mục đích: `NFR-03` phát biểu theo p95 nên 1 lần đo không kết luận được — 10 lần đo là mẫu tối thiểu chạy tay được, cho phép đúng 1 lần vượt ngưỡng. · Căn cứ: `DOC-v1.1-01` §9 NFR-03. Chạy trên 10 đơn khác nhau vì ảnh đã ghi mốc thì không xoá để tải lại được (`BR07-07`, xem TC-DLV-048). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Đo 10 lần trên CÙNG 1 đơn bằng cách thoát màn không submit (ảnh chưa ghi mốc thì chưa bất biến) — thay cho cách cũ cần 10 đơn.</t>
         </is>
       </c>
       <c r="N85" s="6" t="inlineStr">
@@ -19218,34 +19186,32 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Người được uỷ quyền", nhập tên "Nguyễn Văn Bảy" và số điện thoại "0912345678", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở lần lượt Trang chủ, tab "Bảng tin", tab "Hoạt động" ở cả hai tab con, tab "Thông báo" và màn hồ sơ cá nhân.
-5. Check từng màn ở step 4 xem có chỗ nào hiện tên "Nguyễn Văn Bảy" hoặc số "0912345678" không.</t>
+          <t>1. (setup) Dùng đơn #2 `SEED-DLV-02` đã "Đã giao" sau TC-DLV-044 (có tên "Nguyễn Văn Bảy" · SĐT "0912345678" trong nhật ký) — ⛔ không tạo đơn mới.
+2. Lần lượt với tài khoản B rồi tài khoản A: mở Trang chủ, tab "Bảng tin", tab "Hoạt động" (cả hai tab con), tab "Thông báo" và màn hồ sơ cá nhân.
+3. Check từng màn ở step 2 xem có chỗ nào hiện tên "Nguyễn Văn Bảy" hoặc số "0912345678" không.</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>5. KHÔNG màn nào trong số đó hiện tên "Nguyễn Văn Bảy" hay số "0912345678"; hai giá trị này chỉ xuất hiện ở block "LỊCH SỬ" của đơn.</t>
+          <t>3. KHÔNG màn nào trong số đó hiện tên "Nguyễn Văn Bảy" hay số "0912345678"; hai giá trị này chỉ xuất hiện ở block "LỊCH SỬ" của đơn.</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>Tên và SĐT người nhận thay đã ghi vào nhật ký (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
+          <t>Đơn #2 `SEED-DLV-02` sau TC-DLV-044 (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
         </is>
       </c>
       <c r="L86" s="5" t="n"/>
       <c r="M86" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: dữ liệu người nhận thay là dữ liệu cá nhân của bên thứ ba ngoài 3 vai của đơn — rò ra bề mặt khác là vi phạm quyền riêng tư, không chỉ lỗi hiển thị. · Căn cứ: `DOC-v1.1-01` §9 NFR-12. Phạm vi rà giới hạn ở các màn end-user; dự án không có bề mặt báo cáo hay Admin Portal trong scope v1.1.</t>
+          <t>Mục đích: dữ liệu người nhận thay là dữ liệu cá nhân của bên thứ ba ngoài 3 vai của đơn — rò ra bề mặt khác là vi phạm quyền riêng tư, không chỉ lỗi hiển thị. · Căn cứ: `DOC-v1.1-01` §9 NFR-12. Phạm vi rà giới hạn ở các màn end-user; dự án không có bề mặt báo cáo hay Admin Portal trong scope v1.1. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N86" s="5" t="inlineStr">
@@ -19298,28 +19264,27 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó và xác nhận. (setup)
-3. Nhấn tab "Hoạt động" và mở đơn đó. (setup)
-4. Ghi lại số điện thoại liên hệ đang hiển thị trên màn Theo dõi đơn.
-5. Nhấn icon copy cạnh số điện thoại đó.
-6. Dán nội dung vừa copy vào ô tìm kiếm ở tab "Bảng tin" và check nội dung dán ra cùng trạng thái icon copy lúc vừa nhấn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-06` đang ở trạng thái "Đã ghép" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó. (setup)
+3. Ghi lại số điện thoại liên hệ đang hiển thị trên màn Theo dõi đơn.
+4. Nhấn icon copy cạnh số điện thoại đó và quay màn hình (screenrecord) trong ~3 giây sau khi nhấn.
+5. Dán nội dung vừa copy vào ô tìm kiếm ở tab "Bảng tin"; check nội dung dán ra và đoạn quay màu icon copy.</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>6. Nội dung dán ra đúng nguyên văn số điện thoại đã ghi ở step 4, và icon copy đã đổi trạng thái sang màu xanh khoảng 2 giây rồi trở lại bình thường.</t>
+          <t>5. Nội dung dán ra đúng nguyên văn số điện thoại đã ghi ở step 3, và icon copy đổi sang màu xanh khoảng 2 giây rồi trở lại bình thường.</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Số điện thoại liên hệ trên màn Theo dõi đơn (test_data_catalog §DLV — SĐT người nhận thay)</t>
+          <t>`SEED-DLV-06` ở "Đã ghép"; SĐT liên hệ trên màn Theo dõi đơn (test_data_catalog §DLV — SĐT người nhận thay)</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
@@ -19329,7 +19294,7 @@
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-081 — hai instance icon copy nằm ở hai vùng khác nhau của cùng màn, hỏng độc lập. · Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04. Rule ghi 1,8 giây nhưng đây là hiệu ứng thị giác — chấp nhận dung sai quanh 2 giây, ⛔ không bấm giờ đòi đúng 1,8 giây. Instance ở màn Chi tiết tin thuộc `FEED`, không rà ở đây.</t>
+          <t>Mục đích: cặp với TC-DLV-081 — hai instance icon copy nằm ở hai vùng khác nhau của cùng màn, hỏng độc lập. · Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04. Rule ghi 1,8 giây nhưng đây là hiệu ứng thị giác — chấp nhận dung sai quanh 2 giây, ⛔ không bấm giờ đòi đúng 1,8 giây. Instance ở màn Chi tiết tin thuộc `FEED`, không rà ở đây. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Hiệu ứng ~2 giây: bắt buộc quay màn hình, ⛔ không kết luận từ ảnh chụp rời (QC từng bác kết luận kiểu này ở TC-ORD-085).</t>
         </is>
       </c>
       <c r="N87" s="6" t="inlineStr">
@@ -19382,28 +19347,27 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó và xác nhận. (setup)
-3. Nhấn tab "Hoạt động" và mở đơn đó. (setup)
-4. Ghi lại địa chỉ giao đang hiển thị trên màn Theo dõi đơn.
-5. Nhấn icon copy cạnh địa chỉ giao đó.
-6. Dán nội dung vừa copy vào ô tìm kiếm ở tab "Bảng tin" và check nội dung dán ra cùng trạng thái icon copy lúc vừa nhấn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-06` đang ở trạng thái "Đã ghép" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó. (setup)
+3. Ghi lại địa chỉ giao đang hiển thị trên màn Theo dõi đơn.
+4. Nhấn icon copy cạnh địa chỉ giao đó và quay màn hình (screenrecord) trong ~3 giây sau khi nhấn.
+5. Dán nội dung vừa copy vào ô tìm kiếm ở tab "Bảng tin"; check nội dung dán ra và đoạn quay màu icon copy.</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>6. Nội dung dán ra đúng nguyên văn địa chỉ giao đã ghi ở step 4, và icon copy đã đổi trạng thái sang màu xanh khoảng 2 giây rồi trở lại bình thường.</t>
+          <t>5. Nội dung dán ra đúng nguyên văn địa chỉ giao đã ghi ở step 3, và icon copy đổi sang màu xanh khoảng 2 giây rồi trở lại bình thường.</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>Địa chỉ giao trên màn Theo dõi đơn (test_data_catalog §DLV — Nơi hẹn)</t>
+          <t>`SEED-DLV-06` ở "Đã ghép"; địa chỉ giao trên màn Theo dõi đơn (test_data_catalog §DLV — Nơi hẹn)</t>
         </is>
       </c>
       <c r="L88" s="5" t="inlineStr">
@@ -19413,7 +19377,7 @@
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04 — rule đặt icon copy cạnh CẢ địa chỉ giao và số điện thoại.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04 — rule đặt icon copy cạnh CẢ địa chỉ giao và số điện thoại. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Hiệu ứng ~2 giây: bắt buộc quay màn hình, ⛔ không kết luận từ ảnh chụp rời.</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr">
@@ -34253,33 +34217,31 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Giao lại" (đã chạy xong TC-DLV-072) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn nút hành động chính ở cuối màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Xem lịch hẹn giao lại".</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn giao lại".</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Giao lại" (RESCHEDULED); vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: 1 trong 3 ô vai của nhóm trạng thái `RESCHEDULED` — mỗi vai fail độc lập. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. ⚠ Thanh timeline vẫn hiện đúng 5 mốc và mốc "Đang giao" đang active — đây là thiết kế đã chốt (`C-DLV-05(d)` Resolved 2026-09-17), ⛔ không FAIL vì thiếu mốc mới.</t>
+          <t>Mục đích: 1 trong 3 ô vai của nhóm trạng thái `RESCHEDULED` — mỗi vai fail độc lập. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. ⚠ Thanh timeline vẫn hiện đúng 5 mốc và mốc "Đang giao" đang active — đây là thiết kế đã chốt (`C-DLV-05(d)` Resolved 2026-09-17), ⛔ không FAIL vì thiếu mốc mới. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Người vận chuyển đang giữ hàng · sẽ giao lại theo lịch hẹn").</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -34332,33 +34294,31 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau", nhập lịch hẹn hợp lệ và xác nhận. (setup)
-4. Nhấn tab "Hoạt động" và mở lại đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Giao lại" (đã chạy xong TC-DLV-072) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn và trạng thái nút hành động chính — ⛔ KHÔNG nhấn (nhấn sẽ đẩy đơn về "Đang giao", thuộc TC-DLV-062).</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Giao lại theo lịch" và nhấn được để mở lại màn giao hàng.</t>
+          <t>3. Nhãn hành động chính hiển thị "Giao lại theo lịch" ở trạng thái enable.</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Giao lại" (RESCHEDULED); vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L4" s="6" t="n"/>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED — đây là vai DUY NHẤT có nút hành động thật ở trạng thái này, 2 vai kia chỉ xem.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED — đây là vai DUY NHẤT có nút hành động thật ở trạng thái này, 2 vai kia chỉ xem. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Bỏ vế "nhấn được để mở lại màn giao hàng" khỏi Expected vì nhấn sẽ tiêu trạng thái của TC-DLV-031/033/072 — vế này đã do TC-DLV-062 phủ. Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Giao lại cho người nhận").</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
@@ -34411,33 +34371,31 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản C, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Giao lại" (đã chạy xong TC-DLV-072) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản C, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn nút hành động chính và các nút khác trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Xem lịch hẹn" và KHÔNG có nút giao lại nào.</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn" và KHÔNG có nút giao lại nào.</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Giao lại" (RESCHEDULED); vai người nhận C (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng với TC-DLV-032 — quyền giao lại chỉ thuộc người vận chuyển. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED.</t>
+          <t>Mục đích: đối chứng với TC-DLV-032 — quyền giao lại chỉ thuộc người vận chuyển. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Người vận chuyển sẽ giao lại theo lịch hẹn").</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -34490,33 +34448,31 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Trả hàng" (đã chạy xong TC-DLV-066) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn, trạng thái nút hành động chính và mục lịch hẹn trả hàng trên màn — ⛔ KHÔNG nhấn nút (thuộc TC-DLV-063).</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Xác nhận đã nhận lại hàng" ở trạng thái enable và màn có mục xem lịch hẹn trả hàng.</t>
+          <t>3. Nhãn hành động chính hiển thị "Xác nhận đã nhận lại hàng" ở trạng thái enable và màn có mục xem lịch hẹn trả hàng.</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RETURNING`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Trả hàng" (RETURNING); vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: người gửi là vai DUY NHẤT đóng được đơn ở nhánh hoàn hàng — cặp với TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
+          <t>Mục đích: người gửi là vai DUY NHẤT đóng được đơn ở nhánh hoàn hàng — cặp với TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Đã lấy lại hàng từ người giao").</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
@@ -34569,33 +34525,31 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận. (setup)
-4. Nhấn tab "Hoạt động" và mở lại đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Trả hàng" (đã chạy xong TC-DLV-066) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn nút hành động chính và các nút khác trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Xem lịch hẹn trả hàng" và KHÔNG có nút xác nhận đóng đơn.</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn trả hàng" và KHÔNG có nút xác nhận đóng đơn.</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNING`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Trả hàng" (RETURNING); vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. ⚠ Demo cho B nút "Đã trả hàng cho người gửi" (ngược Expected) — gặp trên STG ⇒ FAIL + log bug dẫn §8.12.3.</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
@@ -34648,33 +34602,31 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản C, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Trả hàng" (đã chạy xong TC-DLV-066) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản C, nhấn tab "Hoạt động" và mở đơn đó.
+3. Check nhãn nút hành động chính trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>5. Nhãn hành động chính hiển thị "Xem lý do hoàn hàng".</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lý do hoàn hàng".</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RETURNING`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở trạng thái "Trả hàng" (RETURNING); vai người nhận C (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L8" s="6" t="n"/>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Không giao được · hàng đang được trả lại người gửi").</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
@@ -34727,34 +34679,32 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động", mở đơn đó và nhấn "Xác nhận đã nhận lại hàng". (setup)
-5. Đăng 1 tin NEED khác rồi huỷ đơn đó, và để 1 tin NEED thứ ba quá "Đến ngày" mà không ai nhận. (setup)
-6. Mở lần lượt cả ba đơn ở tab "Đã hoàn thành" và check nhãn hành động chính của từng đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "đã trả người gửi" (đã chạy xong TC-DLV-063) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. (setup) Đăng nhập A, đăng 1 tin NEED mới rồi nhấn "Huỷ đơn", nhập lý do và xác nhận ⇒ có 1 đơn "Đã huỷ".
+3. (setup) Trong tab "Hoạt động" của A, tìm 1 tin CŨ đã quá "Đến ngày" mà chưa ai ghép (cách 1 của `SEED-ORD-05`). Không có ⇒ ghi Notes "thiếu đơn hết hạn", vẫn chạy 2 đơn còn lại.
+4. Mở lần lượt 3 đơn ở tab chứa đơn (dự kiến "Đã hoàn thành") và check nhãn hành động chính của từng đơn.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6. Cả ba đơn đều hiển thị nhãn "Xem lý do" kèm lựa chọn "Đăng lại".</t>
+          <t>4. Cả ba đơn đều hiển thị nhãn "Xem lý do" kèm lựa chọn "Đăng lại".</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED`, `CANCELLED`, `EXPIRED`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` (RETURNED) + 1 đơn A tự huỷ (CANCELLED) + 1 tin cũ quá hạn (EXPIRED, theo `SEED-ORD-05` cách 1); vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: nhóm ba trạng thái đóng phải cho CÙNG một nhãn — lệch giữa ba đơn mới là defect. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng (PRD chỉ mô tả cấp danh mục, không có microcopy riêng cho từng trạng thái).</t>
+          <t>Mục đích: nhóm ba trạng thái đóng phải cho CÙNG một nhãn — lệch giữa ba đơn mới là defect. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng (PRD chỉ mô tả cấp danh mục, không có microcopy riêng cho từng trạng thái). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Đơn hết hạn lấy từ tin cũ có sẵn trên STG, ⛔ không chờ dev. Thiếu đơn hết hạn ⇒ verdict chỉ dựa trên 2 đơn, ghi rõ trong Notes.</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
@@ -34807,34 +34757,31 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận. (setup)
-4. Đăng nhập bằng tài khoản A, mở đơn đó và nhấn "Xác nhận đã nhận lại hàng", rồi đăng xuất. (setup)
-5. Đăng nhập lại bằng tài khoản B, nhấn tab "Hoạt động" và mở đơn đó ở tab "Đã hoàn thành". (setup)
-6. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "đã trả người gửi" (đã chạy xong TC-DLV-063) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó. (tìm ở tab "Đã hoàn thành")
+3. Check nhãn nút hành động chính trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>6. Nhãn hành động chính hiển thị "Xem lý do" và KHÔNG có lựa chọn "Đăng lại".</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lý do" và KHÔNG có lựa chọn "Đăng lại".</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` (RETURNED); vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L10" s="6" t="n"/>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng với TC-DLV-037 — quyền đăng lại chỉ thuộc người gửi. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng.</t>
+          <t>Mục đích: đối chứng với TC-DLV-037 — quyền đăng lại chỉ thuộc người gửi. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
@@ -34887,34 +34834,31 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", chọn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, mở đơn đó và nhấn "Xác nhận đã nhận lại hàng", rồi đăng xuất. (setup)
-5. Đăng nhập bằng tài khoản C, nhấn tab "Hoạt động" và mở đơn đó ở tab "Đã hoàn thành". (setup)
-6. Check nhãn hành động chính trên màn Theo dõi đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "đã trả người gửi" (đã chạy xong TC-DLV-063) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản C, nhấn tab "Hoạt động" và mở đơn đó. (tìm ở tab "Đã hoàn thành")
+3. Check nhãn nút hành động chính trên màn Theo dõi đơn.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6. Nhãn hành động chính hiển thị "Xem lý do" và KHÔNG có lựa chọn "Đăng lại".</t>
+          <t>3. Nhãn hành động chính hiển thị "Xem lý do" và KHÔNG có lựa chọn "Đăng lại".</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` (RETURNED); vai người nhận C (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -34974,35 +34918,34 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Dev/QA hỗ trợ lùi timestamp đơn để vượt mốc 2 giờ và 4 giờ — ⛔ không tái tạo được qua UI.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Báo cáo sự cố", gửi form báo sự cố cho đơn này, rồi đăng xuất. (setup)
-4. Nhờ dev/QA lùi timestamp của đơn để vượt qua cả mốc 2 giờ và mốc 4 giờ. (setup)
-5. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-6. Check trạng thái đơn và tab chứa đơn.</t>
+          <t>1. (setup) Tạo 1 đơn riêng: đăng nhập A, đăng 1 tin NEED khai C là người nhận, đăng xuất; đăng nhập B, nhấn "Tôi mang giúp được" và xác nhận, rồi nhấn "Tôi đã lấy hàng" → ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" → tại màn "Xác nhận đã lấy hàng" nhấn "Xác nhận" → ở popup "Đã lấy hàng" nhấn "Đồng ý".
+2. Nhấn "Báo cáo sự cố", gửi form báo sự cố cho đơn này, rồi đăng xuất. (setup)
+3. Nhờ dev/QA lùi timestamp của đơn để vượt qua cả mốc 2 giờ và mốc 4 giờ. (setup)
+4. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+5. Check trạng thái đơn và tab chứa đơn.</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>6. Đơn KHÔNG ở trạng thái "Hoàn thành" và vẫn nằm ở tab "Đang diễn ra".</t>
+          <t>5. Đơn KHÔNG ở trạng thái "Hoàn thành" và vẫn nằm ở tab "Đang diễn ra".</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Đơn `INCIDENT` đã vượt mốc 2h và 4h = `SEED-DLV-04` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-04` — đơn có sự cố (INCIDENT) đã vượt mốc 2h và 4h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L13" s="6" t="n"/>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: chốt ranh giới nhánh sự cố ⟷ luồng tự đóng thường — dễ lập trình sai thành "quá giờ thì đóng". · Căn cứ: `DOC-v1.1-01` §8.10.1 BR10-04 (SC mới gắn REQ giữ ID, không sửa `SC-DLV-024` v1.0 vốn đúng cho nhánh thường). ⛔ Không assert vế "admin xử lý" — role admin out of scope v1.1 (`C-DLV-07` Resolved 2026-09-17).</t>
+          <t>Mục đích: chốt ranh giới nhánh sự cố ⟷ luồng tự đóng thường — dễ lập trình sai thành "quá giờ thì đóng". · Căn cứ: `DOC-v1.1-01` §8.10.1 BR10-04 (SC mới gắn REQ giữ ID, không sửa `SC-DLV-024` v1.0 vốn đúng cho nhánh thường). ⛔ Không assert vế "admin xử lý" — role admin out of scope v1.1 (`C-DLV-07` Resolved 2026-09-17). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). 🚫 Deferred — cần dev lùi timestamp, chạy chung lô với TC-DLV-057/067, TC-DLV-024 (v1.0) và SC-TS-006.</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
@@ -35062,29 +35005,29 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó và xác nhận. (setup)
-3. Nhấn "Tôi đã lấy hàng".
-4. Đính 1 ảnh JPG từ thư viện thiết bị.
-5. Nhấn "Xác nhận".
+          <t>1. (setup) Dùng đơn #1 của `SEED-DLV-02` đang ở trạng thái "Đã ghép" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó. (setup)
+3. Nhấn "Tôi đã lấy hàng", ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" để mở màn "Xác nhận đã lấy hàng".
+4. Đính 1 ảnh JPG từ thư viện thiết bị vào khối "ẢNH BẰNG CHỨNG (TÙY CHỌN)".
+5. Nhấn "Xác nhận" và nhấn "Đồng ý" ở popup "Đã lấy hàng".
 6. Mở lại đơn đó và check trạng thái đơn cùng nội dung block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6. Đơn ở trạng thái "Đang giao"; block "LỊCH SỬ" có mốc "Tôi đã lấy hàng" kèm dấu hiệu có ảnh bằng chứng và mở xem được đúng ảnh vừa đính.</t>
+          <t>6. Đơn ở trạng thái "Đang giao"; block "LỊCH SỬ" có mốc lấy hàng kèm dấu hiệu có ảnh bằng chứng (chữ "có ảnh bằng chứng" hoặc icon ảnh) và mở xem được đúng ảnh vừa đính.</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>1 ảnh JPG ≤5MB (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
+          <t>Đơn #1 `SEED-DLV-02` ở "Đã ghép"; 1 ảnh JPG ≤5MB (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -35094,7 +35037,7 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 — `C-DLV-04` Resolved 2026-09-15 (ảnh lúc lấy hàng có tồn tại). ⚠ `RISK-DLV-11`: popup "Tôi đã lấy hàng" trên demo chưa thấy field ảnh — không thấy ô đính ảnh trên STG ⇒ log bug, ⛔ không sửa TC theo demo.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 — `C-DLV-04` Resolved 2026-09-15 (ảnh lúc lấy hàng có tồn tại). ⚠ `RISK-DLV-11`: popup "Tôi đã lấy hàng" trên demo chưa thấy field ảnh — không thấy ô đính ảnh trên STG ⇒ log bug, ⛔ không sửa TC theo demo. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Ô ảnh nằm ở màn thứ 2 "Xác nhận đã lấy hàng", KHÔNG ở popup lớp 1 (VR-021 — `RISK-DLV-11` đã đính chính).</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
@@ -35147,16 +35090,16 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó và xác nhận. (setup)
-3. Nhấn "Tôi đã lấy hàng".
-4. Nhấn "Xác nhận" mà KHÔNG đính ảnh nào.
+          <t>1. (setup) Dùng đơn #2 của `SEED-DLV-02` đang ở trạng thái "Đã ghép" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó. (setup)
+3. Nhấn "Tôi đã lấy hàng", ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" để mở màn "Xác nhận đã lấy hàng".
+4. Nhấn "Xác nhận" mà KHÔNG đính ảnh nào, rồi nhấn "Đồng ý" ở popup "Đã lấy hàng".
 5. Check trạng thái đơn trên màn Theo dõi đơn.</t>
         </is>
       </c>
@@ -35167,7 +35110,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>0 ảnh — biên dưới hợp lệ (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
+          <t>Đơn #2 `SEED-DLV-02` ở "Đã ghép"; 0 ảnh — biên dưới hợp lệ (test_data_catalog §DLV — Ảnh lúc lấy hàng)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -35177,7 +35120,7 @@
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp biên dưới với TC-DLV-041 — ảnh lúc lấy hàng là tuỳ chọn, khác hẳn ảnh lúc giao hàng (bắt buộc ≥1, xem TC-DLV-047). · Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 *"tuỳ chọn nhưng được khuyến nghị mạnh"*.</t>
+          <t>Mục đích: cặp biên dưới với TC-DLV-041 — ảnh lúc lấy hàng là tuỳ chọn, khác hẳn ảnh lúc giao hàng (bắt buộc ≥1, xem TC-DLV-047). · Căn cứ: `DOC-v1.1-01` §8.6.1 BR06-01 *"tuỳ chọn nhưng được khuyến nghị mạnh"*. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
@@ -35237,30 +35180,29 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
-4. Chọn "Người nhận" ở field "Giao cho".
-5. Đính 1 ảnh JPG từ thư viện thiết bị.
-6. Nhấn "Xác nhận đã giao hàng" và đồng ý ở popup xác nhận.
-7. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Dùng đơn #1 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Chạy sau TC-DLV-049.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Người nhận" ở field "Giao cho".
+4. Đính 1 ảnh JPG từ thư viện thiết bị.
+5. Nhấn "Xác nhận đã giao hàng" và nhấn "Xác nhận" ở popup cảnh báo không thể hoàn tác.
+6. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã giao tận tay người nhận" kèm thời điểm.</t>
+          <t>6. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã giao tận tay người nhận" kèm thời điểm.</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02`; đối tượng nhận "Người nhận" + 1 ảnh bằng chứng (test_data_catalog §DLV — Đối tượng nhận, Ảnh bằng chứng giao hàng)</t>
+          <t>Đơn #1 `SEED-DLV-02` ở "Đang giao"; "Người nhận" + 1 ảnh (test_data_catalog §DLV — Đối tượng nhận, Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -35270,7 +35212,7 @@
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: luồng chính của `FR07` mở rộng — 3 nhánh còn lại (TC-DLV-044/045/046) đều rẽ từ đúng màn này. · Căn cứ: `DOC-v1.1-01` §8.7.2 + §8.12.4 mẫu câu 1. `RISK-DLV-08` đã Confirmed qua demo 2026-09-16 (luồng submit chạy đúng); vẫn double-check locator trên STG trước khi hardening. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
+          <t>Mục đích: luồng chính của `FR07` mở rộng — 3 nhánh còn lại (TC-DLV-044/045/046) đều rẽ từ đúng màn này. · Căn cứ: `DOC-v1.1-01` §8.7.2 + §8.12.4 mẫu câu 1. `RISK-DLV-08` đã Confirmed qua demo 2026-09-16 (luồng submit chạy đúng); vẫn double-check locator trên STG trước khi hardening. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-068: 1 lần submit, chụp 2 ảnh evidence riêng. Popup lớp 1 phải nhấn "Xác nhận" — VR-020 nhấn "Huỷ" nên từng chấm BLOCKED sai.</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
@@ -35323,38 +35265,37 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
-4. Chọn "Người được uỷ quyền" ở field "Giao cho".
-5. Nhập "Nguyễn Văn Bảy" vào ô tên người nhận thay.
-6. Nhập "0912345678" vào ô số điện thoại người nhận thay.
-7. Đính 1 ảnh JPG từ thư viện thiết bị.
-8. Nhấn "Xác nhận đã giao hàng" và đồng ý ở popup xác nhận.
-9. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Dùng đơn #2 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Người được uỷ quyền" ở field "Giao cho"; nếu 2 ô tên/SĐT người nhận thay đã được điền sẵn thì xoá trắng trước.
+4. Nhập "Nguyễn Văn Bảy" vào ô tên người nhận thay.
+5. Nhập "0912345678" vào ô số điện thoại người nhận thay.
+6. Đính 1 ảnh JPG từ thư viện thiết bị.
+7. Nhấn "Xác nhận đã giao hàng" và nhấn "Xác nhận" ở popup.
+8. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>9. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã giao cho người được uỷ quyền — Nguyễn Văn Bảy · 0912345678 — uỷ quyền bởi Người nhận".</t>
+          <t>8. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã giao cho người được uỷ quyền — Nguyễn Văn Bảy · 0912345678 — uỷ quyền bởi Người nhận".</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #2 của `SEED-DLV-02`; tên 12 ký tự + SĐT hợp lệ (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
+          <t>Đơn #2 `SEED-DLV-02` ở "Đang giao"; tên 12 ký tự + SĐT hợp lệ (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
         </is>
       </c>
       <c r="L19" s="6" t="n"/>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: chốt giá trị tự sinh của "Uỷ quyền bởi" theo MÀN VÀO chứ không theo loại đối tượng nhận — đối chứng âm là TC-DLV-051 (vào từ màn "Liên hệ người gửi" thì tự sinh "Người gửi"). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03/BR07-04/BR07-05 + §8.12.4 mẫu câu 2. Trường "Uỷ quyền bởi" chỉ đọc, không sửa được. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
+          <t>Mục đích: chốt giá trị tự sinh của "Uỷ quyền bởi" theo MÀN VÀO chứ không theo loại đối tượng nhận — đối chứng âm là TC-DLV-051 (vào từ màn "Liên hệ người gửi" thì tự sinh "Người gửi"). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03/BR07-04/BR07-05 + §8.12.4 mẫu câu 2. Trường "Uỷ quyền bởi" chỉ đọc, không sửa được. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-069 (1 lần submit, 2 evidence). ⚠ Demo tách dòng: tiêu đề "Đã giao cho người được uỷ quyền" + dòng phụ "Nguyễn Văn Bảy · 0912345678 · uỷ quyền bởi người nhận · &lt;tên C&gt;" — STG lệch đúng kiểu này (đủ 3 thành phần, chỉ khác cách xuống dòng/dấu nối) ⇒ ghi Notes, hỏi BA, chưa log bug.</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
@@ -35407,38 +35348,37 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
-4. Chọn "Quầy lễ tân" ở field "Giao cho".
-5. Đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" khi vẫn để trống cả hai ô của khối "NGƯỜI NHẬN TẠI QUẦY".
-6. Nhập "Trần Thị Lan" vào ô "Họ tên người trực quầy".
-7. Nhập "0987654321" vào ô "Số điện thoại".
-8. Nhấn "Xác nhận đã giao hàng" và đồng ý ở popup xác nhận.
-9. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Dùng đơn #3 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Chạy sau TC-DLV-077 (nếu chạy 077).
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Quầy lễ tân" ở field "Giao cho".
+4. Đính 1 ảnh JPG, để TRỐNG cả hai ô của khối "NGƯỜI NHẬN TẠI QUẦY" rồi nhấn "Xác nhận đã giao hàng" — form phải không đi tiếp.
+5. Nhập "Trần Thị Lan" vào ô "Họ tên người trực quầy".
+6. Nhập "0987654321" vào ô "Số điện thoại".
+7. Nhấn "Xác nhận đã giao hàng" và nhấn "Xác nhận" ở popup.
+8. Check trạng thái đơn và dòng mới nhất ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã gửi tại quầy lễ tân — Trần Thị Lan".</t>
+          <t>8. Đơn chuyển sang trạng thái "Đã giao"; block "LỊCH SỬ" có dòng mới "Đã gửi tại quầy lễ tân — Trần Thị Lan".</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #3 của `SEED-DLV-02`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
+          <t>Đơn #3 `SEED-DLV-02` ở "Đang giao"; tên người trực quầy + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: step 5 là vế âm gộp trong cùng TC — submit khi 2 ô trống phải không đi được, nên step 9 mới quan sát được kết quả dương. · Căn cứ: `C-DLV-06` Resolved 2026-09-17 (BA *"trên UI có dấu * bắt buộc mà"*, QA submit thử với 2 ô trống thì form không đi) + `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 3. ⛔ Chưa assert cờ "không liên lạc được" và `NTF-05`/`NTF-11` — `C-DLV-08` (a)(b) còn Partially, QA tự xác minh qua block "LỊCH SỬ" trước khi siết TC. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
+          <t>Mục đích: step 5 là vế âm gộp trong cùng TC — submit khi 2 ô trống phải không đi được, nên step 9 mới quan sát được kết quả dương. · Căn cứ: `C-DLV-06` Resolved 2026-09-17 (BA *"trên UI có dấu * bắt buộc mà"*, QA submit thử với 2 ô trống thì form không đi) + `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 3. ⛔ Chưa assert cờ "không liên lạc được" và `NTF-05`/`NTF-11` — `C-DLV-08` (a)(b) còn Partially, QA tự xác minh qua block "LỊCH SỬ" trước khi siết TC. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-070 (1 lần submit, 2 evidence). Step 4 mà form đi tiếp được ⇒ FAIL ngay tại step 4.</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -35491,38 +35431,37 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
-4. Chọn "Quầy bảo vệ" ở field "Giao cho".
-5. Nhập "Lê Văn Tám" vào ô "Họ tên người trực quầy".
-6. Nhập "0901112223" vào ô "Số điện thoại".
-7. Đính 1 ảnh JPG từ thư viện thiết bị.
-8. Nhấn "Xác nhận đã giao hàng" và đồng ý ở popup xác nhận.
-9. Check dòng mới nhất ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Dùng đơn #4 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Quầy bảo vệ" ở field "Giao cho".
+4. Nhập "Lê Văn Tám" vào ô "Họ tên người trực quầy".
+5. Nhập "0901112223" vào ô "Số điện thoại".
+6. Đính 1 ảnh JPG từ thư viện thiết bị.
+7. Nhấn "Xác nhận đã giao hàng" và nhấn "Xác nhận" ở popup.
+8. Check dòng mới nhất ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>9. Block "LỊCH SỬ" có dòng mới "Đã gửi tại quầy bảo vệ — Lê Văn Tám", ⛔ KHÔNG dùng chữ "quầy lễ tân".</t>
+          <t>8. Block "LỊCH SỬ" có dòng mới "Đã gửi tại quầy bảo vệ — Lê Văn Tám", ⛔ KHÔNG dùng chữ "quầy lễ tân".</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #4 của `SEED-DLV-02`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
+          <t>Đơn #4 `SEED-DLV-02` ở "Đang giao"; tên người trực quầy + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
       <c r="L21" s="6" t="n"/>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-045 — hai quầy dùng hai mẫu câu nhật ký khác nhau, lập trình gộp 1 chuỗi là defect. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 4. ⛔ Chưa assert cờ/`NTF` — `C-DLV-08` (a)(b) còn Partially. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
+          <t>Mục đích: cặp với TC-DLV-045 — hai quầy dùng hai mẫu câu nhật ký khác nhau, lập trình gộp 1 chuỗi là defect. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-03 + §8.12.4 mẫu câu 4. ⛔ Chưa assert cờ/`NTF` — `C-DLV-08` (a)(b) còn Partially. · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-071 (1 lần submit, 2 evidence).</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
@@ -35575,36 +35514,35 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Nhấn "Đã đến địa điểm giao hàng" để mở màn "Xác nhận đã giao".
-4. Chọn "Người nhận" ở field "Giao cho" mà chưa đính ảnh nào.
-5. Check trạng thái nút "Xác nhận đã giao hàng".
-6. Đính 1 ảnh JPG từ thư viện thiết bị.
-7. Check lại trạng thái nút "Xác nhận đã giao hàng".</t>
+          <t>1. (setup) Dùng đơn #1 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Người nhận" ở field "Giao cho" mà chưa đính ảnh nào.
+4. Check trạng thái nút "Xác nhận đã giao hàng".
+5. Đính 1 ảnh JPG từ thư viện thiết bị.
+6. Check lại trạng thái nút "Xác nhận đã giao hàng", rồi nhấn Back thoát màn — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>7. Nút "Xác nhận đã giao hàng" ở trạng thái disable tại step 5 khi chưa có ảnh, và chuyển sang enable ngay sau khi đính ảnh đầu tiên.</t>
+          <t>6. Nút "Xác nhận đã giao hàng" disable khi chưa có ảnh (quan sát ở step 4) và chuyển sang enable ngay sau khi đính ảnh đầu tiên.</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02`; 0 ảnh (chặn) và 1 ảnh (biên dưới hợp lệ) (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
+          <t>Đơn #1 `SEED-DLV-02` ở "Đang giao"; 0 ảnh (chặn) và 1 ảnh (biên dưới hợp lệ) (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: cặp biên dưới 0⟷1 của ảnh bằng chứng lúc giao — ngược hẳn ảnh lúc lấy hàng (TC-DLV-042, 0 ảnh vẫn hợp lệ). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-02. Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1 vì TC đó sẽ đẩy đơn sang "Đã giao". · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044.</t>
+          <t>Mục đích: cặp biên dưới 0⟷1 của ảnh bằng chứng lúc giao — ngược hẳn ảnh lúc lấy hàng (TC-DLV-042, 0 ảnh vẫn hợp lệ). · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-02. Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1 vì TC đó sẽ đẩy đơn sang "Đã giao". · 🔁 Đính chính 2026-09-22 (QC): bước 3 nêu rõ tên nút chính thức "Đã đến địa điểm giao hàng" (v1.1, đổi tên so với "Đã giao cho người nhận" của v1.0) — STG hiện chưa đổi tên, xem BUG-044. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Thứ tự trên đơn #1: TC-DLV-047 → 049 → 043 (+068) → 048.</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
@@ -35657,35 +35595,34 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Người nhận", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở block "LỊCH SỬ" và mở ảnh bằng chứng vừa ghi.
-5. Nhấn giữ vào ảnh và tìm thao tác xoá ảnh.
-6. Check ảnh bằng chứng ở mốc "Đã giao" sau khi đã thử xoá.</t>
+          <t>1. (setup) Dùng đơn #1 `SEED-DLV-02` đã "Đã giao" sau TC-DLV-043 (= `SEED-DLV-05`) — ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và nhấn vào ảnh bằng chứng ở mốc giao hàng để mở màn xem ảnh.
+4. Nhấn giữ ảnh ~2 giây, rồi rà đủ 3 vị trí: menu vừa hiện (nếu có) · icon/nút trên màn xem ảnh (thùng rác, "Xoá", menu ⋮) · vuốt ảnh sang trái. Rà xong 3 vị trí thì dừng.
+5. Đóng màn xem ảnh và check ảnh bằng chứng ở mốc "Đã giao".</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>6. KHÔNG có thao tác xoá nào khả dụng và ảnh bằng chứng vẫn còn nguyên ở mốc nhật ký.</t>
+          <t>5. KHÔNG có thao tác xoá nào khả dụng ở cả 3 vị trí và ảnh bằng chứng vẫn còn nguyên ở mốc nhật ký.</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Đơn `DELIVERED` có 1 ảnh bằng chứng = `SEED-DLV-05` (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
+          <t>`SEED-DLV-05` = đơn #1 `SEED-DLV-02` sau TC-DLV-043 (test_data_catalog §DLV — Ảnh bằng chứng giao hàng)</t>
         </is>
       </c>
       <c r="L23" s="6" t="n"/>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-07 — ảnh gắn vào mốc nhật ký là bất biến. Liên quan cùng nhóm bất biến với TC-DLV-078 (log append-only).</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-07 — ảnh gắn vào mốc nhật ký là bất biến. Liên quan cùng nhóm bất biến với TC-DLV-078 (log append-only). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
@@ -35738,19 +35675,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Người nhận" và đính 1 ảnh JPG. (setup)
+          <t>1. (setup) Dùng đơn #1 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Chạy sau TC-DLV-047.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Người nhận" ở field "Giao cho" và đính 1 ảnh JPG. (setup)
 4. Nhấn "Xác nhận đã giao hàng".
-5. Check nội dung popup xác nhận.
-6. Nhấn nút huỷ ở popup.
+5. Check nội dung popup xác nhận (có nêu thao tác không thể hoàn tác).
+6. Nhấn "Huỷ" ở popup.
 7. Check trạng thái đơn và số dòng ở block "LỊCH SỬ".</t>
         </is>
       </c>
@@ -35761,13 +35698,13 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` đơn #1 của `SEED-DLV-02` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>Đơn #1 `SEED-DLV-02` ở "Đang giao" (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng âm cho TC-DLV-043 — popup phải là gate thật, không phải thông báo trang trí. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-06 (popup nêu rõ hệ quả không thể hoàn tác trước khi ghi mốc). Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1.</t>
+          <t>Mục đích: đối chứng âm cho TC-DLV-043 — popup phải là gate thật, không phải thông báo trang trí. · Căn cứ: `DOC-v1.1-01` §8.7.1 BR07-06 (popup nêu rõ hệ quả không thể hoàn tác trước khi ghi mốc). Chạy TRƯỚC TC-DLV-043 trên cùng đơn #1. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
@@ -35827,20 +35764,20 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao" và nhấn "Không thể liên lạc cho người nhận?".
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Đây là TC ĐẦU TIÊN của chuỗi 03-A.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Nhấn link "Không thể liên lạc cho người nhận?".
 4. Check tên màn vừa mở và các thành phần trên màn đó.
 5. Nhấn "Không thể liên lạc với người gửi và người nhận?".
 6. Check tiêu đề và hai lựa chọn của modal vừa hiện.
 7. Nhấn "Xử lý đơn hàng".
-8. Check tên màn vừa mở và thứ tự các phương án trên màn đó.</t>
+8. Check tên màn vừa mở và thứ tự các phương án trên màn đó, rồi nhấn Back — ⛔ không chọn phương án nào.</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
@@ -35850,17 +35787,17 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao" (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: `BR08-02` ghi thứ tự NGƯỢC (lễ tân trước bảo vệ) và mô tả 1 danh sách 4 bước — assert theo PRD sẽ FAIL oan. · Căn cứ: `C-DLV-06` **Resolved 2026-09-17** — cấu trúc 4 tầng (màn "Xác nhận đã giao" → màn "Liên hệ người gửi" → modal "Chưa liên lạc được?" → màn "Xử lý đơn hàng") và thứ tự bảo-vệ-trước là oracle chính thức, khớp `AC-17.1.01`/`§8.8.2`. App lệch bản này ⇒ log bug và dẫn `C-DLV-06`, ⛔ không sửa TC theo `BR08-02`.</t>
+          <t>Mục đích: `BR08-02` ghi thứ tự NGƯỢC (lễ tân trước bảo vệ) và mô tả 1 danh sách 4 bước — assert theo PRD sẽ FAIL oan. · Căn cứ: `C-DLV-06` **Resolved 2026-09-17** — cấu trúc 4 tầng (màn "Xác nhận đã giao" → màn "Liên hệ người gửi" → modal "Chưa liên lạc được?" → màn "Xử lý đơn hàng") và thứ tự bảo-vệ-trước là oracle chính thức, khớp `AC-17.1.01`/`§8.8.2`. App lệch bản này ⇒ log bug và dẫn `C-DLV-06`, ⛔ không sửa TC theo `BR08-02`. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Steps giữ ĐÚNG cấu trúc 4 tầng BA chốt (`C-DLV-06`) vì đó chính là điểm kiểm. STG hiện hiện bottom sheet 2 lựa chọn ("Liên hệ người gửi"/"Xử lý đơn hàng") ngay sau step 3 ⇒ lệch từ step 4 — đã log FE-333 (chờ BA). Status đổi Pass → Fail: verdict Pass của VR-021 chỉ quan sát tới bottom sheet, chưa từng thấy màn ở step 8. Chạy lại khi FE-333 có kết luận.</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
@@ -35913,17 +35850,17 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao" và nhấn "Không thể liên lạc cho người nhận?". (setup)
-4. Chọn "Người được uỷ quyền" ở field "Giao cho" trên màn "Liên hệ người gửi".
-5. Check giá trị hai ô tên và số điện thoại người nhận thay, dòng "Uỷ quyền bởi", khu vực liên hệ người gửi và dấu bắt buộc của ô ảnh.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-050) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Nhấn link "Không thể liên lạc cho người nhận?" để mở màn "Liên hệ người gửi" (STG hiện: chọn "Liên hệ người gửi" ở bottom sheet — FE-333).
+4. Chọn "Người được uỷ quyền" ở field "Giao cho".
+5. Check giá trị hai ô tên và số điện thoại người nhận thay, dòng "Uỷ quyền bởi", khu vực liên hệ người gửi và dấu bắt buộc của ô ảnh; rồi nhấn Back — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -35933,13 +35870,13 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03` (test_data_catalog §DLV — Tên người nhận thay)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao" (test_data_catalog §DLV — Tên người nhận thay)</t>
         </is>
       </c>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng với TC-DLV-044 — cùng loại đối tượng nhận nhưng khác MÀN VÀO nên "Uỷ quyền bởi" phải ra giá trị ngược lại; và ở màn này ⛔ KHÔNG prefill người uỷ quyền người gửi đã khai. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-03 + §8.7.1 BR07-05. Gộp bốn quan sát vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả bốn thuộc cùng một trạng thái tĩnh của màn.</t>
+          <t>Mục đích: đối chứng với TC-DLV-044 — cùng loại đối tượng nhận nhưng khác MÀN VÀO nên "Uỷ quyền bởi" phải ra giá trị ngược lại; và ở màn này ⛔ KHÔNG prefill người uỷ quyền người gửi đã khai. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-03 + §8.7.1 BR07-05. Gộp bốn quan sát vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả bốn thuộc cùng một trạng thái tĩnh của màn. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -35992,16 +35929,16 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", nhấn "Không thể liên lạc với người gửi và người nhận?" rồi nhấn "Xử lý đơn hàng". (setup)
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-B` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-053) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
 4. Nhấn "Gửi tại quầy lễ tân".
 5. Nhập "Phạm Thị Hoa" vào ô "Họ tên người trực quầy".
 6. Nhập "0933444555" vào ô "Số điện thoại".
@@ -36017,13 +35954,13 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; tên người trực quầy cụ thể + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
+          <t>`SEED-DLV-03-B` ở "Đang giao" → "Đã giao"; tên người trực quầy + SĐT hợp lệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
       <c r="L28" s="6" t="n"/>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: đường thứ hai tới cùng kết cục của TC-DLV-045 — hai đường phải cùng đòi tên người trực quầy, SĐT và ảnh. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-04 + §8.12.4 mẫu câu 3. ⛔ Chưa assert điểm phân biệt với TC-DLV-045 (cờ "không liên lạc được" / `NTF-05` ⟷ `NTF-11`) — `C-DLV-08` (a)(b) còn Partially, QA vibe-check block "LỊCH SỬ" xong mới siết. ⛔ Không assert hạn giữ hàng 4h/24h — out of scope v1.1.</t>
+          <t>Mục đích: đường thứ hai tới cùng kết cục của TC-DLV-045 — hai đường phải cùng đòi tên người trực quầy, SĐT và ảnh. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-04 + §8.12.4 mẫu câu 3. ⛔ Chưa assert điểm phân biệt với TC-DLV-045 (cờ "không liên lạc được" / `NTF-05` ⟷ `NTF-11`) — `C-DLV-08` (a)(b) còn Partially, QA vibe-check block "LỊCH SỬ" xong mới siết. ⛔ Không assert hạn giữ hàng 4h/24h — out of scope v1.1. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
@@ -36076,36 +36013,36 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", nhấn "Không thể liên lạc với người gửi và người nhận?" rồi nhấn "Xử lý đơn hàng". (setup)
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-B` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Đây là TC ĐẦU TIÊN của chuỗi 03-B.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
 4. Nhấn "Gửi tại chốt bảo vệ".
-5. Đính 1 ảnh JPG và để TRỐNG ô "Họ tên người trực quầy".
+5. Đính 1 ảnh JPG và để TRỐNG ô "Họ tên người trực quầy" và ô "Số điện thoại".
 6. Nhấn nút xác nhận.
-7. Check trạng thái đơn và các phương án còn khả dụng trên màn.</t>
+7. Check nút xác nhận, màn đang đứng và trạng thái đơn.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>7. Đơn vẫn ở trạng thái "Đang giao" và màn vẫn còn phương án "Cầm hàng về" để chọn tiếp.</t>
+          <t>7. Không submit được (nút xác nhận disable hoặc báo lỗi bắt buộc ở ô "Họ tên người trực quầy"), không có popup xác nhận; màn vẫn là "Xử lý đơn hàng" với phương án "Cầm hàng về" chọn được; đơn vẫn "Đang giao".</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; ô tên người trực quầy rỗng (test_data_catalog §DLV — Tên người trực quầy, nhánh invalid)</t>
+          <t>`SEED-DLV-03-B` ở "Đang giao"; ô tên người trực quầy rỗng (test_data_catalog §DLV — Tên người trực quầy, nhánh invalid)</t>
         </is>
       </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: chốt đường thoát khi không có người trực quầy — nhánh gửi quầy phải đóng lại chứ không được cho qua với tên rỗng. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-07 + `C-DLV-06` Resolved 2026-09-17 (2 ô quầy là ràng buộc thật, QA đã submit thử với ô trống và form không đi).</t>
+          <t>Mục đích: chốt đường thoát khi không có người trực quầy — nhánh gửi quầy phải đóng lại chứ không được cho qua với tên rỗng. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-07 + `C-DLV-06` Resolved 2026-09-17 (2 ô quầy là ràng buộc thật, QA đã submit thử với ô trống và form không đi). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ⚠ Demo không bắt buộc ô tên ở màn "Xử lý đơn hàng" — lệch `C-DLV-06` (2 ô bắt buộc đã chốt); STG cho submit ⇒ FAIL + log bug dẫn C-DLV-06.</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -36158,34 +36095,32 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Gửi tại quầy lễ tân", nhập tên người trực quầy và số điện thoại, đính 1 ảnh rồi xác nhận, sau đó đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-B` đang ở trạng thái "Đã giao" (đã chạy xong TC-DLV-052) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>5. Block "LỊCH SỬ" hiển thị cảnh báo không liên lạc được người nhận gắn đúng mốc gửi quầy.</t>
+          <t>3. Block "LỊCH SỬ" có dòng cảnh báo chứa chữ "Không liên lạc được người nhận" (màu cảnh báo) gắn với lần giao này, và dòng mốc gửi quầy có chú thích "không liên lạc được người nhận tại thời điểm giao".</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-B` sau TC-DLV-052; vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L30" s="6" t="n"/>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: 1 trong 3 ô vai — cảnh báo phải hiện cho CẢ 3 bên, ẩn với 1 vai là defect. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
+          <t>Mục đích: 1 trong 3 ô vai — cảnh báo phải hiện cho CẢ 3 bên, ẩn với 1 vai là defect. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chữ cảnh báo lấy từ demo 2026-09-23 — PRD BR08-05 chỉ nói "hiện cảnh báo", không đặc tả chữ: so khớp theo nghĩa (không phân biệt hoa thường/dấu nối); STG có cảnh báo nhưng khác chữ ⇒ vẫn PASS, ghi nguyên văn vào Notes; KHÔNG có cảnh báo ⇒ FAIL.</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
@@ -36238,34 +36173,32 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Gửi tại quầy lễ tân", nhập tên người trực quầy và số điện thoại, đính 1 ảnh rồi xác nhận. (setup)
-4. Nhấn tab "Hoạt động" và mở lại đơn đó. (setup)
-5. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-B` đang ở trạng thái "Đã giao" (đã chạy xong TC-DLV-052) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>5. Block "LỊCH SỬ" hiển thị cảnh báo không liên lạc được người nhận gắn đúng mốc gửi quầy.</t>
+          <t>3. Block "LỊCH SỬ" có dòng cảnh báo chứa chữ "Không liên lạc được người nhận" (màu cảnh báo) gắn với lần giao này, và dòng mốc gửi quầy có chú thích "không liên lạc được người nhận tại thời điểm giao".</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-B` sau TC-DLV-052; vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chữ cảnh báo lấy từ demo 2026-09-23 — PRD BR08-05 chỉ nói "hiện cảnh báo", không đặc tả chữ: so khớp theo nghĩa (không phân biệt hoa thường/dấu nối); STG có cảnh báo nhưng khác chữ ⇒ vẫn PASS, ghi nguyên văn vào Notes; KHÔNG có cảnh báo ⇒ FAIL.</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -36318,34 +36251,32 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Gửi tại quầy lễ tân", nhập tên người trực quầy và số điện thoại, đính 1 ảnh rồi xác nhận, sau đó đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản C, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-B` đang ở trạng thái "Đã giao" (đã chạy xong TC-DLV-052) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản C, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và check cảnh báo gắn với mốc gửi quầy.</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>5. Block "LỊCH SỬ" hiển thị cảnh báo không liên lạc được người nhận gắn đúng mốc gửi quầy.</t>
+          <t>3. Block "LỊCH SỬ" có dòng cảnh báo chứa chữ "Không liên lạc được người nhận" (màu cảnh báo) gắn với lần giao này, và dòng mốc gửi quầy có chú thích "không liên lạc được người nhận tại thời điểm giao".</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Đơn đã đi qua nhánh không liên lạc được = `SEED-DLV-03`; vai người nhận (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-B` sau TC-DLV-052; vai người nhận C (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L32" s="6" t="n"/>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: vai nhạy cảm nhất của bộ ba — chính người nhận là bên bị ghi "không liên lạc được" nên dễ bị ẩn cảnh báo nhất. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05.</t>
+          <t>Mục đích: vai nhạy cảm nhất của bộ ba — chính người nhận là bên bị ghi "không liên lạc được" nên dễ bị ẩn cảnh báo nhất. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-05. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chữ cảnh báo lấy từ demo 2026-09-23 — PRD BR08-05 chỉ nói "hiện cảnh báo", không đặc tả chữ: so khớp theo nghĩa (không phân biệt hoa thường/dấu nối); STG có cảnh báo nhưng khác chữ ⇒ vẫn PASS, ghi nguyên văn vào Notes; KHÔNG có cảnh báo ⇒ FAIL.</t>
         </is>
       </c>
       <c r="N32" s="6" t="inlineStr">
@@ -36398,18 +36329,18 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Dev/QA hỗ trợ lùi timestamp đơn để vượt mốc 4 giờ — ⛔ không tái tạo được qua UI.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Quầy lễ tân", nhập tên người trực quầy và số điện thoại, đính 1 ảnh rồi xác nhận, sau đó đăng xuất. (setup)
-4. Nhờ dev/QA lùi timestamp của mốc gửi quầy để vượt mốc 4 giờ, rồi chờ tới hết ngày làm việc mà tài khoản C không xác nhận đã nhận hàng. (setup)
-5. Đăng nhập bằng tài khoản C, nhấn tab "Thông báo" và check các thông báo của đơn này.</t>
+          <t>1. (setup) Tạo 1 đơn riêng: đăng nhập A, đăng 1 tin NEED khai C là người nhận, đăng xuất; đăng nhập B, nhấn "Tôi mang giúp được" và xác nhận, rồi nhấn "Tôi đã lấy hàng" → ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" → tại màn "Xác nhận đã lấy hàng" nhấn "Xác nhận" → ở popup "Đã lấy hàng" nhấn "Đồng ý". Đăng xuất.
+2. Đăng nhập lại tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao". (setup)
+3. Chọn "Quầy lễ tân", nhập tên "Trần Thị Lan" và số "0987654321", đính 1 ảnh rồi nhấn "Xác nhận đã giao hàng" và xác nhận ở popup, sau đó đăng xuất. (setup)
+4. Nhờ dev/QA lùi timestamp của mốc gửi quầy để vượt mốc 4 giờ, rồi chờ tới hết ngày làm việc mà C không xác nhận đã nhận hàng. (setup)
+5. Đăng nhập tài khoản C, nhấn tab "Thông báo" và check các thông báo của đơn này.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -36419,13 +36350,13 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>Đơn gửi quầy chưa xác nhận, đã vượt mốc 4h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>1 đơn riêng gửi quầy lễ tân, chưa xác nhận, đã vượt mốc 4h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: `§8.13.1` liệt kê 15 loại thông báo và KHÔNG có loại "nhắc" nào — TC này chính là điểm đối chiếu danh mục với hành vi thật. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-06 + `C-DLV-07` Resolved 2026-09-17 (hệ thống CHỈ gửi remind). ⛔ Không assert giờ cụ thể của "cuối ngày" và không FAIL vì kênh push hay in-app — BA không đặc tả, giới hạn đã chấp nhận. ⛔ Không assert vế "sau 24h chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-067 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
+          <t>Mục đích: `§8.13.1` liệt kê 15 loại thông báo và KHÔNG có loại "nhắc" nào — TC này chính là điểm đối chiếu danh mục với hành vi thật. · Căn cứ: `DOC-v1.1-01` §8.8.1 BR08-06 + `C-DLV-07` Resolved 2026-09-17 (hệ thống CHỈ gửi remind). ⛔ Không assert giờ cụ thể của "cuối ngày" và không FAIL vì kênh push hay in-app — BA không đặc tả, giới hạn đã chấp nhận. ⛔ Không assert vế "sau 24h chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-067 và SC-TS-006 (QC GiangDC2, 2026-09-17) · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
@@ -36485,17 +36416,17 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng" rồi nhấn "Cầm hàng về". (setup)
-4. Chọn "Tôi sẽ giao lại sau".
-5. Check tiêu đề khối lịch hẹn và nhãn ô địa điểm.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-051) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau".
+5. Check tiêu đề khối lịch hẹn và nhãn ô địa điểm — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
@@ -36505,13 +36436,13 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `retry` (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao"; chế độ giao lại (retry) (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
       <c r="L35" s="6" t="n"/>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-059 — hai chế độ dùng chung một form nên rất dễ bị lập trình cứng một bộ nhãn. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02.</t>
+          <t>Mục đích: cặp với TC-DLV-059 — hai chế độ dùng chung một form nên rất dễ bị lập trình cứng một bộ nhãn. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
@@ -36564,17 +36495,17 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng" rồi nhấn "Cầm hàng về". (setup)
-4. Chọn "Tôi sẽ trả về cho người gửi".
-5. Check tiêu đề khối lịch hẹn và nhãn ô địa điểm.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-058) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi".
+5. Check tiêu đề khối lịch hẹn và nhãn ô địa điểm, rồi nhấn Back — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -36584,13 +36515,13 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `return` (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao"; chế độ trả hàng (return) (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02 + vibe-check demo 2026-09-17 (`C-DLV-05` — khối "Hẹn trả hàng" do chính Carrier nhập tại màn "Xử lý đơn hàng").</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-02 + vibe-check demo 2026-09-17 (`C-DLV-05` — khối "Hẹn trả hàng" do chính Carrier nhập tại màn "Xử lý đơn hàng"). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
@@ -36643,34 +36574,35 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau". (setup)
-4. Chọn ngày hẹn là ngày hiện tại cộng 7 ngày.
-5. Chọn lại ngày hẹn là ngày hiện tại cộng 8 ngày.
-6. Check trạng thái ô "Ngày hẹn" và thông báo lỗi nếu có.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-059) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về" rồi chọn "Tôi sẽ giao lại sau". (setup)
+5. Chọn "Ngày hẹn" = ngày hiện tại + 7 ngày và quan sát ô "Ngày hẹn".
+6. Chọn lại "Ngày hẹn" = ngày hiện tại + 8 ngày.
+7. Check trạng thái ô "Ngày hẹn" và thông báo lỗi nếu có — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>6. Ngày cộng 7 được nhận không báo lỗi, còn ngày cộng 8 bị chặn kèm thông báo lỗi ở ô "Ngày hẹn".</t>
+          <t>7. Ngày +7 được nhận không báo lỗi (quan sát ở step 5), còn ngày +8 bị chặn (không chọn được hoặc báo lỗi ở ô "Ngày hẹn").</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>Ngày hẹn +7 ngày (hợp lệ) và +8 ngày (chặn) (test_data_catalog §DLV — Ngày hẹn cầm hàng về, biên)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao"; ngày hẹn +7 (hợp lệ) và +8 (chặn) (test_data_catalog §DLV — Ngày hẹn cầm hàng về, biên)</t>
         </is>
       </c>
       <c r="L37" s="6" t="n"/>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp biên trên của trần 7 ngày — hai giá trị liền kề fail độc lập nên phải nằm trong cùng 1 TC để so được. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-04.</t>
+          <t>Mục đích: cặp biên trên của trần 7 ngày — hai giá trị liền kề fail độc lập nên phải nằm trong cùng 1 TC để so được. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-04. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N37" s="6" t="inlineStr">
@@ -36723,35 +36655,36 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ giao lại sau" và chọn ngày hẹn hợp lệ. (setup)
-4. Chọn giờ từ "09:00" và giờ đến "09:30".
-5. Chọn lại giờ đến "09:29".
-6. Chọn lại giờ đến "08:30".
-7. Check trạng thái hai ô giờ và thông báo lỗi nếu có.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-060) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về", chọn "Tôi sẽ giao lại sau" và chọn "Ngày hẹn" = ngày mai. (setup)
+5. Chọn giờ từ "09:00" và giờ đến "09:30", quan sát hai ô giờ.
+6. Chọn lại giờ đến "09:29".
+7. Chọn lại giờ đến "08:30".
+8. Check trạng thái hai ô giờ và thông báo lỗi nếu có — ⛔ không submit.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>7. Khoảng 09:00–09:30 được nhận không báo lỗi, còn khoảng 09:00–09:29 và khoảng có giờ đến nhỏ hơn giờ từ đều bị chặn kèm thông báo lỗi.</t>
+          <t>8. Khoảng 09:00–09:30 được nhận không báo lỗi, còn khoảng 09:00–09:29 và khoảng có giờ đến nhỏ hơn giờ từ đều bị chặn kèm thông báo lỗi.</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Giờ hẹn 30 phút (hợp lệ), 29 phút (chặn), giờ đến ≤ giờ từ (chặn) (test_data_catalog §DLV — Giờ hẹn từ–đến, biên)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao"; giờ hẹn 30 phút (hợp lệ), 29 phút (chặn), giờ đến ≤ giờ từ (chặn) (test_data_catalog §DLV — Giờ hẹn từ–đến, biên)</t>
         </is>
       </c>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: gộp ba giá trị vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả ba cùng thuộc một trạng thái tĩnh của form, không mất khả năng bắt lỗi riêng vì Expected nêu đích danh từng khoảng. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-03.</t>
+          <t>Mục đích: gộp ba giá trị vào 1 step Check cuối theo `Project_rule §10.4` mục 1 — cả ba cùng thuộc một trạng thái tĩnh của form, không mất khả năng bắt lỗi riêng vì Expected nêu đích danh từng khoảng. · Căn cứ: `DOC-v1.1-01` §8.9.2 BR09-03. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
@@ -36804,34 +36737,32 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ giao lại sau", nhập lịch hẹn hợp lệ và xác nhận. (setup)
-4. Nhấn tab "Hoạt động" và mở lại đơn đó.
-5. Nhấn "Giao lại theo lịch".
-6. Check màn vừa mở và trạng thái đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Giao lại" (đã chạy xong TC-DLV-031/032/033) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Nhấn nút hành động chính (tài liệu: "Giao lại theo lịch"; demo: "Giao lại cho người nhận").
+4. Check màn vừa mở và trạng thái đơn (nhấn Back về màn Theo dõi đơn nếu cần) — ⛔ không submit giao hàng.</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>6. Màn giao hàng mở lại được và đơn trở về trạng thái "Đang giao".</t>
+          <t>4. Màn giao hàng mở lại được và đơn trở về trạng thái "Đang giao".</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED` = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở "Giao lại" (RESCHEDULED); vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L39" s="6" t="n"/>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: `AC-18.1.01` viết *"theo lịch hẹn, đơn quay lại IN_TRANSIT"* — đọc được thành hệ thống tự chuyển, chạy TC theo cách hiểu đó sẽ treo chờ đúng giờ. · Căn cứ: `C-DLV-05` **Resolved 2026-09-17** — chính người vận chuyển bấm, không có gate chặn theo giờ nên bấm sớm hơn lịch hẹn vẫn đi được; không giới hạn số lần hẹn. App chặn theo giờ ⇒ log bug và dẫn `C-DLV-05`.</t>
+          <t>Mục đích: `AC-18.1.01` viết *"theo lịch hẹn, đơn quay lại IN_TRANSIT"* — đọc được thành hệ thống tự chuyển, chạy TC theo cách hiểu đó sẽ treo chờ đúng giờ. · Căn cứ: `C-DLV-05` **Resolved 2026-09-17** — chính người vận chuyển bấm, không có gate chặn theo giờ nên bấm sớm hơn lịch hẹn vẫn đi được; không giới hạn số lần hẹn. App chặn theo giờ ⇒ log bug và dẫn `C-DLV-05`. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Không cần chờ tới giờ hẹn (không có gate theo giờ — `C-DLV-05`).</t>
         </is>
       </c>
       <c r="N39" s="6" t="inlineStr">
@@ -36884,34 +36815,32 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-5. Nhấn "Xác nhận đã nhận lại hàng" và đồng ý ở popup xác nhận.
-6. Check trạng thái đơn và tab chứa đơn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Trả hàng" (đã chạy xong TC-DLV-034/035/036 và step 1 của TC-DLV-065) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Nhấn "Xác nhận đã nhận lại hàng" và đồng ý ở popup xác nhận.
+4. Check nhãn trạng thái đơn, nút hành động chính và tab chứa đơn.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>6. Đơn chuyển sang trạng thái đã trả lại người gửi và nằm ở tab "Đã hoàn thành".</t>
+          <t>4. Đơn nằm ở tab "Đã hoàn thành", nhãn trạng thái KHÔNG phải "Hoàn thành" (đơn trả người gửi khác đơn hoàn thành — BR09-06) và nút "Xác nhận đã nhận lại hàng" không còn.</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNING` = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` ở "Trả hàng" (RETURNING) → RETURNED; vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đây là bước tạo trạng thái `RETURNED` dùng chung cho TC-DLV-037/038/039, TC-DLV-064/065, TC-DLV-073 và cho `GIFT`/`ACT` — chạy xong mới chạy nhóm đó.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đây là bước tạo trạng thái `RETURNED` dùng chung cho TC-DLV-037/038/039, TC-DLV-064/065, TC-DLV-073 và cho `GIFT`/`ACT` — chạy xong mới chạy nhóm đó. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Ghi nguyên văn nhãn trạng thái STG hiển thị vào Notes (PRD không đặc tả chữ). ⚠ Demo 2026-09-23 lệch PRD: cần CẢ B bấm "Đã trả hàng cho người gửi" và A bấm "Đã lấy lại hàng từ người giao", rồi đơn thành "Hoàn thành" — STG làm như demo ⇒ FAIL + log bug dẫn BR09-06.</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
@@ -36964,33 +36893,32 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, mở đơn đó và nhấn "Xác nhận đã nhận lại hàng". (setup)
-5. Check màn Theo dõi đơn ngay sau khi xác nhận và các nút trên đơn ở tab "Đã hoàn thành".</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Trả hàng" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Nhấn "Xác nhận đã nhận lại hàng" và đồng ý ở popup (chính là step 3 của TC-DLV-063 — chạy chung).
+4. Check màn hiện ra ngay sau khi xác nhận, rồi mở đơn ở tab "Đã hoàn thành" và check các nút trên đơn.</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>5. KHÔNG có bước tặng quà nào mở ra và đơn KHÔNG có nút tặng quà.</t>
+          <t>4. KHÔNG có bước tặng quà nào mở ra và đơn KHÔNG có nút "Cảm ơn người vận chuyển" hay nút tặng quà nào.</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED` = `SEED-DLV-03`; vai người gửi (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` → RETURNED; vai người gửi A (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L41" s="6" t="n"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: oracle bảo vệ ranh giới `RETURNED` ⟷ `COMPLETED` — lỗi hay gặp nhất là coi hoàn hàng như một dạng hoàn thành. Chạy sớm nhất trong nhóm hậu-hoàn-hàng. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06 + §8.14.1 (bước tặng quà chỉ mở ở đơn Hoàn thành). Cặp với TC-DLV-065.</t>
+          <t>Mục đích: oracle bảo vệ ranh giới `RETURNED` ⟷ `COMPLETED` — lỗi hay gặp nhất là coi hoàn hàng như một dạng hoàn thành. Chạy sớm nhất trong nhóm hậu-hoàn-hàng. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06 + §8.14.1 (bước tặng quà chỉ mở ở đơn Hoàn thành). Cặp với TC-DLV-065. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-063 (1 lần xác nhận, 2 evidence). Demo có nút "Cảm ơn người vận chuyển" ở đơn trả hàng — gặp trên STG ⇒ FAIL.</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
@@ -37043,34 +36971,31 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, mở Trang chủ và ghi lại con số "đơn đã giúp" ở khối hero. (setup)
-3. Nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-4. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-5. Đăng nhập bằng tài khoản A, mở đơn đó, nhấn "Xác nhận đã nhận lại hàng" rồi đăng xuất. (setup)
-6. Đăng nhập lại bằng tài khoản B, mở Trang chủ và check con số "đơn đã giúp" ở khối hero.</t>
+          <t>1. (setup) TRƯỚC khi chạy TC-DLV-063: đăng nhập B, mở Trang chủ và ghi lại con số "đơn đã giúp" ở khối hero.
+2. (setup) Chạy TC-DLV-063 (A xác nhận đã nhận lại hàng trên `SEED-DLV-03-A`).
+3. Đăng nhập lại tài khoản B, mở Trang chủ và check con số "đơn đã giúp" ở khối hero.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>6. Con số "đơn đã giúp" bằng đúng con số đã ghi ở step 2, không tăng.</t>
+          <t>3. Con số "đơn đã giúp" bằng đúng con số đã ghi ở step 1, không tăng.</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED` = `SEED-DLV-03`; vai người vận chuyển (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` trước/sau khi thành RETURNED; vai người vận chuyển B (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: điểm fail độc lập với TC-DLV-064 — bước tặng quà và chỉ số đóng góp là hai bề mặt khác nhau, khoá một bề mặt không đảm bảo khoá bề mặt kia. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đơn vẫn phải xuất hiện trong tab "Đã hoàn thành" — verify ở TC-DLV-063.</t>
+          <t>Mục đích: điểm fail độc lập với TC-DLV-064 — bước tặng quà và chỉ số đóng góp là hai bề mặt khác nhau, khoá một bề mặt không đảm bảo khoá bề mặt kia. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đơn vẫn phải xuất hiện trong tab "Đã hoàn thành" — verify ở TC-DLV-063. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
@@ -37123,18 +37048,18 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng" rồi nhấn "Cầm hàng về". (setup)
-4. Chọn "Tôi sẽ trả về cho người gửi".
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-062) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về" rồi chọn "Tôi sẽ trả về cho người gửi".
 5. Nhập "Người nhận từ chối nhận hàng" vào ô ghi chú.
-6. Nhập lịch hẹn hợp lệ và nhấn xác nhận.
+6. Nhập "Ngày hẹn" = ngày mai, giờ từ "09:00" đến "10:00", "Nơi nhận lại hàng" = "Sảnh toà FPT Tower", nhấn nút xác nhận và đồng ý ở popup.
 7. Mở block "LỊCH SỬ" và check ghi chú kèm mốc cầm hàng về.</t>
         </is>
       </c>
@@ -37145,13 +37070,13 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>Đơn `IN_TRANSIT` = `SEED-DLV-03`; chế độ `return` + ghi chú lý do từ chối (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao" → sau TC này thành "Trả hàng" (RETURNING); ghi chú lý do từ chối (test_data_catalog §DLV — Chế độ cầm hàng về)</t>
         </is>
       </c>
       <c r="L43" s="6" t="n"/>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-07 — từ chối nhận hàng đi chung nhánh return, phân biệt với nhánh không liên lạc được chỉ bằng ghi chú.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-07 — từ chối nhận hàng đi chung nhánh return, phân biệt với nhánh không liên lạc được chỉ bằng ghi chú. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). TC này là bước đẩy chuỗi 03-A sang "Trả hàng" — chạy xong mới chạy TC-DLV-034/035/036.</t>
         </is>
       </c>
       <c r="N43" s="6" t="inlineStr">
@@ -37204,35 +37129,36 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Dev/QA hỗ trợ lùi timestamp lịch hẹn để vượt mốc 24 giờ — ⛔ không tái tạo được qua UI.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ giao lại sau", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Nhờ dev/QA lùi timestamp lịch hẹn để vượt mốc 24 giờ mà không ai đóng đơn. (setup)
-5. Đăng nhập bằng tài khoản A, nhấn tab "Hoạt động" và mở đơn đó. (setup)
-6. Check trạng thái đơn, nhãn trên đơn và tab chứa đơn.</t>
+          <t>1. (setup) Tạo 1 đơn riêng: đăng nhập A, đăng 1 tin NEED khai C là người nhận, đăng xuất; đăng nhập B, nhấn "Tôi mang giúp được" và xác nhận, rồi nhấn "Tôi đã lấy hàng" → ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" → tại màn "Xác nhận đã lấy hàng" nhấn "Xác nhận" → ở popup "Đã lấy hàng" nhấn "Đồng ý". Đăng xuất.
+2. Đăng nhập lại tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao". (setup)
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333). (setup)
+4. Nhấn "Cầm hàng về". Chọn "Tôi sẽ giao lại sau", nhập "Ngày hẹn" = ngày mai, giờ từ "09:00" đến "10:00", "Nơi giao lại" = "Sảnh toà FPT Tower", nhấn nút xác nhận và đồng ý ở popup. Rồi đăng xuất. (setup)
+5. Nhờ dev/QA lùi timestamp lịch hẹn để vượt mốc 24 giờ mà không ai đóng đơn. (setup)
+6. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+7. Check trạng thái đơn, nhãn trên đơn và tab chứa đơn.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>6. Đơn KHÔNG ở trạng thái "Hoàn thành", KHÔNG có nhãn hay cờ mới nào so với trước mốc, và vẫn nằm ở tab "Đang diễn ra".</t>
+          <t>7. Đơn KHÔNG ở trạng thái "Hoàn thành", KHÔNG có nhãn hay cờ mới nào so với trước mốc, và vẫn nằm ở tab "Đang diễn ra".</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED` đã quá lịch hẹn 24h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>1 đơn riêng ở "Giao lại" (RESCHEDULED) đã quá lịch hẹn 24h (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L44" s="5" t="n"/>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: vế duy nhất còn assert được của `BR09-04` sau khi BA cắt scope — dễ bị bỏ sót vì cả câu rule đã bị coi là out of scope. · Căn cứ: `AC-23.2.01` câu cuối + `C-DLV-07` Resolved 2026-09-17 (chỉ gửi remind, đơn không đổi trạng thái/nhãn/cờ). ⛔ Không assert vế "chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-057 và SC-TS-006 (QC GiangDC2, 2026-09-17)</t>
+          <t>Mục đích: vế duy nhất còn assert được của `BR09-04` sau khi BA cắt scope — dễ bị bỏ sót vì cả câu rule đã bị coi là out of scope. · Căn cứ: `AC-23.2.01` câu cuối + `C-DLV-07` Resolved 2026-09-17 (chỉ gửi remind, đơn không đổi trạng thái/nhãn/cờ). ⛔ Không assert vế "chuyển admin hỗ trợ" — out of scope v1.1, KHÔNG log bug khi không thấy. · 🚫 Deferred — cần tiền đề thời gian thực, chạy chung lô với TC-DLV-024 (v1.0), TC-DLV-057 và SC-TS-006 (QC GiangDC2, 2026-09-17) · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
@@ -37292,27 +37218,25 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Người nhận", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
+          <t>1. (setup) Dùng đơn #1 `SEED-DLV-02` ngay sau khi TC-DLV-043 submit xong — chạy chung, ⛔ không tạo đơn mới.
+2. Trên màn Theo dõi đơn (vai B), mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>4. Dòng mốc giao hàng ghi đúng nguyên văn "Đã giao tận tay người nhận", kèm thời điểm và dấu hiệu có ảnh bằng chứng.</t>
+          <t>2. Dòng mốc giao hàng có tiêu đề đúng nguyên văn "Đã giao tận tay người nhận", kèm thời điểm và chữ "có ảnh bằng chứng".</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>Đơn `DELIVERED` qua nhánh giao tận tay = `SEED-DLV-05` (test_data_catalog §DLV — Đối tượng nhận)</t>
+          <t>Đơn #1 `SEED-DLV-02` vừa "Đã giao" qua nhánh giao tận tay (test_data_catalog §DLV — Đối tượng nhận)</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
@@ -37322,7 +37246,7 @@
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: 1 trong 6 mẫu câu nhật ký của `§8.12.4` — mỗi mẫu câu là 1 chuỗi verbatim riêng, sai chữ nào là defect chữ đó. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 1 + dòng "Mọi dòng" (thời điểm + cờ không liên lạc nếu có + dấu hiệu có ảnh). Assert nguyên văn kể cả dấu gạch ngang, ⛔ không paraphrase.</t>
+          <t>Mục đích: 1 trong 6 mẫu câu nhật ký của `§8.12.4` — mỗi mẫu câu là 1 chuỗi verbatim riêng, sai chữ nào là defect chữ đó. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 1 + dòng "Mọi dòng" (thời điểm + cờ không liên lạc nếu có + dấu hiệu có ảnh). Assert nguyên văn kể cả dấu gạch ngang, ⛔ không paraphrase. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chữ "có ảnh bằng chứng" lấy từ demo 2026-09-23 (PRD §8.12.4 chỉ nói "dấu hiệu có ảnh") — STG dùng icon thay chữ ⇒ vẫn PASS, ghi Notes.</t>
         </is>
       </c>
       <c r="N46" s="6" t="inlineStr">
@@ -37375,33 +37299,31 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Người được uỷ quyền", nhập tên "Nguyễn Văn Bảy" và số điện thoại "0912345678", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
+          <t>1. (setup) Dùng đơn #2 `SEED-DLV-02` ngay sau khi TC-DLV-044 submit xong — chạy chung, ⛔ không tạo đơn mới.
+2. Trên màn Theo dõi đơn (vai B), mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>4. Dòng mốc giao hàng ghi đúng nguyên văn "Đã giao cho người được uỷ quyền — Nguyễn Văn Bảy · 0912345678 — uỷ quyền bởi Người nhận", kèm thời điểm và dấu hiệu có ảnh bằng chứng.</t>
+          <t>2. Dòng mốc giao hàng ghi đúng nguyên văn "Đã giao cho người được uỷ quyền — Nguyễn Văn Bảy · 0912345678 — uỷ quyền bởi Người nhận", kèm thời điểm và chữ "có ảnh bằng chứng".</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>Đơn `DELIVERED` qua nhánh uỷ quyền; tên 12 ký tự + SĐT hợp lệ (test_data_catalog §DLV — Tên người nhận thay)</t>
+          <t>Đơn #2 `SEED-DLV-02` vừa "Đã giao" qua nhánh uỷ quyền (test_data_catalog §DLV — Tên người nhận thay)</t>
         </is>
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: mẫu câu phức tạp nhất trong 6 mẫu — có 2 biến nội dung và 1 biến nguồn uỷ quyền, dễ ghép sai thứ tự. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 2. Assert nguyên văn kể cả dấu gạch ngang và dấu chấm giữa tên với số điện thoại.</t>
+          <t>Mục đích: mẫu câu phức tạp nhất trong 6 mẫu — có 2 biến nội dung và 1 biến nguồn uỷ quyền, dễ ghép sai thứ tự. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 2. Assert nguyên văn kể cả dấu gạch ngang và dấu chấm giữa tên với số điện thoại. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Xem ghi chú định dạng demo ở TC-DLV-044.</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
@@ -37454,33 +37376,31 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Quầy lễ tân", nhập tên "Trần Thị Lan" và số điện thoại "0987654321", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
+          <t>1. (setup) Dùng đơn #3 `SEED-DLV-02` ngay sau khi TC-DLV-045 submit xong — chạy chung, ⛔ không tạo đơn mới.
+2. Trên màn Theo dõi đơn (vai B), mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>4. Dòng mốc giao hàng ghi đúng nguyên văn "Đã gửi tại quầy lễ tân — Trần Thị Lan", kèm thời điểm và dấu hiệu có ảnh bằng chứng.</t>
+          <t>2. Dòng mốc giao hàng ghi đúng nguyên văn "Đã gửi tại quầy lễ tân — Trần Thị Lan", kèm thời điểm và chữ "có ảnh bằng chứng".</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Đơn `DELIVERED` qua nhánh quầy lễ tân (test_data_catalog §DLV — Tên người trực quầy)</t>
+          <t>Đơn #3 `SEED-DLV-02` vừa "Đã giao" qua nhánh quầy lễ tân (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
       <c r="L48" s="6" t="n"/>
       <c r="M48" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 3. Assert nguyên văn, ⛔ không paraphrase.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 3. Assert nguyên văn, ⛔ không paraphrase. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N48" s="6" t="inlineStr">
@@ -37533,33 +37453,31 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Quầy bảo vệ", nhập tên "Lê Văn Tám" và số điện thoại "0901112223", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
+          <t>1. (setup) Dùng đơn #4 `SEED-DLV-02` ngay sau khi TC-DLV-046 submit xong — chạy chung, ⛔ không tạo đơn mới.
+2. Trên màn Theo dõi đơn (vai B), mở block "LỊCH SỬ" và check dòng mốc giao hàng.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>4. Dòng mốc giao hàng ghi đúng nguyên văn "Đã gửi tại quầy bảo vệ — Lê Văn Tám", kèm thời điểm và dấu hiệu có ảnh bằng chứng.</t>
+          <t>2. Dòng mốc giao hàng ghi đúng nguyên văn "Đã gửi tại quầy bảo vệ — Lê Văn Tám", kèm thời điểm và chữ "có ảnh bằng chứng".</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>Đơn `DELIVERED` qua nhánh quầy bảo vệ (test_data_catalog §DLV — Tên người trực quầy)</t>
+          <t>Đơn #4 `SEED-DLV-02` vừa "Đã giao" qua nhánh quầy bảo vệ (test_data_catalog §DLV — Tên người trực quầy)</t>
         </is>
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-070 — hai quầy là hai mẫu câu tách biệt trong bảng `§8.12.4`, gộp 1 chuỗi có tham số là defect. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 4.</t>
+          <t>Mục đích: cặp với TC-DLV-070 — hai quầy là hai mẫu câu tách biệt trong bảng `§8.12.4`, gộp 1 chuỗi có tham số là defect. · Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 4. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr">
@@ -37612,32 +37530,33 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ giao lại sau", nhập ngày hẹn hợp lệ, giờ "09:00" đến "10:00", nơi hẹn "Sảnh toà FPT Tower" rồi xác nhận. (setup)
-4. Mở block "LỊCH SỬ" và check dòng mốc cầm hàng về.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "Đang giao" (đã chạy xong TC-DLV-061) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Trên màn "Xác nhận đã giao", nhấn link "Không thể liên lạc cho người nhận?" và đi tới màn "Xử lý đơn hàng" (STG hiện: hiện bottom sheet 2 lựa chọn ⇒ chọn "Xử lý đơn hàng" — lệch cấu trúc BA chốt, xem FE-333).
+4. Nhấn "Cầm hàng về". Chọn "Tôi sẽ giao lại sau", nhập "Ngày hẹn" = ngày mai, giờ từ "09:00" đến "10:00", "Nơi giao lại" = "Sảnh toà FPT Tower", nhấn nút xác nhận và đồng ý ở popup.
+5. Mở block "LỊCH SỬ" và check dòng mốc cầm hàng về.</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>4. Dòng mốc ghi đúng nguyên văn "Cầm hàng về — hẹn giao lại" kèm đúng ngày hẹn, khoảng giờ 09:00–10:00 và nơi hẹn "Sảnh toà FPT Tower" đã nhập.</t>
+          <t>5. Dòng mốc ghi đúng nguyên văn "Cầm hàng về — hẹn giao lại" kèm đúng ngày hẹn (ngày mai), khoảng giờ 09:00–10:00 và nơi hẹn "Sảnh toà FPT Tower".</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>Đơn `RESCHEDULED` = `SEED-DLV-03`; lịch hẹn hợp lệ + nơi hẹn (test_data_catalog §DLV — Ngày hẹn, Giờ hẹn từ–đến, Nơi hẹn)</t>
+          <t>`SEED-DLV-03-A` ở "Đang giao" → sau TC này thành "Giao lại" (RESCHEDULED); ngày mai · 09:00–10:00 · "Sảnh toà FPT Tower" (test_data_catalog §DLV — Ngày hẹn, Giờ hẹn từ–đến, Nơi hẹn)</t>
         </is>
       </c>
       <c r="L50" s="6" t="n"/>
       <c r="M50" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 5 — ba biến ngày/giờ/nơi hẹn phải khớp đúng giá trị vừa nhập ở form.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 5 — ba biến ngày/giờ/nơi hẹn phải khớp đúng giá trị vừa nhập ở form. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). TC này là bước đẩy chuỗi 03-A sang "Giao lại" — chạy xong mới chạy TC-DLV-031/032/033. ⚠ Demo ghi 2 dòng "Người vận chuyển giữ hàng để giao lại" + "Hẹn giao lại · &lt;ngày&gt; · 09:00 – 10:00 / Sảnh toà FPT Tower" — khác nguyên văn PRD §8.12.4; STG lệch kiểu này ⇒ ghi Notes, hỏi BA.</t>
         </is>
       </c>
       <c r="N50" s="6" t="inlineStr">
@@ -37690,33 +37609,31 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", nhấn "Không thể liên lạc cho người nhận?", đi tiếp tới màn "Xử lý đơn hàng", nhấn "Cầm hàng về", chọn "Tôi sẽ trả về cho người gửi", nhập lịch hẹn hợp lệ và xác nhận, rồi đăng xuất. (setup)
-4. Đăng nhập bằng tài khoản A, mở đơn đó và nhấn "Xác nhận đã nhận lại hàng". (setup)
-5. Mở block "LỊCH SỬ" và check dòng mốc cuối cùng.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-03-A` đang ở trạng thái "đã trả người gửi" (đã chạy xong TC-DLV-063) — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản A, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và check dòng mốc cuối cùng.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>5. Dòng mốc cuối cùng ghi đúng nguyên văn "Đã trả lại người gửi", kèm thời điểm.</t>
+          <t>3. Dòng mốc cuối cùng ghi đúng nguyên văn "Đã trả lại người gửi", kèm thời điểm.</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>Đơn `RETURNED` = `SEED-DLV-03` (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+          <t>`SEED-DLV-03-A` (RETURNED) (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
         </is>
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 6 — mẫu câu duy nhất do người gửi kích hoạt, 5 mẫu còn lại do người vận chuyển.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 6 — mẫu câu duy nhất do người gửi kích hoạt, 5 mẫu còn lại do người vận chuyển. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ⚠ Demo ghi "Người gửi xác nhận đã nhận lại hàng" / "Đơn đóng · hàng đã về người gửi" — khác PRD §8.12.4; STG lệch ⇒ log bug.</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
@@ -37776,15 +37693,15 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Có sẵn công cụ proxy chặn và phát lại request trỏ vào app FoxEco trên STG.</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận. (setup)
-2. Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác. (setup)
+          <t>1. (setup) Đăng nhập A, đăng 1 tin NEED khai C là người nhận (đơn ở "Chờ ghép").
+2. (setup) Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác.
 3. Sửa request đã ghi thành yêu cầu chuyển đơn đang ở "Chờ ghép" sang "Đã giao" và phát lại request đó.
 4. Mở lại đơn đó trên app và check trạng thái đơn cùng số dòng ở block "LỊCH SỬ".</t>
         </is>
@@ -37796,7 +37713,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>Transition `POSTED` → `DELIVERED` — ngoài bảng transition hợp lệ (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
+          <t>Chuyển "Chờ ghép" → "Đã giao" (POSTED → DELIVERED) — ngoài bảng transition hợp lệ (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
@@ -37806,7 +37723,7 @@
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: tầng backend của rule đã có TC ở tầng UI (`TC-DLV-021` v1.0 chỉ verify màn hình không cho nhảy bước) — UI chặn không đảm bảo backend cũng chặn. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-01 + bảng §8.12.2. Dự án không có API spec/HTTP Status Contract nên assert theo hệ quả quan sát được trên app, không assert mã status.</t>
+          <t>Mục đích: tầng backend của rule đã có TC ở tầng UI (`TC-DLV-021` v1.0 chỉ verify màn hình không cho nhảy bước) — UI chặn không đảm bảo backend cũng chặn. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-01 + bảng §8.12.2. Dự án không có API spec/HTTP Status Contract nên assert theo hệ quả quan sát được trên app, không assert mã status. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N53" s="6" t="inlineStr">
@@ -37859,28 +37776,27 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Có sẵn công cụ proxy chặn và phát lại request trỏ vào app FoxEco trên STG.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác. (setup)
-4. Sửa request đã ghi thành yêu cầu chuyển đơn đang ở "Đang giao" thẳng sang trạng thái đã trả người gửi, bỏ qua bước hoàn hàng, và phát lại request đó.
-5. Mở lại đơn đó trên app và check trạng thái đơn cùng số dòng ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Tạo 1 đơn riêng: đăng nhập A, đăng 1 tin NEED khai C là người nhận, đăng xuất; đăng nhập B, nhấn "Tôi mang giúp được" và xác nhận, rồi nhấn "Tôi đã lấy hàng" → ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" → tại màn "Xác nhận đã lấy hàng" nhấn "Xác nhận" → ở popup "Đã lấy hàng" nhấn "Đồng ý".
+2. (setup) Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác.
+3. Sửa request đã ghi thành yêu cầu chuyển đơn đang ở "Đang giao" thẳng sang trạng thái đã trả người gửi, bỏ qua bước trả hàng, và phát lại request đó.
+4. Mở lại đơn đó trên app và check trạng thái đơn cùng số dòng ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>5. Đơn vẫn ở trạng thái "Đang giao" và block "LỊCH SỬ" KHÔNG có dòng mốc mới nào được thêm.</t>
+          <t>4. Đơn vẫn ở trạng thái "Đang giao" và block "LỊCH SỬ" KHÔNG có dòng mốc mới nào được thêm.</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>Transition `IN_TRANSIT` → `RETURNED` bỏ qua `RETURNING` (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
+          <t>Chuyển "Đang giao" → đã trả người gửi (IN_TRANSIT → RETURNED) bỏ qua RETURNING (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -37890,7 +37806,7 @@
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: nhánh nhảy bậc nguy hiểm nhất — đóng đơn ở kết cục hoàn hàng mà không có bước người gửi xác nhận nhận lại, tức mất luôn oracle của TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02.</t>
+          <t>Mục đích: nhánh nhảy bậc nguy hiểm nhất — đóng đơn ở kết cục hoàn hàng mà không có bước người gửi xác nhận nhận lại, tức mất luôn oracle của TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr">
@@ -37943,28 +37859,27 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Có sẵn công cụ proxy chặn và phát lại request trỏ vào app FoxEco trên STG.</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác. (setup)
-4. Sửa request đã ghi thành yêu cầu chuyển đơn đang ở "Đang giao" thẳng sang "Hoàn thành", bỏ qua bước "Đã giao", và phát lại request đó.
-5. Mở lại đơn đó trên app và check trạng thái đơn cùng số dòng ở block "LỊCH SỬ".</t>
+          <t>1. (setup) Tạo 1 đơn riêng: đăng nhập A, đăng 1 tin NEED khai C là người nhận, đăng xuất; đăng nhập B, nhấn "Tôi mang giúp được" và xác nhận, rồi nhấn "Tôi đã lấy hàng" → ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" → tại màn "Xác nhận đã lấy hàng" nhấn "Xác nhận" → ở popup "Đã lấy hàng" nhấn "Đồng ý".
+2. (setup) Bật proxy chặn request và ghi lại request app gửi đi khi xác nhận một mốc trạng thái ở đơn khác.
+3. Sửa request đã ghi thành yêu cầu chuyển đơn đang ở "Đang giao" thẳng sang "Hoàn thành", bỏ qua bước "Đã giao", và phát lại request đó.
+4. Mở lại đơn đó trên app và check trạng thái đơn cùng số dòng ở block "LỊCH SỬ".</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>5. Đơn vẫn ở trạng thái "Đang giao" và block "LỊCH SỬ" KHÔNG có dòng mốc mới nào được thêm.</t>
+          <t>4. Đơn vẫn ở trạng thái "Đang giao" và block "LỊCH SỬ" KHÔNG có dòng mốc mới nào được thêm.</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>Transition `IN_TRANSIT` → `COMPLETED` bỏ qua `DELIVERED` (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
+          <t>Chuyển "Đang giao" → "Hoàn thành" (IN_TRANSIT → COMPLETED) bỏ qua DELIVERED (test_data_catalog §DLV — Trạng thái đơn mở rộng, nhánh invalid)</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
@@ -37974,7 +37889,7 @@
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-075 — hai đích nhảy bậc khác nhau từ cùng một trạng thái nguồn, chặn được đích này không suy ra chặn được đích kia. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02. Bỏ qua "Đã giao" còn xoá luôn yêu cầu ảnh bằng chứng của `BR07-02`.</t>
+          <t>Mục đích: cặp với TC-DLV-075 — hai đích nhảy bậc khác nhau từ cùng một trạng thái nguồn, chặn được đích này không suy ra chặn được đích kia. · Căn cứ: `DOC-v1.1-01` §8.12.1 BR12-02. Bỏ qua "Đã giao" còn xoá luôn yêu cầu ảnh bằng chứng của `BR07-02`. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N55" s="6" t="inlineStr">
@@ -38034,7 +37949,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thiết bị đang dùng mạng 4G, đã tắt Wi-Fi.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh đúng 5MB.
@@ -38043,12 +37958,12 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao" và chọn "Người nhận". (setup)
+          <t>1. (setup) Dùng đơn #3 của `SEED-DLV-02` đang ở trạng thái "Đang giao" — xem sheet Seed, ⛔ không tạo đơn mới. Chạy TRƯỚC TC-DLV-045 — TC này không submit nên không tiêu đơn.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động", mở đơn đó rồi nhấn nút chính "Đã đến địa điểm giao hàng" (STG hiện vẫn tên "Đã giao cho người nhận" — BUG-044); ở popup xác nhận nhanh (lớp 1) nhấn "Xác nhận" — ⛔ KHÔNG nhấn "Huỷ" — để mở màn "Xác nhận đã giao".
+3. Chọn "Người nhận" ở field "Giao cho".
 4. Khởi động đồng hồ bấm giờ rồi đính cùng lúc 5 ảnh JPG 5MB từ thư viện thiết bị.
-5. Dừng đồng hồ bấm giờ khi cả 5 ảnh hiện đủ trong ô ảnh.
-6. Lặp lại step 3 đến step 5 thêm 9 lần trên 9 đơn khác nhau và ghi lại 10 số đo.
+5. Dừng đồng hồ khi cả 5 ảnh hiện đủ trong ô ảnh; ghi lại số đo.
+6. Nhấn Back thoát màn (⛔ không submit), mở lại màn "Xác nhận đã giao" như step 2 và lặp step 3–5 thêm 9 lần.
 7. Check 10 số đo đã ghi và chỉ báo tiến trình quan sát được trong lúc tải.</t>
         </is>
       </c>
@@ -38059,13 +37974,13 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>5 ảnh JPG đúng 5MB, mạng 4G (test_data_catalog §DLV — Upload ảnh hiệu năng)</t>
+          <t>Đơn #3 `SEED-DLV-02` ở "Đang giao"; 5 ảnh JPG đúng 5MB, mạng 4G (test_data_catalog §DLV — Upload ảnh hiệu năng)</t>
         </is>
       </c>
       <c r="L57" s="5" t="n"/>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: `NFR-03` phát biểu theo p95 nên 1 lần đo không kết luận được — 10 lần đo là mẫu tối thiểu chạy tay được, cho phép đúng 1 lần vượt ngưỡng. · Căn cứ: `DOC-v1.1-01` §9 NFR-03. Chạy trên 10 đơn khác nhau vì ảnh đã ghi mốc thì không xoá để tải lại được (`BR07-07`, xem TC-DLV-048).</t>
+          <t>Mục đích: `NFR-03` phát biểu theo p95 nên 1 lần đo không kết luận được — 10 lần đo là mẫu tối thiểu chạy tay được, cho phép đúng 1 lần vượt ngưỡng. · Căn cứ: `DOC-v1.1-01` §9 NFR-03. Chạy trên 10 đơn khác nhau vì ảnh đã ghi mốc thì không xoá để tải lại được (`BR07-07`, xem TC-DLV-048). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Đo 10 lần trên CÙNG 1 đơn bằng cách thoát màn không submit (ảnh chưa ghi mốc thì chưa bất biến) — thay cho cách cũ cần 10 đơn.</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr">
@@ -38118,39 +38033,34 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
-- Host app FoxPro đã cài trên thiết bị Android/iOS.
-- Có sẵn công cụ proxy chặn và phát lại request trỏ vào app FoxEco trên STG.</t>
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
+- Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó và xác nhận. (setup)
-3. Mở block "LỊCH SỬ" và ghi lại toàn bộ các dòng mốc hiện có.
-4. Nhấn "Huỷ nhận đơn" và xác nhận.
-5. Bật proxy, ghi lại request app gửi đi khi thao tác trên đơn, rồi sửa thành yêu cầu sửa hoặc xoá một dòng nhật ký đã có và phát lại request đó.
-6. Mở lại block "LỊCH SỬ" của đơn đó và check toàn bộ các dòng mốc.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-06` đang ở trạng thái "Đã ghép" — xem sheet Seed, ⛔ không tạo đơn mới. Chạy SAU TC-DLV-080/081 vì TC này tiêu đơn.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó.
+3. Mở block "LỊCH SỬ" và ghi lại (chụp ảnh) toàn bộ các dòng mốc hiện có, gồm dòng "Ghép thành công".
+4. Nhấn "Huỷ nhận đơn", nhập lý do và xác nhận.
+5. Đăng nhập tài khoản A, nhấn tab "Hoạt động", mở đơn đó và mở block "LỊCH SỬ".
+6. Check toàn bộ các dòng mốc so với ảnh đã chụp ở step 3.</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>6. Block "LỊCH SỬ" vẫn giữ đủ mọi dòng mốc đã ghi ở step 3, gồm cả dòng ghép thành công, và KHÔNG dòng nào bị sửa hay biến mất.</t>
+          <t>6. Block "LỊCH SỬ" vẫn giữ đủ mọi dòng mốc đã ghi ở step 3, gồm cả dòng "Ghép thành công", và KHÔNG dòng nào bị sửa hay biến mất.</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Đơn `MATCHED` rồi bị huỷ nhận đơn (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
-        </is>
-      </c>
-      <c r="L58" s="6" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
+          <t>`SEED-DLV-06` ở "Đã ghép" rồi bị B huỷ nhận đơn (test_data_catalog §DLV — Trạng thái đơn mở rộng)</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="n"/>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: neo vào `RISK-DLV-09` — bug audit đã biết (`RISK-TS-01`: huỷ nhận đơn xoá dòng "Ghép thành công") vi phạm trực tiếp rule này, nên TC **dự kiến FAIL có chủ đích** cho tới khi bug được fix. · Căn cứ: `DOC-v1.1-01` §9 NFR-07 (log append-only, không API sửa/xoá). FAIL ⇒ log bug và cross-ref `RISK-TS-01`, ⛔ không hạ Expected theo hành vi hiện tại.</t>
+          <t>Mục đích: neo vào `RISK-DLV-09` — bug audit đã biết (`RISK-TS-01`: huỷ nhận đơn xoá dòng "Ghép thành công") vi phạm trực tiếp rule này, nên TC **dự kiến FAIL có chủ đích** cho tới khi bug được fix. · Căn cứ: `DOC-v1.1-01` §9 NFR-07 (log append-only, không API sửa/xoá). FAIL ⇒ log bug và cross-ref `RISK-TS-01`, ⛔ không hạ Expected theo hành vi hiện tại. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Bỏ phụ thuộc proxy: vế UI (huỷ nhận đơn không được xoá dòng) chạy được bằng thao tác thường nên Status Skipped → chạy được. Vế "không có API sửa/xoá dòng nhật ký" cần proxy — ghi nợ, chưa phủ. Vẫn 🔴 dự kiến FAIL có chủ đích theo `RISK-TS-01`.</t>
         </is>
       </c>
       <c r="N58" s="6" t="inlineStr">
@@ -38203,34 +38113,32 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.
 - Thư viện ảnh thiết bị có sẵn ≥5 ảnh JPG, mỗi ảnh ≤5MB.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó, nhấn "Tôi đã lấy hàng" và xác nhận. (setup)
-3. Mở màn "Xác nhận đã giao", chọn "Người được uỷ quyền", nhập tên "Nguyễn Văn Bảy" và số điện thoại "0912345678", đính 1 ảnh JPG rồi nhấn "Xác nhận đã giao hàng" và đồng ý ở popup. (setup)
-4. Mở lần lượt Trang chủ, tab "Bảng tin", tab "Hoạt động" ở cả hai tab con, tab "Thông báo" và màn hồ sơ cá nhân.
-5. Check từng màn ở step 4 xem có chỗ nào hiện tên "Nguyễn Văn Bảy" hoặc số "0912345678" không.</t>
+          <t>1. (setup) Dùng đơn #2 `SEED-DLV-02` đã "Đã giao" sau TC-DLV-044 (có tên "Nguyễn Văn Bảy" · SĐT "0912345678" trong nhật ký) — ⛔ không tạo đơn mới.
+2. Lần lượt với tài khoản B rồi tài khoản A: mở Trang chủ, tab "Bảng tin", tab "Hoạt động" (cả hai tab con), tab "Thông báo" và màn hồ sơ cá nhân.
+3. Check từng màn ở step 2 xem có chỗ nào hiện tên "Nguyễn Văn Bảy" hoặc số "0912345678" không.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>5. KHÔNG màn nào trong số đó hiện tên "Nguyễn Văn Bảy" hay số "0912345678"; hai giá trị này chỉ xuất hiện ở block "LỊCH SỬ" của đơn.</t>
+          <t>3. KHÔNG màn nào trong số đó hiện tên "Nguyễn Văn Bảy" hay số "0912345678"; hai giá trị này chỉ xuất hiện ở block "LỊCH SỬ" của đơn.</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>Tên và SĐT người nhận thay đã ghi vào nhật ký (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
+          <t>Đơn #2 `SEED-DLV-02` sau TC-DLV-044 (test_data_catalog §DLV — Tên người nhận thay, SĐT người nhận thay)</t>
         </is>
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: dữ liệu người nhận thay là dữ liệu cá nhân của bên thứ ba ngoài 3 vai của đơn — rò ra bề mặt khác là vi phạm quyền riêng tư, không chỉ lỗi hiển thị. · Căn cứ: `DOC-v1.1-01` §9 NFR-12. Phạm vi rà giới hạn ở các màn end-user; dự án không có bề mặt báo cáo hay Admin Portal trong scope v1.1.</t>
+          <t>Mục đích: dữ liệu người nhận thay là dữ liệu cá nhân của bên thứ ba ngoài 3 vai của đơn — rò ra bề mặt khác là vi phạm quyền riêng tư, không chỉ lỗi hiển thị. · Căn cứ: `DOC-v1.1-01` §9 NFR-12. Phạm vi rà giới hạn ở các màn end-user; dự án không có bề mặt báo cáo hay Admin Portal trong scope v1.1. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr">
@@ -38290,28 +38198,27 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó và xác nhận. (setup)
-3. Nhấn tab "Hoạt động" và mở đơn đó. (setup)
-4. Ghi lại số điện thoại liên hệ đang hiển thị trên màn Theo dõi đơn.
-5. Nhấn icon copy cạnh số điện thoại đó.
-6. Dán nội dung vừa copy vào ô tìm kiếm ở tab "Bảng tin" và check nội dung dán ra cùng trạng thái icon copy lúc vừa nhấn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-06` đang ở trạng thái "Đã ghép" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó. (setup)
+3. Ghi lại số điện thoại liên hệ đang hiển thị trên màn Theo dõi đơn.
+4. Nhấn icon copy cạnh số điện thoại đó và quay màn hình (screenrecord) trong ~3 giây sau khi nhấn.
+5. Dán nội dung vừa copy vào ô tìm kiếm ở tab "Bảng tin"; check nội dung dán ra và đoạn quay màu icon copy.</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>6. Nội dung dán ra đúng nguyên văn số điện thoại đã ghi ở step 4, và icon copy đã đổi trạng thái sang màu xanh khoảng 2 giây rồi trở lại bình thường.</t>
+          <t>5. Nội dung dán ra đúng nguyên văn số điện thoại đã ghi ở step 3, và icon copy đổi sang màu xanh khoảng 2 giây rồi trở lại bình thường.</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Số điện thoại liên hệ trên màn Theo dõi đơn (test_data_catalog §DLV — SĐT người nhận thay)</t>
+          <t>`SEED-DLV-06` ở "Đã ghép"; SĐT liên hệ trên màn Theo dõi đơn (test_data_catalog §DLV — SĐT người nhận thay)</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
@@ -38321,7 +38228,7 @@
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: cặp với TC-DLV-081 — hai instance icon copy nằm ở hai vùng khác nhau của cùng màn, hỏng độc lập. · Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04. Rule ghi 1,8 giây nhưng đây là hiệu ứng thị giác — chấp nhận dung sai quanh 2 giây, ⛔ không bấm giờ đòi đúng 1,8 giây. Instance ở màn Chi tiết tin thuộc `FEED`, không rà ở đây.</t>
+          <t>Mục đích: cặp với TC-DLV-081 — hai instance icon copy nằm ở hai vùng khác nhau của cùng màn, hỏng độc lập. · Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04. Rule ghi 1,8 giây nhưng đây là hiệu ứng thị giác — chấp nhận dung sai quanh 2 giây, ⛔ không bấm giờ đòi đúng 1,8 giây. Instance ở màn Chi tiết tin thuộc `FEED`, không rà ở đây. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Hiệu ứng ~2 giây: bắt buộc quay màn hình, ⛔ không kết luận từ ảnh chụp rời (QC từng bác kết luận kiểu này ở TC-ORD-085).</t>
         </is>
       </c>
       <c r="N61" s="6" t="inlineStr">
@@ -38374,28 +38281,27 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>- Tài khoản A, B, C là ba CBNV khác nhau trên STG.
+          <t>- Tài khoản A (người gửi), B (người vận chuyển), C (người nhận) là ba CBNV khác nhau trên STG — lấy theo `04_test-data/valid/USR-accounts.md §2`; đăng nhập email + OTP cố định.
 - Host app FoxPro đã cài trên thiết bị Android/iOS.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>1. Đăng nhập bằng tài khoản A, đăng 1 tin NEED khai tài khoản C là người nhận, rồi đăng xuất. (setup)
-2. Đăng nhập bằng tài khoản B, nhận đơn đó và xác nhận. (setup)
-3. Nhấn tab "Hoạt động" và mở đơn đó. (setup)
-4. Ghi lại địa chỉ giao đang hiển thị trên màn Theo dõi đơn.
-5. Nhấn icon copy cạnh địa chỉ giao đó.
-6. Dán nội dung vừa copy vào ô tìm kiếm ở tab "Bảng tin" và check nội dung dán ra cùng trạng thái icon copy lúc vừa nhấn.</t>
+          <t>1. (setup) Dùng đơn `SEED-DLV-06` đang ở trạng thái "Đã ghép" — xem sheet Seed, ⛔ không tạo đơn mới.
+2. Đăng nhập tài khoản B, nhấn tab "Hoạt động" và mở đơn đó. (setup)
+3. Ghi lại địa chỉ giao đang hiển thị trên màn Theo dõi đơn.
+4. Nhấn icon copy cạnh địa chỉ giao đó và quay màn hình (screenrecord) trong ~3 giây sau khi nhấn.
+5. Dán nội dung vừa copy vào ô tìm kiếm ở tab "Bảng tin"; check nội dung dán ra và đoạn quay màu icon copy.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>6. Nội dung dán ra đúng nguyên văn địa chỉ giao đã ghi ở step 4, và icon copy đã đổi trạng thái sang màu xanh khoảng 2 giây rồi trở lại bình thường.</t>
+          <t>5. Nội dung dán ra đúng nguyên văn địa chỉ giao đã ghi ở step 3, và icon copy đổi sang màu xanh khoảng 2 giây rồi trở lại bình thường.</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>Địa chỉ giao trên màn Theo dõi đơn (test_data_catalog §DLV — Nơi hẹn)</t>
+          <t>`SEED-DLV-06` ở "Đã ghép"; địa chỉ giao trên màn Theo dõi đơn (test_data_catalog §DLV — Nơi hẹn)</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
@@ -38405,7 +38311,7 @@
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04 — rule đặt icon copy cạnh CẢ địa chỉ giao và số điện thoại.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.18.1 BR18-04 — rule đặt icon copy cạnh CẢ địa chỉ giao và số điện thoại. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Hiệu ứng ~2 giây: bắt buộc quay màn hình, ⛔ không kết luận từ ảnh chụp rời.</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr">

--- a/03_test-cases/TC-MASTER-LATEST.xlsx
+++ b/03_test-cases/TC-MASTER-LATEST.xlsx
@@ -15539,7 +15539,7 @@
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: oracle bảo vệ ranh giới `RETURNED` ⟷ `COMPLETED` — lỗi hay gặp nhất là coi hoàn hàng như một dạng hoàn thành. Chạy sớm nhất trong nhóm hậu-hoàn-hàng. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06 + §8.14.1 (bước tặng quà chỉ mở ở đơn Hoàn thành). Cặp với TC-DLV-065. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-063 (1 lần xác nhận, 2 evidence). Demo có nút "Cảm ơn người vận chuyển" ở đơn trả hàng — gặp trên STG ⇒ FAIL.</t>
+          <t>Mục đích: oracle bảo vệ ranh giới `RETURNED` ⟷ `COMPLETED` — lỗi hay gặp nhất là coi hoàn hàng như một dạng hoàn thành. Chạy sớm nhất trong nhóm hậu-hoàn-hàng. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06 + §8.14.1 (bước tặng quà chỉ mở ở đơn Hoàn thành). Cặp với TC-DLV-065. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-063 (1 lần xác nhận, 2 evidence). Demo có nút "Cảm ơn người vận chuyển" ở đơn trả hàng — gặp trên STG ⇒ FAIL. ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
@@ -15616,7 +15616,7 @@
       <c r="L41" s="6" t="n"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: điểm fail độc lập với TC-DLV-064 — bước tặng quà và chỉ số đóng góp là hai bề mặt khác nhau, khoá một bề mặt không đảm bảo khoá bề mặt kia. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đơn vẫn phải xuất hiện trong tab "Đã hoàn thành" — verify ở TC-DLV-063. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
+          <t>Mục đích: điểm fail độc lập với TC-DLV-064 — bước tặng quà và chỉ số đóng góp là hai bề mặt khác nhau, khoá một bề mặt không đảm bảo khoá bề mặt kia. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đơn vẫn phải xuất hiện trong tab "Đã hoàn thành" — verify ở TC-DLV-063. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn giao lại".</t>
+          <t>3. Màn Theo dõi đơn của người gửi hiển thị lịch hẹn giao lại (ngày · khoảng giờ · nơi giao lại) và người gửi KHÔNG có nút hành động nào để đổi trạng thái đơn.</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -16022,7 +16022,7 @@
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: 1 trong 3 ô vai của nhóm trạng thái `RESCHEDULED` — mỗi vai fail độc lập. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. ⚠ Thanh timeline vẫn hiện đúng 5 mốc và mốc "Đang giao" đang active — đây là thiết kế đã chốt (`C-DLV-05(d)` Resolved 2026-09-17), ⛔ không FAIL vì thiếu mốc mới. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Người vận chuyển đang giữ hàng · sẽ giao lại theo lịch hẹn").</t>
+          <t>Mục đích: 1 trong 3 ô vai của nhóm trạng thái `RESCHEDULED` — mỗi vai fail độc lập. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. ⚠ Thanh timeline vẫn hiện đúng 5 mốc và mốc "Đang giao" đang active — đây là thiết kế đã chốt (`C-DLV-05(d)` Resolved 2026-09-17), ⛔ không FAIL vì thiếu mốc mới. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Expected so theo NGHĨA: PRD §8.12.3 chỉ đặt trong ngoặc kép những chữ là nhãn nút thật; ô này KHÔNG có ngoặc kép ⇒ là mô tả việc vai đó làm được, ⛔ không đòi đúng từng chữ. Ghi nguyên văn nhãn STG vào Notes. Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): khối "Sẽ giao lại cho người nhận" + nút xám "Người vận chuyển đang giữ hàng · sẽ giao lại theo lịch hẹn" ⇒ thoả.</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Giao lại theo lịch" ở trạng thái enable.</t>
+          <t>3. Nút hành động chính của người vận chuyển ở trạng thái enable và là hành động giao lại cho người nhận (mở lại màn giao hàng khi nhấn — việc nhấn thuộc TC-DLV-062).</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
@@ -16099,7 +16099,7 @@
       <c r="L47" s="6" t="n"/>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED — đây là vai DUY NHẤT có nút hành động thật ở trạng thái này, 2 vai kia chỉ xem. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Bỏ vế "nhấn được để mở lại màn giao hàng" khỏi Expected vì nhấn sẽ tiêu trạng thái của TC-DLV-031/033/072 — vế này đã do TC-DLV-062 phủ. Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Giao lại cho người nhận").</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED — đây là vai DUY NHẤT có nút hành động thật ở trạng thái này, 2 vai kia chỉ xem. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Expected so theo NGHĨA: PRD §8.12.3 chỉ đặt trong ngoặc kép những chữ là nhãn nút thật; ô này KHÔNG có ngoặc kép ⇒ là mô tả việc vai đó làm được, ⛔ không đòi đúng từng chữ. Ghi nguyên văn nhãn STG vào Notes. Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): nút cam "Giao lại cho người nhận" ⇒ thoả. Bỏ vế "nhấn được" khỏi TC này vì nhấn sẽ tiêu trạng thái của TC-DLV-031/033/072.</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn" và KHÔNG có nút giao lại nào.</t>
+          <t>3. Màn Theo dõi đơn của người nhận hiển thị lịch hẹn giao lại (ngày · khoảng giờ · nơi) và người nhận KHÔNG có nút giao lại hay nút hành động nào.</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -16176,7 +16176,7 @@
       <c r="L48" s="5" t="n"/>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng với TC-DLV-032 — quyền giao lại chỉ thuộc người vận chuyển. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Người vận chuyển sẽ giao lại theo lịch hẹn").</t>
+          <t>Mục đích: đối chứng với TC-DLV-032 — quyền giao lại chỉ thuộc người vận chuyển. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Expected so theo NGHĨA: PRD §8.12.3 chỉ đặt trong ngoặc kép những chữ là nhãn nút thật; ô này KHÔNG có ngoặc kép ⇒ là mô tả việc vai đó làm được, ⛔ không đòi đúng từng chữ. Ghi nguyên văn nhãn STG vào Notes. Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): khối lịch hẹn + nút xám "Người vận chuyển sẽ giao lại theo lịch hẹn" ⇒ thoả.</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Xác nhận đã nhận lại hàng" ở trạng thái enable và màn có mục xem lịch hẹn trả hàng.</t>
+          <t>3. Nút hành động chính hiển thị đúng chữ "Xác nhận đã nhận lại hàng" ở trạng thái enable và màn hiển thị lịch hẹn trả hàng (ngày · khoảng giờ · nơi).</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
@@ -16253,7 +16253,7 @@
       <c r="L49" s="6" t="n"/>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: người gửi là vai DUY NHẤT đóng được đơn ở nhánh hoàn hàng — cặp với TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Đã lấy lại hàng từ người giao").</t>
+          <t>Mục đích: người gửi là vai DUY NHẤT đóng được đơn ở nhánh hoàn hàng — cặp với TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23 (theo PRD): CHỈ người gửi đóng đơn trả hàng, nhãn nút đúng chữ "Xác nhận đã nhận lại hàng"; đơn sau khi người gửi nhận lại hiển thị trạng thái "Hoàn thành". Demo ghi "Đã lấy lại hàng từ người giao" ⇒ STG giống demo = FAIL + log bug dẫn §8.12.3. Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): khối "Đơn chuyển sang trả hàng" có lịch hẹn.</t>
         </is>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn trả hàng" và KHÔNG có nút xác nhận đóng đơn.</t>
+          <t>3. Màn Theo dõi đơn của người vận chuyển hiển thị lịch hẹn trả hàng (ngày · khoảng giờ · nơi) và KHÔNG có nút xác nhận đã trả hàng / đóng đơn nào.</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -16330,7 +16330,7 @@
       <c r="L50" s="5" t="n"/>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. ⚠ Demo cho B nút "Đã trả hàng cho người gửi" (ngược Expected) — gặp trên STG ⇒ FAIL + log bug dẫn §8.12.3.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23 (theo PRD): CHỈ người gửi đóng đơn trả hàng, nhãn nút đúng chữ "Xác nhận đã nhận lại hàng"; đơn sau khi người gửi nhận lại hiển thị trạng thái "Hoàn thành". Người vận chuyển KHÔNG có nút đóng/xác nhận trả hàng. Expected so theo NGHĨA: PRD §8.12.3 chỉ đặt trong ngoặc kép những chữ là nhãn nút thật; ô này KHÔNG có ngoặc kép ⇒ là mô tả việc vai đó làm được, ⛔ không đòi đúng từng chữ. Ghi nguyên văn nhãn STG vào Notes. ⚠ Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): người vận chuyển CÓ nút cam "Đã trả hàng cho người gửi" ⇒ trái quyết định trên; STG giống demo ⇒ FAIL + log bug dẫn §8.12.3 + quyết định QC 2026-09-23.</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Xem lý do hoàn hàng".</t>
+          <t>3. Màn Theo dõi đơn của người nhận cho biết đơn không giao được và đang được trả lại người gửi, hiển thị lý do/ghi chú của người vận chuyển, và người nhận KHÔNG có nút hành động nào.</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
@@ -16407,7 +16407,7 @@
       <c r="L51" s="6" t="n"/>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Không giao được · hàng đang được trả lại người gửi").</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Expected so theo NGHĨA: PRD §8.12.3 chỉ đặt trong ngoặc kép những chữ là nhãn nút thật; ô này KHÔNG có ngoặc kép ⇒ là mô tả việc vai đó làm được, ⛔ không đòi đúng từng chữ. Ghi nguyên văn nhãn STG vào Notes. Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): khối "Đơn chuyển sang trả hàng" + ghi chú "Người nhận từ chối nhận hàng" + nút xám "Không giao được · hàng đang được trả lại người gửi" ⇒ thoả.</t>
         </is>
       </c>
       <c r="N51" s="6" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>4. Đơn nằm ở tab "Đã hoàn thành", nhãn trạng thái KHÔNG phải "Hoàn thành" (đơn trả người gửi khác đơn hoàn thành — BR09-06) và nút "Xác nhận đã nhận lại hàng" không còn.</t>
+          <t>4. Đơn hiển thị nhãn trạng thái "Hoàn thành", nút "Xác nhận đã nhận lại hàng" không còn, và đơn nằm ở tab "Đã hoàn thành".</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
@@ -17622,7 +17622,7 @@
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đây là bước tạo trạng thái `RETURNED` dùng chung cho TC-DLV-037/038/039, TC-DLV-064/065, TC-DLV-073 và cho `GIFT`/`ACT` — chạy xong mới chạy nhóm đó. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Ghi nguyên văn nhãn trạng thái STG hiển thị vào Notes (PRD không đặc tả chữ). ⚠ Demo 2026-09-23 lệch PRD: cần CẢ B bấm "Đã trả hàng cho người gửi" và A bấm "Đã lấy lại hàng từ người giao", rồi đơn thành "Hoàn thành" — STG làm như demo ⇒ FAIL + log bug dẫn BR09-06.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đây là bước tạo trạng thái `RETURNED` dùng chung cho TC-DLV-037/038/039, TC-DLV-064/065, TC-DLV-073 và cho `GIFT`/`ACT` — chạy xong mới chạy nhóm đó. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23 (theo PRD): CHỈ người gửi đóng đơn trả hàng, nhãn nút đúng chữ "Xác nhận đã nhận lại hàng"; đơn sau khi người gửi nhận lại hiển thị trạng thái "Hoàn thành". ⇒ Expected đổi từ "KHÔNG phải Hoàn thành" sang nhãn "Hoàn thành" (khác cách đọc BR09-06 trước đây; phần "không mở tặng quà / không cộng Đơn đã giúp" vẫn assert ở TC-DLV-064/065). Tab chứa đơn "Đã hoàn thành": QC chốt giữ nguyên 2026-09-23. ⚠ Demo bắt CẢ 2 bên xác nhận mới đóng — trái quyết định trên; STG giống demo ⇒ FAIL + log bug.</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr">
@@ -18171,7 +18171,7 @@
       <c r="L73" s="6" t="n"/>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 6 — mẫu câu duy nhất do người gửi kích hoạt, 5 mẫu còn lại do người vận chuyển. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ⚠ Demo ghi "Người gửi xác nhận đã nhận lại hàng" / "Đơn đóng · hàng đã về người gửi" — khác PRD §8.12.4; STG lệch ⇒ log bug.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 6 — mẫu câu duy nhất do người gửi kích hoạt, 5 mẫu còn lại do người vận chuyển. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ⚠ Demo ghi "Người gửi xác nhận đã nhận lại hàng" / "Đơn đóng · hàng đã về người gửi" — khác PRD §8.12.4; STG lệch ⇒ log bug. ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N73" s="6" t="inlineStr">
@@ -18249,7 +18249,7 @@
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: nhóm ba trạng thái đóng phải cho CÙNG một nhãn — lệch giữa ba đơn mới là defect. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng (PRD chỉ mô tả cấp danh mục, không có microcopy riêng cho từng trạng thái). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Đơn hết hạn lấy từ tin cũ có sẵn trên STG, ⛔ không chờ dev. Thiếu đơn hết hạn ⇒ verdict chỉ dựa trên 2 đơn, ghi rõ trong Notes.</t>
+          <t>Mục đích: nhóm ba trạng thái đóng phải cho CÙNG một nhãn — lệch giữa ba đơn mới là defect. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng (PRD chỉ mô tả cấp danh mục, không có microcopy riêng cho từng trạng thái). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Đơn hết hạn lấy từ tin cũ có sẵn trên STG, ⛔ không chờ dev. Thiếu đơn hết hạn ⇒ verdict chỉ dựa trên 2 đơn, ghi rõ trong Notes. ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr">
@@ -18326,7 +18326,7 @@
       <c r="L75" s="6" t="n"/>
       <c r="M75" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng với TC-DLV-037 — quyền đăng lại chỉ thuộc người gửi. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
+          <t>Mục đích: đối chứng với TC-DLV-037 — quyền đăng lại chỉ thuộc người gửi. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N75" s="6" t="inlineStr">
@@ -18403,7 +18403,7 @@
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr">
@@ -34230,7 +34230,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn giao lại".</t>
+          <t>3. Màn Theo dõi đơn của người gửi hiển thị lịch hẹn giao lại (ngày · khoảng giờ · nơi giao lại) và người gửi KHÔNG có nút hành động nào để đổi trạng thái đơn.</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -34241,7 +34241,7 @@
       <c r="L3" s="5" t="n"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: 1 trong 3 ô vai của nhóm trạng thái `RESCHEDULED` — mỗi vai fail độc lập. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. ⚠ Thanh timeline vẫn hiện đúng 5 mốc và mốc "Đang giao" đang active — đây là thiết kế đã chốt (`C-DLV-05(d)` Resolved 2026-09-17), ⛔ không FAIL vì thiếu mốc mới. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Người vận chuyển đang giữ hàng · sẽ giao lại theo lịch hẹn").</t>
+          <t>Mục đích: 1 trong 3 ô vai của nhóm trạng thái `RESCHEDULED` — mỗi vai fail độc lập. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. ⚠ Thanh timeline vẫn hiện đúng 5 mốc và mốc "Đang giao" đang active — đây là thiết kế đã chốt (`C-DLV-05(d)` Resolved 2026-09-17), ⛔ không FAIL vì thiếu mốc mới. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Expected so theo NGHĨA: PRD §8.12.3 chỉ đặt trong ngoặc kép những chữ là nhãn nút thật; ô này KHÔNG có ngoặc kép ⇒ là mô tả việc vai đó làm được, ⛔ không đòi đúng từng chữ. Ghi nguyên văn nhãn STG vào Notes. Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): khối "Sẽ giao lại cho người nhận" + nút xám "Người vận chuyển đang giữ hàng · sẽ giao lại theo lịch hẹn" ⇒ thoả.</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -34307,7 +34307,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Giao lại theo lịch" ở trạng thái enable.</t>
+          <t>3. Nút hành động chính của người vận chuyển ở trạng thái enable và là hành động giao lại cho người nhận (mở lại màn giao hàng khi nhấn — việc nhấn thuộc TC-DLV-062).</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -34318,7 +34318,7 @@
       <c r="L4" s="6" t="n"/>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED — đây là vai DUY NHẤT có nút hành động thật ở trạng thái này, 2 vai kia chỉ xem. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Bỏ vế "nhấn được để mở lại màn giao hàng" khỏi Expected vì nhấn sẽ tiêu trạng thái của TC-DLV-031/033/072 — vế này đã do TC-DLV-062 phủ. Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Giao lại cho người nhận").</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED — đây là vai DUY NHẤT có nút hành động thật ở trạng thái này, 2 vai kia chỉ xem. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Expected so theo NGHĨA: PRD §8.12.3 chỉ đặt trong ngoặc kép những chữ là nhãn nút thật; ô này KHÔNG có ngoặc kép ⇒ là mô tả việc vai đó làm được, ⛔ không đòi đúng từng chữ. Ghi nguyên văn nhãn STG vào Notes. Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): nút cam "Giao lại cho người nhận" ⇒ thoả. Bỏ vế "nhấn được" khỏi TC này vì nhấn sẽ tiêu trạng thái của TC-DLV-031/033/072.</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn" và KHÔNG có nút giao lại nào.</t>
+          <t>3. Màn Theo dõi đơn của người nhận hiển thị lịch hẹn giao lại (ngày · khoảng giờ · nơi) và người nhận KHÔNG có nút giao lại hay nút hành động nào.</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -34395,7 +34395,7 @@
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng với TC-DLV-032 — quyền giao lại chỉ thuộc người vận chuyển. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Người vận chuyển sẽ giao lại theo lịch hẹn").</t>
+          <t>Mục đích: đối chứng với TC-DLV-032 — quyền giao lại chỉ thuộc người vận chuyển. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RESCHEDULED. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Expected so theo NGHĨA: PRD §8.12.3 chỉ đặt trong ngoặc kép những chữ là nhãn nút thật; ô này KHÔNG có ngoặc kép ⇒ là mô tả việc vai đó làm được, ⛔ không đòi đúng từng chữ. Ghi nguyên văn nhãn STG vào Notes. Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): khối lịch hẹn + nút xám "Người vận chuyển sẽ giao lại theo lịch hẹn" ⇒ thoả.</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -34461,7 +34461,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Xác nhận đã nhận lại hàng" ở trạng thái enable và màn có mục xem lịch hẹn trả hàng.</t>
+          <t>3. Nút hành động chính hiển thị đúng chữ "Xác nhận đã nhận lại hàng" ở trạng thái enable và màn hiển thị lịch hẹn trả hàng (ngày · khoảng giờ · nơi).</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -34472,7 +34472,7 @@
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: người gửi là vai DUY NHẤT đóng được đơn ở nhánh hoàn hàng — cặp với TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Đã lấy lại hàng từ người giao").</t>
+          <t>Mục đích: người gửi là vai DUY NHẤT đóng được đơn ở nhánh hoàn hàng — cặp với TC-DLV-063. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23 (theo PRD): CHỈ người gửi đóng đơn trả hàng, nhãn nút đúng chữ "Xác nhận đã nhận lại hàng"; đơn sau khi người gửi nhận lại hiển thị trạng thái "Hoàn thành". Demo ghi "Đã lấy lại hàng từ người giao" ⇒ STG giống demo = FAIL + log bug dẫn §8.12.3. Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): khối "Đơn chuyển sang trả hàng" có lịch hẹn.</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Xem lịch hẹn trả hàng" và KHÔNG có nút xác nhận đóng đơn.</t>
+          <t>3. Màn Theo dõi đơn của người vận chuyển hiển thị lịch hẹn trả hàng (ngày · khoảng giờ · nơi) và KHÔNG có nút xác nhận đã trả hàng / đóng đơn nào.</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -34549,7 +34549,7 @@
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. ⚠ Demo cho B nút "Đã trả hàng cho người gửi" (ngược Expected) — gặp trên STG ⇒ FAIL + log bug dẫn §8.12.3.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23 (theo PRD): CHỈ người gửi đóng đơn trả hàng, nhãn nút đúng chữ "Xác nhận đã nhận lại hàng"; đơn sau khi người gửi nhận lại hiển thị trạng thái "Hoàn thành". Người vận chuyển KHÔNG có nút đóng/xác nhận trả hàng. Expected so theo NGHĨA: PRD §8.12.3 chỉ đặt trong ngoặc kép những chữ là nhãn nút thật; ô này KHÔNG có ngoặc kép ⇒ là mô tả việc vai đó làm được, ⛔ không đòi đúng từng chữ. Ghi nguyên văn nhãn STG vào Notes. ⚠ Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): người vận chuyển CÓ nút cam "Đã trả hàng cho người gửi" ⇒ trái quyết định trên; STG giống demo ⇒ FAIL + log bug dẫn §8.12.3 + quyết định QC 2026-09-23.</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
@@ -34615,7 +34615,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>3. Nhãn hành động chính hiển thị "Xem lý do hoàn hàng".</t>
+          <t>3. Màn Theo dõi đơn của người nhận cho biết đơn không giao được và đang được trả lại người gửi, hiển thị lý do/ghi chú của người vận chuyển, và người nhận KHÔNG có nút hành động nào.</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -34626,7 +34626,7 @@
       <c r="L8" s="6" t="n"/>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Demo 2026-09-23 hiện nhãn KHÁC PRD §8.12.3 ở nhóm trạng thái mới — oracle vẫn theo PRD; STG hiện chữ nào thì ghi nguyên văn vào Notes, lệch PRD ⇒ log bug dẫn §8.12.3, ⛔ không sửa Expected theo demo. (demo: "Không giao được · hàng đang được trả lại người gửi").</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng RETURNING. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Expected so theo NGHĨA: PRD §8.12.3 chỉ đặt trong ngoặc kép những chữ là nhãn nút thật; ô này KHÔNG có ngoặc kép ⇒ là mô tả việc vai đó làm được, ⛔ không đòi đúng từng chữ. Ghi nguyên văn nhãn STG vào Notes. Đã đối chiếu demo bằng Playwright 2026-09-23 (3 vai cùng lúc): khối "Đơn chuyển sang trả hàng" + ghi chú "Người nhận từ chối nhận hàng" + nút xám "Không giao được · hàng đang được trả lại người gửi" ⇒ thoả.</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
@@ -34704,7 +34704,7 @@
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: nhóm ba trạng thái đóng phải cho CÙNG một nhãn — lệch giữa ba đơn mới là defect. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng (PRD chỉ mô tả cấp danh mục, không có microcopy riêng cho từng trạng thái). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Đơn hết hạn lấy từ tin cũ có sẵn trên STG, ⛔ không chờ dev. Thiếu đơn hết hạn ⇒ verdict chỉ dựa trên 2 đơn, ghi rõ trong Notes.</t>
+          <t>Mục đích: nhóm ba trạng thái đóng phải cho CÙNG một nhãn — lệch giữa ba đơn mới là defect. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng (PRD chỉ mô tả cấp danh mục, không có microcopy riêng cho từng trạng thái). · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Đơn hết hạn lấy từ tin cũ có sẵn trên STG, ⛔ không chờ dev. Thiếu đơn hết hạn ⇒ verdict chỉ dựa trên 2 đơn, ghi rõ trong Notes. ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
@@ -34781,7 +34781,7 @@
       <c r="L10" s="6" t="n"/>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: đối chứng với TC-DLV-037 — quyền đăng lại chỉ thuộc người gửi. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
+          <t>Mục đích: đối chứng với TC-DLV-037 — quyền đăng lại chỉ thuộc người gửi. · Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
@@ -34858,7 +34858,7 @@
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.3 dòng nhóm đóng. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -36829,7 +36829,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>4. Đơn nằm ở tab "Đã hoàn thành", nhãn trạng thái KHÔNG phải "Hoàn thành" (đơn trả người gửi khác đơn hoàn thành — BR09-06) và nút "Xác nhận đã nhận lại hàng" không còn.</t>
+          <t>4. Đơn hiển thị nhãn trạng thái "Hoàn thành", nút "Xác nhận đã nhận lại hàng" không còn, và đơn nằm ở tab "Đã hoàn thành".</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -36840,7 +36840,7 @@
       <c r="L40" s="5" t="n"/>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đây là bước tạo trạng thái `RETURNED` dùng chung cho TC-DLV-037/038/039, TC-DLV-064/065, TC-DLV-073 và cho `GIFT`/`ACT` — chạy xong mới chạy nhóm đó. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Ghi nguyên văn nhãn trạng thái STG hiển thị vào Notes (PRD không đặc tả chữ). ⚠ Demo 2026-09-23 lệch PRD: cần CẢ B bấm "Đã trả hàng cho người gửi" và A bấm "Đã lấy lại hàng từ người giao", rồi đơn thành "Hoàn thành" — STG làm như demo ⇒ FAIL + log bug dẫn BR09-06.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đây là bước tạo trạng thái `RETURNED` dùng chung cho TC-DLV-037/038/039, TC-DLV-064/065, TC-DLV-073 và cho `GIFT`/`ACT` — chạy xong mới chạy nhóm đó. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23 (theo PRD): CHỈ người gửi đóng đơn trả hàng, nhãn nút đúng chữ "Xác nhận đã nhận lại hàng"; đơn sau khi người gửi nhận lại hiển thị trạng thái "Hoàn thành". ⇒ Expected đổi từ "KHÔNG phải Hoàn thành" sang nhãn "Hoàn thành" (khác cách đọc BR09-06 trước đây; phần "không mở tặng quà / không cộng Đơn đã giúp" vẫn assert ở TC-DLV-064/065). Tab chứa đơn "Đã hoàn thành": QC chốt giữ nguyên 2026-09-23. ⚠ Demo bắt CẢ 2 bên xác nhận mới đóng — trái quyết định trên; STG giống demo ⇒ FAIL + log bug.</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
@@ -36918,7 +36918,7 @@
       <c r="L41" s="6" t="n"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: oracle bảo vệ ranh giới `RETURNED` ⟷ `COMPLETED` — lỗi hay gặp nhất là coi hoàn hàng như một dạng hoàn thành. Chạy sớm nhất trong nhóm hậu-hoàn-hàng. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06 + §8.14.1 (bước tặng quà chỉ mở ở đơn Hoàn thành). Cặp với TC-DLV-065. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-063 (1 lần xác nhận, 2 evidence). Demo có nút "Cảm ơn người vận chuyển" ở đơn trả hàng — gặp trên STG ⇒ FAIL.</t>
+          <t>Mục đích: oracle bảo vệ ranh giới `RETURNED` ⟷ `COMPLETED` — lỗi hay gặp nhất là coi hoàn hàng như một dạng hoàn thành. Chạy sớm nhất trong nhóm hậu-hoàn-hàng. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06 + §8.14.1 (bước tặng quà chỉ mở ở đơn Hoàn thành). Cặp với TC-DLV-065. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). Chạy CHUNG với TC-DLV-063 (1 lần xác nhận, 2 evidence). Demo có nút "Cảm ơn người vận chuyển" ở đơn trả hàng — gặp trên STG ⇒ FAIL. ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
@@ -36995,7 +36995,7 @@
       <c r="L42" s="5" t="n"/>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: điểm fail độc lập với TC-DLV-064 — bước tặng quà và chỉ số đóng góp là hai bề mặt khác nhau, khoá một bề mặt không đảm bảo khoá bề mặt kia. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đơn vẫn phải xuất hiện trong tab "Đã hoàn thành" — verify ở TC-DLV-063. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận").</t>
+          <t>Mục đích: điểm fail độc lập với TC-DLV-064 — bước tặng quà và chỉ số đóng góp là hai bề mặt khác nhau, khoá một bề mặt không đảm bảo khoá bề mặt kia. · Căn cứ: `DOC-v1.1-01` §8.9.1 BR09-06. Đơn vẫn phải xuất hiện trong tab "Đã hoàn thành" — verify ở TC-DLV-063. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
@@ -37633,7 +37633,7 @@
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 6 — mẫu câu duy nhất do người gửi kích hoạt, 5 mẫu còn lại do người vận chuyển. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ⚠ Demo ghi "Người gửi xác nhận đã nhận lại hàng" / "Đơn đóng · hàng đã về người gửi" — khác PRD §8.12.4; STG lệch ⇒ log bug.</t>
+          <t>Căn cứ: `DOC-v1.1-01` §8.12.4 mẫu câu 6 — mẫu câu duy nhất do người gửi kích hoạt, 5 mẫu còn lại do người vận chuyển. · 🔁 Sửa 2026-09-23 (QC): Steps chuẩn hoá: dùng đơn seed thay vì tạo đơn mới mỗi TC; ghi rõ 2 lớp popup (lớp 1 nhấn "Xác nhận"). ⚠ Demo ghi "Người gửi xác nhận đã nhận lại hàng" / "Đơn đóng · hàng đã về người gửi" — khác PRD §8.12.4; STG lệch ⇒ log bug. ✅ QC chốt 2026-09-23: giữ nguyên Expected hiện tại (theo PRD) — không chờ BA. Demo chưa có UI nhóm trạng thái đóng (gộp vào "Hoàn thành", không có "Xem lý do"/"Đăng lại") ⇒ STG giống demo = FAIL + log bug.</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">

--- a/03_test-cases/TC-MASTER-LATEST.xlsx
+++ b/03_test-cases/TC-MASTER-LATEST.xlsx
@@ -20340,7 +20340,11 @@
           <t>Tài khoản 0 đơn/0 quà (test_data_catalog §GIFT v1.1, biên)</t>
         </is>
       </c>
-      <c r="L100" s="5" t="n"/>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
           <t>Mục đích: hết `[GAP]` của `C-ORD-06` phần GIFT (`EMP-08`) — Resolved bằng tài liệu phê duyệt, không còn dựa suy diễn `KB-GIFT-03` như v1.0. · Căn cứ: `DOC-v1.1-01 §8.17.1 EMP-08` · `§6.2 AC-26.2.01`. ⚠️ Cột CTA của `EMP-08` = "—" là assert thật theo `BR17-01` (tối đa 1 CTA) — không phải thiếu sót. · Đã sửa theo delta v1.1 (2026-09-15): đổi Expected từ "KHÔNG hiển thị loại quà nào" (v1.0, suy diễn) sang assert verbatim text + thống kê 0/0 + không CTA (theo tài liệu chính thức).</t>
@@ -39415,7 +39419,11 @@
           <t>Tài khoản 0 đơn/0 quà (test_data_catalog §GIFT v1.1, biên)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Mục đích: hết `[GAP]` của `C-ORD-06` phần GIFT (`EMP-08`) — Resolved bằng tài liệu phê duyệt, không còn dựa suy diễn `KB-GIFT-03` như v1.0. · Căn cứ: `DOC-v1.1-01 §8.17.1 EMP-08` · `§6.2 AC-26.2.01`. ⚠️ Cột CTA của `EMP-08` = "—" là assert thật theo `BR17-01` (tối đa 1 CTA) — không phải thiếu sót. · Đã sửa theo delta v1.1 (2026-09-15): đổi Expected từ "KHÔNG hiển thị loại quà nào" (v1.0, suy diễn) sang assert verbatim text + thống kê 0/0 + không CTA (theo tài liệu chính thức).</t>

--- a/03_test-cases/TC-MASTER-LATEST.xlsx
+++ b/03_test-cases/TC-MASTER-LATEST.xlsx
@@ -7203,7 +7203,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>9. Màn hiển thị "Đã ghi nhận phản hồi" kèm đúng câu "Đội hỗ trợ FoxEco sẽ liên hệ lại số 0912345678 trong vòng 24 giờ làm việc" và nút "Quay lại đơn hàng".</t>
+          <t>9. Màn xác nhận mặc định của Microsoft Forms hiển thị "Đã gửi phản hồi của bạn." (tiếng Anh: "Your response was submitted." — theo ngôn ngữ tài khoản Microsoft), báo cáo được gửi thành công.</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: chuỗi cam kết 24 giờ là **thứ duy nhất verify được** của quy trình hỗ trợ — hành động thật của Admin nằm ngoài app, ⛔ không mở rộng phạm vi sang đó. · Căn cứ: `AC-31.1.01` + vibe-check demo 2026-09-15 (ảnh `TS_05`, chuỗi verbatim). Màn xác nhận và nút "Quay lại đơn hàng" do **APP** vẽ chứ không phải trang xác nhận của Google Form (`C-TS-03(d)` Resolved 2026-09-17).</t>
+          <t>🔴 Cập nhật 2026-09-24 theo BA (LinhDCC) trả lời trên Jira `FE-323` (Won't Fix): *"màn hình này là mặc định của Microsoft Form, mình không can thiệp được. Sai tài liệu ạ."* ⇒ Then của `AC-31.1.01` ("Đã ghi nhận phản hồi" + cam kết 24 giờ + nút "Quay lại đơn hàng") là tài liệu sai; ⛔ không assert câu 24 giờ / nút "Quay lại đơn hàng". Kết luận `C-TS-03(d)` (màn do APP vẽ) HẾT HIỆU LỰC — hiện hành `C-TS-04(b)`. · Mục đích: xác nhận luồng gửi hợp lệ đi hết tới màn xác nhận; hành động thật của Admin nằm ngoài app, ⛔ không mở rộng phạm vi.</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
@@ -7458,12 +7458,12 @@
 4. Chọn "Góp ý / đề xuất" ở ô "Loại yêu cầu".
 5. Nhập "App hay bị chậm ở màn bảng tin" vào ô "Mô tả chi tiết".
 6. Nhập "0912abc" vào ô "Số điện thoại liên hệ lại".
-7. Check trạng thái nút "Gửi" cùng phần chữ cạnh nút.</t>
+7. Nhấn "Gửi".&lt;br&gt;8. Check phản hồi của form ở ô "Số điện thoại liên hệ lại" và màn hiện ra sau khi gửi.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7. Nút "Gửi" vẫn ở trạng thái bấm được (không disable — cơ chế thật của form là inline error, xem TC-TS-010/TC-TS-011); tuy nhiên SĐT sai định dạng vẫn phải bị chặn không cho gửi (báo lỗi định dạng hoặc tương đương) trước khi form được submit.</t>
+          <t>8. Ô "Số điện thoại liên hệ lại" KHÔNG báo lỗi định dạng; form gửi thành công với giá trị "0912abc" và hiện màn xác nhận mặc định "Đã gửi phản hồi của bạn." (tiếng Anh: "Your response was submitted." — theo ngôn ngữ tài khoản Microsoft) của Microsoft Forms.</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: nhánh khác bản chất với 2 TC kia — ô CÓ dữ liệu nhưng sai định dạng, dễ bị lập trình thành "chỉ kiểm rỗng". · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.1.02 + §8.16.2. Dùng loại yêu cầu thứ ba để đồng thời phủ đủ 3 giá trị enum của ô "Loại yêu cầu" trong cụm này.</t>
+          <t>🔴 Cập nhật 2026-09-24 theo BA (LinhDCC) trả lời trên Jira `FE-324` (Won't Fix): *"Microsoft form không hỗ trợ rang buộc định dạng số điện thoại -&gt; chấp nhận rủi ro data"* ⇒ nhánh "SĐT không hợp lệ" của `AC-31.1.02` bị bỏ, form chỉ kiểm không rỗng (`C-TS-04(c)`). ⚠️ Test Title còn ghi "vô hiệu hoá khi SĐT sai định dạng" — giữ nguyên vì §10.5 không cho sửa Title; Expected mới là oracle. · Mục đích: chốt rủi ro data đã được BA chấp nhận — nếu form bắt đầu chặn SĐT sai thì cũng là thay đổi cần báo lại.</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>8. Màn hiển thị "Đã ghi nhận phản hồi", gửi thành công không có thông báo lỗi đòi ảnh.</t>
+          <t>8. Gửi thành công, hiện màn xác nhận mặc định của Microsoft Forms "Đã gửi phản hồi của bạn." (tiếng Anh: "Your response was submitted." — theo ngôn ngữ tài khoản Microsoft), không có thông báo lỗi đòi ảnh.</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6. Màn hiển thị thông báo lỗi không tải được kèm nút "Thử lại"; form Google không hiện ra.</t>
+          <t>6. App hiển thị màn lỗi "Không tải được trang" kèm dòng "Vui lòng kiểm tra kết nối mạng và thử lại." và nút "Thử lại"; form Microsoft Forms không hiện ra.</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §6.2 AC-31.2.01 + **Dev trả lời `C-TS-03(c)` 2026-09-17** (*"App hiển thị nhé"*) — nút "Thử lại" do CHÍNH APP vẽ, tách biệt khỏi khung nhúng, nên assert được dù `BR16-01` dùng Custom Tabs. ⛔ Không assert công nghệ nhúng cụ thể (WebView trần hay Custom Tabs) — không quan sát được từ UI.</t>
+          <t>🔴 Cập nhật lần 2 ngày 2026-09-24 — QC GiangDC2 chốt Expected theo hành vi hiện tại của app (VR-029): mất mạng thì APP tự vẽ màn lỗi + nút "Thử lại", đúng spec gốc `DOC-v1.1-01` §6.2 AC-31.2.01. Bản Expected sửa sáng cùng ngày ("trang lỗi mặc định của WebView, không có nút Thử lại") HẾT HIỆU LỰC — viết khi app còn hiện trang lỗi Chromium `net::ERR_INTERNET_DISCONNECTED` (VR-019, `FE-322` Won't Fix). Status Pass theo evidence `VR-029-TS-2026-09-24/screenshots/TC-TS-016__verify-mat-mang-man-loi-app.png`. Xem `C-TS-04(a)`.</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: fail độc lập với `TC-TS-016` — hiện được nút "Thử lại" không đảm bảo app còn giữ ngữ cảnh đơn; lỗi hay gặp là thử lại xong mở form trắng, mất mã đơn. · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.2.01 (*"KHÔNG mất ngữ cảnh đơn"*).</t>
+          <t>⛔ DESCOPED 2026-09-24 — BA (LinhDCC) trả lời `FE-322` (Won't Fix): *"Form đang dùng là của bên thứ 3 nên mình không kiểm soát được các vấn đề này -&gt; tài liệu sai, bỏ giúp em BR16-04"*. Không còn nút "Thử lại" nên không còn luồng thử lại để kiểm giữ ngữ cảnh đơn. `SC-TS-012` → DEPRECATED (`C-TS-04(a)`). Giữ nguyên dòng theo `Project_rule §10.5`, không tính vào mẫu số coverage.</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>DESCOPED</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr"/>
@@ -8166,7 +8166,7 @@
 3. Nhấn "Báo cáo sự cố".
 4. Chọn "Sự cố đơn hàng", nhập mô tả "Thử ảnh hưởng trạng thái" và nhập số điện thoại "0912345678".
 5. Nhấn "Gửi".
-6. Nhấn "Quay lại đơn hàng".
+6. Nhấn nút "←" trên thanh tiêu đề để thoát màn xác nhận của Microsoft Forms.
 7. Check trạng thái đơn và nhãn trên màn "Theo dõi đơn".</t>
         </is>
       </c>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: neo vào `C-TS-02(b)` Resolved 2026-09-17 — BA: *"ver hiện tại không chuyển trạng thái gì"*. `§8.12.2` định nghĩa `INCIDENT` = *"có báo cáo sự cố sau khi đơn đã sang IN_TRANSIT"*, đọc được là **tự chuyển**, nên TC này là oracle chặn đúng cách đọc sai đó. · Căn cứ: form Google không gọi được API app ⇒ `INCIDENT` chỉ vào được qua Dev xử lý tay; đơn tự đổi trạng thái ⇒ FAIL và dẫn `C-TS-02`. Kết luận này là căn cứ để `SC-CNL-015`/`SC-DLV-034` out of scope test qua UI.</t>
+          <t>🔴 Cập nhật 2026-09-24 theo BA (LinhDCC) trả lời trên Jira `FE-323`: màn xác nhận là mặc định Microsoft Forms, không có nút "Quay lại đơn hàng" ⇒ step 6 thoát bằng nút "←" của thanh tiêu đề. Mục đích: neo vào `C-TS-02(b)` Resolved 2026-09-17 — BA: *"ver hiện tại không chuyển trạng thái gì"*. `§8.12.2` định nghĩa `INCIDENT` = *"có báo cáo sự cố sau khi đơn đã sang IN_TRANSIT"*, đọc được là **tự chuyển**, nên TC này là oracle chặn đúng cách đọc sai đó. · Căn cứ: form Microsoft Forms không gọi được API app ⇒ `INCIDENT` chỉ vào được qua Dev xử lý tay; đơn tự đổi trạng thái ⇒ FAIL và dẫn `C-TS-02`. Kết luận này là căn cứ để `SC-CNL-015`/`SC-DLV-034` out of scope test qua UI.</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -8262,22 +8262,22 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>5. Ô "Mã đơn hàng" hiển thị dạng nhãn tĩnh chứ không phải textbox, bàn phím không bật lên, và giá trị trong ô giữ nguyên mã đơn gốc không có ký tự "X".</t>
+          <t>5. Ô "Mã đơn hàng" là ô nhập liệu sửa được: bàn phím bật lên và ký tự "X" được chèn vào giá trị đã điền sẵn.</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>Mã đơn prefill chỉ đọc (test_data_catalog §TS — Mã đơn hàng prefill)</t>
+          <t>Mã đơn prefill — sửa được (test_data_catalog §TS — Mã đơn hàng prefill)</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>🔴 Áp bản Resolved `C-TS-03(b)` 2026-09-17 — **ĐẢO HẲN Then của `SC-TS-014`** (*"trường prefill CHO PHÉP sửa"*). `§8.16.2` (*"Chỉ đọc · Không sửa"*) là bản đúng, **`BR16-03` là PRD sai**; demo cho thấy ô là nhãn tĩnh, không phải câu trả lời ngắn của Google Form. · Mục đích: kết quả phản trực giác — người chạy đọc `BR16-03` sẽ tưởng "không sửa được" là bug. Sửa được ⇒ FAIL và dẫn `C-TS-03` để BA cập nhật PRD.</t>
+          <t>🔴 Cập nhật 2026-09-24 theo BA (LinhDCC) trả lời trên Jira `FE-326` (Won't Fix): *"Microsoft form không cho phép khoá trường như mô tả → sai tài liệu"* ⇒ `§8.16.2` ("Chỉ đọc · Không sửa") sai tài liệu, `BR16-03` ("người dùng vẫn sửa được") đúng. Kết luận `C-TS-03(b)` (nhãn tĩnh) HẾT HIỆU LỰC — hiện hành `C-TS-04(d)`; Then gốc của `SC-TS-014` có hiệu lực trở lại. ⚠️ Test Title còn ghi "chỉ đọc không sửa được" — giữ nguyên vì §10.5 không cho sửa Title; Expected mới là oracle. Rủi ro đổi nhầm mã đơn được xử lý bằng đối chiếu ở khâu xử lý (`BR16-03`).</t>
         </is>
       </c>
       <c r="N22" s="6" t="inlineStr">
@@ -12013,6 +12013,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
@@ -26131,7 +26132,7 @@
       </c>
       <c r="J171" s="7" t="inlineStr">
         <is>
-          <t>9. Màn hiển thị "Đã ghi nhận phản hồi" kèm đúng câu "Đội hỗ trợ FoxEco sẽ liên hệ lại số 0912345678 trong vòng 24 giờ làm việc" và nút "Quay lại đơn hàng".</t>
+          <t>9. Màn xác nhận mặc định của Microsoft Forms hiển thị "Đã gửi phản hồi của bạn." (tiếng Anh: "Your response was submitted." — theo ngôn ngữ tài khoản Microsoft), báo cáo được gửi thành công.</t>
         </is>
       </c>
       <c r="K171" s="6" t="inlineStr">
@@ -26141,12 +26142,12 @@
       </c>
       <c r="L171" s="6" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: chuỗi cam kết 24 giờ là **thứ duy nhất verify được** của quy trình hỗ trợ — hành động thật của Admin nằm ngoài app, ⛔ không mở rộng phạm vi sang đó. · Căn cứ: `AC-31.1.01` + vibe-check demo 2026-09-15 (ảnh `TS_05`, chuỗi verbatim). Màn xác nhận và nút "Quay lại đơn hàng" do **APP** vẽ chứ không phải trang xác nhận của Google Form (`C-TS-03(d)` Resolved 2026-09-17).</t>
+          <t>🔴 Cập nhật 2026-09-24 theo BA (LinhDCC) trả lời trên Jira `FE-323` (Won't Fix): *"màn hình này là mặc định của Microsoft Form, mình không can thiệp được. Sai tài liệu ạ."* ⇒ Then của `AC-31.1.01` ("Đã ghi nhận phản hồi" + cam kết 24 giờ + nút "Quay lại đơn hàng") là tài liệu sai; ⛔ không assert câu 24 giờ / nút "Quay lại đơn hàng". Kết luận `C-TS-03(d)` (màn do APP vẽ) HẾT HIỆU LỰC — hiện hành `C-TS-04(b)`. · Mục đích: xác nhận luồng gửi hợp lệ đi hết tới màn xác nhận; hành động thật của Admin nằm ngoài app, ⛔ không mở rộng phạm vi.</t>
         </is>
       </c>
       <c r="N171" s="6" t="inlineStr">
@@ -26379,12 +26380,12 @@
 4. Chọn "Góp ý / đề xuất" ở ô "Loại yêu cầu".
 5. Nhập "App hay bị chậm ở màn bảng tin" vào ô "Mô tả chi tiết".
 6. Nhập "0912abc" vào ô "Số điện thoại liên hệ lại".
-7. Check trạng thái nút "Gửi" cùng phần chữ cạnh nút.</t>
+7. Nhấn "Gửi".&lt;br&gt;8. Check phản hồi của form ở ô "Số điện thoại liên hệ lại" và màn hiện ra sau khi gửi.</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>7. Nút "Gửi" vẫn ở trạng thái bấm được (không disable — cơ chế thật của form là inline error, xem TC-TS-010/TC-TS-011); tuy nhiên SĐT sai định dạng vẫn phải bị chặn không cho gửi (báo lỗi định dạng hoặc tương đương) trước khi form được submit.</t>
+          <t>8. Ô "Số điện thoại liên hệ lại" KHÔNG báo lỗi định dạng; form gửi thành công với giá trị "0912abc" và hiện màn xác nhận mặc định "Đã gửi phản hồi của bạn." (tiếng Anh: "Your response was submitted." — theo ngôn ngữ tài khoản Microsoft) của Microsoft Forms.</t>
         </is>
       </c>
       <c r="K174" s="5" t="inlineStr">
@@ -26394,12 +26395,12 @@
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M174" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: nhánh khác bản chất với 2 TC kia — ô CÓ dữ liệu nhưng sai định dạng, dễ bị lập trình thành "chỉ kiểm rỗng". · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.1.02 + §8.16.2. Dùng loại yêu cầu thứ ba để đồng thời phủ đủ 3 giá trị enum của ô "Loại yêu cầu" trong cụm này.</t>
+          <t>🔴 Cập nhật 2026-09-24 theo BA (LinhDCC) trả lời trên Jira `FE-324` (Won't Fix): *"Microsoft form không hỗ trợ rang buộc định dạng số điện thoại -&gt; chấp nhận rủi ro data"* ⇒ nhánh "SĐT không hợp lệ" của `AC-31.1.02` bị bỏ, form chỉ kiểm không rỗng (`C-TS-04(c)`). ⚠️ Test Title còn ghi "vô hiệu hoá khi SĐT sai định dạng" — giữ nguyên vì §10.5 không cho sửa Title; Expected mới là oracle. · Mục đích: chốt rủi ro data đã được BA chấp nhận — nếu form bắt đầu chặn SĐT sai thì cũng là thay đổi cần báo lại.</t>
         </is>
       </c>
       <c r="N174" s="5" t="inlineStr">
@@ -26469,7 +26470,7 @@
       </c>
       <c r="J175" s="7" t="inlineStr">
         <is>
-          <t>6. Màn hiển thị thông báo lỗi không tải được kèm nút "Thử lại"; form Google không hiện ra.</t>
+          <t>6. App hiển thị màn lỗi "Không tải được trang" kèm dòng "Vui lòng kiểm tra kết nối mạng và thử lại." và nút "Thử lại"; form Microsoft Forms không hiện ra.</t>
         </is>
       </c>
       <c r="K175" s="6" t="inlineStr">
@@ -26479,12 +26480,12 @@
       </c>
       <c r="L175" s="6" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
-          <t>Căn cứ: `DOC-v1.1-01` §6.2 AC-31.2.01 + **Dev trả lời `C-TS-03(c)` 2026-09-17** (*"App hiển thị nhé"*) — nút "Thử lại" do CHÍNH APP vẽ, tách biệt khỏi khung nhúng, nên assert được dù `BR16-01` dùng Custom Tabs. ⛔ Không assert công nghệ nhúng cụ thể (WebView trần hay Custom Tabs) — không quan sát được từ UI.</t>
+          <t>🔴 Cập nhật lần 2 ngày 2026-09-24 — QC GiangDC2 chốt Expected theo hành vi hiện tại của app (VR-029): mất mạng thì APP tự vẽ màn lỗi + nút "Thử lại", đúng spec gốc `DOC-v1.1-01` §6.2 AC-31.2.01. Bản Expected sửa sáng cùng ngày ("trang lỗi mặc định của WebView, không có nút Thử lại") HẾT HIỆU LỰC — viết khi app còn hiện trang lỗi Chromium `net::ERR_INTERNET_DISCONNECTED` (VR-019, `FE-322` Won't Fix). Status Pass theo evidence `VR-029-TS-2026-09-24/screenshots/TC-TS-016__verify-mat-mang-man-loi-app.png`. Xem `C-TS-04(a)`.</t>
         </is>
       </c>
       <c r="N175" s="6" t="inlineStr">
@@ -26565,12 +26566,12 @@
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="M176" s="5" t="inlineStr">
         <is>
-          <t>Mục đích: fail độc lập với `TC-TS-016` — hiện được nút "Thử lại" không đảm bảo app còn giữ ngữ cảnh đơn; lỗi hay gặp là thử lại xong mở form trắng, mất mã đơn. · Căn cứ: `DOC-v1.1-01` §6.2 AC-31.2.01 (*"KHÔNG mất ngữ cảnh đơn"*).</t>
+          <t>⛔ DESCOPED 2026-09-24 — BA (LinhDCC) trả lời `FE-322` (Won't Fix): *"Form đang dùng là của bên thứ 3 nên mình không kiểm soát được các vấn đề này -&gt; tài liệu sai, bỏ giúp em BR16-04"*. Không còn nút "Thử lại" nên không còn luồng thử lại để kiểm giữ ngữ cảnh đơn. `SC-TS-012` → DEPRECATED (`C-TS-04(a)`). Giữ nguyên dòng theo `Project_rule §10.5`, không tính vào mẫu số coverage.</t>
         </is>
       </c>
       <c r="N176" s="5" t="inlineStr">
@@ -26580,7 +26581,7 @@
       </c>
       <c r="O176" s="5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>DESCOPED</t>
         </is>
       </c>
       <c r="P176" s="5" t="inlineStr"/>
@@ -26634,7 +26635,7 @@
 3. Nhấn "Báo cáo sự cố".
 4. Chọn "Sự cố đơn hàng", nhập mô tả "Thử ảnh hưởng trạng thái" và nhập số điện thoại "0912345678".
 5. Nhấn "Gửi".
-6. Nhấn "Quay lại đơn hàng".
+6. Nhấn nút "←" trên thanh tiêu đề để thoát màn xác nhận của Microsoft Forms.
 7. Check trạng thái đơn và nhãn trên màn "Theo dõi đơn".</t>
         </is>
       </c>
@@ -26655,7 +26656,7 @@
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
-          <t>Mục đích: neo vào `C-TS-02(b)` Resolved 2026-09-17 — BA: *"ver hiện tại không chuyển trạng thái gì"*. `§8.12.2` định nghĩa `INCIDENT` = *"có báo cáo sự cố sau khi đơn đã sang IN_TRANSIT"*, đọc được là **tự chuyển**, nên TC này là oracle chặn đúng cách đọc sai đó. · Căn cứ: form Google không gọi được API app ⇒ `INCIDENT` chỉ vào được qua Dev xử lý tay; đơn tự đổi trạng thái ⇒ FAIL và dẫn `C-TS-02`. Kết luận này là căn cứ để `SC-CNL-015`/`SC-DLV-034` out of scope test qua UI.</t>
+          <t>🔴 Cập nhật 2026-09-24 theo BA (LinhDCC) trả lời trên Jira `FE-323`: màn xác nhận là mặc định Microsoft Forms, không có nút "Quay lại đơn hàng" ⇒ step 6 thoát bằng nút "←" của thanh tiêu đề. Mục đích: neo vào `C-TS-02(b)` Resolved 2026-09-17 — BA: *"ver hiện tại không chuyển trạng thái gì"*. `§8.12.2` định nghĩa `INCIDENT` = *"có báo cáo sự cố sau khi đơn đã sang IN_TRANSIT"*, đọc được là **tự chuyển**, nên TC này là oracle chặn đúng cách đọc sai đó. · Căn cứ: form Microsoft Forms không gọi được API app ⇒ `INCIDENT` chỉ vào được qua Dev xử lý tay; đơn tự đổi trạng thái ⇒ FAIL và dẫn `C-TS-02`. Kết luận này là căn cứ để `SC-CNL-015`/`SC-DLV-034` out of scope test qua UI.</t>
         </is>
       </c>
       <c r="N177" s="6" t="inlineStr">
@@ -26977,7 +26978,7 @@
       </c>
       <c r="J181" s="7" t="inlineStr">
         <is>
-          <t>8. Màn hiển thị "Đã ghi nhận phản hồi", gửi thành công không có thông báo lỗi đòi ảnh.</t>
+          <t>8. Gửi thành công, hiện màn xác nhận mặc định của Microsoft Forms "Đã gửi phản hồi của bạn." (tiếng Anh: "Your response was submitted." — theo ngôn ngữ tài khoản Microsoft), không có thông báo lỗi đòi ảnh.</t>
         </is>
       </c>
       <c r="K181" s="6" t="inlineStr">
@@ -26987,7 +26988,7 @@
       </c>
       <c r="L181" s="6" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M181" s="6" t="inlineStr">
@@ -27399,22 +27400,22 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>5. Ô "Mã đơn hàng" hiển thị dạng nhãn tĩnh chứ không phải textbox, bàn phím không bật lên, và giá trị trong ô giữ nguyên mã đơn gốc không có ký tự "X".</t>
+          <t>5. Ô "Mã đơn hàng" là ô nhập liệu sửa được: bàn phím bật lên và ký tự "X" được chèn vào giá trị đã điền sẵn.</t>
         </is>
       </c>
       <c r="K186" s="5" t="inlineStr">
         <is>
-          <t>Mã đơn prefill chỉ đọc (test_data_catalog §TS — Mã đơn hàng prefill)</t>
+          <t>Mã đơn prefill — sửa được (test_data_catalog §TS — Mã đơn hàng prefill)</t>
         </is>
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M186" s="5" t="inlineStr">
         <is>
-          <t>🔴 Áp bản Resolved `C-TS-03(b)` 2026-09-17 — **ĐẢO HẲN Then của `SC-TS-014`** (*"trường prefill CHO PHÉP sửa"*). `§8.16.2` (*"Chỉ đọc · Không sửa"*) là bản đúng, **`BR16-03` là PRD sai**; demo cho thấy ô là nhãn tĩnh, không phải câu trả lời ngắn của Google Form. · Mục đích: kết quả phản trực giác — người chạy đọc `BR16-03` sẽ tưởng "không sửa được" là bug. Sửa được ⇒ FAIL và dẫn `C-TS-03` để BA cập nhật PRD.</t>
+          <t>🔴 Cập nhật 2026-09-24 theo BA (LinhDCC) trả lời trên Jira `FE-326` (Won't Fix): *"Microsoft form không cho phép khoá trường như mô tả → sai tài liệu"* ⇒ `§8.16.2` ("Chỉ đọc · Không sửa") sai tài liệu, `BR16-03` ("người dùng vẫn sửa được") đúng. Kết luận `C-TS-03(b)` (nhãn tĩnh) HẾT HIỆU LỰC — hiện hành `C-TS-04(d)`; Then gốc của `SC-TS-014` có hiệu lực trở lại. ⚠️ Test Title còn ghi "chỉ đọc không sửa được" — giữ nguyên vì §10.5 không cho sửa Title; Expected mới là oracle. Rủi ro đổi nhầm mã đơn được xử lý bằng đối chiếu ở khâu xử lý (`BR16-03`).</t>
         </is>
       </c>
       <c r="N186" s="5" t="inlineStr">
